--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G780"/>
+  <dimension ref="A1:G784"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -25158,7 +25158,6 @@
           <t>Si les enquêtes PISA documentent les performances scolaires des élèves, elles incitent à s’intéresser, au-delà des simples résultats, au développement de compétences sociales et émotionnelles.</t>
         </is>
       </c>
-      <c r="G774" t="inlineStr"/>
     </row>
     <row r="775">
       <c r="A775" s="2" t="inlineStr">
@@ -25191,7 +25190,6 @@
           <t>Les dépenses militaires chinoises sont cinq fois supérieures à celles du Japon L’article «&amp;#160;Réaffirmer la clause relative à l’État ennemi&amp;#160;»&amp;#160;: comment Pékin et Moscou se servent de la Charte de l’ONU pour menacer le Japon est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G775" t="inlineStr"/>
     </row>
     <row r="776">
       <c r="A776" s="2" t="inlineStr">
@@ -25224,7 +25222,6 @@
           <t>L’entreprise américaine assure avoir mis fin à chaque tentative L’article Claude, l’IA d’Anthropic, est utilisé pour tenter de développer des missiles et des armes biologiques est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G776" t="inlineStr"/>
     </row>
     <row r="777">
       <c r="A777" s="2" t="inlineStr">
@@ -25257,7 +25254,6 @@
           <t>Les géants de l’intelligence artificielle sapent systématiquement le bien commun le plus fondamental de toute société humaine&amp;#160;: notre cognition L’article L&amp;rsquo;IA est-elle un virus cognitif&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G777" t="inlineStr"/>
     </row>
     <row r="778">
       <c r="A778" s="2" t="inlineStr">
@@ -25290,7 +25286,6 @@
           <t>La voie maritime est la principale alternative au détroit d’Ormuz L’article Les Houthis ont pris le contrôle du détroit de Bab el-Mandeb est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G778" t="inlineStr"/>
     </row>
     <row r="779">
       <c r="A779" s="2" t="inlineStr">
@@ -25323,7 +25318,6 @@
           <t>L&amp;#8217;URGENCE DU MONDE, NOTRE BOUSSOLE DE CITOYENS Le risque incendie a longtemps été circonscrit, en France, à quelques massifs identifiés, aux étés les plus secs, à une intensité que nos dispositifs de lutte savaient globalement contenir. Ce schéma ne tient plus : l&amp;#8217;allongement de la saison sèche, la baisse de l&amp;#8217;humidité des sols et des [&amp;#8230;] L’article Édito 475 Août 2026 : FACE AUX DÉFIS DU MONDE, FAIRE CORPS ET COMMUNAUTÉ est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G779" t="inlineStr"/>
     </row>
     <row r="780">
       <c r="A780" s="2" t="inlineStr">
@@ -25356,7 +25350,138 @@
           <t>ÉDITORIAL. Face aux défis du monde, faire corps et communauté, Joëlle ALAZARD ACTUALITÉS HOMMAGE. Au bonheur des discordances. Hommage à Carlo Ginzburg, Guillaume CALAFAT HOMMAGE. Yves Lacoste Kevin LIMONNIER/ Axel DUC HOMMAGE. Yves Marie Bercé Olivier PONCET HOMMAGE. Bertrand Vergé (1956-2026), Xavier DESBROSSE ENTRETIENS. Le Sénat récompense l&amp;#8217;histoire : entretiens avec Marion Aballéa et Sofian [&amp;#8230;] L’article Sommaire 475 est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G780" t="inlineStr"/>
+    </row>
+    <row r="781">
+      <c r="A781" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 13:36</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>2026-09-13 09:52</t>
+        </is>
+      </c>
+      <c r="D781" s="3" t="inlineStr">
+        <is>
+          <t>Le D-Day économique au Moyen-Orient : gagnants et perdants</t>
+        </is>
+      </c>
+      <c r="E781" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-d-day-economique-au-moyen-orient-gagnants-et-perdants-290600</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>L’élargissement des sanctions américaines met à l’épreuve la résilience de l’Iran, mais aussi la volonté de ses partenaires commerciaux de résister à la puissance financière des États-Unis.</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr"/>
+    </row>
+    <row r="782">
+      <c r="A782" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 13:36</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:30</t>
+        </is>
+      </c>
+      <c r="D782" s="3" t="inlineStr">
+        <is>
+          <t>Qu’est-ce que la prise de contrôle des côtes du détroit de Bab el-Mandeb révèle de la position américaine au Moyen-Orient ?</t>
+        </is>
+      </c>
+      <c r="E782" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/13/quest-ce-que-la-prise-de-controle-des-cotes-du-detroit-de-bab-el-mandeb-revele-de-la-position-americaine-au-moyen-orient/</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>Oman accueillera demain, lundi 14 septembre, un nouveau cycle de négociations entre l’Iran et les pays du Golfe sur l’ouverture du détroit d’Ormuz L’article Qu’est-ce que la prise de contrôle des côtes du détroit de Bab el-Mandeb révèle de la position américaine au Moyen-Orient&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr"/>
+    </row>
+    <row r="783">
+      <c r="A783" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 13:36</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>2026-09-12 18:04</t>
+        </is>
+      </c>
+      <c r="D783" s="3" t="inlineStr">
+        <is>
+          <t>Dario Amodei appelle à ralentir le développement de l’IA (texte intégral)</t>
+        </is>
+      </c>
+      <c r="E783" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/12/dario-amodei-appelle-a-ralentir-le-developpement-de-lia-texte-integral/</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>Face aux risques existentiels de la course à l’intelligence artificielle, le PDG d’Anthropic change-t-il de doctrine&amp;#160;? L’article Dario Amodei appelle à ralentir le développement de l’IA (texte intégral) est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr"/>
+    </row>
+    <row r="784">
+      <c r="A784" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 13:36</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>2026-09-12 14:02</t>
+        </is>
+      </c>
+      <c r="D784" s="3" t="inlineStr">
+        <is>
+          <t>La guerre en Iran creuse l’écart de croissance entre les BRICS et le G7</t>
+        </is>
+      </c>
+      <c r="E784" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/12/la-guerre-en-iran-creuse-lecart-de-croissance-entre-les-brics-et-le-g7/</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>En 2026, la croissance des BRICS devrait être supérieure de 2 points à celle du G7 L’article La guerre en Iran creuse l&amp;rsquo;écart de croissance entre les BRICS et le G7 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -26139,6 +26264,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E778" r:id="rId777"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E779" r:id="rId778"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E780" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E781" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E782" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E783" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E784" r:id="rId783"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G784"/>
+  <dimension ref="A1:G792"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -25382,7 +25382,6 @@
           <t>L’élargissement des sanctions américaines met à l’épreuve la résilience de l’Iran, mais aussi la volonté de ses partenaires commerciaux de résister à la puissance financière des États-Unis.</t>
         </is>
       </c>
-      <c r="G781" t="inlineStr"/>
     </row>
     <row r="782">
       <c r="A782" s="2" t="inlineStr">
@@ -25415,7 +25414,6 @@
           <t>Oman accueillera demain, lundi 14 septembre, un nouveau cycle de négociations entre l’Iran et les pays du Golfe sur l’ouverture du détroit d’Ormuz L’article Qu’est-ce que la prise de contrôle des côtes du détroit de Bab el-Mandeb révèle de la position américaine au Moyen-Orient&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G782" t="inlineStr"/>
     </row>
     <row r="783">
       <c r="A783" s="2" t="inlineStr">
@@ -25448,7 +25446,6 @@
           <t>Face aux risques existentiels de la course à l’intelligence artificielle, le PDG d’Anthropic change-t-il de doctrine&amp;#160;? L’article Dario Amodei appelle à ralentir le développement de l’IA (texte intégral) est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G783" t="inlineStr"/>
     </row>
     <row r="784">
       <c r="A784" s="2" t="inlineStr">
@@ -25481,7 +25478,270 @@
           <t>En 2026, la croissance des BRICS devrait être supérieure de 2 points à celle du G7 L’article La guerre en Iran creuse l&amp;rsquo;écart de croissance entre les BRICS et le G7 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G784" t="inlineStr"/>
+    </row>
+    <row r="785">
+      <c r="A785" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:37</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:23</t>
+        </is>
+      </c>
+      <c r="D785" s="3" t="inlineStr">
+        <is>
+          <t>Apprendre à lire : ce que les données de 9 000 enseignants et 130 000 élèves révèlent des méthodes et de leur efficacité</t>
+        </is>
+      </c>
+      <c r="E785" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/apprendre-a-lire-ce-que-les-donnees-de-9-000-enseignants-et-130-000-eleves-revelent-des-methodes-et-de-leur-efficacite-291310</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>Alors que la dernière enquête PISA sur le niveau des élèves note un net décrochage dans la compréhension de l’écrit, des études offrent des pistes pour améliorer l’enseignement de la lecture.</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr"/>
+    </row>
+    <row r="786">
+      <c r="A786" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:37</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:17</t>
+        </is>
+      </c>
+      <c r="D786" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi j’apprends à mes étudiants en littérature ce que l’IA ne sait pas faire</t>
+        </is>
+      </c>
+      <c r="E786" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-japprends-a-mes-etudiants-en-litterature-ce-que-lia-ne-sait-pas-faire-291182</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>Les enseignants peuvent aborder l’IA de front en distinguant ses capacités de reconnaissance de son incapacité à rêvasser, à se mettre à la place d’autrui et à s’exprimer de manière authentique.</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr"/>
+    </row>
+    <row r="787">
+      <c r="A787" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:37</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:32</t>
+        </is>
+      </c>
+      <c r="D787" s="3" t="inlineStr">
+        <is>
+          <t>Rassemblement national/Reform UK : mêmes combats ?</t>
+        </is>
+      </c>
+      <c r="E787" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/rassemblement-national-reform-uk-memes-combats-291386</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>La proximité affichée par le RN et le parti d’extrême droite britannique Reform&amp;nbsp;UK ne concerne pas seulement l’immigration, mais aussi les guerres culturelles et la politique environnementale.</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr"/>
+    </row>
+    <row r="788">
+      <c r="A788" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:37</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:27</t>
+        </is>
+      </c>
+      <c r="D788" s="3" t="inlineStr">
+        <is>
+          <t>États-Unis : tout comprendre aux midterms</t>
+        </is>
+      </c>
+      <c r="E788" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/etats-unis-tout-comprendre-aux-midterms-284686</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>Les midterms peuvent modifier l’équilibre politique au Congrès et donc faciliter ou bloquer l’action du président.</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr"/>
+    </row>
+    <row r="789">
+      <c r="A789" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:37</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:05</t>
+        </is>
+      </c>
+      <c r="D789" s="3" t="inlineStr">
+        <is>
+          <t>Andy Burnham sera-t-il le dernier Premier ministre du Royaume-Uni ?</t>
+        </is>
+      </c>
+      <c r="E789" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/14/andy-burnham-sera-t-il-le-dernier-premier-ministre-du-royaume-uni/</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>Les dirigeants d’Irlande du Nord, d’Écosse et du pays de Galles accélèrent pour sortir du Royaume-Uni. L’article Andy Burnham sera-t-il le dernier Premier ministre du Royaume-Uni&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr"/>
+    </row>
+    <row r="790">
+      <c r="A790" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:37</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:50</t>
+        </is>
+      </c>
+      <c r="D790" s="3" t="inlineStr">
+        <is>
+          <t>Le progressisme IA a trouvé son discours fondateur</t>
+        </is>
+      </c>
+      <c r="E790" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/14/le-progressisme-ia-a-trouve-son-discours-fondateur/</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>Pour le sénateur de Géorgie, l’angoisse provoquée par l’intelligence artificielle permet aux démocrates de tourner la page Trump L’article Le progressisme IA a trouvé son discours fondateur est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr"/>
+    </row>
+    <row r="791">
+      <c r="A791" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:37</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>2026-09-14 05:07</t>
+        </is>
+      </c>
+      <c r="D791" s="3" t="inlineStr">
+        <is>
+          <t>La Chine veut mettre fin à la guerre en Iran à sa manière</t>
+        </is>
+      </c>
+      <c r="E791" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/14/la-chine-veut-mettre-fin-a-la-guerre-en-iran-a-sa-maniere/</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>En proposant aux BRICS+ de jouer les médiateurs au Moyen-Orient, Xi Jinping catalyse le chaos provoqué par Donald Trump L’article La Chine veut mettre fin à la guerre en Iran à sa manière est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr"/>
+    </row>
+    <row r="792">
+      <c r="A792" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:37</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>2026-09-13 15:52</t>
+        </is>
+      </c>
+      <c r="D792" s="3" t="inlineStr">
+        <is>
+          <t>Choses vues au pays des talibans</t>
+        </is>
+      </c>
+      <c r="E792" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/13/choses-vues-au-pays-des-talibans/</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>En Afghanistan, voyage à l’intérieur d’un régime bâti sur les ruines d’une guerre sans fin L’article Choses vues au pays des talibans est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -26268,6 +26528,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E782" r:id="rId781"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E783" r:id="rId782"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E784" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E785" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E786" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E787" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E788" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E789" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E790" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E791" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E792" r:id="rId791"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G792"/>
+  <dimension ref="A1:G799"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -25510,7 +25510,6 @@
           <t>Alors que la dernière enquête PISA sur le niveau des élèves note un net décrochage dans la compréhension de l’écrit, des études offrent des pistes pour améliorer l’enseignement de la lecture.</t>
         </is>
       </c>
-      <c r="G785" t="inlineStr"/>
     </row>
     <row r="786">
       <c r="A786" s="2" t="inlineStr">
@@ -25543,7 +25542,6 @@
           <t>Les enseignants peuvent aborder l’IA de front en distinguant ses capacités de reconnaissance de son incapacité à rêvasser, à se mettre à la place d’autrui et à s’exprimer de manière authentique.</t>
         </is>
       </c>
-      <c r="G786" t="inlineStr"/>
     </row>
     <row r="787">
       <c r="A787" s="2" t="inlineStr">
@@ -25576,7 +25574,6 @@
           <t>La proximité affichée par le RN et le parti d’extrême droite britannique Reform&amp;nbsp;UK ne concerne pas seulement l’immigration, mais aussi les guerres culturelles et la politique environnementale.</t>
         </is>
       </c>
-      <c r="G787" t="inlineStr"/>
     </row>
     <row r="788">
       <c r="A788" s="2" t="inlineStr">
@@ -25609,7 +25606,6 @@
           <t>Les midterms peuvent modifier l’équilibre politique au Congrès et donc faciliter ou bloquer l’action du président.</t>
         </is>
       </c>
-      <c r="G788" t="inlineStr"/>
     </row>
     <row r="789">
       <c r="A789" s="2" t="inlineStr">
@@ -25642,7 +25638,6 @@
           <t>Les dirigeants d’Irlande du Nord, d’Écosse et du pays de Galles accélèrent pour sortir du Royaume-Uni. L’article Andy Burnham sera-t-il le dernier Premier ministre du Royaume-Uni&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G789" t="inlineStr"/>
     </row>
     <row r="790">
       <c r="A790" s="2" t="inlineStr">
@@ -25675,7 +25670,6 @@
           <t>Pour le sénateur de Géorgie, l’angoisse provoquée par l’intelligence artificielle permet aux démocrates de tourner la page Trump L’article Le progressisme IA a trouvé son discours fondateur est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G790" t="inlineStr"/>
     </row>
     <row r="791">
       <c r="A791" s="2" t="inlineStr">
@@ -25708,7 +25702,6 @@
           <t>En proposant aux BRICS+ de jouer les médiateurs au Moyen-Orient, Xi Jinping catalyse le chaos provoqué par Donald Trump L’article La Chine veut mettre fin à la guerre en Iran à sa manière est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G791" t="inlineStr"/>
     </row>
     <row r="792">
       <c r="A792" s="2" t="inlineStr">
@@ -25741,7 +25734,237 @@
           <t>En Afghanistan, voyage à l’intérieur d’un régime bâti sur les ruines d’une guerre sans fin L’article Choses vues au pays des talibans est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G792" t="inlineStr"/>
+    </row>
+    <row r="793">
+      <c r="A793" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:08</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>2026-09-15 08:29</t>
+        </is>
+      </c>
+      <c r="D793" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi l’ONU soutient-elle une nouvelle carte du monde plus fidèle à la taille de l’Afrique ?</t>
+        </is>
+      </c>
+      <c r="E793" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-lonu-soutient-elle-une-nouvelle-carte-du-monde-plus-fidele-a-la-taille-de-lafrique-291935</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>L’ONU soutient désormais la projection Equal Earth, une carte du monde qui représente plus fidèlement la taille des continents, notamment celle de l’Afrique, longtemps réduite par la projection de Mercator.</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr"/>
+    </row>
+    <row r="794">
+      <c r="A794" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:08</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:40</t>
+        </is>
+      </c>
+      <c r="D794" s="3" t="inlineStr">
+        <is>
+          <t>Derrière la victoire de l’AfD, le rejet des éoliennes ?</t>
+        </is>
+      </c>
+      <c r="E794" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/derriere-la-victoire-de-lafd-le-rejet-des-eoliennes-291806</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>En Allemagne, l’AfD a placé la lutte contre les éoliennes au cœur de sa stratégie électorale. Une victoire en Saxe-Anhalt pourrait-elle lui permettre de freiner la transition énergétique&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr"/>
+    </row>
+    <row r="795">
+      <c r="A795" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:08</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:32</t>
+        </is>
+      </c>
+      <c r="D795" s="3" t="inlineStr">
+        <is>
+          <t>Les États-Unis affirment disposer de capacités militaires en orbite</t>
+        </is>
+      </c>
+      <c r="E795" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/15/les-etats-unis-affirment-disposer-de-capacites-militaires-en-orbite/</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>Washington refuse toutefois de préciser leur nature L’article Les États-Unis affirment disposer de capacités militaires en orbite est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr"/>
+    </row>
+    <row r="796">
+      <c r="A796" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:08</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:30</t>
+        </is>
+      </c>
+      <c r="D796" s="3" t="inlineStr">
+        <is>
+          <t>Le prix de l’indépendance à l’âge de l’IA</t>
+        </is>
+      </c>
+      <c r="E796" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/15/le-prix-de-lindependance-a-lage-de-lia/</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>Selon les calculs du plan Prométhée, financer un laboratoire de frontière en France reste possible L’article Le prix de l’indépendance à l’âge de l’IA est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr"/>
+    </row>
+    <row r="797">
+      <c r="A797" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:08</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:30</t>
+        </is>
+      </c>
+      <c r="D797" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : les personnes fuyant le pays font exploser les prix des logements à Erevan</t>
+        </is>
+      </c>
+      <c r="E797" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/15/economie-russe-les-personnes-fuyant-le-pays-font-exploser-les-prix-des-logements-a-erevan/</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>Le Kremlin tente de dissiper toutes les rumeurs de mobilisation L’article Économie russe&amp;#160;: les personnes fuyant le pays font exploser les prix des logements à Erevan est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr"/>
+    </row>
+    <row r="798">
+      <c r="A798" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:08</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:01</t>
+        </is>
+      </c>
+      <c r="D798" s="3" t="inlineStr">
+        <is>
+          <t>Qui est l’oligarque russe qui a financé la fête de mariage de Donald Trump Jr. ?</t>
+        </is>
+      </c>
+      <c r="E798" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/14/qui-est-loligarque-russe-qui-a-finance-la-fete-de-mariage-de-donald-trump-jr/</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>Portrait d’Umar Kremlev, proche de Poutine, admirateur de Staline et ami du fils du président américain L’article Qui est l’oligarque russe qui a financé la fête de mariage de Donald Trump Jr.&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr"/>
+    </row>
+    <row r="799">
+      <c r="A799" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:08</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:22</t>
+        </is>
+      </c>
+      <c r="D799" s="3" t="inlineStr">
+        <is>
+          <t>La carte du monde selon les BRICS : ce que révèle la Déclaration de New Delhi</t>
+        </is>
+      </c>
+      <c r="E799" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/14/la-carte-du-monde-selon-les-brics-ce-que-revele-la-declaration-de-new-delhi/</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>L’Europe n’est mentionnée à aucune reprise dans le document L’article La carte du monde selon les BRICS&amp;#160;: ce que révèle la Déclaration de New Delhi est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -26536,6 +26759,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E790" r:id="rId789"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E791" r:id="rId790"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E792" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E793" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E794" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E795" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E796" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E797" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E798" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E799" r:id="rId798"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G799"/>
+  <dimension ref="A1:G808"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -25766,7 +25766,6 @@
           <t>L’ONU soutient désormais la projection Equal Earth, une carte du monde qui représente plus fidèlement la taille des continents, notamment celle de l’Afrique, longtemps réduite par la projection de Mercator.</t>
         </is>
       </c>
-      <c r="G793" t="inlineStr"/>
     </row>
     <row r="794">
       <c r="A794" s="2" t="inlineStr">
@@ -25799,7 +25798,6 @@
           <t>En Allemagne, l’AfD a placé la lutte contre les éoliennes au cœur de sa stratégie électorale. Une victoire en Saxe-Anhalt pourrait-elle lui permettre de freiner la transition énergétique&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G794" t="inlineStr"/>
     </row>
     <row r="795">
       <c r="A795" s="2" t="inlineStr">
@@ -25832,7 +25830,6 @@
           <t>Washington refuse toutefois de préciser leur nature L’article Les États-Unis affirment disposer de capacités militaires en orbite est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G795" t="inlineStr"/>
     </row>
     <row r="796">
       <c r="A796" s="2" t="inlineStr">
@@ -25865,7 +25862,6 @@
           <t>Selon les calculs du plan Prométhée, financer un laboratoire de frontière en France reste possible L’article Le prix de l’indépendance à l’âge de l’IA est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G796" t="inlineStr"/>
     </row>
     <row r="797">
       <c r="A797" s="2" t="inlineStr">
@@ -25898,7 +25894,6 @@
           <t>Le Kremlin tente de dissiper toutes les rumeurs de mobilisation L’article Économie russe&amp;#160;: les personnes fuyant le pays font exploser les prix des logements à Erevan est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G797" t="inlineStr"/>
     </row>
     <row r="798">
       <c r="A798" s="2" t="inlineStr">
@@ -25931,7 +25926,6 @@
           <t>Portrait d’Umar Kremlev, proche de Poutine, admirateur de Staline et ami du fils du président américain L’article Qui est l’oligarque russe qui a financé la fête de mariage de Donald Trump Jr.&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G798" t="inlineStr"/>
     </row>
     <row r="799">
       <c r="A799" s="2" t="inlineStr">
@@ -25964,7 +25958,303 @@
           <t>L’Europe n’est mentionnée à aucune reprise dans le document L’article La carte du monde selon les BRICS&amp;#160;: ce que révèle la Déclaration de New Delhi est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G799" t="inlineStr"/>
+    </row>
+    <row r="800">
+      <c r="A800" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>2026-09-16 07:57</t>
+        </is>
+      </c>
+      <c r="D800" s="3" t="inlineStr">
+        <is>
+          <t>Vers un « bilinguisme de l’IA » : apprendre à faire avec et apprendre à faire sans</t>
+        </is>
+      </c>
+      <c r="E800" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/vers-un-bilinguisme-de-lia-apprendre-a-faire-avec-et-apprendre-a-faire-sans-291895</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>Face à des usages et des questions qui peuvent être angoissantes pour les jeunes, leur entourage et les éducateurs, une proposition assez apaisante&amp;nbsp;: celle du «&amp;nbsp;bilinguisme&amp;nbsp;».</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr"/>
+    </row>
+    <row r="801">
+      <c r="A801" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:45</t>
+        </is>
+      </c>
+      <c r="D801" s="3" t="inlineStr">
+        <is>
+          <t>À l’heure de l’IA générative, que signifie encore apprendre une langue ?</t>
+        </is>
+      </c>
+      <c r="E801" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/a-lheure-de-lia-generative-que-signifie-encore-apprendre-une-langue-288545</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>L’intelligence artificielle générative transforme notre rapport aux langues, mais apprendre une langue reste essentiel pour comprendre les autres, interagir et exercer son jugement.</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr"/>
+    </row>
+    <row r="802">
+      <c r="A802" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:46</t>
+        </is>
+      </c>
+      <c r="D802" s="3" t="inlineStr">
+        <is>
+          <t>La percée des houthistes au Yémen met les BRICS face à leurs divisions</t>
+        </is>
+      </c>
+      <c r="E802" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/la-percee-des-houthistes-au-yemen-met-les-brics-face-a-leurs-divisions-291934</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>L’expansion rapide du bloc –&amp;nbsp;qui compte désormais 11&amp;nbsp;membres permanents et 10&amp;nbsp;partenaires&amp;nbsp;– le rend incapable de s’exprimer d’une voix commune.</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr"/>
+    </row>
+    <row r="803">
+      <c r="A803" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:45</t>
+        </is>
+      </c>
+      <c r="D803" s="3" t="inlineStr">
+        <is>
+          <t>Xenia Fedorova, ou comment la propagande russe retourne notre esprit critique contre nous-mêmes</t>
+        </is>
+      </c>
+      <c r="E803" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/xenia-fedorova-ou-comment-la-propagande-russe-retourne-notre-esprit-critique-contre-nous-memes-291061</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Le cas Fedorova est emblématique d’une méthode rhétorique employée par la propagande russe&amp;nbsp;: en appeler à l’esprit critique du public visé pour convaincre celui-ci de se détourner des sources vues comme «&amp;nbsp;officielles&amp;nbsp;» et «&amp;nbsp;dominantes&amp;nbsp;».</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr"/>
+    </row>
+    <row r="804">
+      <c r="A804" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:59</t>
+        </is>
+      </c>
+      <c r="D804" s="3" t="inlineStr">
+        <is>
+          <t>L’armée ukrainienne mène à Lyman sa deuxième contre-offensive majeure de l’année</t>
+        </is>
+      </c>
+      <c r="E804" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/16/larmee-ukrainienne-mene-a-lyman-sa-deuxieme-contre-offensive-majeure-de-lannee/</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>Kiev a provoqué le premier recul russe significatif dans ce secteur depuis 2022 L’article L’armée ukrainienne mène à Lyman sa deuxième contre-offensive majeure de l’année est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr"/>
+    </row>
+    <row r="805">
+      <c r="A805" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:06</t>
+        </is>
+      </c>
+      <c r="D805" s="3" t="inlineStr">
+        <is>
+          <t>Seule l’Europe peut vraiment garantir la souveraineté des Européens</t>
+        </is>
+      </c>
+      <c r="E805" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/16/seule-leurope-peut-vraiment-garantir-la-souverainete-des-europeens/</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>Le discours sur l’état de l’Union d’Ursula Von der Leyen L’article Seule l’Europe peut vraiment garantir la souveraineté des Européens est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr"/>
+    </row>
+    <row r="806">
+      <c r="A806" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:30</t>
+        </is>
+      </c>
+      <c r="D806" s="3" t="inlineStr">
+        <is>
+          <t>Les interdictions de sortie du territoire ont explosé depuis l’arrivée au pouvoir de Xi Jinping</t>
+        </is>
+      </c>
+      <c r="E806" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/16/les-interdictions-de-sortie-du-territoire-ont-explose-depuis-larrivee-au-pouvoir-de-xi-jinping/</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>La Chine compte 18 lois pouvant interdire la sortie du territoire L’article Les interdictions de sortie du territoire ont explosé depuis l’arrivée au pouvoir de Xi Jinping est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr"/>
+    </row>
+    <row r="807">
+      <c r="A807" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:00</t>
+        </is>
+      </c>
+      <c r="D807" s="3" t="inlineStr">
+        <is>
+          <t>L’armée américaine ne sait plus faire la guerre</t>
+        </is>
+      </c>
+      <c r="E807" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/16/larmee-americaine-ne-sait-plus-faire-la-guerre/</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>Comprendre la longue érosion de la première puissance militaire mondiale L’article L’armée américaine ne sait plus faire la guerre est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr"/>
+    </row>
+    <row r="808">
+      <c r="A808" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:46</t>
+        </is>
+      </c>
+      <c r="D808" s="3" t="inlineStr">
+        <is>
+          <t>La fragmentation du commerce mondial pourrait coûter aux pays les plus pauvres près d’un quart de leur PIB</t>
+        </is>
+      </c>
+      <c r="E808" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/15/la-fragmentation-du-commerce-mondial-pourrait-couter-aux-pays-les-plus-pauvres-pres-dun-quart-de-leur-pib/</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>Malgré les tarifs de Donald Trump, les États-Unis font partie des pays les moins impactés L’article La fragmentation du commerce mondial pourrait coûter aux pays les plus pauvres près d&amp;rsquo;un quart de leur PIB est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -26766,6 +27056,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E797" r:id="rId796"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E798" r:id="rId797"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E799" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E800" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E801" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E802" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E803" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E804" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E805" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E806" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E807" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E808" r:id="rId807"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G808"/>
+  <dimension ref="A1:G819"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -25990,7 +25990,6 @@
           <t>Face à des usages et des questions qui peuvent être angoissantes pour les jeunes, leur entourage et les éducateurs, une proposition assez apaisante&amp;nbsp;: celle du «&amp;nbsp;bilinguisme&amp;nbsp;».</t>
         </is>
       </c>
-      <c r="G800" t="inlineStr"/>
     </row>
     <row r="801">
       <c r="A801" s="2" t="inlineStr">
@@ -26023,7 +26022,6 @@
           <t>L’intelligence artificielle générative transforme notre rapport aux langues, mais apprendre une langue reste essentiel pour comprendre les autres, interagir et exercer son jugement.</t>
         </is>
       </c>
-      <c r="G801" t="inlineStr"/>
     </row>
     <row r="802">
       <c r="A802" s="2" t="inlineStr">
@@ -26056,7 +26054,6 @@
           <t>L’expansion rapide du bloc –&amp;nbsp;qui compte désormais 11&amp;nbsp;membres permanents et 10&amp;nbsp;partenaires&amp;nbsp;– le rend incapable de s’exprimer d’une voix commune.</t>
         </is>
       </c>
-      <c r="G802" t="inlineStr"/>
     </row>
     <row r="803">
       <c r="A803" s="2" t="inlineStr">
@@ -26089,7 +26086,6 @@
           <t>Le cas Fedorova est emblématique d’une méthode rhétorique employée par la propagande russe&amp;nbsp;: en appeler à l’esprit critique du public visé pour convaincre celui-ci de se détourner des sources vues comme «&amp;nbsp;officielles&amp;nbsp;» et «&amp;nbsp;dominantes&amp;nbsp;».</t>
         </is>
       </c>
-      <c r="G803" t="inlineStr"/>
     </row>
     <row r="804">
       <c r="A804" s="2" t="inlineStr">
@@ -26122,7 +26118,6 @@
           <t>Kiev a provoqué le premier recul russe significatif dans ce secteur depuis 2022 L’article L’armée ukrainienne mène à Lyman sa deuxième contre-offensive majeure de l’année est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G804" t="inlineStr"/>
     </row>
     <row r="805">
       <c r="A805" s="2" t="inlineStr">
@@ -26155,7 +26150,6 @@
           <t>Le discours sur l’état de l’Union d’Ursula Von der Leyen L’article Seule l’Europe peut vraiment garantir la souveraineté des Européens est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G805" t="inlineStr"/>
     </row>
     <row r="806">
       <c r="A806" s="2" t="inlineStr">
@@ -26188,7 +26182,6 @@
           <t>La Chine compte 18 lois pouvant interdire la sortie du territoire L’article Les interdictions de sortie du territoire ont explosé depuis l’arrivée au pouvoir de Xi Jinping est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G806" t="inlineStr"/>
     </row>
     <row r="807">
       <c r="A807" s="2" t="inlineStr">
@@ -26221,7 +26214,6 @@
           <t>Comprendre la longue érosion de la première puissance militaire mondiale L’article L’armée américaine ne sait plus faire la guerre est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G807" t="inlineStr"/>
     </row>
     <row r="808">
       <c r="A808" s="2" t="inlineStr">
@@ -26254,7 +26246,369 @@
           <t>Malgré les tarifs de Donald Trump, les États-Unis font partie des pays les moins impactés L’article La fragmentation du commerce mondial pourrait coûter aux pays les plus pauvres près d&amp;rsquo;un quart de leur PIB est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G808" t="inlineStr"/>
+    </row>
+    <row r="809">
+      <c r="A809" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:04</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:27</t>
+        </is>
+      </c>
+      <c r="D809" s="3" t="inlineStr">
+        <is>
+          <t>Brève histoire de l’opéra dans les Balkans et en Turquie</t>
+        </is>
+      </c>
+      <c r="E809" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/breve-histoire-de-lopera-dans-les-balkans-et-en-turquie-290883</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>De Vienne à Istanbul, de Zagreb à Belgrade, compositeurs et institutions ont fait de l’art lyrique un instrument de modernisation autant qu’un espace d’affirmation identitaire.</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr"/>
+    </row>
+    <row r="810">
+      <c r="A810" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:04</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:29</t>
+        </is>
+      </c>
+      <c r="D810" s="3" t="inlineStr">
+        <is>
+          <t>Comment l’écriture en miroir reflète la richesse de l’écriture manuscrite</t>
+        </is>
+      </c>
+      <c r="E810" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-lecriture-en-miroir-reflete-la-richesse-de-lecriture-manuscrite-287819</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>Face à la multiplication des claviers, l’écriture manuscrite se raréfie. Les pratiques scolaires nous rappellent la richesse de ses gestes.</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr"/>
+    </row>
+    <row r="811">
+      <c r="A811" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:04</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:31</t>
+        </is>
+      </c>
+      <c r="D811" s="3" t="inlineStr">
+        <is>
+          <t>Il y a beaucoup moins de bombes atomiques qu’en 1990. Alors pourquoi le risque nucléaire augmente-t-il ?</t>
+        </is>
+      </c>
+      <c r="E811" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/il-y-a-beaucoup-moins-de-bombes-atomiques-quen-1990-alors-pourquoi-le-risque-nucleaire-augmente-t-il-291060</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>Le monde est passé de 70&amp;nbsp;000, au début des années&amp;nbsp;1980, à 12&amp;nbsp;000&amp;nbsp;têtes nucléaires. Il serait erroné de croire que, pour autant, le risque de l’emploi de l’arme atomique se serait réduit, au contraire même.</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr"/>
+    </row>
+    <row r="812">
+      <c r="A812" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:04</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:30</t>
+        </is>
+      </c>
+      <c r="D812" s="3" t="inlineStr">
+        <is>
+          <t>Eisenkot-Nétanyahou : la bataille pour l’avenir d’Israël</t>
+        </is>
+      </c>
+      <c r="E812" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/eisenkot-netanyahou-la-bataille-pour-lavenir-disrael-291392</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>À l’approche des législatives, Eisenkot talonne Nétanyahou. Mais le scrutin se jouera surtout sur les coalitions et sur le modèle d’Israël après le 7-Octobre.</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr"/>
+    </row>
+    <row r="813">
+      <c r="A813" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:04</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:27</t>
+        </is>
+      </c>
+      <c r="D813" s="3" t="inlineStr">
+        <is>
+          <t>Après les restrictions du commerce avec les colonies israéliennes, l’accord de libre-échange avec l’UE est-il menacé ?</t>
+        </is>
+      </c>
+      <c r="E813" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/apres-les-restrictions-du-commerce-avec-les-colonies-israeliennes-laccord-de-libre-echange-avec-lue-est-il-menace-291884</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>Les États membres de l’UE, qui est la première partenaire commerciale d’Israël, sont toujours divisés sur la remise en cause des avantages du volet de libre-échange de l’accord d’association UE-Israël.</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:04</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:22</t>
+        </is>
+      </c>
+      <c r="D814" s="3" t="inlineStr">
+        <is>
+          <t>Peut-on ignorer les implications sécuritaires de la « starlinkisation » du réseau Internet en Afrique ?</t>
+        </is>
+      </c>
+      <c r="E814" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/peut-on-ignorer-les-implications-securitaires-de-la-starlinkisation-du-reseau-internet-en-afrique-290198</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>L’expansion de Starlink en Afrique peut servir aux forces armées locales, mais aussi aux groupes armés illégaux.</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr"/>
+    </row>
+    <row r="815">
+      <c r="A815" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:04</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:25</t>
+        </is>
+      </c>
+      <c r="D815" s="3" t="inlineStr">
+        <is>
+          <t>Le moment des États-Unis d’Europe est venu</t>
+        </is>
+      </c>
+      <c r="E815" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/17/le-moment-des-etats-unis-deurope-est-venu/</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>Selon le candidat à la présidentielle, nous avons la responsabilité historique d'accélérer la construction européenne L’article Le moment des États-Unis d&amp;rsquo;Europe est venu est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr"/>
+    </row>
+    <row r="816">
+      <c r="A816" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:04</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:10</t>
+        </is>
+      </c>
+      <c r="D816" s="3" t="inlineStr">
+        <is>
+          <t>Mark Carney et la nouvelle alliance transatlantique</t>
+        </is>
+      </c>
+      <c r="E816" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/17/mark-carney-et-la-nouvelle-alliance-transatlantique/</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>Le discours intégral du premier ministre canadien devant le Parlement européen L’article Mark Carney et la nouvelle alliance transatlantique est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr"/>
+    </row>
+    <row r="817">
+      <c r="A817" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:04</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:30</t>
+        </is>
+      </c>
+      <c r="D817" s="3" t="inlineStr">
+        <is>
+          <t>Pékin inaugure son premier méga-canal depuis 1949</t>
+        </is>
+      </c>
+      <c r="E817" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/17/pekin-inaugure-son-premier-mega-canal-depuis-1949/</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>Les 134 kilomètres du canal de Pinglu ont été construits en quatre ans L’article Pékin inaugure son premier méga-canal depuis 1949 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr"/>
+    </row>
+    <row r="818">
+      <c r="A818" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:04</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:00</t>
+        </is>
+      </c>
+      <c r="D818" s="3" t="inlineStr">
+        <is>
+          <t>Pour une souveraineté technologique sélective</t>
+        </is>
+      </c>
+      <c r="E818" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/17/pour-une-souverainete-technologique-selective/</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>Entre l’illusion d’une souveraineté technologique totale et la résignation à une vassalisation brutale, l’Europe doit inventer une troisième voie dans la course à l’IA L’article Pour une souveraineté technologique sélective est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr"/>
+    </row>
+    <row r="819">
+      <c r="A819" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:04</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>2026-09-16 17:23</t>
+        </is>
+      </c>
+      <c r="D819" s="3" t="inlineStr">
+        <is>
+          <t>En visant la Russie, le Congrès américain va-t-il donner de nouveaux pouvoirs à Trump en matière de tarifs ?</t>
+        </is>
+      </c>
+      <c r="E819" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/16/en-visant-la-russie-le-congres-americain-va-t-il-donner-de-nouveaux-pouvoirs-a-trump-en-matiere-de-tarifs/</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>Le président américain pourrait imposer des tarifs de 100&amp;#160;% sur les principaux importateurs d’énergie russe L’article En visant la Russie, le Congrès américain va-t-il donner de nouveaux pouvoirs à Trump en matière de tarifs&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -27065,6 +27419,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E806" r:id="rId805"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E807" r:id="rId806"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E808" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E809" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E810" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E811" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E812" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E813" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E814" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E815" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E816" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E817" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E818" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E819" r:id="rId818"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G819"/>
+  <dimension ref="A1:G826"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -26278,7 +26278,6 @@
           <t>De Vienne à Istanbul, de Zagreb à Belgrade, compositeurs et institutions ont fait de l’art lyrique un instrument de modernisation autant qu’un espace d’affirmation identitaire.</t>
         </is>
       </c>
-      <c r="G809" t="inlineStr"/>
     </row>
     <row r="810">
       <c r="A810" s="2" t="inlineStr">
@@ -26311,7 +26310,6 @@
           <t>Face à la multiplication des claviers, l’écriture manuscrite se raréfie. Les pratiques scolaires nous rappellent la richesse de ses gestes.</t>
         </is>
       </c>
-      <c r="G810" t="inlineStr"/>
     </row>
     <row r="811">
       <c r="A811" s="2" t="inlineStr">
@@ -26344,7 +26342,6 @@
           <t>Le monde est passé de 70&amp;nbsp;000, au début des années&amp;nbsp;1980, à 12&amp;nbsp;000&amp;nbsp;têtes nucléaires. Il serait erroné de croire que, pour autant, le risque de l’emploi de l’arme atomique se serait réduit, au contraire même.</t>
         </is>
       </c>
-      <c r="G811" t="inlineStr"/>
     </row>
     <row r="812">
       <c r="A812" s="2" t="inlineStr">
@@ -26377,7 +26374,6 @@
           <t>À l’approche des législatives, Eisenkot talonne Nétanyahou. Mais le scrutin se jouera surtout sur les coalitions et sur le modèle d’Israël après le 7-Octobre.</t>
         </is>
       </c>
-      <c r="G812" t="inlineStr"/>
     </row>
     <row r="813">
       <c r="A813" s="2" t="inlineStr">
@@ -26410,7 +26406,6 @@
           <t>Les États membres de l’UE, qui est la première partenaire commerciale d’Israël, sont toujours divisés sur la remise en cause des avantages du volet de libre-échange de l’accord d’association UE-Israël.</t>
         </is>
       </c>
-      <c r="G813" t="inlineStr"/>
     </row>
     <row r="814">
       <c r="A814" s="2" t="inlineStr">
@@ -26443,7 +26438,6 @@
           <t>L’expansion de Starlink en Afrique peut servir aux forces armées locales, mais aussi aux groupes armés illégaux.</t>
         </is>
       </c>
-      <c r="G814" t="inlineStr"/>
     </row>
     <row r="815">
       <c r="A815" s="2" t="inlineStr">
@@ -26476,7 +26470,6 @@
           <t>Selon le candidat à la présidentielle, nous avons la responsabilité historique d'accélérer la construction européenne L’article Le moment des États-Unis d&amp;rsquo;Europe est venu est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G815" t="inlineStr"/>
     </row>
     <row r="816">
       <c r="A816" s="2" t="inlineStr">
@@ -26509,7 +26502,6 @@
           <t>Le discours intégral du premier ministre canadien devant le Parlement européen L’article Mark Carney et la nouvelle alliance transatlantique est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G816" t="inlineStr"/>
     </row>
     <row r="817">
       <c r="A817" s="2" t="inlineStr">
@@ -26542,7 +26534,6 @@
           <t>Les 134 kilomètres du canal de Pinglu ont été construits en quatre ans L’article Pékin inaugure son premier méga-canal depuis 1949 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G817" t="inlineStr"/>
     </row>
     <row r="818">
       <c r="A818" s="2" t="inlineStr">
@@ -26575,7 +26566,6 @@
           <t>Entre l’illusion d’une souveraineté technologique totale et la résignation à une vassalisation brutale, l’Europe doit inventer une troisième voie dans la course à l’IA L’article Pour une souveraineté technologique sélective est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G818" t="inlineStr"/>
     </row>
     <row r="819">
       <c r="A819" s="2" t="inlineStr">
@@ -26608,7 +26598,237 @@
           <t>Le président américain pourrait imposer des tarifs de 100&amp;#160;% sur les principaux importateurs d’énergie russe L’article En visant la Russie, le Congrès américain va-t-il donner de nouveaux pouvoirs à Trump en matière de tarifs&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G819" t="inlineStr"/>
+    </row>
+    <row r="820">
+      <c r="A820" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:20</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:29</t>
+        </is>
+      </c>
+      <c r="D820" s="3" t="inlineStr">
+        <is>
+          <t>Nigel Farage : la fin de l’état de grâce ?</t>
+        </is>
+      </c>
+      <c r="E820" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/nigel-farage-la-fin-de-letat-de-grace-291887</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>Confronté à plusieurs affaires embarrassantes et à un nouveau premier ministre qui séduit les classes populaires, Nigel&amp;nbsp;Farage ne caracole plus en tête des sondages.</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr"/>
+    </row>
+    <row r="821">
+      <c r="A821" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:20</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:28</t>
+        </is>
+      </c>
+      <c r="D821" s="3" t="inlineStr">
+        <is>
+          <t>Au sein de l’opposition russe, la bataille des idées</t>
+        </is>
+      </c>
+      <c r="E821" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/au-sein-de-lopposition-russe-la-bataille-des-idees-290460</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>Composée de nombreuses personnalités actives et désireuses de peser sur l’avenir de leur pays, l’opposition russe est traversée par des débats de fond sur de nombreux sujets clés.</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr"/>
+    </row>
+    <row r="822">
+      <c r="A822" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:20</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:05</t>
+        </is>
+      </c>
+      <c r="D822" s="3" t="inlineStr">
+        <is>
+          <t>Qui est Oemis Romagoza Durruthy, le professeur de danse cubain recruté par Moscou pour mener des opérations de sabotage en Europe</t>
+        </is>
+      </c>
+      <c r="E822" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/18/qui-est-oemis-romagoza-durruthy-le-professeur-de-danse-cubain-recrute-par-moscou-pour-mener-des-operations-de-sabotage-en-europe/</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>Au moins une douzaine de personnes ont été cooptées par Romagoza depuis 2024 L’article Qui est Oemis Romagoza Durruthy, le professeur de danse cubain recruté par Moscou pour mener des opérations de sabotage en Europe est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr"/>
+    </row>
+    <row r="823">
+      <c r="A823" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:20</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:30</t>
+        </is>
+      </c>
+      <c r="D823" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi la Chine mise sur l’open source dans la course à l’IA</t>
+        </is>
+      </c>
+      <c r="E823" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/18/pourquoi-la-chine-mise-sur-lopen-source-dans-la-course-a-lia/</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>Et comment Pékin pourrait s’en servir pour étendre son influence au sein du Sud global L’article Pourquoi la Chine mise sur l’open source dans la course à l’IA est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr"/>
+    </row>
+    <row r="824">
+      <c r="A824" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:20</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:30</t>
+        </is>
+      </c>
+      <c r="D824" s="3" t="inlineStr">
+        <is>
+          <t>Le test des trois Chinois (fois treize)</t>
+        </is>
+      </c>
+      <c r="E824" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/18/test-des-trois-chinois-fois-treize/</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>Pour la rentrée, nous avons demandé à treize sinologues et China watchers de passer le fameux test lancé par la revue L’article Le test des trois Chinois (fois treize) est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:20</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>2026-09-17 17:00</t>
+        </is>
+      </c>
+      <c r="D825" s="3" t="inlineStr">
+        <is>
+          <t>La guerre en Iran devrait faire baisser les émissions de CO₂ liées à l’énergie</t>
+        </is>
+      </c>
+      <c r="E825" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/17/la-guerre-en-iran-devrait-faire-baisser-les-emissions-de-co%e2%82%82-liees-a-lenergie/</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>ll s’agirait du premier recul depuis la pandémie de Covid-19 L’article La guerre en Iran devrait faire baisser les émissions de CO₂ liées à l’énergie est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr"/>
+    </row>
+    <row r="826">
+      <c r="A826" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:20</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:19</t>
+        </is>
+      </c>
+      <c r="D826" s="3" t="inlineStr">
+        <is>
+          <t>Que peut l’Arabie saoudite face aux Houthis ?</t>
+        </is>
+      </c>
+      <c r="E826" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/17/que-peut-larabie-saoudite-face-aux-houthis/</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>L’organisation islamiste s’est emparée en seulement quelques jours du détroit de Bab el-Mandeb L’article Que peut l’Arabie saoudite face aux Houthis&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -27430,6 +27650,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E817" r:id="rId816"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E818" r:id="rId817"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E819" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E820" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E821" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E822" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E823" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E824" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E825" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E826" r:id="rId825"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G826"/>
+  <dimension ref="A1:G849"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -26630,7 +26630,6 @@
           <t>Confronté à plusieurs affaires embarrassantes et à un nouveau premier ministre qui séduit les classes populaires, Nigel&amp;nbsp;Farage ne caracole plus en tête des sondages.</t>
         </is>
       </c>
-      <c r="G820" t="inlineStr"/>
     </row>
     <row r="821">
       <c r="A821" s="2" t="inlineStr">
@@ -26663,7 +26662,6 @@
           <t>Composée de nombreuses personnalités actives et désireuses de peser sur l’avenir de leur pays, l’opposition russe est traversée par des débats de fond sur de nombreux sujets clés.</t>
         </is>
       </c>
-      <c r="G821" t="inlineStr"/>
     </row>
     <row r="822">
       <c r="A822" s="2" t="inlineStr">
@@ -26696,7 +26694,6 @@
           <t>Au moins une douzaine de personnes ont été cooptées par Romagoza depuis 2024 L’article Qui est Oemis Romagoza Durruthy, le professeur de danse cubain recruté par Moscou pour mener des opérations de sabotage en Europe est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G822" t="inlineStr"/>
     </row>
     <row r="823">
       <c r="A823" s="2" t="inlineStr">
@@ -26729,7 +26726,6 @@
           <t>Et comment Pékin pourrait s’en servir pour étendre son influence au sein du Sud global L’article Pourquoi la Chine mise sur l’open source dans la course à l’IA est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G823" t="inlineStr"/>
     </row>
     <row r="824">
       <c r="A824" s="2" t="inlineStr">
@@ -26762,7 +26758,6 @@
           <t>Pour la rentrée, nous avons demandé à treize sinologues et China watchers de passer le fameux test lancé par la revue L’article Le test des trois Chinois (fois treize) est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G824" t="inlineStr"/>
     </row>
     <row r="825">
       <c r="A825" s="2" t="inlineStr">
@@ -26795,7 +26790,6 @@
           <t>ll s’agirait du premier recul depuis la pandémie de Covid-19 L’article La guerre en Iran devrait faire baisser les émissions de CO₂ liées à l’énergie est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G825" t="inlineStr"/>
     </row>
     <row r="826">
       <c r="A826" s="2" t="inlineStr">
@@ -26828,7 +26822,757 @@
           <t>L’organisation islamiste s’est emparée en seulement quelques jours du détroit de Bab el-Mandeb L’article Que peut l’Arabie saoudite face aux Houthis&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G826" t="inlineStr"/>
+    </row>
+    <row r="827">
+      <c r="A827" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>2026-09-19 07:41</t>
+        </is>
+      </c>
+      <c r="D827" s="3" t="inlineStr">
+        <is>
+          <t>Les mots qui voyagent : du rromani aux pratiques langagières françaises</t>
+        </is>
+      </c>
+      <c r="E827" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-mots-qui-voyagent-du-rromani-aux-pratiques-langagieres-francaises-291581</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>S’intéresser au rromani en sociolexicologie, c’est observer la manière dont une langue et les populations qui la parlent ont participé et participent à l’histoire linguistique du français.</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr"/>
+    </row>
+    <row r="828">
+      <c r="A828" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>2026-09-19 07:26</t>
+        </is>
+      </c>
+      <c r="D828" s="3" t="inlineStr">
+        <is>
+          <t>Jeanne d’Arc, Clemenceau, les frères Lumière, Colette… l’incroyable galerie des refusés pour figurer sur un billet de banque</t>
+        </is>
+      </c>
+      <c r="E828" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/jeanne-darc-clemenceau-les-freres-lumiere-colette-lincroyable-galerie-des-refuses-pour-figurer-sur-un-billet-de-banque-289782</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>Au cours de son existence, la Banque de France a envisagé de nombreuses célébrités mais en a écarté un certain nombre. Pour quelles raisons ?</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr"/>
+    </row>
+    <row r="829">
+      <c r="A829" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>2026-09-19 07:40</t>
+        </is>
+      </c>
+      <c r="D829" s="3" t="inlineStr">
+        <is>
+          <t>Repas à un euro : quels autres leviers pour améliorer l’alimentation des étudiants ?</t>
+        </is>
+      </c>
+      <c r="E829" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/repas-a-un-euro-quels-autres-leviers-pour-ameliorer-lalimentation-des-etudiants-284890</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>Une expérimentation menée auprès d’étudiants à Lyon montre que l’amélioration durable de l’alimentation passe par des aides financières associées à un accompagnement adapté.</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr"/>
+    </row>
+    <row r="830">
+      <c r="A830" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:04</t>
+        </is>
+      </c>
+      <c r="D830" s="3" t="inlineStr">
+        <is>
+          <t>Rapprochement Canada-UE : l’Histoire donne-t-elle raison à Mark Carney ?</t>
+        </is>
+      </c>
+      <c r="E830" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/rapprochement-canada-ue-lhistoire-donne-t-elle-raison-a-mark-carney-292339</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>Face aux pressions de Donald Trump, Ottawa se tourne vers l’Europe. Une inflexion qui prolonge une vieille tradition canadienne d’autonomie.</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr"/>
+    </row>
+    <row r="831">
+      <c r="A831" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:03</t>
+        </is>
+      </c>
+      <c r="D831" s="3" t="inlineStr">
+        <is>
+          <t>Des dollars à l’effigie de Trump ? Une pratique rarissime hors des monarchies</t>
+        </is>
+      </c>
+      <c r="E831" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/des-dollars-a-leffigie-de-trump-une-pratique-rarissime-hors-des-monarchies-292246</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>L’administration Trump veut faire figurer le président américain sur des pièces et billets. Une pratique presque exclusivement réservée aux monarchies héréditaires, selon une analyse des monnaies en circulation dans le monde.</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr"/>
+    </row>
+    <row r="832">
+      <c r="A832" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:02</t>
+        </is>
+      </c>
+      <c r="D832" s="3" t="inlineStr">
+        <is>
+          <t>Remplacer Churchill par des animaux sauvages, est-ce effacer l’histoire ?</t>
+        </is>
+      </c>
+      <c r="E832" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/remplacer-churchill-par-des-animaux-sauvages-est-ce-effacer-lhistoire-292248</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>Le projet de retirer Winston Churchill du billet de cinq livres a suscité une vive polémique au Royaume-Uni. Derrière la défense d’une figure historique se joue surtout une bataille autour de la mémoire collective et de l’identité britannique.</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr"/>
+    </row>
+    <row r="833">
+      <c r="A833" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>2026-09-18 16:02</t>
+        </is>
+      </c>
+      <c r="D833" s="3" t="inlineStr">
+        <is>
+          <t>Près d’un billet de banque sur six dans le monde représente un animal sauvage – et pas toujours celui auquel on s’attendrait</t>
+        </is>
+      </c>
+      <c r="E833" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pres-dun-billet-de-banque-sur-six-dans-le-monde-represente-un-animal-sauvage-et-pas-toujours-celui-auquel-on-sattendrait-292249</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>Des animaux sauvages figurent sur près d’un billet de banque sur six dans le monde. Mettre en avant les espèces menacées pourrait contribuer à mieux les faire connaître et à sensibiliser le public à leur protection.</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr"/>
+    </row>
+    <row r="834">
+      <c r="A834" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:30</t>
+        </is>
+      </c>
+      <c r="D834" s="3" t="inlineStr">
+        <is>
+          <t>À l’Oktoberfest le prix de la chope de bière a été multiplié par deux en 20 ans</t>
+        </is>
+      </c>
+      <c r="E834" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/19/oktoberfest-a-munich-le-prix-de-la-chope-de-biere-a-ete-multiplie-par-deux-en-20-ans/</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>La Maß de bière devrait être vendue 15,61 euros en moyenne en 2026 L’article À l&amp;rsquo;Oktoberfest le prix de la chope de bière a été multiplié par deux en 20 ans est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr"/>
+    </row>
+    <row r="835">
+      <c r="A835" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:28</t>
+        </is>
+      </c>
+      <c r="D835" s="3" t="inlineStr">
+        <is>
+          <t>Chez Anthropic, 26 % de la R&amp;D est pilotée par l’IA</t>
+        </is>
+      </c>
+      <c r="E835" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/18/chez-anthropic-26-de-la-rd-est-pilotee-par-lia/</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>Cette part pourrait atteindre environ 80&amp;#160;% à la fin de l’année L’article Chez Anthropic, 26&amp;#160;% de la R&amp;amp;D est pilotée par l’IA est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr"/>
+    </row>
+    <row r="836">
+      <c r="A836" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>2026-09-19 10:02</t>
+        </is>
+      </c>
+      <c r="D836" s="3" t="inlineStr">
+        <is>
+          <t>Demi-journée d’étude : Malraux, la traversée du siècle : de la guerre d’Espagne à la Seconde Guerre mondiale</t>
+        </is>
+      </c>
+      <c r="E836" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/demi-journee-detude-malraux-la-traversee-du-siecle-de-la-guerre-despagne-a-la-seconde-guerre-mondiale/</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>À l’occasion du cinquantenaire de la disparition d’André Malraux, l’APHG est heureuse de s’associer à l’ONaCVG et au CNC pour vous proposer une journée d’étude consacrée à cette figure majeure du XXᵉ siècle. &amp;#160; Date : Samedi 14 novembre 2026, de 14h à 19h Lieu : Lycée Louis-le-Grand &amp;#8211; 123 rue Saint-Jacques, 75005 Paris. &amp;#160; Au programme [&amp;#8230;] L’article Demi-journée d&amp;rsquo;étude : Malraux, la traversée du siècle : de la guerre d’Espagne à la Seconde Guerre mondiale est apparu en</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr"/>
+    </row>
+    <row r="837">
+      <c r="A837" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:45</t>
+        </is>
+      </c>
+      <c r="D837" s="3" t="inlineStr">
+        <is>
+          <t>L’immobilier en Chine, entre vulnérabilité et relance</t>
+        </is>
+      </c>
+      <c r="E837" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-regionaux/la-chine/articles-scientifiques/limmobilier-en-chine-entre-vulnerabilite-et-relance</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>Les annonces de faillites de géants de l'immobilier en Chine ont provoqué une onde médiatique en Europe sur le thème de la fin du modèle de croissance chinois. En réalité, la crise a été provoquée par le Parti pour éviter un éclatement brutal de la bulle spéculative. La croissance économique se poursuit, malgré une légère rétractation du secteur immobilier. Et localement, les constructions continuent, comme le montrent les exemples de la métropolisation à Shanghai et des chantiers urbains à Xi'a</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr"/>
+    </row>
+    <row r="838">
+      <c r="A838" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:10</t>
+        </is>
+      </c>
+      <c r="D838" s="3" t="inlineStr">
+        <is>
+          <t>Parution des rapports du jury, CAPES, CAPLP et agrégation, 2026</t>
+        </is>
+      </c>
+      <c r="E838" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/veille/concours-examens-programmes/parution-des-rapports-du-jury-capes-caplp-et-agregation-2026</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>Le site Devenir enseignant a publié les rapports d'agrégation du CAPES bac+3, du CAPES bac+5 et de l'agrégation de géographie et de l'agrégation interne d'histoire-géographie.</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr"/>
+    </row>
+    <row r="839">
+      <c r="A839" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:05</t>
+        </is>
+      </c>
+      <c r="D839" s="3" t="inlineStr">
+        <is>
+          <t>Prix du livre de géographie des lycéens et des étudiants 2027 : les cinq ouvrages sélectionnés</t>
+        </is>
+      </c>
+      <c r="E839" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/veille/evenements/prix-du-livre-de-geographie-des-lyceens-et-des-etudiants-2027-les-cinq-ouvrages-selectionnes</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Le Prix du livre de géographie des lycéens et des étudiants a annoncé la sélection 2027 :</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr"/>
+    </row>
+    <row r="840">
+      <c r="A840" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>2026-09-14 06:00</t>
+        </is>
+      </c>
+      <c r="D840" s="3" t="inlineStr">
+        <is>
+          <t>Lettre d'information n° 225</t>
+        </is>
+      </c>
+      <c r="E840" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/a-propos/lettres-dinformation/lettre-information-225</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr"/>
+      <c r="G840" t="inlineStr"/>
+    </row>
+    <row r="841">
+      <c r="A841" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>2026-09-11 12:45</t>
+        </is>
+      </c>
+      <c r="D841" s="3" t="inlineStr">
+        <is>
+          <t>L’Abkhazie, de l’État autoproclamé au protectorat russe</t>
+        </is>
+      </c>
+      <c r="E841" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-regionaux/la-russie-des-territoires-en-recomposition/articles-scientifiques/abkhazie-de-letat-autoproclame-au-protectorat-russe</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>Indépendante depuis 1992, reconnue par seulement cinq États membres des Nations Unies, la petite république autoproclamée d’Abkhazie peine à faire valoir son indépendance sur la scène internationale. Malgré une ambition souveraine majoritaire, l’isolement diplomatique de ce petit État de facto du Sud-Caucase le contraint à s’arrimer à son voisin russe.</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr"/>
+    </row>
+    <row r="842">
+      <c r="A842" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>2026-09-08 13:20</t>
+        </is>
+      </c>
+      <c r="D842" s="3" t="inlineStr">
+        <is>
+          <t>Les cabanes alpines à l’épreuve des transformations du tourisme et du climat</t>
+        </is>
+      </c>
+      <c r="E842" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/ageoda/les-cabanes-alpines-a-l2019epreuve-des-transformations-du-tourisme-et-du-climat</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>Conférence</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr"/>
+    </row>
+    <row r="843">
+      <c r="A843" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>2026-09-08 13:05</t>
+        </is>
+      </c>
+      <c r="D843" s="3" t="inlineStr">
+        <is>
+          <t>Des Malouines à l'Antarctique : géopolitique et changement d'échelle</t>
+        </is>
+      </c>
+      <c r="E843" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/veille/breves/des-malouines-a-lantarctique-geopolitique-et-changement-dechelle</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La mobilisation de la démarche géopolitique, qui définit l'« étude des rivalités de pouvoirs sur un territoire » (Yves Lacoste), s'avère efficace pour comprendre tel ou tel conflit. Mais il convient parfois aussi, en changeant d'échelle, d'introduire une démarche géostratégique pour mieux cerner ce qui est en jeu. C’est ce dont témoigne la brutale réaffirmation des revendications argentines par le président Milei contre le Royaume-Uni à propos des îles appelées Malouines en français (Falkland / </t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr"/>
+    </row>
+    <row r="844">
+      <c r="A844" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>2026-09-08 07:26</t>
+        </is>
+      </c>
+      <c r="D844" s="3" t="inlineStr">
+        <is>
+          <t>L'Amérique latine : ressources sur Géoconfluences</t>
+        </is>
+      </c>
+      <c r="E844" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-regionaux/amerique-latine/lamerique-latine-ressources-sur-geoconfluences</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr"/>
+      <c r="G844" t="inlineStr"/>
+    </row>
+    <row r="845">
+      <c r="A845" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:03</t>
+        </is>
+      </c>
+      <c r="D845" s="3" t="inlineStr">
+        <is>
+          <t>Bienvenue en 2055 dans un monde neutre en carbone</t>
+        </is>
+      </c>
+      <c r="E845" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/ageoda/bienvenue-en-2055-dans-un-monde-neutre-en-carbone</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>Café virtuel</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>2026-09-02 08:57</t>
+        </is>
+      </c>
+      <c r="D846" s="3" t="inlineStr">
+        <is>
+          <t>Entrez en matière ! Du grain de sable à la ville durable</t>
+        </is>
+      </c>
+      <c r="E846" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/ageoda/entrez-en-matiere-du-grain-de-sable-a-la-ville-durable</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>Expo</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:45</t>
+        </is>
+      </c>
+      <c r="D847" s="3" t="inlineStr">
+        <is>
+          <t>Image à la une. La militarisation de la petite île japonaise de Yonaguni</t>
+        </is>
+      </c>
+      <c r="E847" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/a-la-une/image-a-la-une/image-a-la-une-la-militarisation-de-la-petite-ile-japonaise-de-yonaguni</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>Située aux confins occidentaux de la préfecture d’Okinawa, à une centaine de kilomètres de Taïwan, l'île de Yonaguni (environ 28 km²) accueille une garnison des Forces d’autodéfense japonaises depuis 2016. Le déploiement de cette dernière a suscité des controverses qui mettent en lumière des rivalités politiques à différentes échelles, et constitue en outre un choix d’aménagement ayant des répercussions importantes sur le territoire.</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr"/>
+    </row>
+    <row r="848">
+      <c r="A848" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:09</t>
+        </is>
+      </c>
+      <c r="D848" s="3" t="inlineStr">
+        <is>
+          <t>Mourir en Antarctique</t>
+        </is>
+      </c>
+      <c r="E848" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/ageoda/mourir-en-antarctique</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>Café géo</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr"/>
+    </row>
+    <row r="849">
+      <c r="A849" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:50</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>2026-08-31 07:40</t>
+        </is>
+      </c>
+      <c r="D849" s="3" t="inlineStr">
+        <is>
+          <t>Le détroit d'Ormuz, un verrou géopolitique, du libre passage au blocage et à la guerre</t>
+        </is>
+      </c>
+      <c r="E849" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/eclairage/le-detroit-d-ormuz-verrou-geopolitique</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>Le détroit d'Ormuz est un point de passage stratégique à l'échelle mondiale : c'est la seule route maritime entre le principal pôle de production pétrolière et les plus gros importateurs, en particulier des États d'Asie fortement dépendants des hydrocarbures du Golfe. L'attaque de l'Iran par les États-Unis et Israël, au mépris du droit international, et le verrouillage du détroit qui a suivi, ont porté un coup à l'économie régionale et mondiale, dont on ne mesure pas encore toutes les conséquenc</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -27657,6 +28401,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E824" r:id="rId823"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E825" r:id="rId824"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E826" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E827" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E828" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E829" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E830" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E831" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E832" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E833" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E834" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E835" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E836" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E837" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E838" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E839" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E840" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E841" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E842" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E843" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E844" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E845" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E846" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E847" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E848" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E849" r:id="rId848"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G849"/>
+  <dimension ref="A1:G853"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -26854,7 +26854,6 @@
           <t>S’intéresser au rromani en sociolexicologie, c’est observer la manière dont une langue et les populations qui la parlent ont participé et participent à l’histoire linguistique du français.</t>
         </is>
       </c>
-      <c r="G827" t="inlineStr"/>
     </row>
     <row r="828">
       <c r="A828" s="2" t="inlineStr">
@@ -26887,7 +26886,6 @@
           <t>Au cours de son existence, la Banque de France a envisagé de nombreuses célébrités mais en a écarté un certain nombre. Pour quelles raisons ?</t>
         </is>
       </c>
-      <c r="G828" t="inlineStr"/>
     </row>
     <row r="829">
       <c r="A829" s="2" t="inlineStr">
@@ -26920,7 +26918,6 @@
           <t>Une expérimentation menée auprès d’étudiants à Lyon montre que l’amélioration durable de l’alimentation passe par des aides financières associées à un accompagnement adapté.</t>
         </is>
       </c>
-      <c r="G829" t="inlineStr"/>
     </row>
     <row r="830">
       <c r="A830" s="2" t="inlineStr">
@@ -26953,7 +26950,6 @@
           <t>Face aux pressions de Donald Trump, Ottawa se tourne vers l’Europe. Une inflexion qui prolonge une vieille tradition canadienne d’autonomie.</t>
         </is>
       </c>
-      <c r="G830" t="inlineStr"/>
     </row>
     <row r="831">
       <c r="A831" s="2" t="inlineStr">
@@ -26986,7 +26982,6 @@
           <t>L’administration Trump veut faire figurer le président américain sur des pièces et billets. Une pratique presque exclusivement réservée aux monarchies héréditaires, selon une analyse des monnaies en circulation dans le monde.</t>
         </is>
       </c>
-      <c r="G831" t="inlineStr"/>
     </row>
     <row r="832">
       <c r="A832" s="2" t="inlineStr">
@@ -27019,7 +27014,6 @@
           <t>Le projet de retirer Winston Churchill du billet de cinq livres a suscité une vive polémique au Royaume-Uni. Derrière la défense d’une figure historique se joue surtout une bataille autour de la mémoire collective et de l’identité britannique.</t>
         </is>
       </c>
-      <c r="G832" t="inlineStr"/>
     </row>
     <row r="833">
       <c r="A833" s="2" t="inlineStr">
@@ -27052,7 +27046,6 @@
           <t>Des animaux sauvages figurent sur près d’un billet de banque sur six dans le monde. Mettre en avant les espèces menacées pourrait contribuer à mieux les faire connaître et à sensibiliser le public à leur protection.</t>
         </is>
       </c>
-      <c r="G833" t="inlineStr"/>
     </row>
     <row r="834">
       <c r="A834" s="2" t="inlineStr">
@@ -27085,7 +27078,6 @@
           <t>La Maß de bière devrait être vendue 15,61 euros en moyenne en 2026 L’article À l&amp;rsquo;Oktoberfest le prix de la chope de bière a été multiplié par deux en 20 ans est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G834" t="inlineStr"/>
     </row>
     <row r="835">
       <c r="A835" s="2" t="inlineStr">
@@ -27118,7 +27110,6 @@
           <t>Cette part pourrait atteindre environ 80&amp;#160;% à la fin de l’année L’article Chez Anthropic, 26&amp;#160;% de la R&amp;amp;D est pilotée par l’IA est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G835" t="inlineStr"/>
     </row>
     <row r="836">
       <c r="A836" s="2" t="inlineStr">
@@ -27151,7 +27142,6 @@
           <t>À l’occasion du cinquantenaire de la disparition d’André Malraux, l’APHG est heureuse de s’associer à l’ONaCVG et au CNC pour vous proposer une journée d’étude consacrée à cette figure majeure du XXᵉ siècle. &amp;#160; Date : Samedi 14 novembre 2026, de 14h à 19h Lieu : Lycée Louis-le-Grand &amp;#8211; 123 rue Saint-Jacques, 75005 Paris. &amp;#160; Au programme [&amp;#8230;] L’article Demi-journée d&amp;rsquo;étude : Malraux, la traversée du siècle : de la guerre d’Espagne à la Seconde Guerre mondiale est apparu en</t>
         </is>
       </c>
-      <c r="G836" t="inlineStr"/>
     </row>
     <row r="837">
       <c r="A837" s="2" t="inlineStr">
@@ -27184,7 +27174,6 @@
           <t>Les annonces de faillites de géants de l'immobilier en Chine ont provoqué une onde médiatique en Europe sur le thème de la fin du modèle de croissance chinois. En réalité, la crise a été provoquée par le Parti pour éviter un éclatement brutal de la bulle spéculative. La croissance économique se poursuit, malgré une légère rétractation du secteur immobilier. Et localement, les constructions continuent, comme le montrent les exemples de la métropolisation à Shanghai et des chantiers urbains à Xi'a</t>
         </is>
       </c>
-      <c r="G837" t="inlineStr"/>
     </row>
     <row r="838">
       <c r="A838" s="2" t="inlineStr">
@@ -27217,7 +27206,6 @@
           <t>Le site Devenir enseignant a publié les rapports d'agrégation du CAPES bac+3, du CAPES bac+5 et de l'agrégation de géographie et de l'agrégation interne d'histoire-géographie.</t>
         </is>
       </c>
-      <c r="G838" t="inlineStr"/>
     </row>
     <row r="839">
       <c r="A839" s="2" t="inlineStr">
@@ -27250,7 +27238,6 @@
           <t>Le Prix du livre de géographie des lycéens et des étudiants a annoncé la sélection 2027 :</t>
         </is>
       </c>
-      <c r="G839" t="inlineStr"/>
     </row>
     <row r="840">
       <c r="A840" s="2" t="inlineStr">
@@ -27278,8 +27265,6 @@
           <t>https://geoconfluences.ens-lyon.fr/a-propos/lettres-dinformation/lettre-information-225</t>
         </is>
       </c>
-      <c r="F840" t="inlineStr"/>
-      <c r="G840" t="inlineStr"/>
     </row>
     <row r="841">
       <c r="A841" s="2" t="inlineStr">
@@ -27312,7 +27297,6 @@
           <t>Indépendante depuis 1992, reconnue par seulement cinq États membres des Nations Unies, la petite république autoproclamée d’Abkhazie peine à faire valoir son indépendance sur la scène internationale. Malgré une ambition souveraine majoritaire, l’isolement diplomatique de ce petit État de facto du Sud-Caucase le contraint à s’arrimer à son voisin russe.</t>
         </is>
       </c>
-      <c r="G841" t="inlineStr"/>
     </row>
     <row r="842">
       <c r="A842" s="2" t="inlineStr">
@@ -27345,7 +27329,6 @@
           <t>Conférence</t>
         </is>
       </c>
-      <c r="G842" t="inlineStr"/>
     </row>
     <row r="843">
       <c r="A843" s="2" t="inlineStr">
@@ -27378,7 +27361,6 @@
           <t xml:space="preserve">La mobilisation de la démarche géopolitique, qui définit l'« étude des rivalités de pouvoirs sur un territoire » (Yves Lacoste), s'avère efficace pour comprendre tel ou tel conflit. Mais il convient parfois aussi, en changeant d'échelle, d'introduire une démarche géostratégique pour mieux cerner ce qui est en jeu. C’est ce dont témoigne la brutale réaffirmation des revendications argentines par le président Milei contre le Royaume-Uni à propos des îles appelées Malouines en français (Falkland / </t>
         </is>
       </c>
-      <c r="G843" t="inlineStr"/>
     </row>
     <row r="844">
       <c r="A844" s="2" t="inlineStr">
@@ -27406,8 +27388,6 @@
           <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-regionaux/amerique-latine/lamerique-latine-ressources-sur-geoconfluences</t>
         </is>
       </c>
-      <c r="F844" t="inlineStr"/>
-      <c r="G844" t="inlineStr"/>
     </row>
     <row r="845">
       <c r="A845" s="2" t="inlineStr">
@@ -27440,7 +27420,6 @@
           <t>Café virtuel</t>
         </is>
       </c>
-      <c r="G845" t="inlineStr"/>
     </row>
     <row r="846">
       <c r="A846" s="2" t="inlineStr">
@@ -27473,7 +27452,6 @@
           <t>Expo</t>
         </is>
       </c>
-      <c r="G846" t="inlineStr"/>
     </row>
     <row r="847">
       <c r="A847" s="2" t="inlineStr">
@@ -27506,7 +27484,6 @@
           <t>Située aux confins occidentaux de la préfecture d’Okinawa, à une centaine de kilomètres de Taïwan, l'île de Yonaguni (environ 28 km²) accueille une garnison des Forces d’autodéfense japonaises depuis 2016. Le déploiement de cette dernière a suscité des controverses qui mettent en lumière des rivalités politiques à différentes échelles, et constitue en outre un choix d’aménagement ayant des répercussions importantes sur le territoire.</t>
         </is>
       </c>
-      <c r="G847" t="inlineStr"/>
     </row>
     <row r="848">
       <c r="A848" s="2" t="inlineStr">
@@ -27539,7 +27516,6 @@
           <t>Café géo</t>
         </is>
       </c>
-      <c r="G848" t="inlineStr"/>
     </row>
     <row r="849">
       <c r="A849" s="2" t="inlineStr">
@@ -27572,7 +27548,138 @@
           <t>Le détroit d'Ormuz est un point de passage stratégique à l'échelle mondiale : c'est la seule route maritime entre le principal pôle de production pétrolière et les plus gros importateurs, en particulier des États d'Asie fortement dépendants des hydrocarbures du Golfe. L'attaque de l'Iran par les États-Unis et Israël, au mépris du droit international, et le verrouillage du détroit qui a suivi, ont porté un coup à l'économie régionale et mondiale, dont on ne mesure pas encore toutes les conséquenc</t>
         </is>
       </c>
-      <c r="G849" t="inlineStr"/>
+    </row>
+    <row r="850">
+      <c r="A850" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 13:25</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:06</t>
+        </is>
+      </c>
+      <c r="D850" s="3" t="inlineStr">
+        <is>
+          <t>Les faucons russes, idéologues du conservatisme modernisateur</t>
+        </is>
+      </c>
+      <c r="E850" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-faucons-russes-ideologues-du-conservatisme-modernisateur-290015</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>Depuis l'époque soviétique, certains penseurs russes, de plus en plus influents, refusent toute convergence de la Russie avec l’Occident et défendent une modernisation fondée sur la puissance de l’État et des valeurs traditionnelles.</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr"/>
+    </row>
+    <row r="851">
+      <c r="A851" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 13:25</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:30</t>
+        </is>
+      </c>
+      <c r="D851" s="3" t="inlineStr">
+        <is>
+          <t>En Allemagne, un nouveau succès de l’AfD aux élections régionales pourrait faire tomber Merz</t>
+        </is>
+      </c>
+      <c r="E851" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/20/en-allemagne-un-nouveau-succes-de-lafd-aux-elections-regionales-pourrait-faire-tomber-merz/</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>Deux élections régionales ont lieu aujourd’hui, le 20 septembre, dans les Länder de Berlin et de Mecklembourg-Poméranie-Occidentale L’article En Allemagne, un nouveau succès de l’AfD aux élections régionales pourrait faire tomber Merz est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr"/>
+    </row>
+    <row r="852">
+      <c r="A852" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 13:25</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:00</t>
+        </is>
+      </c>
+      <c r="D852" s="3" t="inlineStr">
+        <is>
+          <t>Le plan de la Nouvelle Droite pour conquérir l’Allemagne</t>
+        </is>
+      </c>
+      <c r="E852" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/20/comment-lextreme-droite-conquiert-lallemagne/</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>Pour comprendre l’explosion de l’AfD, il faut s’intéresser à une guerre culturelle et à son stratège&amp;#160;: Götz Kubitschek. L’article Le plan de la Nouvelle Droite pour conquérir l’Allemagne est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr"/>
+    </row>
+    <row r="853">
+      <c r="A853" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 13:25</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>2026-09-19 13:19</t>
+        </is>
+      </c>
+      <c r="D853" s="3" t="inlineStr">
+        <is>
+          <t>Que sait-on de l’accord que Donald Trump a annoncé sur le Groenland ?</t>
+        </is>
+      </c>
+      <c r="E853" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/19/que-sait-on-de-laccord-que-donald-trump-a-annonce-sur-le-groenland/</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>Les États-Unis obtiendraient un droit de veto sur les investissements étrangers jugés sensibles et «&amp;#160;toute la liberté pour prendre les mesures qui s'imposent&amp;#160;» en matière de défense. L’article Que sait-on de l’accord que Donald Trump a annoncé sur le Groenland&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -28424,6 +28531,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E847" r:id="rId846"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E848" r:id="rId847"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E849" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E850" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E851" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E852" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E853" r:id="rId852"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G853"/>
+  <dimension ref="A1:G859"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -27580,7 +27580,6 @@
           <t>Depuis l'époque soviétique, certains penseurs russes, de plus en plus influents, refusent toute convergence de la Russie avec l’Occident et défendent une modernisation fondée sur la puissance de l’État et des valeurs traditionnelles.</t>
         </is>
       </c>
-      <c r="G850" t="inlineStr"/>
     </row>
     <row r="851">
       <c r="A851" s="2" t="inlineStr">
@@ -27613,7 +27612,6 @@
           <t>Deux élections régionales ont lieu aujourd’hui, le 20 septembre, dans les Länder de Berlin et de Mecklembourg-Poméranie-Occidentale L’article En Allemagne, un nouveau succès de l’AfD aux élections régionales pourrait faire tomber Merz est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G851" t="inlineStr"/>
     </row>
     <row r="852">
       <c r="A852" s="2" t="inlineStr">
@@ -27646,7 +27644,6 @@
           <t>Pour comprendre l’explosion de l’AfD, il faut s’intéresser à une guerre culturelle et à son stratège&amp;#160;: Götz Kubitschek. L’article Le plan de la Nouvelle Droite pour conquérir l’Allemagne est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G852" t="inlineStr"/>
     </row>
     <row r="853">
       <c r="A853" s="2" t="inlineStr">
@@ -27679,7 +27676,204 @@
           <t>Les États-Unis obtiendraient un droit de veto sur les investissements étrangers jugés sensibles et «&amp;#160;toute la liberté pour prendre les mesures qui s'imposent&amp;#160;» en matière de défense. L’article Que sait-on de l’accord que Donald Trump a annoncé sur le Groenland&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G853" t="inlineStr"/>
+    </row>
+    <row r="854">
+      <c r="A854" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:37</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:40</t>
+        </is>
+      </c>
+      <c r="D854" s="3" t="inlineStr">
+        <is>
+          <t>Filles ou garçons : le prestige des études n’influence pas leurs choix d’orientation de la même manière</t>
+        </is>
+      </c>
+      <c r="E854" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/filles-ou-garcons-le-prestige-des-etudes-ninfluence-pas-leurs-choix-dorientation-de-la-meme-maniere-275697</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>Avec un recul de 120 ans sur les inscriptions universitaires, une recherche montre comment le prestige social des professions agit sur les choix d’orientation en médecine et en droit.</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr"/>
+    </row>
+    <row r="855">
+      <c r="A855" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:37</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>2026-09-21 10:11</t>
+        </is>
+      </c>
+      <c r="D855" s="3" t="inlineStr">
+        <is>
+          <t>Donald Trump crie victoire au Groenland, mais l’accord révèle une profonde crise de confiance</t>
+        </is>
+      </c>
+      <c r="E855" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/donald-trump-crie-victoire-au-groenland-mais-laccord-revele-une-profonde-crise-de-confiance-292481</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>L’accord conclu entre les États-Unis, le Danemark et le Groenland écarte le risque d’une crise immédiate mais soulève des questions sur l’influence de Washington dans l’Arctique et sur l’avenir de la confiance au sein de l’OTAN.</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr"/>
+    </row>
+    <row r="856">
+      <c r="A856" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:37</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>2026-09-21 10:08</t>
+        </is>
+      </c>
+      <c r="D856" s="3" t="inlineStr">
+        <is>
+          <t>Le parti de Poutine obtient le plus grand nombre de sièges de son histoire à la Douma</t>
+        </is>
+      </c>
+      <c r="E856" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/21/le-parti-de-poutine-obtient-le-plus-grand-nombre-de-sieges-de-son-histoire-a-la-douma/</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>Le vote pour Russie Unie aurait été gonflé d’environ 16 points L’article Le parti de Poutine obtient le plus grand nombre de sièges de son histoire à la Douma est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr"/>
+    </row>
+    <row r="857">
+      <c r="A857" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:37</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>2026-09-21 05:20</t>
+        </is>
+      </c>
+      <c r="D857" s="3" t="inlineStr">
+        <is>
+          <t>L’Europe peut se défendre seule</t>
+        </is>
+      </c>
+      <c r="E857" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/21/leurope-peut-se-defendre-seule/</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>L’ancien Major général des armées sort de son silence pour poser un diagnostic et une feuille de route L’article L’Europe peut se défendre seule est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr"/>
+    </row>
+    <row r="858">
+      <c r="A858" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:37</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:30</t>
+        </is>
+      </c>
+      <c r="D858" s="3" t="inlineStr">
+        <is>
+          <t>Le dernier modèle d’OpenAI peut opérer un drone pour « surveiller » des individus en toute autonomie</t>
+        </is>
+      </c>
+      <c r="E858" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/21/le-dernier-modele-dopenai-peut-operer-un-drone-pour-surveiller-des-individus-en-toute-autonomie/</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>GPT-6 Astra est le premier modèle d’IA à passer le benchmark d’Andon Labs L’article Le dernier modèle d’OpenAI peut opérer un drone pour «&amp;#160;surveiller&amp;#160;» des individus en toute autonomie est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:37</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>2026-09-20 17:09</t>
+        </is>
+      </c>
+      <c r="D859" s="3" t="inlineStr">
+        <is>
+          <t>Allemagne : l’AfD progresse, la gauche en position de gouverner les deux régions</t>
+        </is>
+      </c>
+      <c r="E859" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/20/mecklembourg-pomeranie-occidentale-et-berlin-lafd-progresse-la-gauche-en-position-de-gouverner-les-deux-regions/</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>L’AfD double presque son score en Mecklembourg-Poméranie-Occidentale, tandis que Die Linke arrive en première position à Berlin L’article Allemagne&amp;#160;: l’AfD progresse, la gauche en position de gouverner les deux régions est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -28535,6 +28729,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E851" r:id="rId850"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E852" r:id="rId851"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E853" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E854" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E855" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E856" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E857" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E858" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E859" r:id="rId858"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G859"/>
+  <dimension ref="A1:G866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -27708,7 +27708,6 @@
           <t>Avec un recul de 120 ans sur les inscriptions universitaires, une recherche montre comment le prestige social des professions agit sur les choix d’orientation en médecine et en droit.</t>
         </is>
       </c>
-      <c r="G854" t="inlineStr"/>
     </row>
     <row r="855">
       <c r="A855" s="2" t="inlineStr">
@@ -27741,7 +27740,6 @@
           <t>L’accord conclu entre les États-Unis, le Danemark et le Groenland écarte le risque d’une crise immédiate mais soulève des questions sur l’influence de Washington dans l’Arctique et sur l’avenir de la confiance au sein de l’OTAN.</t>
         </is>
       </c>
-      <c r="G855" t="inlineStr"/>
     </row>
     <row r="856">
       <c r="A856" s="2" t="inlineStr">
@@ -27774,7 +27772,6 @@
           <t>Le vote pour Russie Unie aurait été gonflé d’environ 16 points L’article Le parti de Poutine obtient le plus grand nombre de sièges de son histoire à la Douma est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G856" t="inlineStr"/>
     </row>
     <row r="857">
       <c r="A857" s="2" t="inlineStr">
@@ -27807,7 +27804,6 @@
           <t>L’ancien Major général des armées sort de son silence pour poser un diagnostic et une feuille de route L’article L’Europe peut se défendre seule est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G857" t="inlineStr"/>
     </row>
     <row r="858">
       <c r="A858" s="2" t="inlineStr">
@@ -27840,7 +27836,6 @@
           <t>GPT-6 Astra est le premier modèle d’IA à passer le benchmark d’Andon Labs L’article Le dernier modèle d’OpenAI peut opérer un drone pour «&amp;#160;surveiller&amp;#160;» des individus en toute autonomie est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G858" t="inlineStr"/>
     </row>
     <row r="859">
       <c r="A859" s="2" t="inlineStr">
@@ -27873,7 +27868,237 @@
           <t>L’AfD double presque son score en Mecklembourg-Poméranie-Occidentale, tandis que Die Linke arrive en première position à Berlin L’article Allemagne&amp;#160;: l’AfD progresse, la gauche en position de gouverner les deux régions est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G859" t="inlineStr"/>
+    </row>
+    <row r="860">
+      <c r="A860" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 13:51</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:56</t>
+        </is>
+      </c>
+      <c r="D860" s="3" t="inlineStr">
+        <is>
+          <t>Quand les archéologues révèlent les habitudes alimentaires d’autrefois</t>
+        </is>
+      </c>
+      <c r="E860" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/quand-les-archeologues-revelent-les-habitudes-alimentaires-dautrefois-290893</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>Le laboratoire ARC-Nucléart travaille sur la conservation d’œuvres et d’objets archéologiques en matériaux organiques, permettant de comprendre ce qu'on mangeait jadis, et comment on cuisinait.</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr"/>
+    </row>
+    <row r="861">
+      <c r="A861" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 13:51</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>2026-09-22 13:59</t>
+        </is>
+      </c>
+      <c r="D861" s="3" t="inlineStr">
+        <is>
+          <t>Yémen, péninsule Arabique, mer Rouge : les houthistes à l’assaut de la région</t>
+        </is>
+      </c>
+      <c r="E861" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/yemen-peninsule-arabique-mer-rouge-les-houthistes-a-lassaut-de-la-region-292538</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>Dans le viseur des houthistes&amp;nbsp;: le gouvernement yéménite internationalement reconnu, mais aussi la famille Al-Saoud qui dirige l’Arabie saoudite et contrôle les Lieux saints de l’islam.</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr"/>
+    </row>
+    <row r="862">
+      <c r="A862" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 13:51</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:41</t>
+        </is>
+      </c>
+      <c r="D862" s="3" t="inlineStr">
+        <is>
+          <t>La bibliothèque assiégée : Comment l’administration Trump fait des rayonnages un champ de bataille culturelle</t>
+        </is>
+      </c>
+      <c r="E862" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/la-bibliotheque-assiegee-comment-ladministration-trump-fait-des-rayonnages-un-champ-de-bataille-culturelle-291719</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>Aux États-Unis, la censure des livres s’étend aux bibliothèques publiques et devient un enjeu politique, menaçant aussi celles et ceux qui les font vivre.</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 13:51</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:30</t>
+        </is>
+      </c>
+      <c r="D863" s="3" t="inlineStr">
+        <is>
+          <t>Le S&amp;P 500 performe moins bien sous Trump que sous Obama</t>
+        </is>
+      </c>
+      <c r="E863" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/22/le-sp-500-performe-moins-bien-sous-trump-que-sous-obama/</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>20 mois depuis le retour de Trump, l’indice a gagné 28&amp;#160;% – contre 32&amp;#160;% sous Obama L’article Le S&amp;amp;P 500 performe moins bien sous Trump que sous Obama est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr"/>
+    </row>
+    <row r="864">
+      <c r="A864" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 13:51</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:30</t>
+        </is>
+      </c>
+      <c r="D864" s="3" t="inlineStr">
+        <is>
+          <t>L’Europe doit apprendre à dire non à la Chine</t>
+        </is>
+      </c>
+      <c r="E864" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/22/leurope-doit-apprendre-a-dire-non-a-la-chine/</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>La puissance industrielle de Pékin menace nos fondements économiques. Pour y répondre, l’Union peut transformer son marché en instrument de puissance. L’article L’Europe doit apprendre à dire non à la Chine est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 13:51</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:37</t>
+        </is>
+      </c>
+      <c r="D865" s="3" t="inlineStr">
+        <is>
+          <t>La grande peur de Xi face à l’IA</t>
+        </is>
+      </c>
+      <c r="E865" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/21/la-grande-peur-du-parti-face-a-lia/</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>En Chine la course à l’IA est indissociable d’un impératif&amp;#160;: préserver le contrôle du Parti L’article La grande peur de Xi face à l’IA est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr"/>
+    </row>
+    <row r="866">
+      <c r="A866" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 13:51</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:22</t>
+        </is>
+      </c>
+      <c r="D866" s="3" t="inlineStr">
+        <is>
+          <t>La Russie impose un couvre-feu à sa frontière avec l’Estonie</t>
+        </is>
+      </c>
+      <c r="E866" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/21/la-russie-impose-un-couvre-feu-a-sa-frontiere-avec-lestonie/</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>Les gardes-frontières estoniens n’ont pas été informés en amont L’article La Russie impose un couvre-feu à sa frontière avec l’Estonie est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -28735,6 +28960,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E857" r:id="rId856"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E858" r:id="rId857"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E859" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E860" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E861" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E862" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E863" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E864" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E865" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E866" r:id="rId865"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G866"/>
+  <dimension ref="A1:G883"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -27900,7 +27900,6 @@
           <t>Le laboratoire ARC-Nucléart travaille sur la conservation d’œuvres et d’objets archéologiques en matériaux organiques, permettant de comprendre ce qu'on mangeait jadis, et comment on cuisinait.</t>
         </is>
       </c>
-      <c r="G860" t="inlineStr"/>
     </row>
     <row r="861">
       <c r="A861" s="2" t="inlineStr">
@@ -27933,7 +27932,6 @@
           <t>Dans le viseur des houthistes&amp;nbsp;: le gouvernement yéménite internationalement reconnu, mais aussi la famille Al-Saoud qui dirige l’Arabie saoudite et contrôle les Lieux saints de l’islam.</t>
         </is>
       </c>
-      <c r="G861" t="inlineStr"/>
     </row>
     <row r="862">
       <c r="A862" s="2" t="inlineStr">
@@ -27966,7 +27964,6 @@
           <t>Aux États-Unis, la censure des livres s’étend aux bibliothèques publiques et devient un enjeu politique, menaçant aussi celles et ceux qui les font vivre.</t>
         </is>
       </c>
-      <c r="G862" t="inlineStr"/>
     </row>
     <row r="863">
       <c r="A863" s="2" t="inlineStr">
@@ -27999,7 +27996,6 @@
           <t>20 mois depuis le retour de Trump, l’indice a gagné 28&amp;#160;% – contre 32&amp;#160;% sous Obama L’article Le S&amp;amp;P 500 performe moins bien sous Trump que sous Obama est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G863" t="inlineStr"/>
     </row>
     <row r="864">
       <c r="A864" s="2" t="inlineStr">
@@ -28032,7 +28028,6 @@
           <t>La puissance industrielle de Pékin menace nos fondements économiques. Pour y répondre, l’Union peut transformer son marché en instrument de puissance. L’article L’Europe doit apprendre à dire non à la Chine est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G864" t="inlineStr"/>
     </row>
     <row r="865">
       <c r="A865" s="2" t="inlineStr">
@@ -28065,7 +28060,6 @@
           <t>En Chine la course à l’IA est indissociable d’un impératif&amp;#160;: préserver le contrôle du Parti L’article La grande peur de Xi face à l’IA est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G865" t="inlineStr"/>
     </row>
     <row r="866">
       <c r="A866" s="2" t="inlineStr">
@@ -28098,7 +28092,567 @@
           <t>Les gardes-frontières estoniens n’ont pas été informés en amont L’article La Russie impose un couvre-feu à sa frontière avec l’Estonie est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G866" t="inlineStr"/>
+    </row>
+    <row r="867">
+      <c r="A867" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:01</t>
+        </is>
+      </c>
+      <c r="D867" s="3" t="inlineStr">
+        <is>
+          <t>Comment soignait-on la gueule de bois autrefois ? Du chou aux poumons de chèvre</t>
+        </is>
+      </c>
+      <c r="E867" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-soignait-on-la-gueule-de-bois-autrefois-du-chou-aux-poumons-de-chevre-292010</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>Du chou aux clous de girofle, en passant par les poumons de chèvre&amp;nbsp;: depuis l’Antiquité, les remèdes contre la gueule de bois racontent notre rapport à l’ivresse, au corps et à la culpabilité.</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr"/>
+    </row>
+    <row r="868">
+      <c r="A868" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:01</t>
+        </is>
+      </c>
+      <c r="D868" s="3" t="inlineStr">
+        <is>
+          <t>Comment une agence immobilière du XIXᵉ siècle proposait des visites en 3D avant l’invention même de la photographie</t>
+        </is>
+      </c>
+      <c r="E868" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-une-agence-immobiliere-du-xix-siecle-proposait-des-visites-en-3d-avant-linvention-meme-de-la-photographie-292282</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>Bien avant les visites virtuelles en ligne, une agence immobilière londonienne a utilisé, dès 1838, le cosmorama, un dispositif immersif produisant un effet 3D, pour présenter de prestigieuses propriétés à vendre à de riches potentiels acheteurs.</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr"/>
+    </row>
+    <row r="869">
+      <c r="A869" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:00</t>
+        </is>
+      </c>
+      <c r="D869" s="3" t="inlineStr">
+        <is>
+          <t>France-Togo : la fin d’une relation privilégiée ?</t>
+        </is>
+      </c>
+      <c r="E869" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/france-togo-la-fin-dune-relation-privilegiee-291584</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>La récente arrestation de deux journalistes français révèle la dégradation des relations Paris-Lomé, sur fond de rapprochement du Togo avec la Russie et l’Alliance des États du Sahel.</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr"/>
+    </row>
+    <row r="870">
+      <c r="A870" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>2026-09-23 09:59</t>
+        </is>
+      </c>
+      <c r="D870" s="3" t="inlineStr">
+        <is>
+          <t>Les 400 ans de la Marine nationale : un anniversaire amnésique ? Du Levant au Ponant, les origines oubliées de la flotte française</t>
+        </is>
+      </c>
+      <c r="E870" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-400-ans-de-la-marine-nationale-un-anniversaire-amnesique-du-levant-au-ponant-les-origines-oubliees-de-la-flotte-francaise-290800</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>On fête en 2026 les 400 ans de l’édit de Richelieu, créant la Marine nationale. Mais pour comprendre son histoire, il faut revenir sur la naissance au XVIᵉ&amp;nbsp;siècle des marines du Levant et du Ponant.</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr"/>
+    </row>
+    <row r="871">
+      <c r="A871" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:48</t>
+        </is>
+      </c>
+      <c r="D871" s="3" t="inlineStr">
+        <is>
+          <t>Politiques sportives : comment lutter vraiment contre le décrochage des jeunes ?</t>
+        </is>
+      </c>
+      <c r="E871" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/politiques-sportives-comment-lutter-vraiment-contre-le-decrochage-des-jeunes-291529</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>Si de nombreux jeunes ont déjà pratiqué un sport, beaucoup décrochent à l’adolescence. Le véritable enjeu n’est-il pas alors de fidéliser ce public&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr"/>
+    </row>
+    <row r="872">
+      <c r="A872" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:54</t>
+        </is>
+      </c>
+      <c r="D872" s="3" t="inlineStr">
+        <is>
+          <t>D’État-tampon à État-charnière : comment la Mongolie réinvente sa diplomatie</t>
+        </is>
+      </c>
+      <c r="E872" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/detat-tampon-a-etat-charniere-comment-la-mongolie-reinvente-sa-diplomatie-291059</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>La Mongolie tente de transformer son enclavement entre la Chine et la Russie en atout diplomatique.</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr"/>
+    </row>
+    <row r="873">
+      <c r="A873" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:53</t>
+        </is>
+      </c>
+      <c r="D873" s="3" t="inlineStr">
+        <is>
+          <t>Dieu contre « le bon diable » : retour sur les récents discours théologico-politiques au Cameroun</t>
+        </is>
+      </c>
+      <c r="E873" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/dieu-contre-le-bon-diable-retour-sur-les-recents-discours-theologico-politiques-au-cameroun-291721</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>Au Cameroun, Dieu et le diable se sont invités dans la crise politique que le pays a connue autour de la présidentielle, il y a un an, et qui continue de se faire ressentir aujourd’hui.</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr"/>
+    </row>
+    <row r="874">
+      <c r="A874" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:37</t>
+        </is>
+      </c>
+      <c r="D874" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : l’Ukraine exporte désormais plus de céréales que la Russie</t>
+        </is>
+      </c>
+      <c r="E874" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/23/economie-russe-lukraine-exporte-desormais-plus-de-cereales-que-la-russie/</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>Les exportations russes de céréales ont chuté de 76&amp;#160;% sur la période du 11 au 20 septembre L’article Économie russe&amp;#160;: l’Ukraine exporte désormais plus de céréales que la Russie est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr"/>
+    </row>
+    <row r="875">
+      <c r="A875" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30</t>
+        </is>
+      </c>
+      <c r="D875" s="3" t="inlineStr">
+        <is>
+          <t>Les clefs de la puissance houthiste</t>
+        </is>
+      </c>
+      <c r="E875" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/23/les-clefs-de-la-puissance-houthiste/</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>Pourquoi personne n’arrive à vaincre ce mouvement tribal et sa violence théologico-politique L’article Les clefs de la puissance houthiste est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr"/>
+    </row>
+    <row r="876">
+      <c r="A876" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30</t>
+        </is>
+      </c>
+      <c r="D876" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi Trump accueille-t-il Xi Jinping avec un fastueux protocole ?</t>
+        </is>
+      </c>
+      <c r="E876" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/23/pourquoi-trump-accueille-t-il-xi-jinping-avec-un-fastueux-protocole/</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>Trump sera le premier président depuis Kennedy à accueillir un dirigeant sur le tarmac L’article Pourquoi Trump accueille-t-il Xi Jinping avec un fastueux protocole&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr"/>
+    </row>
+    <row r="877">
+      <c r="A877" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:38</t>
+        </is>
+      </c>
+      <c r="D877" s="3" t="inlineStr">
+        <is>
+          <t>Au Groenland, la stratégie européenne pour résister à Trump a fini par payer</t>
+        </is>
+      </c>
+      <c r="E877" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/22/au-groenland-la-strategie-europeenne-pour-resister-a-trump-a-fini-par-payer/</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>L’accord entre les États-Unis et le Danemark pourrait mettre un terme au prétentions territoriales du président américain L’article Au Groenland, la stratégie européenne pour résister à Trump a fini par payer est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr"/>
+    </row>
+    <row r="878">
+      <c r="A878" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>2026-09-22 17:14</t>
+        </is>
+      </c>
+      <c r="D878" s="3" t="inlineStr">
+        <is>
+          <t>Les 5 points à retenir du discours néo-conservateur de Trump aux Nations unies</t>
+        </is>
+      </c>
+      <c r="E878" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/22/les-5-points-a-retenir-du-discours-neo-conservateur-de-trump-aux-nations-unies/</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>Enlisé en Iran, Trump a défendu et surenchéri son action internationale L’article Les 5 points à retenir du discours néo-conservateur de Trump aux Nations unies est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr"/>
+    </row>
+    <row r="879">
+      <c r="A879" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>2026-09-22 16:20</t>
+        </is>
+      </c>
+      <c r="D879" s="3" t="inlineStr">
+        <is>
+          <t>Comment la France est devenue la fille déclassée de l’Église</t>
+        </is>
+      </c>
+      <c r="E879" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/22/comment-la-france-est-devenue-fille-declassee-de-leglise/</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>L’étrange histoire de la République et des papes L’article Comment la France est devenue la fille déclassée de l’Église est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr"/>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:40</t>
+        </is>
+      </c>
+      <c r="D880" s="3" t="inlineStr">
+        <is>
+          <t>Face à la hausse des prix, Trump va-t-il suspendre les exportations de carburant ?</t>
+        </is>
+      </c>
+      <c r="E880" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/22/face-a-la-hausse-des-prix-trump-va-t-il-suspendre-les-exportations-de-carburant/</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>Une telle mesure aurait des effets contre-productifs à long terme L’article Face à la hausse des prix, Trump va-t-il suspendre les exportations de carburant&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr"/>
+    </row>
+    <row r="881">
+      <c r="A881" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:56</t>
+        </is>
+      </c>
+      <c r="D881" s="3" t="inlineStr">
+        <is>
+          <t>Yves Lacoste, la revue Hérodote et la géopolitique</t>
+        </is>
+      </c>
+      <c r="E881" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/ageoda/yves-lacoste-la-revue-herodote-et-la-geopolitique</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>Café géo</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr"/>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>2026-09-22 08:33</t>
+        </is>
+      </c>
+      <c r="D882" s="3" t="inlineStr">
+        <is>
+          <t>Le panda, géant diplomatique ou espèce victime de son succès ?</t>
+        </is>
+      </c>
+      <c r="E882" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-thematiques/changement-global/geographie-des-animaux/le-panda-geant-diplomatique-ou-espece-victime-de-son-succes</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>Depuis 1990, la Chine loue des pandas pour de longues durées à des pays soigneusement choisis, en lien avec ses intérêts économiques et politiques. Si la diplomatie du panda fait intégralement partie du soft power chinois, et ce depuis longtemps, l’instrumentalisation à des fins mercantiles d’une espèce classée vulnérable par l’Union internationale de la conservation de la nature et, plus largement, d’un animal symbole de l’environnement, pose problème.</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr"/>
+    </row>
+    <row r="883">
+      <c r="A883" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:35</t>
+        </is>
+      </c>
+      <c r="D883" s="3" t="inlineStr">
+        <is>
+          <t>La démocratie municipale face aux habitants : controverse autour de l'aménagement d'un plan d'eau à Grenoble</t>
+        </is>
+      </c>
+      <c r="E883" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-thematiques/geographie-du-politique/articles/la-democratie-municipale-face-aux-habitants-controverse-autour-de-lamenagement-dun-plan-deau</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>Le quartier de la Villeneuve à Grenoble accueille un plan d’eau artificiel dont la rénovation, portée par la municipalité, vise à le sécuriser et le rendre baignable. Le projet s’inscrit dans un renouvellement urbain piloté par la Métropole et l’ANRU, qui le présentent comme le « premier écoquartier populaire ». Certains habitants, dans ce quartier marqué par de fortes divergences de participation politique, dénoncent toutefois une conduite jugée verticale. Ce projet éclaire les paradoxes et les</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -28967,6 +29521,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E864" r:id="rId863"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E865" r:id="rId864"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E866" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E867" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E868" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E869" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E870" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E871" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E872" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E873" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E874" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E875" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E876" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E877" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E878" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E879" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E880" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E881" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E882" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E883" r:id="rId882"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G883"/>
+  <dimension ref="A1:G899"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -28124,7 +28124,6 @@
           <t>Du chou aux clous de girofle, en passant par les poumons de chèvre&amp;nbsp;: depuis l’Antiquité, les remèdes contre la gueule de bois racontent notre rapport à l’ivresse, au corps et à la culpabilité.</t>
         </is>
       </c>
-      <c r="G867" t="inlineStr"/>
     </row>
     <row r="868">
       <c r="A868" s="2" t="inlineStr">
@@ -28157,7 +28156,6 @@
           <t>Bien avant les visites virtuelles en ligne, une agence immobilière londonienne a utilisé, dès 1838, le cosmorama, un dispositif immersif produisant un effet 3D, pour présenter de prestigieuses propriétés à vendre à de riches potentiels acheteurs.</t>
         </is>
       </c>
-      <c r="G868" t="inlineStr"/>
     </row>
     <row r="869">
       <c r="A869" s="2" t="inlineStr">
@@ -28190,7 +28188,6 @@
           <t>La récente arrestation de deux journalistes français révèle la dégradation des relations Paris-Lomé, sur fond de rapprochement du Togo avec la Russie et l’Alliance des États du Sahel.</t>
         </is>
       </c>
-      <c r="G869" t="inlineStr"/>
     </row>
     <row r="870">
       <c r="A870" s="2" t="inlineStr">
@@ -28223,7 +28220,6 @@
           <t>On fête en 2026 les 400 ans de l’édit de Richelieu, créant la Marine nationale. Mais pour comprendre son histoire, il faut revenir sur la naissance au XVIᵉ&amp;nbsp;siècle des marines du Levant et du Ponant.</t>
         </is>
       </c>
-      <c r="G870" t="inlineStr"/>
     </row>
     <row r="871">
       <c r="A871" s="2" t="inlineStr">
@@ -28256,7 +28252,6 @@
           <t>Si de nombreux jeunes ont déjà pratiqué un sport, beaucoup décrochent à l’adolescence. Le véritable enjeu n’est-il pas alors de fidéliser ce public&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G871" t="inlineStr"/>
     </row>
     <row r="872">
       <c r="A872" s="2" t="inlineStr">
@@ -28289,7 +28284,6 @@
           <t>La Mongolie tente de transformer son enclavement entre la Chine et la Russie en atout diplomatique.</t>
         </is>
       </c>
-      <c r="G872" t="inlineStr"/>
     </row>
     <row r="873">
       <c r="A873" s="2" t="inlineStr">
@@ -28322,7 +28316,6 @@
           <t>Au Cameroun, Dieu et le diable se sont invités dans la crise politique que le pays a connue autour de la présidentielle, il y a un an, et qui continue de se faire ressentir aujourd’hui.</t>
         </is>
       </c>
-      <c r="G873" t="inlineStr"/>
     </row>
     <row r="874">
       <c r="A874" s="2" t="inlineStr">
@@ -28355,7 +28348,6 @@
           <t>Les exportations russes de céréales ont chuté de 76&amp;#160;% sur la période du 11 au 20 septembre L’article Économie russe&amp;#160;: l’Ukraine exporte désormais plus de céréales que la Russie est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G874" t="inlineStr"/>
     </row>
     <row r="875">
       <c r="A875" s="2" t="inlineStr">
@@ -28388,7 +28380,6 @@
           <t>Pourquoi personne n’arrive à vaincre ce mouvement tribal et sa violence théologico-politique L’article Les clefs de la puissance houthiste est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G875" t="inlineStr"/>
     </row>
     <row r="876">
       <c r="A876" s="2" t="inlineStr">
@@ -28421,7 +28412,6 @@
           <t>Trump sera le premier président depuis Kennedy à accueillir un dirigeant sur le tarmac L’article Pourquoi Trump accueille-t-il Xi Jinping avec un fastueux protocole&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G876" t="inlineStr"/>
     </row>
     <row r="877">
       <c r="A877" s="2" t="inlineStr">
@@ -28454,7 +28444,6 @@
           <t>L’accord entre les États-Unis et le Danemark pourrait mettre un terme au prétentions territoriales du président américain L’article Au Groenland, la stratégie européenne pour résister à Trump a fini par payer est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G877" t="inlineStr"/>
     </row>
     <row r="878">
       <c r="A878" s="2" t="inlineStr">
@@ -28487,7 +28476,6 @@
           <t>Enlisé en Iran, Trump a défendu et surenchéri son action internationale L’article Les 5 points à retenir du discours néo-conservateur de Trump aux Nations unies est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G878" t="inlineStr"/>
     </row>
     <row r="879">
       <c r="A879" s="2" t="inlineStr">
@@ -28520,7 +28508,6 @@
           <t>L’étrange histoire de la République et des papes L’article Comment la France est devenue la fille déclassée de l’Église est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G879" t="inlineStr"/>
     </row>
     <row r="880">
       <c r="A880" s="2" t="inlineStr">
@@ -28553,7 +28540,6 @@
           <t>Une telle mesure aurait des effets contre-productifs à long terme L’article Face à la hausse des prix, Trump va-t-il suspendre les exportations de carburant&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G880" t="inlineStr"/>
     </row>
     <row r="881">
       <c r="A881" s="2" t="inlineStr">
@@ -28586,7 +28572,6 @@
           <t>Café géo</t>
         </is>
       </c>
-      <c r="G881" t="inlineStr"/>
     </row>
     <row r="882">
       <c r="A882" s="2" t="inlineStr">
@@ -28619,7 +28604,6 @@
           <t>Depuis 1990, la Chine loue des pandas pour de longues durées à des pays soigneusement choisis, en lien avec ses intérêts économiques et politiques. Si la diplomatie du panda fait intégralement partie du soft power chinois, et ce depuis longtemps, l’instrumentalisation à des fins mercantiles d’une espèce classée vulnérable par l’Union internationale de la conservation de la nature et, plus largement, d’un animal symbole de l’environnement, pose problème.</t>
         </is>
       </c>
-      <c r="G882" t="inlineStr"/>
     </row>
     <row r="883">
       <c r="A883" s="2" t="inlineStr">
@@ -28652,7 +28636,534 @@
           <t>Le quartier de la Villeneuve à Grenoble accueille un plan d’eau artificiel dont la rénovation, portée par la municipalité, vise à le sécuriser et le rendre baignable. Le projet s’inscrit dans un renouvellement urbain piloté par la Métropole et l’ANRU, qui le présentent comme le « premier écoquartier populaire ». Certains habitants, dans ce quartier marqué par de fortes divergences de participation politique, dénoncent toutefois une conduite jugée verticale. Ce projet éclaire les paradoxes et les</t>
         </is>
       </c>
-      <c r="G883" t="inlineStr"/>
+    </row>
+    <row r="884">
+      <c r="A884" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:23</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>2026-09-25 07:00</t>
+        </is>
+      </c>
+      <c r="D884" s="3" t="inlineStr">
+        <is>
+          <t>Que révèlent la devise et les armoiries du pape Léon XIV ?</t>
+        </is>
+      </c>
+      <c r="E884" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/que-revelent-la-devise-et-les-armoiries-du-pape-leon-xiv-292795</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>En choisissant les symboles de saint Augustin, le nouveau pape affirme son attachement à l’unité et à l’humilité, deux thèmes que l’art de la Renaissance a souvent associés au fondateur de son ordre.</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr"/>
+    </row>
+    <row r="885">
+      <c r="A885" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:23</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:59</t>
+        </is>
+      </c>
+      <c r="D885" s="3" t="inlineStr">
+        <is>
+          <t>Ce que « Le Semeur », tableau lumineux de Van Gogh, révèle du message de Léon XIV</t>
+        </is>
+      </c>
+      <c r="E885" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/ce-que-le-semeur-tableau-lumineux-de-van-gogh-revele-du-message-de-leon-xiv-292794</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>Lors de sa première audience générale, le pape Léon XIV avait évoqué « Le Semeur au soleil couchant » de Van Gogh comme un symbole d’espérance. Ce tableau, inspiré d’une parabole biblique, éclaire aussi l’importance qu’il accorde à la dignité du travail.</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr"/>
+    </row>
+    <row r="886">
+      <c r="A886" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:23</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:14</t>
+        </is>
+      </c>
+      <c r="D886" s="3" t="inlineStr">
+        <is>
+          <t>Développons les capacités créatives des universités</t>
+        </is>
+      </c>
+      <c r="E886" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/developpons-les-capacites-creatives-des-universites-287236</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>Contrairement à une idée reçue, la créativité n’est pas une compétence spontanée. Elle s’épanouit d’autant mieux dans certains contextes. Les universités françaises en profitent-elles&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr"/>
+    </row>
+    <row r="887">
+      <c r="A887" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:23</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:26</t>
+        </is>
+      </c>
+      <c r="D887" s="3" t="inlineStr">
+        <is>
+          <t>Au Brésil, l’affaire Banco Master fait trembler le monde politique et éclabousse la campagne présidentielle</t>
+        </is>
+      </c>
+      <c r="E887" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/au-bresil-laffaire-banco-master-fait-trembler-le-monde-politique-et-eclabousse-la-campagne-presidentielle-292846</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>Le scandale Banco Master secoue le Brésil à quelques semaines de l’élection présidentielle. Cette vaste affaire de fraude bancaire révèle un réseau d’influence qui touche la classe politique et la Cour suprême.</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr"/>
+    </row>
+    <row r="888">
+      <c r="A888" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:23</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:18</t>
+        </is>
+      </c>
+      <c r="D888" s="3" t="inlineStr">
+        <is>
+          <t>Différend France-Vanuatu sur les îles Matthew et Hunter : l’option de la cogestion</t>
+        </is>
+      </c>
+      <c r="E888" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/differend-france-vanuatu-sur-les-iles-matthew-et-hunter-loption-de-la-cogestion-291790</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>La France et le Vanuatu s’opposent sur deux îlots inhabités. La cogestion pourrait permettre de préserver leurs revendications tout en gérant ensemble le territoire.</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr"/>
+    </row>
+    <row r="889">
+      <c r="A889" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:23</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:13</t>
+        </is>
+      </c>
+      <c r="D889" s="3" t="inlineStr">
+        <is>
+          <t>Washington refuse qu’Anthropic et OpenAI soumettent leurs derniers modèles à une évaluation indépendante</t>
+        </is>
+      </c>
+      <c r="E889" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/25/washington-refuse-quanthropic-et-openai-soumettent-leurs-derniers-modeles-a-une-evaluation-independante/</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>Le gouvernement américain serait le premier à avoir accès aux nouveaux modèles de frontière L’article Washington refuse qu’Anthropic et OpenAI soumettent leurs derniers modèles à une évaluation indépendante est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr"/>
+    </row>
+    <row r="890">
+      <c r="A890" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:23</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>2026-09-25 08:55</t>
+        </is>
+      </c>
+      <c r="D890" s="3" t="inlineStr">
+        <is>
+          <t>Le précédent et le sens de la visite apostolique historique de Léon XIV en France</t>
+        </is>
+      </c>
+      <c r="E890" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/25/le-precedent-le-sens-de-la-visite-apostolique-historique-de-leon-xiv-en-france/</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>Que suivre lors des quatres jours du pape en France L’article Le précédent et le sens de la visite apostolique historique de Léon XIV en France est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr"/>
+    </row>
+    <row r="891">
+      <c r="A891" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:23</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:30</t>
+        </is>
+      </c>
+      <c r="D891" s="3" t="inlineStr">
+        <is>
+          <t>La Chine et les États-Unis peuvent-ils s’accorder sur la sécurité de l’IA ?</t>
+        </is>
+      </c>
+      <c r="E891" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/25/la-chine-et-les-etats-unis-peuvent-ils-saccorder-sur-la-securite-de-lia/</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>Pourquoi le retard de Pékin ne garantit pas une absence d’incidents L’article La Chine et les États-Unis peuvent-ils s’accorder sur la sécurité de l’IA&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr"/>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:23</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:06</t>
+        </is>
+      </c>
+      <c r="D892" s="3" t="inlineStr">
+        <is>
+          <t>Que révèle la « découverte » par Anthropic d’une nouvelle enzyme ?</t>
+        </is>
+      </c>
+      <c r="E892" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/24/que-revele-la-decouverte-par-anthropic-dune-nouvelle-enzyme/</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>L’annonce d’Amodei brouille la frontière entre science et communication L’article Que révèle la «&amp;#160;découverte&amp;#160;» par Anthropic d’une nouvelle enzyme&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr"/>
+    </row>
+    <row r="893">
+      <c r="A893" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:23</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:11</t>
+        </is>
+      </c>
+      <c r="D893" s="3" t="inlineStr">
+        <is>
+          <t>Le Pakistan multiplie les raids aériens en Afghanistan</t>
+        </is>
+      </c>
+      <c r="E893" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/24/le-pakistan-multiplie-les-raids-aeriens-en-afghanistan/</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>Le Pakistan dit avoir visé 10 sites utilisés pour le lancement de drones L’article Le Pakistan multiplie les raids aériens en Afghanistan est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr"/>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:23</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:30</t>
+        </is>
+      </c>
+      <c r="D894" s="3" t="inlineStr">
+        <is>
+          <t>En amont des midterms, des candidats républicains se distancient de Trump</t>
+        </is>
+      </c>
+      <c r="E894" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/24/en-amont-des-midterms-des-candidats-republicains-se-distancient-de-trump/</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>L’impopularité de Trump est perçue comme un risque L’article En amont des midterms, des candidats républicains se distancient de Trump est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr"/>
+    </row>
+    <row r="895">
+      <c r="A895" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:23</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:00</t>
+        </is>
+      </c>
+      <c r="D895" s="3" t="inlineStr">
+        <is>
+          <t>En Iran, Khamenei est-il en train de gagner la guerre ?</t>
+        </is>
+      </c>
+      <c r="E895" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/24/en-iran-khamenei-est-en-train-de-gagner-la-guerre/</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>Trump et Netanyahou voulaient renverser le régime, ils pourraient avoir consacré la doctrine du guide assassiné L’article En Iran, Khamenei est-il en train de gagner la guerre&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr"/>
+    </row>
+    <row r="896">
+      <c r="A896" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:23</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>2026-09-23 17:03</t>
+        </is>
+      </c>
+      <c r="D896" s="3" t="inlineStr">
+        <is>
+          <t>L’Europe doit retrouver l’Afrique</t>
+        </is>
+      </c>
+      <c r="E896" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/23/leurope-doit-retrouver-lafrique/</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>Selon le nouveau directeur du Collège de Bruges, un nouveau partenariat est devenu nécessaire L’article L&amp;rsquo;Europe doit retrouver l&amp;rsquo;Afrique est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr"/>
+    </row>
+    <row r="897">
+      <c r="A897" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:23</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>2026-09-23 15:59</t>
+        </is>
+      </c>
+      <c r="D897" s="3" t="inlineStr">
+        <is>
+          <t>La reprise des combats au Tigré menace d’embraser la région</t>
+        </is>
+      </c>
+      <c r="E897" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/23/la-reprise-des-combats-au-tigre-menace-dembraser-la-region/</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>Le TPLF aurait pris le contrôle de plusieurs aéroports du Tigré L’article La reprise des combats au Tigré menace d’embraser la région est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr"/>
+    </row>
+    <row r="898">
+      <c r="A898" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:23</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>2026-09-24 19:02</t>
+        </is>
+      </c>
+      <c r="D898" s="3" t="inlineStr">
+        <is>
+          <t>Communiqué – Cérémonies du 11 novembre dans les établissements scolaires : la vigilance de l’APHG</t>
+        </is>
+      </c>
+      <c r="E898" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/communique-ceremonies-du-11-novembre-dans-les-etablissements-scolaires-la-vigilance-de-laphg/</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L&amp;#8217;APHG mesure le poids symbolique que représente, pour les professeurs d&amp;#8217;histoire-géographie déjà très sollicités ces dernières années, l&amp;#8217;organisation d&amp;#8217;une commémoration obligatoire. Dans un temps saturé de minutes de silence et d&amp;#8217;hommages, une mise en œuvre plus progressive et plus concertée aurait été préférable. L&amp;#8217;APHG note aussi avec une certaine ironie qu&amp;#8217;on exige des jeunes une [&amp;#8230;] L’article Communiqué &amp;#8211; Cérémonies du 11 novembre dans </t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr"/>
+    </row>
+    <row r="899">
+      <c r="A899" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:23</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:47</t>
+        </is>
+      </c>
+      <c r="D899" s="3" t="inlineStr">
+        <is>
+          <t>« Sur le chemin de la mémoire » de V. Igounet – ressource pédagogique</t>
+        </is>
+      </c>
+      <c r="E899" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/sur-le-chemin-de-la-memoire-de-v-igounet-ressource-pedagogique/</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>« Empruntant aux codes du roman autobiographique, du journal intime et du roman historique, Sur le chemin de la mémoire est un récit touchant, instructif et captivant qui, de surcroît, offre aux enseignants des perspectives pédagogiques intéressantes. En effet la lecture de ce roman, cursive ou par extraits, peut parfaitement s’inscrire dans la mise en œuvre [&amp;#8230;] L’article « Sur le chemin de la mémoire » de V. Igounet &amp;#8211; ressource pédagogique est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -29538,6 +30049,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E881" r:id="rId880"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E882" r:id="rId881"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E883" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E884" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E885" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E886" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E887" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E888" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E889" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E890" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E891" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E892" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E893" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E894" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E895" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E896" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E897" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E898" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E899" r:id="rId898"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G899"/>
+  <dimension ref="A1:G904"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -28668,7 +28668,6 @@
           <t>En choisissant les symboles de saint Augustin, le nouveau pape affirme son attachement à l’unité et à l’humilité, deux thèmes que l’art de la Renaissance a souvent associés au fondateur de son ordre.</t>
         </is>
       </c>
-      <c r="G884" t="inlineStr"/>
     </row>
     <row r="885">
       <c r="A885" s="2" t="inlineStr">
@@ -28701,7 +28700,6 @@
           <t>Lors de sa première audience générale, le pape Léon XIV avait évoqué « Le Semeur au soleil couchant » de Van Gogh comme un symbole d’espérance. Ce tableau, inspiré d’une parabole biblique, éclaire aussi l’importance qu’il accorde à la dignité du travail.</t>
         </is>
       </c>
-      <c r="G885" t="inlineStr"/>
     </row>
     <row r="886">
       <c r="A886" s="2" t="inlineStr">
@@ -28734,7 +28732,6 @@
           <t>Contrairement à une idée reçue, la créativité n’est pas une compétence spontanée. Elle s’épanouit d’autant mieux dans certains contextes. Les universités françaises en profitent-elles&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G886" t="inlineStr"/>
     </row>
     <row r="887">
       <c r="A887" s="2" t="inlineStr">
@@ -28767,7 +28764,6 @@
           <t>Le scandale Banco Master secoue le Brésil à quelques semaines de l’élection présidentielle. Cette vaste affaire de fraude bancaire révèle un réseau d’influence qui touche la classe politique et la Cour suprême.</t>
         </is>
       </c>
-      <c r="G887" t="inlineStr"/>
     </row>
     <row r="888">
       <c r="A888" s="2" t="inlineStr">
@@ -28800,7 +28796,6 @@
           <t>La France et le Vanuatu s’opposent sur deux îlots inhabités. La cogestion pourrait permettre de préserver leurs revendications tout en gérant ensemble le territoire.</t>
         </is>
       </c>
-      <c r="G888" t="inlineStr"/>
     </row>
     <row r="889">
       <c r="A889" s="2" t="inlineStr">
@@ -28833,7 +28828,6 @@
           <t>Le gouvernement américain serait le premier à avoir accès aux nouveaux modèles de frontière L’article Washington refuse qu’Anthropic et OpenAI soumettent leurs derniers modèles à une évaluation indépendante est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G889" t="inlineStr"/>
     </row>
     <row r="890">
       <c r="A890" s="2" t="inlineStr">
@@ -28866,7 +28860,6 @@
           <t>Que suivre lors des quatres jours du pape en France L’article Le précédent et le sens de la visite apostolique historique de Léon XIV en France est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G890" t="inlineStr"/>
     </row>
     <row r="891">
       <c r="A891" s="2" t="inlineStr">
@@ -28899,7 +28892,6 @@
           <t>Pourquoi le retard de Pékin ne garantit pas une absence d’incidents L’article La Chine et les États-Unis peuvent-ils s’accorder sur la sécurité de l’IA&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G891" t="inlineStr"/>
     </row>
     <row r="892">
       <c r="A892" s="2" t="inlineStr">
@@ -28932,7 +28924,6 @@
           <t>L’annonce d’Amodei brouille la frontière entre science et communication L’article Que révèle la «&amp;#160;découverte&amp;#160;» par Anthropic d’une nouvelle enzyme&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G892" t="inlineStr"/>
     </row>
     <row r="893">
       <c r="A893" s="2" t="inlineStr">
@@ -28965,7 +28956,6 @@
           <t>Le Pakistan dit avoir visé 10 sites utilisés pour le lancement de drones L’article Le Pakistan multiplie les raids aériens en Afghanistan est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G893" t="inlineStr"/>
     </row>
     <row r="894">
       <c r="A894" s="2" t="inlineStr">
@@ -28998,7 +28988,6 @@
           <t>L’impopularité de Trump est perçue comme un risque L’article En amont des midterms, des candidats républicains se distancient de Trump est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G894" t="inlineStr"/>
     </row>
     <row r="895">
       <c r="A895" s="2" t="inlineStr">
@@ -29031,7 +29020,6 @@
           <t>Trump et Netanyahou voulaient renverser le régime, ils pourraient avoir consacré la doctrine du guide assassiné L’article En Iran, Khamenei est-il en train de gagner la guerre&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G895" t="inlineStr"/>
     </row>
     <row r="896">
       <c r="A896" s="2" t="inlineStr">
@@ -29064,7 +29052,6 @@
           <t>Selon le nouveau directeur du Collège de Bruges, un nouveau partenariat est devenu nécessaire L’article L&amp;rsquo;Europe doit retrouver l&amp;rsquo;Afrique est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G896" t="inlineStr"/>
     </row>
     <row r="897">
       <c r="A897" s="2" t="inlineStr">
@@ -29097,7 +29084,6 @@
           <t>Le TPLF aurait pris le contrôle de plusieurs aéroports du Tigré L’article La reprise des combats au Tigré menace d’embraser la région est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G897" t="inlineStr"/>
     </row>
     <row r="898">
       <c r="A898" s="2" t="inlineStr">
@@ -29130,7 +29116,6 @@
           <t xml:space="preserve">L&amp;#8217;APHG mesure le poids symbolique que représente, pour les professeurs d&amp;#8217;histoire-géographie déjà très sollicités ces dernières années, l&amp;#8217;organisation d&amp;#8217;une commémoration obligatoire. Dans un temps saturé de minutes de silence et d&amp;#8217;hommages, une mise en œuvre plus progressive et plus concertée aurait été préférable. L&amp;#8217;APHG note aussi avec une certaine ironie qu&amp;#8217;on exige des jeunes une [&amp;#8230;] L’article Communiqué &amp;#8211; Cérémonies du 11 novembre dans </t>
         </is>
       </c>
-      <c r="G898" t="inlineStr"/>
     </row>
     <row r="899">
       <c r="A899" s="2" t="inlineStr">
@@ -29163,7 +29148,171 @@
           <t>« Empruntant aux codes du roman autobiographique, du journal intime et du roman historique, Sur le chemin de la mémoire est un récit touchant, instructif et captivant qui, de surcroît, offre aux enseignants des perspectives pédagogiques intéressantes. En effet la lecture de ce roman, cursive ou par extraits, peut parfaitement s’inscrire dans la mise en œuvre [&amp;#8230;] L’article « Sur le chemin de la mémoire » de V. Igounet &amp;#8211; ressource pédagogique est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G899" t="inlineStr"/>
+    </row>
+    <row r="900">
+      <c r="A900" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 13:35</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>2026-09-26 07:14</t>
+        </is>
+      </c>
+      <c r="D900" s="3" t="inlineStr">
+        <is>
+          <t>La visite du pape, une communion médiatique unique en son genre</t>
+        </is>
+      </c>
+      <c r="E900" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/la-visite-du-pape-une-communion-mediatique-unique-en-son-genre-292906</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>Le séjour papal va rassembler des dizaines de millions de spectateurs, qui «&amp;nbsp;communieront&amp;nbsp;» derrière leurs écrans.</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr"/>
+    </row>
+    <row r="901">
+      <c r="A901" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 13:35</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>2026-09-26 07:07</t>
+        </is>
+      </c>
+      <c r="D901" s="3" t="inlineStr">
+        <is>
+          <t>Une journée à Lille au Moyen Âge, ou comment passer de l’archive à l’immersion dans le passé</t>
+        </is>
+      </c>
+      <c r="E901" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/une-journee-a-lille-au-moyen-age-ou-comment-passer-de-larchive-a-limmersion-dans-le-passe-286170</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>L’histoire nous aide à penser la ville de demain&amp;nbsp;: comment fabriquait-on l’espace public au Moyen Âge&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr"/>
+    </row>
+    <row r="902">
+      <c r="A902" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 13:35</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>2026-09-25 16:53</t>
+        </is>
+      </c>
+      <c r="D902" s="3" t="inlineStr">
+        <is>
+          <t>Le pape Léon XIV peut contribuer à améliorer les opérations de secours aux naufragés en Méditerranée</t>
+        </is>
+      </c>
+      <c r="E902" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-pape-leon-xiv-peut-contribuer-a-ameliorer-les-operations-de-secours-aux-naufrages-en-mediterranee-292872</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>La Méditerranée est un cimetière qui ne cesse de se remplir. La voix du pape est suffisamment forte pour susciter certains changements indispensables dans le sauvetage en mer.</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr"/>
+    </row>
+    <row r="903">
+      <c r="A903" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 13:35</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:30</t>
+        </is>
+      </c>
+      <c r="D903" s="3" t="inlineStr">
+        <is>
+          <t>Bab el-Mandeb : le contrôle houthiste fait peser un risque sur les approvisionnements européens en diesel et kérosène</t>
+        </is>
+      </c>
+      <c r="E903" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/26/bab-el-mandeb-le-controle-houthiste-fait-peser-un-risque-sur-les-approvisionnements-europeens-en-diesel-et-kerosene/</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>Près d’un tiers du diesel importé par l’Union provenait du Golfe en 2025 L’article Bab el-Mandeb&amp;#160;: le contrôle houthiste fait peser un risque sur les approvisionnements européens en diesel et kérosène est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr"/>
+    </row>
+    <row r="904">
+      <c r="A904" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 13:35</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>2026-09-25 16:36</t>
+        </is>
+      </c>
+      <c r="D904" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi à gauche on aime Poutine ?</t>
+        </is>
+      </c>
+      <c r="E904" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/25/pourquoi-gauche-on-aime-poutine/</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>Comment l’anti-impérialisme occidental peut empêcher de voir l’impérialisme russe L’article Pourquoi à gauche on aime Poutine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -30065,6 +30214,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E897" r:id="rId896"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E898" r:id="rId897"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E899" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E900" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E901" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E902" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E903" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E904" r:id="rId903"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G904"/>
+  <dimension ref="A1:G920"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -29180,7 +29180,6 @@
           <t>Le séjour papal va rassembler des dizaines de millions de spectateurs, qui «&amp;nbsp;communieront&amp;nbsp;» derrière leurs écrans.</t>
         </is>
       </c>
-      <c r="G900" t="inlineStr"/>
     </row>
     <row r="901">
       <c r="A901" s="2" t="inlineStr">
@@ -29213,7 +29212,6 @@
           <t>L’histoire nous aide à penser la ville de demain&amp;nbsp;: comment fabriquait-on l’espace public au Moyen Âge&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G901" t="inlineStr"/>
     </row>
     <row r="902">
       <c r="A902" s="2" t="inlineStr">
@@ -29246,7 +29244,6 @@
           <t>La Méditerranée est un cimetière qui ne cesse de se remplir. La voix du pape est suffisamment forte pour susciter certains changements indispensables dans le sauvetage en mer.</t>
         </is>
       </c>
-      <c r="G902" t="inlineStr"/>
     </row>
     <row r="903">
       <c r="A903" s="2" t="inlineStr">
@@ -29279,7 +29276,6 @@
           <t>Près d’un tiers du diesel importé par l’Union provenait du Golfe en 2025 L’article Bab el-Mandeb&amp;#160;: le contrôle houthiste fait peser un risque sur les approvisionnements européens en diesel et kérosène est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G903" t="inlineStr"/>
     </row>
     <row r="904">
       <c r="A904" s="2" t="inlineStr">
@@ -29312,7 +29308,534 @@
           <t>Comment l’anti-impérialisme occidental peut empêcher de voir l’impérialisme russe L’article Pourquoi à gauche on aime Poutine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G904" t="inlineStr"/>
+    </row>
+    <row r="905">
+      <c r="A905" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:32</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>2026-09-27 09:00</t>
+        </is>
+      </c>
+      <c r="D905" s="3" t="inlineStr">
+        <is>
+          <t>Un questionnaire de l’éducation nationale sur les violences sexuelles : un outil de repérage, mais peut-il vraiment entendre les enfants ?</t>
+        </is>
+      </c>
+      <c r="E905" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/un-questionnaire-de-leducation-nationale-sur-les-violences-sexuelles-un-outil-de-reperage-mais-peut-il-vraiment-entendre-les-enfants-292280</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>Face aux violences sexuelles, les enfants parlent, mais les institutions ne savent pas toujours les entendre. La systématisation d’un questionnaire dans le cadre scolaire peut-elle changer la donne&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr"/>
+    </row>
+    <row r="906">
+      <c r="A906" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:32</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>2026-09-27 09:01</t>
+        </is>
+      </c>
+      <c r="D906" s="3" t="inlineStr">
+        <is>
+          <t>Révisionnisme historique et contre-discours mémoriel au cœur de l’idéologie de l’AfD</t>
+        </is>
+      </c>
+      <c r="E906" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/revisionnisme-historique-et-contre-discours-memoriel-au-coeur-de-lideologie-de-lafd-292013</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>L’AfD veut réorienter la mémoire allemande : relativisation de la période nazie, valorisation d’un passé national «&amp;nbsp;positif&amp;nbsp;» et remise en cause du cadre mémoriel établi.</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr"/>
+    </row>
+    <row r="907">
+      <c r="A907" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:32</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>2026-09-27 09:00</t>
+        </is>
+      </c>
+      <c r="D907" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi le PIB par habitant en Chine reste-t-il bas ?</t>
+        </is>
+      </c>
+      <c r="E907" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-le-pib-par-habitant-en-chine-reste-t-il-bas-288026</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>En 2025, le PIB par habitant atteignait environ 25&amp;nbsp;975&amp;nbsp;euros en Chine, contre plus de 58&amp;nbsp;651&amp;nbsp;euros en France.</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr"/>
+    </row>
+    <row r="908">
+      <c r="A908" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:32</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>2026-09-27 08:15</t>
+        </is>
+      </c>
+      <c r="D908" s="3" t="inlineStr">
+        <is>
+          <t>L’Amérique n’a toujours pas cédé à Trump</t>
+        </is>
+      </c>
+      <c r="E908" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/27/lamerique-na-toujours-pas-cede-a-trump/</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Derrière la résistance au président, une révolution contre le pouvoir des oligarques de la tech est en train de prendre forme L’article L’Amérique n’a toujours pas cédé à Trump est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr"/>
+    </row>
+    <row r="909">
+      <c r="A909" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:32</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>2026-09-27 04:30</t>
+        </is>
+      </c>
+      <c r="D909" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : la production de pétrole va tomber en 2026 à son niveau le plus bas depuis 2009</t>
+        </is>
+      </c>
+      <c r="E909" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/27/economie-russe-la-production-de-petrole-va-tomber-en-2026-a-son-niveau-le-plus-bas-depuis-2009/</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>Moscou attribue la baisse de la production à des «&amp;#160;travaux de maintenance imprévus&amp;#160;» L’article Économie russe&amp;#160;: la production de pétrole va tomber en 2026 à son niveau le plus bas depuis 2009 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr"/>
+    </row>
+    <row r="910">
+      <c r="A910" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:32</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>2026-09-26 17:19</t>
+        </is>
+      </c>
+      <c r="D910" s="3" t="inlineStr">
+        <is>
+          <t>Faut-il avoir peur de l’identité chrétienne ?</t>
+        </is>
+      </c>
+      <c r="E910" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/26/faut-il-avoir-peur-de-lidentite-chretienne/</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>Le paradoxe du christianisme selon l’évêque de Nanterre L’article Faut-il avoir peur de l’identité chrétienne&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr"/>
+    </row>
+    <row r="911">
+      <c r="A911" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:32</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:03</t>
+        </is>
+      </c>
+      <c r="D911" s="3" t="inlineStr">
+        <is>
+          <t>La doctrine Sánchez pour refonder l’ordre mondial</t>
+        </is>
+      </c>
+      <c r="E911" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/26/la-doctrine-sanchez-pour-refonder-lordre-mondial/</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>Le texte intégral du discours du Premier ministre espagnol à la tribune des Nations unies L’article La doctrine Sánchez pour refonder l&amp;rsquo;ordre mondial est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr"/>
+    </row>
+    <row r="912">
+      <c r="A912" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:32</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>2026-09-26 14:40</t>
+        </is>
+      </c>
+      <c r="D912" s="3" t="inlineStr">
+        <is>
+          <t>En Uruguay, le projet techno-libertarien d’une communauté qui se prépare au monde post-IA pourrait voir le jour dès 2027</t>
+        </is>
+      </c>
+      <c r="E912" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/26/en-uruguay-le-projet-techno-libertarien-dune-communaute-qui-se-prepare-au-monde-post-ia-pourrait-voir-le-jour-des-2027/</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>Praxis a bénéficié du soutien de Peter Thiel et de Marc Andreessen L’article En Uruguay, le projet techno-libertarien d’une communauté qui se prépare au monde post-IA pourrait voir le jour dès 2027 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr"/>
+    </row>
+    <row r="913">
+      <c r="A913" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:32</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>2026-09-26 06:37</t>
+        </is>
+      </c>
+      <c r="D913" s="3" t="inlineStr">
+        <is>
+          <t>Arnaud Orain – Le monde confisqué. Essai sur le capitalisme de la finitude (XVIe-XXIe siècle)</t>
+        </is>
+      </c>
+      <c r="E913" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/arnaud-orain-le-monde-confisque-essai-sur-le-capitalisme-de-la-finitude-xvie-xxie-siecle/</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>« Les transformations contemporaines de la mondialisation, de ses flux et de ses rapports de force sont éclairées par les travaux d’Arnaud Orain qui définit un « capitalisme de la finitude », également existant au XVI-XVIII et de la fin du XIX à 1945. Ces travaux questionnent plusieurs notions abordées au lycée, sur tous les [&amp;#8230;] L’article Arnaud Orain &amp;#8211; Le monde confisqué. Essai sur le capitalisme de la finitude (XVIe-XXIe siècle) est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr"/>
+    </row>
+    <row r="914">
+      <c r="A914" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:32</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>2026-09-26 06:33</t>
+        </is>
+      </c>
+      <c r="D914" s="3" t="inlineStr">
+        <is>
+          <t>Magali Reghezza-Zitt – Bienvenue en 2055. Dans un monde neutre en carbone</t>
+        </is>
+      </c>
+      <c r="E914" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/magali-reghezza-zitt-bienvenue-en-2055-dans-un-monde-neutre-en-carbone/</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1229800000?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr"/>
+    </row>
+    <row r="915">
+      <c r="A915" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:32</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>2026-09-26 06:22</t>
+        </is>
+      </c>
+      <c r="D915" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce CAPES interne – Méthodologie du dossier RAEP</t>
+        </is>
+      </c>
+      <c r="E915" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/coup-de-pouce-capes-interne-methodologie-du-dossier-raep/</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>Pour cette deuxième séance, Marie Digout, Thomas Gosselin et Marine Sorano vous proposent d&amp;#8217;aborder la méthodologie du dossier RAEP. Vous pouvez également télécharger le support de la séance: Méthodologie du dossier RAEP &amp;#8211; 22 septembre 2026 &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1229799957?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr"/>
+    </row>
+    <row r="916">
+      <c r="A916" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:32</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>2026-09-26 06:16</t>
+        </is>
+      </c>
+      <c r="D916" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce Agrégation interne – Thomas Leyris – Citoyenneté et sujétion dans l’empire français (1885-1962)</t>
+        </is>
+      </c>
+      <c r="E916" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/coup-de-pouce-agregation-interne-thomas-leyris-citoyennete-et-sujetion-dans-lempire-francais-1885-1962/</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Thomas Leyris autour du sujet « Citoyenneté et sujétion dans l&amp;#8217;empire français (1885-1962) ». Le podcast est proposé en [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Thomas Leyris &amp;#8211; Citoyenneté et sujétion dans l&amp;#8217;empire fra</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr"/>
+    </row>
+    <row r="917">
+      <c r="A917" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:32</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>2026-09-26 06:10</t>
+        </is>
+      </c>
+      <c r="D917" s="3" t="inlineStr">
+        <is>
+          <t>La mondialisation des savoirs astronomiques à la Belle époque</t>
+        </is>
+      </c>
+      <c r="E917" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/la-mondialisation-des-savoirs-astronomiques-a-la-belle-epoque/</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>&amp;#60;div style= »padding:50% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1229805412?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; allow= »autoplay; fullscreen; picture-in-picture; clipboard-write; encrypted-media; web-share » referrerpolicy= »strict-origin-when-cross-origin » style= »position:absolute;top:0;left:0;width:100%;height:100%; » title= »FSC-L_Gui</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr"/>
+    </row>
+    <row r="918">
+      <c r="A918" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:32</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>2026-09-26 06:07</t>
+        </is>
+      </c>
+      <c r="D918" s="3" t="inlineStr">
+        <is>
+          <t>La circulation des savoirs astronomiques au XIXème siècle</t>
+        </is>
+      </c>
+      <c r="E918" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/la-circulation-des-savoirs-astronomiques-au-xixeme-siecle/</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>&amp;#60;div style= »padding:75% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1229805415?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; allow= »autoplay; fullscreen; picture-in-picture; clipboard-write; encrypted-media; web-share » referrerpolicy= »strict-origin-when-cross-origin » style= »position:absolute;top:0;left:0;width:100%;height:100%; » title= »FSC-F_Kni</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr"/>
+    </row>
+    <row r="919">
+      <c r="A919" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:32</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>2026-09-26 06:06</t>
+        </is>
+      </c>
+      <c r="D919" s="3" t="inlineStr">
+        <is>
+          <t>La colonisation côtés jardins</t>
+        </is>
+      </c>
+      <c r="E919" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/la-colonisation-cotes-jardins/</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>&amp;#60;div style= »padding:56.3% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1229807223?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; allow= »autoplay; fullscreen; picture-in-picture; clipboard-write; encrypted-media; web-share » referrerpolicy= »strict-origin-when-cross-origin » style= »position:absolute;top:0;left:0;width:100%;height:100%; » title= »FSC-H_B</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr"/>
+    </row>
+    <row r="920">
+      <c r="A920" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:32</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>2026-09-26 06:03</t>
+        </is>
+      </c>
+      <c r="D920" s="3" t="inlineStr">
+        <is>
+          <t>La Maison des mines : la genèse révolutionnaire d’un corps d’ingénieurs civils (1794-1814)</t>
+        </is>
+      </c>
+      <c r="E920" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/la-maison-des-mines-la-genese-revolutionnaire-dun-corps-dingenieurs-civils-1794-1814/</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>&amp;#60;div style= »padding:75% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1229805413?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; allow= »autoplay; fullscreen; picture-in-picture; clipboard-write; encrypted-media; web-share » referrerpolicy= »strict-origin-when-cross-origin » style= »position:absolute;top:0;left:0;width:100%;height:100%; » title= »FSC-I_Lab</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -30219,6 +30742,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E902" r:id="rId901"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E903" r:id="rId902"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E904" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E905" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E906" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E907" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E908" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E909" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E910" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E911" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E912" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E913" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E914" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E915" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E916" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E917" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E918" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E919" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E920" r:id="rId919"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G920"/>
+  <dimension ref="A1:G928"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -29340,7 +29340,6 @@
           <t>Face aux violences sexuelles, les enfants parlent, mais les institutions ne savent pas toujours les entendre. La systématisation d’un questionnaire dans le cadre scolaire peut-elle changer la donne&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G905" t="inlineStr"/>
     </row>
     <row r="906">
       <c r="A906" s="2" t="inlineStr">
@@ -29373,7 +29372,6 @@
           <t>L’AfD veut réorienter la mémoire allemande : relativisation de la période nazie, valorisation d’un passé national «&amp;nbsp;positif&amp;nbsp;» et remise en cause du cadre mémoriel établi.</t>
         </is>
       </c>
-      <c r="G906" t="inlineStr"/>
     </row>
     <row r="907">
       <c r="A907" s="2" t="inlineStr">
@@ -29406,7 +29404,6 @@
           <t>En 2025, le PIB par habitant atteignait environ 25&amp;nbsp;975&amp;nbsp;euros en Chine, contre plus de 58&amp;nbsp;651&amp;nbsp;euros en France.</t>
         </is>
       </c>
-      <c r="G907" t="inlineStr"/>
     </row>
     <row r="908">
       <c r="A908" s="2" t="inlineStr">
@@ -29439,7 +29436,6 @@
           <t>Derrière la résistance au président, une révolution contre le pouvoir des oligarques de la tech est en train de prendre forme L’article L’Amérique n’a toujours pas cédé à Trump est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G908" t="inlineStr"/>
     </row>
     <row r="909">
       <c r="A909" s="2" t="inlineStr">
@@ -29472,7 +29468,6 @@
           <t>Moscou attribue la baisse de la production à des «&amp;#160;travaux de maintenance imprévus&amp;#160;» L’article Économie russe&amp;#160;: la production de pétrole va tomber en 2026 à son niveau le plus bas depuis 2009 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G909" t="inlineStr"/>
     </row>
     <row r="910">
       <c r="A910" s="2" t="inlineStr">
@@ -29505,7 +29500,6 @@
           <t>Le paradoxe du christianisme selon l’évêque de Nanterre L’article Faut-il avoir peur de l’identité chrétienne&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G910" t="inlineStr"/>
     </row>
     <row r="911">
       <c r="A911" s="2" t="inlineStr">
@@ -29538,7 +29532,6 @@
           <t>Le texte intégral du discours du Premier ministre espagnol à la tribune des Nations unies L’article La doctrine Sánchez pour refonder l&amp;rsquo;ordre mondial est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G911" t="inlineStr"/>
     </row>
     <row r="912">
       <c r="A912" s="2" t="inlineStr">
@@ -29571,7 +29564,6 @@
           <t>Praxis a bénéficié du soutien de Peter Thiel et de Marc Andreessen L’article En Uruguay, le projet techno-libertarien d’une communauté qui se prépare au monde post-IA pourrait voir le jour dès 2027 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G912" t="inlineStr"/>
     </row>
     <row r="913">
       <c r="A913" s="2" t="inlineStr">
@@ -29604,7 +29596,6 @@
           <t>« Les transformations contemporaines de la mondialisation, de ses flux et de ses rapports de force sont éclairées par les travaux d’Arnaud Orain qui définit un « capitalisme de la finitude », également existant au XVI-XVIII et de la fin du XIX à 1945. Ces travaux questionnent plusieurs notions abordées au lycée, sur tous les [&amp;#8230;] L’article Arnaud Orain &amp;#8211; Le monde confisqué. Essai sur le capitalisme de la finitude (XVIe-XXIe siècle) est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G913" t="inlineStr"/>
     </row>
     <row r="914">
       <c r="A914" s="2" t="inlineStr">
@@ -29637,7 +29628,6 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1229800000?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
         </is>
       </c>
-      <c r="G914" t="inlineStr"/>
     </row>
     <row r="915">
       <c r="A915" s="2" t="inlineStr">
@@ -29670,7 +29660,6 @@
           <t>Pour cette deuxième séance, Marie Digout, Thomas Gosselin et Marine Sorano vous proposent d&amp;#8217;aborder la méthodologie du dossier RAEP. Vous pouvez également télécharger le support de la séance: Méthodologie du dossier RAEP &amp;#8211; 22 septembre 2026 &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1229799957?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58</t>
         </is>
       </c>
-      <c r="G915" t="inlineStr"/>
     </row>
     <row r="916">
       <c r="A916" s="2" t="inlineStr">
@@ -29703,7 +29692,6 @@
           <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Thomas Leyris autour du sujet « Citoyenneté et sujétion dans l&amp;#8217;empire français (1885-1962) ». Le podcast est proposé en [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Thomas Leyris &amp;#8211; Citoyenneté et sujétion dans l&amp;#8217;empire fra</t>
         </is>
       </c>
-      <c r="G916" t="inlineStr"/>
     </row>
     <row r="917">
       <c r="A917" s="2" t="inlineStr">
@@ -29736,7 +29724,6 @@
           <t>&amp;#60;div style= »padding:50% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1229805412?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; allow= »autoplay; fullscreen; picture-in-picture; clipboard-write; encrypted-media; web-share » referrerpolicy= »strict-origin-when-cross-origin » style= »position:absolute;top:0;left:0;width:100%;height:100%; » title= »FSC-L_Gui</t>
         </is>
       </c>
-      <c r="G917" t="inlineStr"/>
     </row>
     <row r="918">
       <c r="A918" s="2" t="inlineStr">
@@ -29769,7 +29756,6 @@
           <t>&amp;#60;div style= »padding:75% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1229805415?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; allow= »autoplay; fullscreen; picture-in-picture; clipboard-write; encrypted-media; web-share » referrerpolicy= »strict-origin-when-cross-origin » style= »position:absolute;top:0;left:0;width:100%;height:100%; » title= »FSC-F_Kni</t>
         </is>
       </c>
-      <c r="G918" t="inlineStr"/>
     </row>
     <row r="919">
       <c r="A919" s="2" t="inlineStr">
@@ -29802,7 +29788,6 @@
           <t>&amp;#60;div style= »padding:56.3% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1229807223?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; allow= »autoplay; fullscreen; picture-in-picture; clipboard-write; encrypted-media; web-share » referrerpolicy= »strict-origin-when-cross-origin » style= »position:absolute;top:0;left:0;width:100%;height:100%; » title= »FSC-H_B</t>
         </is>
       </c>
-      <c r="G919" t="inlineStr"/>
     </row>
     <row r="920">
       <c r="A920" s="2" t="inlineStr">
@@ -29835,7 +29820,270 @@
           <t>&amp;#60;div style= »padding:75% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1229805413?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; allow= »autoplay; fullscreen; picture-in-picture; clipboard-write; encrypted-media; web-share » referrerpolicy= »strict-origin-when-cross-origin » style= »position:absolute;top:0;left:0;width:100%;height:100%; » title= »FSC-I_Lab</t>
         </is>
       </c>
-      <c r="G920" t="inlineStr"/>
+    </row>
+    <row r="921">
+      <c r="A921" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:18</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:24</t>
+        </is>
+      </c>
+      <c r="D921" s="3" t="inlineStr">
+        <is>
+          <t>C’est quoi, réussir sa première année post-bac ?</t>
+        </is>
+      </c>
+      <c r="E921" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/cest-quoi-reussir-sa-premiere-annee-post-bac-288549</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>Le décrochage universitaire est-il avant tout un problème individuel ou plutôt une préoccupation financière pour l’État&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr"/>
+    </row>
+    <row r="922">
+      <c r="A922" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:18</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:23</t>
+        </is>
+      </c>
+      <c r="D922" s="3" t="inlineStr">
+        <is>
+          <t>Minerais, pêche, tourisme : les trois fronts de l’exploitation en Antarctique en question à l’horizon 2048 ?</t>
+        </is>
+      </c>
+      <c r="E922" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/minerais-peche-tourisme-les-trois-fronts-de-lexploitation-en-antarctique-en-question-a-lhorizon-2048-292751</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>En Antarctique, le mythe d’une ouverture du sous-sol en 2048 masque l’essor de la pêche et du tourisme, dont les règles de protection s’affaiblissent.</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr"/>
+    </row>
+    <row r="923">
+      <c r="A923" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:18</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>2026-09-27 09:00</t>
+        </is>
+      </c>
+      <c r="D923" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi le PIB par habitant en Chine reste-t-il bas par rapport à la France ?</t>
+        </is>
+      </c>
+      <c r="E923" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-le-pib-par-habitant-en-chine-reste-t-il-bas-par-rapport-a-la-france-288026</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>En 2025, le PIB par habitant atteignait environ 25&amp;nbsp;975&amp;nbsp;euros en Chine, contre plus de 58&amp;nbsp;651&amp;nbsp;euros en France.</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr"/>
+    </row>
+    <row r="924">
+      <c r="A924" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:18</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>2026-09-28 16:18</t>
+        </is>
+      </c>
+      <c r="D924" s="3" t="inlineStr">
+        <is>
+          <t>Le candidat de Futuro Nazionale, le parti du général Roberto Vannacci, obtiendrait 9 % des voix en Calabre</t>
+        </is>
+      </c>
+      <c r="E924" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/28/le-candidat-de-futuro-nazionale-le-parti-du-general-roberto-vannacci-obtiendrait-9-des-voix-en-calabre/</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>Ce score devrait conforter Giorgia Meloni L’article Le candidat de Futuro Nazionale, le parti du général Roberto Vannacci, obtiendrait 9&amp;#160;% des voix en Calabre est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr"/>
+    </row>
+    <row r="925">
+      <c r="A925" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:18</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:21</t>
+        </is>
+      </c>
+      <c r="D925" s="3" t="inlineStr">
+        <is>
+          <t>Les « incidents » impliquant des agents d’IA se comptent en dizaines de milliers</t>
+        </is>
+      </c>
+      <c r="E925" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/28/les-incidents-impliquant-des-agents-dia-se-comptent-en-dizaines-de-milliers/</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>L'ampleur réelle du phénomène reste inconnue L’article Les «&amp;#160;incidents&amp;#160;» impliquant des agents d’IA se comptent en dizaines de milliers est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr"/>
+    </row>
+    <row r="926">
+      <c r="A926" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:18</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>2026-09-28 08:24</t>
+        </is>
+      </c>
+      <c r="D926" s="3" t="inlineStr">
+        <is>
+          <t>La guerre en Iran entre dans son huitième mois</t>
+        </is>
+      </c>
+      <c r="E926" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/28/la-guerre-en-iran-entre-dans-son-huitieme-mois/</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>Il semble peu probable que le conflit prenne fin d’ici les élections de mi-mandat aux États-Unis L’article La guerre en Iran entre dans son huitième mois est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr"/>
+    </row>
+    <row r="927">
+      <c r="A927" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:18</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>2026-09-28 06:21</t>
+        </is>
+      </c>
+      <c r="D927" s="3" t="inlineStr">
+        <is>
+          <t>Marine Le Pen peut-elle vraiment rompre avec Poutine ?</t>
+        </is>
+      </c>
+      <c r="E927" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/28/marine-le-pen-peut-elle-vraiment-rompre-avec-poutine/</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>Entre l’Ukraine et la Russie, enquête dans les coulisses sur le grand écart du Rassemblement national L’article Marine Le Pen peut-elle vraiment rompre avec Poutine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr"/>
+    </row>
+    <row r="928">
+      <c r="A928" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:18</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>2026-09-27 16:24</t>
+        </is>
+      </c>
+      <c r="D928" s="3" t="inlineStr">
+        <is>
+          <t>L’émir et les Lumières</t>
+        </is>
+      </c>
+      <c r="E928" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/27/lemir-et-les-lumieres/</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>Les Lumières sont attaquées sur tous les fronts. Et si le débat était mal posé&amp;#160;? L’article L&amp;rsquo;émir et les Lumières est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -30758,6 +31006,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E918" r:id="rId917"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E919" r:id="rId918"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E920" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E921" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E922" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E923" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E924" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E925" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E926" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E927" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E928" r:id="rId927"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G928"/>
+  <dimension ref="A1:G935"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -29852,7 +29852,6 @@
           <t>Le décrochage universitaire est-il avant tout un problème individuel ou plutôt une préoccupation financière pour l’État&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G921" t="inlineStr"/>
     </row>
     <row r="922">
       <c r="A922" s="2" t="inlineStr">
@@ -29885,7 +29884,6 @@
           <t>En Antarctique, le mythe d’une ouverture du sous-sol en 2048 masque l’essor de la pêche et du tourisme, dont les règles de protection s’affaiblissent.</t>
         </is>
       </c>
-      <c r="G922" t="inlineStr"/>
     </row>
     <row r="923">
       <c r="A923" s="2" t="inlineStr">
@@ -29918,7 +29916,6 @@
           <t>En 2025, le PIB par habitant atteignait environ 25&amp;nbsp;975&amp;nbsp;euros en Chine, contre plus de 58&amp;nbsp;651&amp;nbsp;euros en France.</t>
         </is>
       </c>
-      <c r="G923" t="inlineStr"/>
     </row>
     <row r="924">
       <c r="A924" s="2" t="inlineStr">
@@ -29951,7 +29948,6 @@
           <t>Ce score devrait conforter Giorgia Meloni L’article Le candidat de Futuro Nazionale, le parti du général Roberto Vannacci, obtiendrait 9&amp;#160;% des voix en Calabre est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G924" t="inlineStr"/>
     </row>
     <row r="925">
       <c r="A925" s="2" t="inlineStr">
@@ -29984,7 +29980,6 @@
           <t>L'ampleur réelle du phénomène reste inconnue L’article Les «&amp;#160;incidents&amp;#160;» impliquant des agents d’IA se comptent en dizaines de milliers est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G925" t="inlineStr"/>
     </row>
     <row r="926">
       <c r="A926" s="2" t="inlineStr">
@@ -30017,7 +30012,6 @@
           <t>Il semble peu probable que le conflit prenne fin d’ici les élections de mi-mandat aux États-Unis L’article La guerre en Iran entre dans son huitième mois est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G926" t="inlineStr"/>
     </row>
     <row r="927">
       <c r="A927" s="2" t="inlineStr">
@@ -30050,7 +30044,6 @@
           <t>Entre l’Ukraine et la Russie, enquête dans les coulisses sur le grand écart du Rassemblement national L’article Marine Le Pen peut-elle vraiment rompre avec Poutine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G927" t="inlineStr"/>
     </row>
     <row r="928">
       <c r="A928" s="2" t="inlineStr">
@@ -30083,7 +30076,237 @@
           <t>Les Lumières sont attaquées sur tous les fronts. Et si le débat était mal posé&amp;#160;? L’article L&amp;rsquo;émir et les Lumières est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G928" t="inlineStr"/>
+    </row>
+    <row r="929">
+      <c r="A929" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:19</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:15</t>
+        </is>
+      </c>
+      <c r="D929" s="3" t="inlineStr">
+        <is>
+          <t>Le baptême de l’Amérique à Saint-Dié par des humanistes vosgiens, un épisode historique méconnu</t>
+        </is>
+      </c>
+      <c r="E929" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-bapteme-de-lamerique-a-saint-die-par-des-humanistes-vosgiens-un-episode-historique-meconnu-292919</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>Ce n’est pas un hasard si la ville de Saint-Dié, dans les Vosges, accueille un festival annuel consacré à la géographie depuis&amp;nbsp;1990. Au début du XVIᵉ&amp;nbsp;siècle, elle abritait une communauté d’humanistes qui s’intéressaient particulièrement à cette discipline.</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr"/>
+    </row>
+    <row r="930">
+      <c r="A930" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:19</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:50</t>
+        </is>
+      </c>
+      <c r="D930" s="3" t="inlineStr">
+        <is>
+          <t>L’Europe vue par Léon XIV</t>
+        </is>
+      </c>
+      <c r="E930" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/leurope-vue-par-leon-xiv-293064</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>Léon&amp;nbsp;XIV défend une Europe fondée sur le multilatéralisme et le dépassement des nationalismes, tout en réaffirmant ses racines chrétiennes.</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr"/>
+    </row>
+    <row r="931">
+      <c r="A931" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:19</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:09</t>
+        </is>
+      </c>
+      <c r="D931" s="3" t="inlineStr">
+        <is>
+          <t>Le Brésil peut faire basculer le trumpisme en Amérique</t>
+        </is>
+      </c>
+      <c r="E931" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/29/le-bresil-peut-faire-basculer-le-trumpisme-en-amerique/</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>La bataille pour Brasília décidera jusqu’où peut aller la recolonisation états-unienne du continent L’article Le Brésil peut faire basculer le trumpisme en Amérique est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr"/>
+    </row>
+    <row r="932">
+      <c r="A932" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:19</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:46</t>
+        </is>
+      </c>
+      <c r="D932" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : en 2027, la Russie de Poutine dépensera plus que jamais pour la guerre</t>
+        </is>
+      </c>
+      <c r="E932" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/29/economie-russe-la-russie-de-poutine-na-jamais-autant-depense-pour-la-guerre/</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>Le Kremlin prévoit d’augmenter de 32&amp;#160;% ses dépenses militaires en 2027 L’article Économie russe&amp;#160;: en 2027, la Russie de Poutine dépensera plus que jamais pour la guerre est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr"/>
+    </row>
+    <row r="933">
+      <c r="A933" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:19</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>2026-09-29 04:30</t>
+        </is>
+      </c>
+      <c r="D933" s="3" t="inlineStr">
+        <is>
+          <t>La contre-révolution culturelle est un échec</t>
+        </is>
+      </c>
+      <c r="E933" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/29/la-contre-revolution-culturelle-est-un-echec/</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>Pourquoi le projet populiste se confronte à un paradoxe anthropologique insurmontable L’article La contre-révolution culturelle est un échec est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr"/>
+    </row>
+    <row r="934">
+      <c r="A934" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:19</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>2026-09-29 04:30</t>
+        </is>
+      </c>
+      <c r="D934" s="3" t="inlineStr">
+        <is>
+          <t>Pékin s’apprêterait à autoriser ByteDance et Alibaba à acheter des milliards de dollars de puces Nvidia</t>
+        </is>
+      </c>
+      <c r="E934" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/29/pekin-sappreterait-a-autoriser-bytedance-et-alibaba-a-acheter-des-milliards-de-dollars-de-puces-nvidia/</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>Une telle autorisation traduirait un certain pragmatisme du régime chinois L’article Pékin s&amp;rsquo;apprêterait à autoriser ByteDance et Alibaba à acheter des milliards de dollars de puces Nvidia est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr"/>
+    </row>
+    <row r="935">
+      <c r="A935" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:19</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:55</t>
+        </is>
+      </c>
+      <c r="D935" s="3" t="inlineStr">
+        <is>
+          <t>Léon XIV à Metz</t>
+        </is>
+      </c>
+      <c r="E935" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/28/leon-xiv-a-metz/</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>L’Europe guelfe a-t-elle trouvé son discours&amp;#160;? Nous commentons les mots du pape L’article Léon XIV à Metz est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -31014,6 +31237,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E926" r:id="rId925"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E927" r:id="rId926"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E928" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E929" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E930" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E931" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E932" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E933" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E934" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E935" r:id="rId934"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G935"/>
+  <dimension ref="A1:G943"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -30108,7 +30108,6 @@
           <t>Ce n’est pas un hasard si la ville de Saint-Dié, dans les Vosges, accueille un festival annuel consacré à la géographie depuis&amp;nbsp;1990. Au début du XVIᵉ&amp;nbsp;siècle, elle abritait une communauté d’humanistes qui s’intéressaient particulièrement à cette discipline.</t>
         </is>
       </c>
-      <c r="G929" t="inlineStr"/>
     </row>
     <row r="930">
       <c r="A930" s="2" t="inlineStr">
@@ -30141,7 +30140,6 @@
           <t>Léon&amp;nbsp;XIV défend une Europe fondée sur le multilatéralisme et le dépassement des nationalismes, tout en réaffirmant ses racines chrétiennes.</t>
         </is>
       </c>
-      <c r="G930" t="inlineStr"/>
     </row>
     <row r="931">
       <c r="A931" s="2" t="inlineStr">
@@ -30174,7 +30172,6 @@
           <t>La bataille pour Brasília décidera jusqu’où peut aller la recolonisation états-unienne du continent L’article Le Brésil peut faire basculer le trumpisme en Amérique est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G931" t="inlineStr"/>
     </row>
     <row r="932">
       <c r="A932" s="2" t="inlineStr">
@@ -30207,7 +30204,6 @@
           <t>Le Kremlin prévoit d’augmenter de 32&amp;#160;% ses dépenses militaires en 2027 L’article Économie russe&amp;#160;: en 2027, la Russie de Poutine dépensera plus que jamais pour la guerre est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G932" t="inlineStr"/>
     </row>
     <row r="933">
       <c r="A933" s="2" t="inlineStr">
@@ -30240,7 +30236,6 @@
           <t>Pourquoi le projet populiste se confronte à un paradoxe anthropologique insurmontable L’article La contre-révolution culturelle est un échec est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G933" t="inlineStr"/>
     </row>
     <row r="934">
       <c r="A934" s="2" t="inlineStr">
@@ -30273,7 +30268,6 @@
           <t>Une telle autorisation traduirait un certain pragmatisme du régime chinois L’article Pékin s&amp;rsquo;apprêterait à autoriser ByteDance et Alibaba à acheter des milliards de dollars de puces Nvidia est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G934" t="inlineStr"/>
     </row>
     <row r="935">
       <c r="A935" s="2" t="inlineStr">
@@ -30306,7 +30300,270 @@
           <t>L’Europe guelfe a-t-elle trouvé son discours&amp;#160;? Nous commentons les mots du pape L’article Léon XIV à Metz est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G935" t="inlineStr"/>
+    </row>
+    <row r="936">
+      <c r="A936" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:34</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>2026-09-30 14:10</t>
+        </is>
+      </c>
+      <c r="D936" s="3" t="inlineStr">
+        <is>
+          <t>Elizabeth Ire, Virginia Woolf, Debbie Harry : ces figures qui ont marqué l’histoire culturelle sont encore jugées parce qu’elles n’ont pas eu d’enfant</t>
+        </is>
+      </c>
+      <c r="E936" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/elizabeth-ire-virginia-woolf-debbie-harry-ces-figures-qui-ont-marque-lhistoire-culturelle-sont-encore-jugees-parce-quelles-nont-pas-eu-denfant-293126</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>Lorsqu’une femme construit autre chose qu’une famille, la société peine à y voir un héritage.</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr"/>
+    </row>
+    <row r="937">
+      <c r="A937" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:34</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>2026-09-30 14:11</t>
+        </is>
+      </c>
+      <c r="D937" s="3" t="inlineStr">
+        <is>
+          <t>Législatives au Maroc : recomposition politique ou simple changement de couleurs ?</t>
+        </is>
+      </c>
+      <c r="E937" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/legislatives-au-maroc-recomposition-politique-ou-simple-changement-de-couleurs-293118</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>Au Maroc, le PAM prend la tête, le PJD revient et l’abstention progresse. Une nouvelle carte politique qui pose une question&amp;nbsp;: recomposition réelle ou simple changement de couleurs&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr"/>
+    </row>
+    <row r="938">
+      <c r="A938" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:34</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:03</t>
+        </is>
+      </c>
+      <c r="D938" s="3" t="inlineStr">
+        <is>
+          <t>Fromages, terroir et libre-échange : l’Argentine prise entre l’Europe et les États-Unis</t>
+        </is>
+      </c>
+      <c r="E938" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/fromages-terroir-et-libre-echange-largentine-prise-entre-leurope-et-les-etats-unis-291333</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>Washington tente de passer des accords bilatéraux avec les États du continent pour faciliter l’exportation de ses produits, faisant fi du respect des appellations d’origine protégée.</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr"/>
+    </row>
+    <row r="939">
+      <c r="A939" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:34</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:23</t>
+        </is>
+      </c>
+      <c r="D939" s="3" t="inlineStr">
+        <is>
+          <t>En Roumanie, le Premier ministre Siegfried Mureșan n’a pas obtenu la confiance du Parlement</t>
+        </is>
+      </c>
+      <c r="E939" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/30/en-roumanie-le-premier-ministre-siegfried-muresan-na-pas-obtenu-la-confiance-du-parlement/</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>Le pays se dirige-t-il vers des élections anticipées&amp;#160;? L’article En Roumanie, le Premier ministre Siegfried Mureșan n’a pas obtenu la confiance du Parlement est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr"/>
+    </row>
+    <row r="940">
+      <c r="A940" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:34</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:10</t>
+        </is>
+      </c>
+      <c r="D940" s="3" t="inlineStr">
+        <is>
+          <t>La dette française est en train de décrocher</t>
+        </is>
+      </c>
+      <c r="E940" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/30/la-dette-francaise-est-en-train-de-decrocher/</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>«&amp;#160;Personne ne semble avoir pris conscience de la zone de danger dans laquelle nous entrons&amp;#160;» L’article La dette française est en train de décrocher est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr"/>
+    </row>
+    <row r="941">
+      <c r="A941" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:34</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>2026-09-30 04:30</t>
+        </is>
+      </c>
+      <c r="D941" s="3" t="inlineStr">
+        <is>
+          <t>Poutine augmente la taille de l’armée russe pour la quatrième fois en six mois</t>
+        </is>
+      </c>
+      <c r="E941" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/30/poutine-augmente-la-taille-de-larmee-russe-pour-la-quatrieme-fois-en-six-mois/</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>Les effectifs de l’armée ont augmenté de 50 000 hommes en 2026 L’article Poutine augmente la taille de l’armée russe pour la quatrième fois en six mois est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr"/>
+    </row>
+    <row r="942">
+      <c r="A942" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:34</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>2026-09-30 04:00</t>
+        </is>
+      </c>
+      <c r="D942" s="3" t="inlineStr">
+        <is>
+          <t>25 livres à lire en octobre 2026</t>
+        </is>
+      </c>
+      <c r="E942" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/30/25-livres-a-lire-en-octobre-2026/</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>De la course à l’IA aux élites de Poutine, de l’arctique à la Chine&amp;#160;: 25 livres que nous lirons de près L’article 25 livres à lire en octobre 2026 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr"/>
+    </row>
+    <row r="943">
+      <c r="A943" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:34</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>2026-09-29 17:09</t>
+        </is>
+      </c>
+      <c r="D943" s="3" t="inlineStr">
+        <is>
+          <t>La Chine installe cinq fois plus de robots industriels que l’Europe</t>
+        </is>
+      </c>
+      <c r="E943" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/29/la-chine-installe-cinq-fois-plus-de-robots-industriels-que-leurope/</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>L’Europe a installé 73 000 robots l’an dernier, et la Chine 354 000 L’article La Chine installe cinq fois plus de robots industriels que l’Europe est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -31244,6 +31501,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E933" r:id="rId932"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E934" r:id="rId933"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E935" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E936" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E937" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E938" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E939" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E940" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E941" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E942" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E943" r:id="rId942"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G943"/>
+  <dimension ref="A1:G952"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -30332,7 +30332,6 @@
           <t>Lorsqu’une femme construit autre chose qu’une famille, la société peine à y voir un héritage.</t>
         </is>
       </c>
-      <c r="G936" t="inlineStr"/>
     </row>
     <row r="937">
       <c r="A937" s="2" t="inlineStr">
@@ -30365,7 +30364,6 @@
           <t>Au Maroc, le PAM prend la tête, le PJD revient et l’abstention progresse. Une nouvelle carte politique qui pose une question&amp;nbsp;: recomposition réelle ou simple changement de couleurs&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G937" t="inlineStr"/>
     </row>
     <row r="938">
       <c r="A938" s="2" t="inlineStr">
@@ -30398,7 +30396,6 @@
           <t>Washington tente de passer des accords bilatéraux avec les États du continent pour faciliter l’exportation de ses produits, faisant fi du respect des appellations d’origine protégée.</t>
         </is>
       </c>
-      <c r="G938" t="inlineStr"/>
     </row>
     <row r="939">
       <c r="A939" s="2" t="inlineStr">
@@ -30431,7 +30428,6 @@
           <t>Le pays se dirige-t-il vers des élections anticipées&amp;#160;? L’article En Roumanie, le Premier ministre Siegfried Mureșan n’a pas obtenu la confiance du Parlement est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G939" t="inlineStr"/>
     </row>
     <row r="940">
       <c r="A940" s="2" t="inlineStr">
@@ -30464,7 +30460,6 @@
           <t>«&amp;#160;Personne ne semble avoir pris conscience de la zone de danger dans laquelle nous entrons&amp;#160;» L’article La dette française est en train de décrocher est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G940" t="inlineStr"/>
     </row>
     <row r="941">
       <c r="A941" s="2" t="inlineStr">
@@ -30497,7 +30492,6 @@
           <t>Les effectifs de l’armée ont augmenté de 50 000 hommes en 2026 L’article Poutine augmente la taille de l’armée russe pour la quatrième fois en six mois est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G941" t="inlineStr"/>
     </row>
     <row r="942">
       <c r="A942" s="2" t="inlineStr">
@@ -30530,7 +30524,6 @@
           <t>De la course à l’IA aux élites de Poutine, de l’arctique à la Chine&amp;#160;: 25 livres que nous lirons de près L’article 25 livres à lire en octobre 2026 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G942" t="inlineStr"/>
     </row>
     <row r="943">
       <c r="A943" s="2" t="inlineStr">
@@ -30563,7 +30556,303 @@
           <t>L’Europe a installé 73 000 robots l’an dernier, et la Chine 354 000 L’article La Chine installe cinq fois plus de robots industriels que l’Europe est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G943" t="inlineStr"/>
+    </row>
+    <row r="944">
+      <c r="A944" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:58</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:41</t>
+        </is>
+      </c>
+      <c r="D944" s="3" t="inlineStr">
+        <is>
+          <t>Les volailles au Moyen Âge : de la poularde au pigeonneau, une diversité oubliée et une science du goût à redécouvrir</t>
+        </is>
+      </c>
+      <c r="E944" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-volailles-au-moyen-age-de-la-poularde-au-pigeonneau-une-diversite-oubliee-et-une-science-du-gout-a-redecouvrir-290182</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>Si la filière volaille se vante d’avoir maintenu l’élevage de huit&amp;nbsp;espèces en France, les livres du Moyen Âge n’en recensaient pas moins de 32. Comment le poulet s’est-il imposé sur nos tables&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr"/>
+    </row>
+    <row r="945">
+      <c r="A945" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:58</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:39</t>
+        </is>
+      </c>
+      <c r="D945" s="3" t="inlineStr">
+        <is>
+          <t>Le régime iranien va-t-il perdre son influence sur l’Irak ?</t>
+        </is>
+      </c>
+      <c r="E945" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-regime-iranien-va-t-il-perdre-son-influence-sur-lirak-292968</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>L’Iran mobilise les milices irakiennes dans ses opérations visant l’Arabie saoudite, ce qui suscite un mécontentement de plus en plus sensible des leaders irakiens.</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr"/>
+    </row>
+    <row r="946">
+      <c r="A946" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:58</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:38</t>
+        </is>
+      </c>
+      <c r="D946" s="3" t="inlineStr">
+        <is>
+          <t>Tentative de détournement du vol Flydubai quel impact sur les législatives israéliennes ?</t>
+        </is>
+      </c>
+      <c r="E946" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/tentative-de-detournement-du-vol-flydubai-quel-impact-sur-les-legislatives-israeliennes-293366</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>Benyamin Nétanyahou tente de renouer avec son image de protecteur d’Israël, écornée par les récentes révélations sur son refus d’entendre les avertissements avant le massacre du 7&amp;nbsp;octobre 2023.</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr"/>
+    </row>
+    <row r="947">
+      <c r="A947" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:58</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:44</t>
+        </is>
+      </c>
+      <c r="D947" s="3" t="inlineStr">
+        <is>
+          <t>Élections au Brésil : une campagne terne et numérique qui accroît l’incertitude sur l’issue du scrutin</t>
+        </is>
+      </c>
+      <c r="E947" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/elections-au-bresil-une-campagne-terne-et-numerique-qui-accroit-lincertitude-sur-lissue-du-scrutin-293250</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>À quelques jours de l’élection présidentielle au Brésil, Lula devance Flávio Bolsonaro dans les sondages. Mais le nombre élevé d’indécis et une campagne atone entretiennent l’incertitude.</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr"/>
+    </row>
+    <row r="948">
+      <c r="A948" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:58</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:43</t>
+        </is>
+      </c>
+      <c r="D948" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi Trump refuse de ralentir le développement de l’IA</t>
+        </is>
+      </c>
+      <c r="E948" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/01/pourquoi-trump-refuse-de-ralentir-le-developpement-de-lia/</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>L’avenir de l’économie américaine est désormais lié à la technologie L’article Pourquoi Trump refuse de ralentir le développement de l’IA est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr"/>
+    </row>
+    <row r="949">
+      <c r="A949" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:58</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:33</t>
+        </is>
+      </c>
+      <c r="D949" s="3" t="inlineStr">
+        <is>
+          <t>La Chine et les États-Unis exportent leur crise en Europe</t>
+        </is>
+      </c>
+      <c r="E949" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/01/la-chine-et-les-etats-unis-exportent-leur-crise-en-europe/</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>Comprendre la mécanique invisible de la nouvelle configuration géoéconomique L’article La Chine et les États-Unis exportent leur crise en Europe est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr"/>
+    </row>
+    <row r="950">
+      <c r="A950" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:58</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>2026-10-01 04:30</t>
+        </is>
+      </c>
+      <c r="D950" s="3" t="inlineStr">
+        <is>
+          <t>La guerre des villes : la doctrine russe pour dévaster l’Ukraine</t>
+        </is>
+      </c>
+      <c r="E950" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/01/la-guerre-des-villes-la-doctrine-russe-pour-devaster-lukraine/</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>Moscou veut transformer l’Ukraine en un «&amp;#160;actif inutile&amp;#160;» L’article La guerre des villes&amp;#160;: la doctrine russe pour dévaster l’Ukraine est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr"/>
+    </row>
+    <row r="951">
+      <c r="A951" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:58</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:25</t>
+        </is>
+      </c>
+      <c r="D951" s="3" t="inlineStr">
+        <is>
+          <t>De Le Pen à Macron : que disaient les sondages 200 jours avant les précédentes élections présidentielles ?</t>
+        </is>
+      </c>
+      <c r="E951" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/30/de-le-pen-a-macron-que-disaient-les-sondages-200-jours-avant-les-precedentes-elections-presidentielles/</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>Depuis 2002, le candidat en tête à ce stade de la campagne a remporté le premier tour quatre fois sur cinq L’article De Le Pen à Macron&amp;#160;: que disaient les sondages 200 jours avant les précédentes élections présidentielles&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr"/>
+    </row>
+    <row r="952">
+      <c r="A952" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:58</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:41</t>
+        </is>
+      </c>
+      <c r="D952" s="3" t="inlineStr">
+        <is>
+          <t>La dette et le mur du réel</t>
+        </is>
+      </c>
+      <c r="E952" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/30/la-dette-et-le-mur-du-reel/</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>La France peut encore choisir entre redressement et austérité L’article La dette et le mur du réel est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -31509,6 +31798,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E941" r:id="rId940"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E942" r:id="rId941"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E943" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E944" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E945" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E946" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E947" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E948" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E949" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E950" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E951" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E952" r:id="rId951"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G952"/>
+  <dimension ref="A1:G961"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -30588,7 +30588,6 @@
           <t>Si la filière volaille se vante d’avoir maintenu l’élevage de huit&amp;nbsp;espèces en France, les livres du Moyen Âge n’en recensaient pas moins de 32. Comment le poulet s’est-il imposé sur nos tables&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G944" t="inlineStr"/>
     </row>
     <row r="945">
       <c r="A945" s="2" t="inlineStr">
@@ -30621,7 +30620,6 @@
           <t>L’Iran mobilise les milices irakiennes dans ses opérations visant l’Arabie saoudite, ce qui suscite un mécontentement de plus en plus sensible des leaders irakiens.</t>
         </is>
       </c>
-      <c r="G945" t="inlineStr"/>
     </row>
     <row r="946">
       <c r="A946" s="2" t="inlineStr">
@@ -30654,7 +30652,6 @@
           <t>Benyamin Nétanyahou tente de renouer avec son image de protecteur d’Israël, écornée par les récentes révélations sur son refus d’entendre les avertissements avant le massacre du 7&amp;nbsp;octobre 2023.</t>
         </is>
       </c>
-      <c r="G946" t="inlineStr"/>
     </row>
     <row r="947">
       <c r="A947" s="2" t="inlineStr">
@@ -30687,7 +30684,6 @@
           <t>À quelques jours de l’élection présidentielle au Brésil, Lula devance Flávio Bolsonaro dans les sondages. Mais le nombre élevé d’indécis et une campagne atone entretiennent l’incertitude.</t>
         </is>
       </c>
-      <c r="G947" t="inlineStr"/>
     </row>
     <row r="948">
       <c r="A948" s="2" t="inlineStr">
@@ -30720,7 +30716,6 @@
           <t>L’avenir de l’économie américaine est désormais lié à la technologie L’article Pourquoi Trump refuse de ralentir le développement de l’IA est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G948" t="inlineStr"/>
     </row>
     <row r="949">
       <c r="A949" s="2" t="inlineStr">
@@ -30753,7 +30748,6 @@
           <t>Comprendre la mécanique invisible de la nouvelle configuration géoéconomique L’article La Chine et les États-Unis exportent leur crise en Europe est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G949" t="inlineStr"/>
     </row>
     <row r="950">
       <c r="A950" s="2" t="inlineStr">
@@ -30786,7 +30780,6 @@
           <t>Moscou veut transformer l’Ukraine en un «&amp;#160;actif inutile&amp;#160;» L’article La guerre des villes&amp;#160;: la doctrine russe pour dévaster l’Ukraine est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G950" t="inlineStr"/>
     </row>
     <row r="951">
       <c r="A951" s="2" t="inlineStr">
@@ -30819,7 +30812,6 @@
           <t>Depuis 2002, le candidat en tête à ce stade de la campagne a remporté le premier tour quatre fois sur cinq L’article De Le Pen à Macron&amp;#160;: que disaient les sondages 200 jours avant les précédentes élections présidentielles&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G951" t="inlineStr"/>
     </row>
     <row r="952">
       <c r="A952" s="2" t="inlineStr">
@@ -30852,7 +30844,303 @@
           <t>La France peut encore choisir entre redressement et austérité L’article La dette et le mur du réel est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G952" t="inlineStr"/>
+    </row>
+    <row r="953">
+      <c r="A953" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 15:19</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>2026-10-02 11:56</t>
+        </is>
+      </c>
+      <c r="D953" s="3" t="inlineStr">
+        <is>
+          <t>Un carnet de Mozart retrouvé à la BnF révèle le talent méconnu d’une de ses élèves</t>
+        </is>
+      </c>
+      <c r="E953" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/un-carnet-de-mozart-retrouve-a-la-bnf-revele-le-talent-meconnu-dune-de-ses-eleves-292699</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>Un carnet de Mozart retrouvé à la Bibliothèque nationale de France révèle les leçons de composition qu’il donna en 1778 à Marie-Louise de Guînes.</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr"/>
+    </row>
+    <row r="954">
+      <c r="A954" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 15:19</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>2026-10-02 11:55</t>
+        </is>
+      </c>
+      <c r="D954" s="3" t="inlineStr">
+        <is>
+          <t>Des Portugais aux Américains, une bataille de cinq siècles pour le contrôle d’Ormuz et de Bab el-Mandeb</t>
+        </is>
+      </c>
+      <c r="E954" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/des-portugais-aux-americains-une-bataille-de-cinq-siecles-pour-le-controle-dormuz-et-de-bab-el-mandeb-293454</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>Des expéditions chinoises de Zheng He à la présence militaire américaine, en passant par les empires portugais, néerlandais et britannique, les détroits d’Ormuz et de Bab el-Mandeb sont disputés depuis des siècles.</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr"/>
+    </row>
+    <row r="955">
+      <c r="A955" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 15:19</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>2026-10-02 15:12</t>
+        </is>
+      </c>
+      <c r="D955" s="3" t="inlineStr">
+        <is>
+          <t>De l’état d’urgence à la « loi martiale » : comment les cercles MAGA se préparent à contester une défaite lors des midterms</t>
+        </is>
+      </c>
+      <c r="E955" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/02/de-letat-durgence-a-la-loi-martiale-comment-les-cercles-maga-se-preparent-a-contester-une-defaite-lors-des-midterms/</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>Trump n’exclut pas la possibilité de déclarer l’état d'urgence à l'approche des midterms L’article De l&amp;rsquo;état d&amp;rsquo;urgence à la «&amp;#160;loi martiale&amp;#160;»&amp;#160;: comment les cercles MAGA se préparent à contester une défaite lors des midterms est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr"/>
+    </row>
+    <row r="956">
+      <c r="A956" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 15:19</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:21</t>
+        </is>
+      </c>
+      <c r="D956" s="3" t="inlineStr">
+        <is>
+          <t>L’affaire Bardella et la longue durée de l’antisemitisme à l’extrême droite</t>
+        </is>
+      </c>
+      <c r="E956" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/02/affaire-bardella-et-la-longue-duree-antisemitisme-extreme-droite/</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>Les révélations de Mediapart ont remis au cœur du présent une histoire ancienne. Deux universitaires de la nouvelle génération nous aident à en démêler les fils L’article L’affaire Bardella et la longue durée de l’antisemitisme à l’extrême droite est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr"/>
+    </row>
+    <row r="957">
+      <c r="A957" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 15:19</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:17</t>
+        </is>
+      </c>
+      <c r="D957" s="3" t="inlineStr">
+        <is>
+          <t>En Ukraine, l’opération « Vivaldi » redessine le front</t>
+        </is>
+      </c>
+      <c r="E957" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/02/en-ukraine-loperation-vivaldi-redessine-le-front/</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>Moscou a enregistré en septembre ses pertes les plus élevées de l’année L’article En Ukraine, l’opération «&amp;#160;Vivaldi&amp;#160;» redessine le front est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr"/>
+    </row>
+    <row r="958">
+      <c r="A958" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 15:19</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:18</t>
+        </is>
+      </c>
+      <c r="D958" s="3" t="inlineStr">
+        <is>
+          <t>Qui se cache vraiment derrière l’affaire Thélyson Orélien ?</t>
+        </is>
+      </c>
+      <c r="E958" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/02/qui-se-cache-vraiment-derriere-laffaire-thelyson-orelien/</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>Un jeune chercheur révèle au Grand Continent pourquoi il a cofondé le collectif «&amp;#160;Balance ton Claude&amp;#160;» L’article Qui se cache vraiment derrière l’affaire Thélyson Orélien&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr"/>
+    </row>
+    <row r="959">
+      <c r="A959" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 15:19</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>2026-10-02 04:30</t>
+        </is>
+      </c>
+      <c r="D959" s="3" t="inlineStr">
+        <is>
+          <t>La fermeture du détroit d’Ormuz redessine le pouvoir de marché de l’OPEP+</t>
+        </is>
+      </c>
+      <c r="E959" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/02/le-blocage-du-detroit-dormuz-redessine-le-pouvoir-de-marche-de-lopep/</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>En 2002, la capacité de réserve de l’OPEP, soit la production qu’un pays peut remettre sur le marché en 30 à 90 jours, puis maintenir, représentait 14,5&amp;#160;% de la production mondiale de brut. Sur les sept premiers mois de 2026, elle ne représentait plus que 1&amp;#160;%. L’article La fermeture du détroit d’Ormuz redessine le pouvoir de marché de l’OPEP+ est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr"/>
+    </row>
+    <row r="960">
+      <c r="A960" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 15:19</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>2026-10-01 18:07</t>
+        </is>
+      </c>
+      <c r="D960" s="3" t="inlineStr">
+        <is>
+          <t>Selon Mario Draghi l’Europe ne peut plus vivre sans croissance</t>
+        </is>
+      </c>
+      <c r="E960" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/01/selon-mario-draghi-leurope-ne-peut-plus-vivre-sans-croissance/</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>La dernière leçon inédite de l’ancien président de la BCE L’article Selon Mario Draghi l’Europe ne peut plus vivre sans croissance est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr"/>
+    </row>
+    <row r="961">
+      <c r="A961" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 15:19</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:50</t>
+        </is>
+      </c>
+      <c r="D961" s="3" t="inlineStr">
+        <is>
+          <t>Les prix agricoles enregistrent leur plus forte hausse depuis l’invasion russe de l’Ukraine</t>
+        </is>
+      </c>
+      <c r="E961" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/01/les-prix-agricoles-enregistrent-leur-plus-forte-hausse-depuis-linvasion-russe-de-lukraine/</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>De mauvaises conditions météo et la guerre en Ukraine pourraient davantage alimenter l’inflation L’article Les prix agricoles enregistrent leur plus forte hausse depuis l’invasion russe de l’Ukraine est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -31807,6 +32095,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E950" r:id="rId949"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E951" r:id="rId950"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E952" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E953" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E954" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E955" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E956" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E957" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E958" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E959" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E960" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E961" r:id="rId960"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G961"/>
+  <dimension ref="A1:G964"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -30876,7 +30876,6 @@
           <t>Un carnet de Mozart retrouvé à la Bibliothèque nationale de France révèle les leçons de composition qu’il donna en 1778 à Marie-Louise de Guînes.</t>
         </is>
       </c>
-      <c r="G953" t="inlineStr"/>
     </row>
     <row r="954">
       <c r="A954" s="2" t="inlineStr">
@@ -30909,7 +30908,6 @@
           <t>Des expéditions chinoises de Zheng He à la présence militaire américaine, en passant par les empires portugais, néerlandais et britannique, les détroits d’Ormuz et de Bab el-Mandeb sont disputés depuis des siècles.</t>
         </is>
       </c>
-      <c r="G954" t="inlineStr"/>
     </row>
     <row r="955">
       <c r="A955" s="2" t="inlineStr">
@@ -30942,7 +30940,6 @@
           <t>Trump n’exclut pas la possibilité de déclarer l’état d'urgence à l'approche des midterms L’article De l&amp;rsquo;état d&amp;rsquo;urgence à la «&amp;#160;loi martiale&amp;#160;»&amp;#160;: comment les cercles MAGA se préparent à contester une défaite lors des midterms est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G955" t="inlineStr"/>
     </row>
     <row r="956">
       <c r="A956" s="2" t="inlineStr">
@@ -30975,7 +30972,6 @@
           <t>Les révélations de Mediapart ont remis au cœur du présent une histoire ancienne. Deux universitaires de la nouvelle génération nous aident à en démêler les fils L’article L’affaire Bardella et la longue durée de l’antisemitisme à l’extrême droite est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G956" t="inlineStr"/>
     </row>
     <row r="957">
       <c r="A957" s="2" t="inlineStr">
@@ -31008,7 +31004,6 @@
           <t>Moscou a enregistré en septembre ses pertes les plus élevées de l’année L’article En Ukraine, l’opération «&amp;#160;Vivaldi&amp;#160;» redessine le front est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G957" t="inlineStr"/>
     </row>
     <row r="958">
       <c r="A958" s="2" t="inlineStr">
@@ -31041,7 +31036,6 @@
           <t>Un jeune chercheur révèle au Grand Continent pourquoi il a cofondé le collectif «&amp;#160;Balance ton Claude&amp;#160;» L’article Qui se cache vraiment derrière l’affaire Thélyson Orélien&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G958" t="inlineStr"/>
     </row>
     <row r="959">
       <c r="A959" s="2" t="inlineStr">
@@ -31074,7 +31068,6 @@
           <t>En 2002, la capacité de réserve de l’OPEP, soit la production qu’un pays peut remettre sur le marché en 30 à 90 jours, puis maintenir, représentait 14,5&amp;#160;% de la production mondiale de brut. Sur les sept premiers mois de 2026, elle ne représentait plus que 1&amp;#160;%. L’article La fermeture du détroit d’Ormuz redessine le pouvoir de marché de l’OPEP+ est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G959" t="inlineStr"/>
     </row>
     <row r="960">
       <c r="A960" s="2" t="inlineStr">
@@ -31107,7 +31100,6 @@
           <t>La dernière leçon inédite de l’ancien président de la BCE L’article Selon Mario Draghi l’Europe ne peut plus vivre sans croissance est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G960" t="inlineStr"/>
     </row>
     <row r="961">
       <c r="A961" s="2" t="inlineStr">
@@ -31140,7 +31132,105 @@
           <t>De mauvaises conditions météo et la guerre en Ukraine pourraient davantage alimenter l’inflation L’article Les prix agricoles enregistrent leur plus forte hausse depuis l’invasion russe de l’Ukraine est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G961" t="inlineStr"/>
+    </row>
+    <row r="962">
+      <c r="A962" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 14:07</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>2026-10-03 08:50</t>
+        </is>
+      </c>
+      <c r="D962" s="3" t="inlineStr">
+        <is>
+          <t>Apprendre à bien manger : comment penser l’éducation à l’alimentation ?</t>
+        </is>
+      </c>
+      <c r="E962" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/apprendre-a-bien-manger-comment-penser-leducation-a-lalimentation-288550</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>Si l’on parle de plus en plus d’éducation à l’alimentation, au singulier, apprendre à s’alimenter ne repose pas sur une seule recette.</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr"/>
+    </row>
+    <row r="963">
+      <c r="A963" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 14:07</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>2026-10-03 14:16</t>
+        </is>
+      </c>
+      <c r="D963" s="3" t="inlineStr">
+        <is>
+          <t>Les démocrates se dirigent-ils vers une victoire écrasante aux élections de mi-mandat ?</t>
+        </is>
+      </c>
+      <c r="E963" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/03/les-democrates-se-dirigent-ils-vers-une-victoire-ecrasante-aux-elections-de-mi-mandat/</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>À un mois du scrutin du 3 novembre, les sondages sont presque unanimes et Donald Trump semble faire l’objet d’un rejet historique L’article Les démocrates se dirigent-ils vers une victoire écrasante aux élections de mi-mandat&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr"/>
+    </row>
+    <row r="964">
+      <c r="A964" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 14:07</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>2026-10-03 04:30</t>
+        </is>
+      </c>
+      <c r="D964" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : sous pression budgétaire, les régions réduisent les indemnités versées aux familles des soldats morts en Ukraine</t>
+        </is>
+      </c>
+      <c r="E964" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/03/economie-russe-sous-pression-budgetaire-les-regions-reduisent-les-indemnites-versees-aux-familles-des-soldats-morts-en-ukraine/</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>À Saratov, le montant passera d’un million de roubles à 100 000 le 1er novembre L’article Économie russe&amp;#160;: sous pression budgétaire, les régions réduisent les indemnités versées aux familles des soldats morts en Ukraine est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -32104,6 +32194,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E959" r:id="rId958"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E960" r:id="rId959"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E961" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E962" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E963" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E964" r:id="rId963"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G964"/>
+  <dimension ref="A1:G971"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -31164,7 +31164,6 @@
           <t>Si l’on parle de plus en plus d’éducation à l’alimentation, au singulier, apprendre à s’alimenter ne repose pas sur une seule recette.</t>
         </is>
       </c>
-      <c r="G962" t="inlineStr"/>
     </row>
     <row r="963">
       <c r="A963" s="2" t="inlineStr">
@@ -31197,7 +31196,6 @@
           <t>À un mois du scrutin du 3 novembre, les sondages sont presque unanimes et Donald Trump semble faire l’objet d’un rejet historique L’article Les démocrates se dirigent-ils vers une victoire écrasante aux élections de mi-mandat&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G963" t="inlineStr"/>
     </row>
     <row r="964">
       <c r="A964" s="2" t="inlineStr">
@@ -31230,7 +31228,237 @@
           <t>À Saratov, le montant passera d’un million de roubles à 100 000 le 1er novembre L’article Économie russe&amp;#160;: sous pression budgétaire, les régions réduisent les indemnités versées aux familles des soldats morts en Ukraine est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G964" t="inlineStr"/>
+    </row>
+    <row r="965">
+      <c r="A965" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04 14:35</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>2026-10-04 07:12</t>
+        </is>
+      </c>
+      <c r="D965" s="3" t="inlineStr">
+        <is>
+          <t>Non, le stoïcisme n'est pas ce « truc de mecs » revendiqué par les masculinistes</t>
+        </is>
+      </c>
+      <c r="E965" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/non-le-sto-cisme-nest-pas-ce-truc-de-mecs-revendique-par-les-masculinistes-293412</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>Marc Aurèle s’était promis d’être un homme de bien, mais qu’entendait-il par là&amp;nbsp;? Les interprétations masculinistes du stoïcisme relèvent du malentendu.</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr"/>
+    </row>
+    <row r="966">
+      <c r="A966" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04 14:35</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>2026-10-04 07:14</t>
+        </is>
+      </c>
+      <c r="D966" s="3" t="inlineStr">
+        <is>
+          <t>À l’école, les arts peuvent-ils libérer la parole des enfants sur les violences ?</t>
+        </is>
+      </c>
+      <c r="E966" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/a-lecole-les-arts-peuvent-ils-liberer-la-parole-des-enfants-sur-les-violences-291525</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>Si les arts génèrent un état émotionnel positif, propice à aborder des sujets graves, peuvent-ils pour autant devenir le support d’une prévention efficace des violences auprès des enfants&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr"/>
+    </row>
+    <row r="967">
+      <c r="A967" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04 14:35</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>2026-10-04 07:14</t>
+        </is>
+      </c>
+      <c r="D967" s="3" t="inlineStr">
+        <is>
+          <t>Les nouveaux besoins (géopolitiques) de l’entreprise</t>
+        </is>
+      </c>
+      <c r="E967" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-nouveaux-besoins-geopolitiques-de-lentreprise-291889</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>Les dirigeants des entreprises ne doivent pas devenir des géopoliticiens, mais l’expertise géopolitique doit être intégrée aux décisions économiques.</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr"/>
+    </row>
+    <row r="968">
+      <c r="A968" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04 14:35</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:00</t>
+        </is>
+      </c>
+      <c r="D968" s="3" t="inlineStr">
+        <is>
+          <t>Pour comprendre l’offensive industrielle du Parti il faut se rendre au Sichuan</t>
+        </is>
+      </c>
+      <c r="E968" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/04/pour-comprendre-loffensive-industrielle-du-parti-il-faut-se-rendre-au-sichuan/</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>De Chengdu aux héritages du «&amp;#160;Troisième front&amp;#160;», portrait à grande échelle d’un épicentre impérial L’article Pour comprendre l’offensive industrielle du Parti il faut se rendre au Sichuan est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr"/>
+    </row>
+    <row r="969">
+      <c r="A969" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04 14:35</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>2026-10-04 04:30</t>
+        </is>
+      </c>
+      <c r="D969" s="3" t="inlineStr">
+        <is>
+          <t>Le Brésil, dernier rempart contre Trump en Amérique du Sud ?</t>
+        </is>
+      </c>
+      <c r="E969" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/04/le-bresil-dernier-rempart-contre-trump-en-amerique-du-sud/</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>La question à suivre lors du scrutin brésilien pourrait être avant tout géopolitique L’article Le Brésil, dernier rempart contre Trump en Amérique du Sud&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr"/>
+    </row>
+    <row r="970">
+      <c r="A970" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04 14:35</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>2026-10-03 15:31</t>
+        </is>
+      </c>
+      <c r="D970" s="3" t="inlineStr">
+        <is>
+          <t>Entre Lula et Bolsonaro le Brésil est nettement divisé en deux</t>
+        </is>
+      </c>
+      <c r="E970" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/03/lula-et-bolsonaro-le-bresil-est-nettement-divise-en-deux/</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>Une grande enquête inédite de Cluster 17 révèle une élection présidentielle disputée comme jamais L’article Entre Lula et Bolsonaro le Brésil est nettement divisé en deux est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr"/>
+    </row>
+    <row r="971">
+      <c r="A971" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04 14:35</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>2026-10-03 18:13</t>
+        </is>
+      </c>
+      <c r="D971" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce Agrégation interne – Jonathan Gaquère – La géographie du Bassin minier</t>
+        </is>
+      </c>
+      <c r="E971" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/coup-de-pouce-agregation-interne-jonathan-gaquere-la-geographie-du-bassin-minier/</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Jonathan Gaquère consacrée au bassin minier. Le podcast est proposé en version audio hybride avec diaporama intégré. [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Jonathan Gaquère &amp;#8211; La géographie du Bassin minier est apparu en premier </t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -32197,6 +32425,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E962" r:id="rId961"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E963" r:id="rId962"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E964" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E965" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E966" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E967" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E968" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E969" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E970" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E971" r:id="rId970"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G971"/>
+  <dimension ref="A1:G981"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -31260,7 +31260,6 @@
           <t>Marc Aurèle s’était promis d’être un homme de bien, mais qu’entendait-il par là&amp;nbsp;? Les interprétations masculinistes du stoïcisme relèvent du malentendu.</t>
         </is>
       </c>
-      <c r="G965" t="inlineStr"/>
     </row>
     <row r="966">
       <c r="A966" s="2" t="inlineStr">
@@ -31293,7 +31292,6 @@
           <t>Si les arts génèrent un état émotionnel positif, propice à aborder des sujets graves, peuvent-ils pour autant devenir le support d’une prévention efficace des violences auprès des enfants&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G966" t="inlineStr"/>
     </row>
     <row r="967">
       <c r="A967" s="2" t="inlineStr">
@@ -31326,7 +31324,6 @@
           <t>Les dirigeants des entreprises ne doivent pas devenir des géopoliticiens, mais l’expertise géopolitique doit être intégrée aux décisions économiques.</t>
         </is>
       </c>
-      <c r="G967" t="inlineStr"/>
     </row>
     <row r="968">
       <c r="A968" s="2" t="inlineStr">
@@ -31359,7 +31356,6 @@
           <t>De Chengdu aux héritages du «&amp;#160;Troisième front&amp;#160;», portrait à grande échelle d’un épicentre impérial L’article Pour comprendre l’offensive industrielle du Parti il faut se rendre au Sichuan est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G968" t="inlineStr"/>
     </row>
     <row r="969">
       <c r="A969" s="2" t="inlineStr">
@@ -31392,7 +31388,6 @@
           <t>La question à suivre lors du scrutin brésilien pourrait être avant tout géopolitique L’article Le Brésil, dernier rempart contre Trump en Amérique du Sud&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G969" t="inlineStr"/>
     </row>
     <row r="970">
       <c r="A970" s="2" t="inlineStr">
@@ -31425,7 +31420,6 @@
           <t>Une grande enquête inédite de Cluster 17 révèle une élection présidentielle disputée comme jamais L’article Entre Lula et Bolsonaro le Brésil est nettement divisé en deux est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G970" t="inlineStr"/>
     </row>
     <row r="971">
       <c r="A971" s="2" t="inlineStr">
@@ -31458,7 +31452,336 @@
           <t xml:space="preserve">Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Jonathan Gaquère consacrée au bassin minier. Le podcast est proposé en version audio hybride avec diaporama intégré. [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Jonathan Gaquère &amp;#8211; La géographie du Bassin minier est apparu en premier </t>
         </is>
       </c>
-      <c r="G971" t="inlineStr"/>
+    </row>
+    <row r="972">
+      <c r="A972" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 17:48</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>2026-10-05 12:16</t>
+        </is>
+      </c>
+      <c r="D972" s="3" t="inlineStr">
+        <is>
+          <t>Protection de l’enfance : quels modèles d’alimentation ?</t>
+        </is>
+      </c>
+      <c r="E972" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/protection-de-lenfance-quels-modeles-dalimentation-290798</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>Dans les foyers de l’aide sociale à l’enfance, le rapport des jeunes à l’alimentation est très lié à ce qu’ils pensent du lieu d’accueil et de leur mesure de placement.</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr"/>
+    </row>
+    <row r="973">
+      <c r="A973" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 17:48</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>2026-10-05 12:11</t>
+        </is>
+      </c>
+      <c r="D973" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi le bonheur des enfants doit être une priorité politique</t>
+        </is>
+      </c>
+      <c r="E973" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-le-bonheur-des-enfants-doit-etre-une-priorite-politique-287108</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>Faire en sorte que les enfants soient heureux devrait être l’objectif de toute politique publique. Des indicateurs fiables mesurent le bonheur des enfants, et des pays les utilisent. À quand la France&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr"/>
+    </row>
+    <row r="974">
+      <c r="A974" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 17:48</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>2026-10-05 12:20</t>
+        </is>
+      </c>
+      <c r="D974" s="3" t="inlineStr">
+        <is>
+          <t>Au Kenya, choisir son poisson devient un véritable dilemme sanitaire</t>
+        </is>
+      </c>
+      <c r="E974" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/au-kenya-choisir-son-poisson-devient-un-veritable-dilemme-sanitaire-292614</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>Compte tenu de la pollution environnementale persistante, s’informer sur les bienfaits et les risques liés à la consommation de poisson est une préoccupation quotidienne pour les consommateurs kenyans. Dans quelle mesure sont-ils influencés par l’étiquetage nutritionnel et les recommandations alimentaires&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr"/>
+    </row>
+    <row r="975">
+      <c r="A975" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 17:48</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:36</t>
+        </is>
+      </c>
+      <c r="D975" s="3" t="inlineStr">
+        <is>
+          <t>La France et l’Allemagne veulent donner à l’Union le pouvoir de fermer son marché</t>
+        </is>
+      </c>
+      <c r="E975" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/05/la-france-et-lallemagne-veulent-donner-a-lunion-le-pouvoir-de-fermer-son-marche/</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>Voilà pourquoi ce serait une petite révolution L’article La France et l’Allemagne veulent donner à l’Union le pouvoir de fermer son marché est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr"/>
+    </row>
+    <row r="976">
+      <c r="A976" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 17:48</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:37</t>
+        </is>
+      </c>
+      <c r="D976" s="3" t="inlineStr">
+        <is>
+          <t>Au sein de l’AfD, on rêve d’annexer les Sudètes, une partie de l’Italie et l’Alsace-Lorraine</t>
+        </is>
+      </c>
+      <c r="E976" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/05/au-sein-de-lafd-on-reve-dannexer-les-sudetes-une-partie-de-litalie-et-l-alsace-lorraine/</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>Nous cartographions les frontières révisionnistes de la «&amp;#160;Grande Allemagne&amp;#160;» L’article Au sein de l’AfD, on rêve d&amp;rsquo;annexer les Sudètes, une partie de l’Italie et l&amp;rsquo;Alsace-Lorraine est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr"/>
+    </row>
+    <row r="977">
+      <c r="A977" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 17:48</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:11</t>
+        </is>
+      </c>
+      <c r="D977" s="3" t="inlineStr">
+        <is>
+          <t>La Russie fait-elle face à une épidémie de peste ?</t>
+        </is>
+      </c>
+      <c r="E977" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/05/la-russie-fait-elle-face-a-une-epidemie-de-peste/</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>Ce que l’on sait sur le décès d’une femme le 2 octobre dans la région d’Irkoutsk L’article La Russie fait-elle face à une épidémie de peste&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr"/>
+    </row>
+    <row r="978">
+      <c r="A978" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 17:48</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>2026-10-05 06:12</t>
+        </is>
+      </c>
+      <c r="D978" s="3" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro : « C’est la fin de Lula »</t>
+        </is>
+      </c>
+      <c r="E978" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/05/flavio-bolsonaro-cest-la-fin-de-lula/</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>Nous traduisons son discours de la victoire placé entre Milei, Bukele et Trump L’article Flávio Bolsonaro&amp;#160;: «&amp;#160;C’est la fin de Lula&amp;#160;» est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr"/>
+    </row>
+    <row r="979">
+      <c r="A979" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 17:48</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>2026-10-05 04:00</t>
+        </is>
+      </c>
+      <c r="D979" s="3" t="inlineStr">
+        <is>
+          <t>« La Chine est en train de tuer le commerce mondial ouvert »</t>
+        </is>
+      </c>
+      <c r="E979" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/05/pascal-lamy-la-chine-est-en-train-de-tuer-le-commerce-mondial-ouvert/</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>Voici comment l’Europe doit réagir L’article «&amp;#160;La Chine est en train de tuer le commerce mondial ouvert&amp;#160;» est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr"/>
+    </row>
+    <row r="980">
+      <c r="A980" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 17:48</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>2026-10-04 04:30</t>
+        </is>
+      </c>
+      <c r="D980" s="3" t="inlineStr">
+        <is>
+          <t>Au Brésil, Flávio Bolsonaro en tête du premier tour</t>
+        </is>
+      </c>
+      <c r="E980" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/04/au-bresil-flavio-bolsonaro-en-tete-du-premier-tour/</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>La question à suivre lors du scrutin brésilien pourrait être avant tout géopolitique L’article Au Brésil, Flávio Bolsonaro en tête du premier tour est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr"/>
+    </row>
+    <row r="981">
+      <c r="A981" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 17:48</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>2026-10-04 15:41</t>
+        </is>
+      </c>
+      <c r="D981" s="3" t="inlineStr">
+        <is>
+          <t>Journée d’étude APHG / ECPAD : « Photographier la guerre »</t>
+        </is>
+      </c>
+      <c r="E981" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/journee-detude-aphg-ecpad-photographier-la-guerre/</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>Journée de formation nationale Samedi 28 novembre 2026, de 9 h à 17 h · Sorbonne (amphi Richelieu le matin, amphi Turgot l&amp;#8217;après-midi) Ce programme a été conçu par l&amp;#8217;ECPAD en accord avec l&amp;#8217;APHG. Nous remercions chaleureusement l&amp;#8217;ECPAD, et tout particulièrement Nadia Wainstain, pour la richesse de cette proposition. De la photographie de guerre dans [&amp;#8230;] L’article Journée d&amp;rsquo;étude APHG / ECPAD : « Photographier la guerre » est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -32432,6 +32755,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E969" r:id="rId968"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E970" r:id="rId969"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E971" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E972" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E973" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E974" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E975" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E976" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E977" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E978" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E979" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E980" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E981" r:id="rId980"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G981"/>
+  <dimension ref="A1:G991"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -31484,7 +31484,6 @@
           <t>Dans les foyers de l’aide sociale à l’enfance, le rapport des jeunes à l’alimentation est très lié à ce qu’ils pensent du lieu d’accueil et de leur mesure de placement.</t>
         </is>
       </c>
-      <c r="G972" t="inlineStr"/>
     </row>
     <row r="973">
       <c r="A973" s="2" t="inlineStr">
@@ -31517,7 +31516,6 @@
           <t>Faire en sorte que les enfants soient heureux devrait être l’objectif de toute politique publique. Des indicateurs fiables mesurent le bonheur des enfants, et des pays les utilisent. À quand la France&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G973" t="inlineStr"/>
     </row>
     <row r="974">
       <c r="A974" s="2" t="inlineStr">
@@ -31550,7 +31548,6 @@
           <t>Compte tenu de la pollution environnementale persistante, s’informer sur les bienfaits et les risques liés à la consommation de poisson est une préoccupation quotidienne pour les consommateurs kenyans. Dans quelle mesure sont-ils influencés par l’étiquetage nutritionnel et les recommandations alimentaires&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G974" t="inlineStr"/>
     </row>
     <row r="975">
       <c r="A975" s="2" t="inlineStr">
@@ -31583,7 +31580,6 @@
           <t>Voilà pourquoi ce serait une petite révolution L’article La France et l’Allemagne veulent donner à l’Union le pouvoir de fermer son marché est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G975" t="inlineStr"/>
     </row>
     <row r="976">
       <c r="A976" s="2" t="inlineStr">
@@ -31616,7 +31612,6 @@
           <t>Nous cartographions les frontières révisionnistes de la «&amp;#160;Grande Allemagne&amp;#160;» L’article Au sein de l’AfD, on rêve d&amp;rsquo;annexer les Sudètes, une partie de l’Italie et l&amp;rsquo;Alsace-Lorraine est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G976" t="inlineStr"/>
     </row>
     <row r="977">
       <c r="A977" s="2" t="inlineStr">
@@ -31649,7 +31644,6 @@
           <t>Ce que l’on sait sur le décès d’une femme le 2 octobre dans la région d’Irkoutsk L’article La Russie fait-elle face à une épidémie de peste&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G977" t="inlineStr"/>
     </row>
     <row r="978">
       <c r="A978" s="2" t="inlineStr">
@@ -31682,7 +31676,6 @@
           <t>Nous traduisons son discours de la victoire placé entre Milei, Bukele et Trump L’article Flávio Bolsonaro&amp;#160;: «&amp;#160;C’est la fin de Lula&amp;#160;» est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G978" t="inlineStr"/>
     </row>
     <row r="979">
       <c r="A979" s="2" t="inlineStr">
@@ -31715,7 +31708,6 @@
           <t>Voici comment l’Europe doit réagir L’article «&amp;#160;La Chine est en train de tuer le commerce mondial ouvert&amp;#160;» est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G979" t="inlineStr"/>
     </row>
     <row r="980">
       <c r="A980" s="2" t="inlineStr">
@@ -31748,7 +31740,6 @@
           <t>La question à suivre lors du scrutin brésilien pourrait être avant tout géopolitique L’article Au Brésil, Flávio Bolsonaro en tête du premier tour est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G980" t="inlineStr"/>
     </row>
     <row r="981">
       <c r="A981" s="2" t="inlineStr">
@@ -31781,7 +31772,336 @@
           <t>Journée de formation nationale Samedi 28 novembre 2026, de 9 h à 17 h · Sorbonne (amphi Richelieu le matin, amphi Turgot l&amp;#8217;après-midi) Ce programme a été conçu par l&amp;#8217;ECPAD en accord avec l&amp;#8217;APHG. Nous remercions chaleureusement l&amp;#8217;ECPAD, et tout particulièrement Nadia Wainstain, pour la richesse de cette proposition. De la photographie de guerre dans [&amp;#8230;] L’article Journée d&amp;rsquo;étude APHG / ECPAD : « Photographier la guerre » est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G981" t="inlineStr"/>
+    </row>
+    <row r="982">
+      <c r="A982" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:39</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:15</t>
+        </is>
+      </c>
+      <c r="D982" s="3" t="inlineStr">
+        <is>
+          <t>Petite histoire sensorielle de la truffe à l’époque moderne</t>
+        </is>
+      </c>
+      <c r="E982" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/petite-histoire-sensorielle-de-la-truffe-a-lepoque-moderne-291384</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>Aux XVIᵉ et XVIIᵉ&amp;nbsp;siècles, la truffe semble connaître un regain d’intérêt, tant chez les naturalistes que chez les spécialistes de l’art culinaire.</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr"/>
+    </row>
+    <row r="983">
+      <c r="A983" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:39</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>2026-10-06 07:53</t>
+        </is>
+      </c>
+      <c r="D983" s="3" t="inlineStr">
+        <is>
+          <t>L’histoire d’Argos, le fidèle chien d’Ulysse, éclaire la place des animaux dans la Grèce antique</t>
+        </is>
+      </c>
+      <c r="E983" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/lhistoire-dargos-le-fidele-chien-dulysse-eclaire-la-place-des-animaux-dans-la-grece-antique-288398</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>Dans l’«&amp;nbsp;Odyssée&amp;nbsp;», les retrouvailles entre Ulysse et son chien Argos comptent parmi les scènes les plus émouvantes de toute la littérature antique. Elles révèlent aussi la place essentielle qu’occupaient les animaux dans la vie quotidienne des Grecs.</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr"/>
+    </row>
+    <row r="984">
+      <c r="A984" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:39</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>2026-10-06 07:38</t>
+        </is>
+      </c>
+      <c r="D984" s="3" t="inlineStr">
+        <is>
+          <t>Le long voyage du riz, de la préhistoire aux rizières du monde entier</t>
+        </is>
+      </c>
+      <c r="E984" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-long-voyage-du-riz-de-la-prehistoire-aux-rizieres-du-monde-entier-288943</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>D’où vient le riz ? Et comment s’est-il diffusé jusqu’à devenir l’un des piliers de la sécurité alimentaire mondiale ?</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr"/>
+    </row>
+    <row r="985">
+      <c r="A985" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:39</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:54</t>
+        </is>
+      </c>
+      <c r="D985" s="3" t="inlineStr">
+        <is>
+          <t>Brésil : le monde ancien est mort, et le nouveau ne peut pas naître</t>
+        </is>
+      </c>
+      <c r="E985" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/bresil-le-monde-ancien-est-mort-et-le-nouveau-ne-peut-pas-naitre-293717</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>Ce projet politique, né au milieu des années&amp;nbsp;1980 sur les décombres de la dictature militaire, a sans doute pris fin ce 4&amp;nbsp;octobre. La question est désormais de savoir ce qui va le remplacer.</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr"/>
+    </row>
+    <row r="986">
+      <c r="A986" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:39</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:53</t>
+        </is>
+      </c>
+      <c r="D986" s="3" t="inlineStr">
+        <is>
+          <t>Les sociétés militaires privées en Amérique latine : de la fin de la guerre froide à Vectus Global</t>
+        </is>
+      </c>
+      <c r="E986" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-societes-militaires-privees-en-amerique-latine-de-la-fin-de-la-guerre-froide-a-vectus-global-291844</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>En Amérique latine, les SMP américaines consolident leur présence tandis que la Chine progresse et que la Russie recule, sur fond de rivalité entre puissances.</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr"/>
+    </row>
+    <row r="987">
+      <c r="A987" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:39</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:22</t>
+        </is>
+      </c>
+      <c r="D987" s="3" t="inlineStr">
+        <is>
+          <t>Avec le Chonk, Mistral a-t-il rattrapé son retard dans la course à la frontière de l’IA ?</t>
+        </is>
+      </c>
+      <c r="E987" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/06/avec-le-chonk-mistral-a-t-il-rattrape-son-retard-dans-la-course-a-la-frontiere-de-lia/</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>La France se place désormais 3e pour ses modèles d’IA de frontière, derrière les États-Unis et la Chine L’article Avec le Chonk, Mistral a-t-il rattrapé son retard dans la course à la frontière de l’IA&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr"/>
+    </row>
+    <row r="988">
+      <c r="A988" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:39</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:58</t>
+        </is>
+      </c>
+      <c r="D988" s="3" t="inlineStr">
+        <is>
+          <t>Vers une résurgence du mouvement des Gilets jaunes ?</t>
+        </is>
+      </c>
+      <c r="E988" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/06/vers-une-resurgence-du-mouvement-des-gilets-jaunes/</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>Les appels à l’organisation d’un mouvement national le 17 octobre se multiplient L’article Vers une résurgence du mouvement des Gilets jaunes&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr"/>
+    </row>
+    <row r="989">
+      <c r="A989" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:39</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:21</t>
+        </is>
+      </c>
+      <c r="D989" s="3" t="inlineStr">
+        <is>
+          <t>L’ère de la guerre politique</t>
+        </is>
+      </c>
+      <c r="E989" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/06/lere-de-la-guerre-politique/</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>Pour comprendre ce que Poutine et Trump font déjà sur le continent, la notion de «&amp;#160;guerre hybride&amp;#160;» est devenue inadéquate L’article L&amp;rsquo;ère de la guerre politique est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr"/>
+    </row>
+    <row r="990">
+      <c r="A990" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:39</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>2026-10-06 04:30</t>
+        </is>
+      </c>
+      <c r="D990" s="3" t="inlineStr">
+        <is>
+          <t>Les grands laboratoires pharmaceutiques se tournent vers les biotechs chinoises</t>
+        </is>
+      </c>
+      <c r="E990" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/06/les-grands-laboratoires-pharmaceutiques-se-tournent-vers-les-biotechs-chinoises/</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>La valeur des accords conclus par des entreprises chinoises avec des partenaires étrangers a plus que doublé en 2025 L’article Les grands laboratoires pharmaceutiques se tournent vers les biotechs chinoises est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr"/>
+    </row>
+    <row r="991">
+      <c r="A991" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:39</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:30</t>
+        </is>
+      </c>
+      <c r="D991" s="3" t="inlineStr">
+        <is>
+          <t>Lycéens et professeurs : les attentes sont les mêmes !</t>
+        </is>
+      </c>
+      <c r="E991" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/lyceens-et-professeurs-les-attentes-sont-les-memes/</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>Alors qu’un mois à peine s’est écoulé depuis la rentrée scolaire, un mouvement lycéen a pris forme et s’accroît de manière considérable. Il a principalement pris l’aspect de blocages d’établissements et de manifestations. Face à cette situation, le gouvernement, faisant passer au second plan les revendications des lycéens et mettant en avant des actes de [&amp;#8230;] L’article Lycéens et professeurs : les attentes sont les mêmes ! est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -32765,6 +33085,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E979" r:id="rId978"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E980" r:id="rId979"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E981" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E982" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E983" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E984" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E985" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E986" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E987" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E988" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E989" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E990" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E991" r:id="rId990"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G991"/>
+  <dimension ref="A1:G1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -31804,7 +31804,6 @@
           <t>Aux XVIᵉ et XVIIᵉ&amp;nbsp;siècles, la truffe semble connaître un regain d’intérêt, tant chez les naturalistes que chez les spécialistes de l’art culinaire.</t>
         </is>
       </c>
-      <c r="G982" t="inlineStr"/>
     </row>
     <row r="983">
       <c r="A983" s="2" t="inlineStr">
@@ -31837,7 +31836,6 @@
           <t>Dans l’«&amp;nbsp;Odyssée&amp;nbsp;», les retrouvailles entre Ulysse et son chien Argos comptent parmi les scènes les plus émouvantes de toute la littérature antique. Elles révèlent aussi la place essentielle qu’occupaient les animaux dans la vie quotidienne des Grecs.</t>
         </is>
       </c>
-      <c r="G983" t="inlineStr"/>
     </row>
     <row r="984">
       <c r="A984" s="2" t="inlineStr">
@@ -31870,7 +31868,6 @@
           <t>D’où vient le riz ? Et comment s’est-il diffusé jusqu’à devenir l’un des piliers de la sécurité alimentaire mondiale ?</t>
         </is>
       </c>
-      <c r="G984" t="inlineStr"/>
     </row>
     <row r="985">
       <c r="A985" s="2" t="inlineStr">
@@ -31903,7 +31900,6 @@
           <t>Ce projet politique, né au milieu des années&amp;nbsp;1980 sur les décombres de la dictature militaire, a sans doute pris fin ce 4&amp;nbsp;octobre. La question est désormais de savoir ce qui va le remplacer.</t>
         </is>
       </c>
-      <c r="G985" t="inlineStr"/>
     </row>
     <row r="986">
       <c r="A986" s="2" t="inlineStr">
@@ -31936,7 +31932,6 @@
           <t>En Amérique latine, les SMP américaines consolident leur présence tandis que la Chine progresse et que la Russie recule, sur fond de rivalité entre puissances.</t>
         </is>
       </c>
-      <c r="G986" t="inlineStr"/>
     </row>
     <row r="987">
       <c r="A987" s="2" t="inlineStr">
@@ -31969,7 +31964,6 @@
           <t>La France se place désormais 3e pour ses modèles d’IA de frontière, derrière les États-Unis et la Chine L’article Avec le Chonk, Mistral a-t-il rattrapé son retard dans la course à la frontière de l’IA&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G987" t="inlineStr"/>
     </row>
     <row r="988">
       <c r="A988" s="2" t="inlineStr">
@@ -32002,7 +31996,6 @@
           <t>Les appels à l’organisation d’un mouvement national le 17 octobre se multiplient L’article Vers une résurgence du mouvement des Gilets jaunes&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G988" t="inlineStr"/>
     </row>
     <row r="989">
       <c r="A989" s="2" t="inlineStr">
@@ -32035,7 +32028,6 @@
           <t>Pour comprendre ce que Poutine et Trump font déjà sur le continent, la notion de «&amp;#160;guerre hybride&amp;#160;» est devenue inadéquate L’article L&amp;rsquo;ère de la guerre politique est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G989" t="inlineStr"/>
     </row>
     <row r="990">
       <c r="A990" s="2" t="inlineStr">
@@ -32068,7 +32060,6 @@
           <t>La valeur des accords conclus par des entreprises chinoises avec des partenaires étrangers a plus que doublé en 2025 L’article Les grands laboratoires pharmaceutiques se tournent vers les biotechs chinoises est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G990" t="inlineStr"/>
     </row>
     <row r="991">
       <c r="A991" s="2" t="inlineStr">
@@ -32101,7 +32092,303 @@
           <t>Alors qu’un mois à peine s’est écoulé depuis la rentrée scolaire, un mouvement lycéen a pris forme et s’accroît de manière considérable. Il a principalement pris l’aspect de blocages d’établissements et de manifestations. Face à cette situation, le gouvernement, faisant passer au second plan les revendications des lycéens et mettant en avant des actes de [&amp;#8230;] L’article Lycéens et professeurs : les attentes sont les mêmes ! est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G991" t="inlineStr"/>
+    </row>
+    <row r="992">
+      <c r="A992" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 16:03</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:54</t>
+        </is>
+      </c>
+      <c r="D992" s="3" t="inlineStr">
+        <is>
+          <t>De la lettre à Internet : communiquons-nous désormais en temps réel ?</t>
+        </is>
+      </c>
+      <c r="E992" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/de-la-lettre-a-internet-communiquons-nous-desormais-en-temps-reel-293129</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>S’il fallait autrefois attendre de longs jours avant de recevoir une missive, notre époque semble avoir aboli les distances et le temps. Mais cette communication si immédiate en apparence n’est qu’une métamorphose de l’attente.</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr"/>
+    </row>
+    <row r="993">
+      <c r="A993" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 16:03</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:19</t>
+        </is>
+      </c>
+      <c r="D993" s="3" t="inlineStr">
+        <is>
+          <t>Des scientifiques avaient prédit la fin du monde pour le vendredi 13 novembre 2026. Faut-il s’inquiéter ?</t>
+        </is>
+      </c>
+      <c r="E993" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/des-scientifiques-avaient-predit-la-fin-du-monde-pour-le-vendredi-13-novembre-2026-faut-il-sinquieter-293842</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>En 1960, des chercheurs annonçaient la fin du monde pour le 13 novembre 2026, sous l’effet d’une croissance démographique incontrôlée. Retour sur une prédiction qui mêlait science rigoureuse et art de la mise en scène.</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr"/>
+    </row>
+    <row r="994">
+      <c r="A994" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 16:03</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:53</t>
+        </is>
+      </c>
+      <c r="D994" s="3" t="inlineStr">
+        <is>
+          <t>Manifestations lycéennes, réponse du gouvernement : pourquoi la situation est inédite – et imprévisible</t>
+        </is>
+      </c>
+      <c r="E994" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/manifestations-lyceennes-reponse-du-gouvernement-pourquoi-la-situation-est-inedite-et-imprevisible-293772</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>Les revendications des lycéens sur les moyens de l’éducation nationale sont récurrentes, mais le contexte global et la forme du mouvement –&amp;nbsp;né dans les banlieues populaires&amp;nbsp;– sont nouveaux, tout comme la réponse, d’abord policière, du gouvernement.</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr"/>
+    </row>
+    <row r="995">
+      <c r="A995" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 16:03</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:52</t>
+        </is>
+      </c>
+      <c r="D995" s="3" t="inlineStr">
+        <is>
+          <t>Le droit, levier de l’Europe face à Pékin</t>
+        </is>
+      </c>
+      <c r="E995" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-droit-levier-de-leurope-face-a-pekin-291888</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>Face à la Chine, l’UE transforme son marché en levier juridique&amp;nbsp;: salariés, subventions et travail forcé deviennent les nouveaux terrains de la confrontation.</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr"/>
+    </row>
+    <row r="996">
+      <c r="A996" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 16:03</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:36</t>
+        </is>
+      </c>
+      <c r="D996" s="3" t="inlineStr">
+        <is>
+          <t>Aux États-Unis, l’IA creuse le déficit commercial</t>
+        </is>
+      </c>
+      <c r="E996" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/07/aux-etats-unis-lia-creuse-le-deficit-commercial/</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>Trump peut-il concilier IA de pointe et réduction du déficit&amp;#160;? L’article Aux États-Unis, l’IA creuse le déficit commercial est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr"/>
+    </row>
+    <row r="997">
+      <c r="A997" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 16:03</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:55</t>
+        </is>
+      </c>
+      <c r="D997" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : les recettes tirées des exportations de pétrole brut atteignent leur niveau le plus élevé depuis 2022</t>
+        </is>
+      </c>
+      <c r="E997" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/07/economie-russe-les-recettes-tirees-des-exportations-de-petrole-brut-atteignent-leur-niveau-le-plus-eleve-depuis-2022/</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>La hausse des exportations de brut n’est toutefois pas nécessairement une bonne nouvelle pour Moscou L’article Économie russe&amp;#160;: les recettes tirées des exportations de pétrole brut atteignent leur niveau le plus élevé depuis 2022 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr"/>
+    </row>
+    <row r="998">
+      <c r="A998" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 16:03</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>2026-10-07 07:01</t>
+        </is>
+      </c>
+      <c r="D998" s="3" t="inlineStr">
+        <is>
+          <t>Trump veut vassaliser la presse américaine</t>
+        </is>
+      </c>
+      <c r="E998" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/07/trump-veut-vassaliser-la-presse-americaine/</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>De Montesquieu à Madison, le coup de force contre la presse marque une rupture historique aux États-Unis L’article Trump veut vassaliser la presse américaine est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr"/>
+    </row>
+    <row r="999">
+      <c r="A999" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 16:03</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>2026-10-07 04:30</t>
+        </is>
+      </c>
+      <c r="D999" s="3" t="inlineStr">
+        <is>
+          <t>L’Iran exerce-t-il toujours un contrôle sur le détroit d’Ormuz ?</t>
+        </is>
+      </c>
+      <c r="E999" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/07/liran-exerce-t-il-toujours-un-controle-sur-le-detroit-dormuz/</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>Les flux pétroliers en provenance du Moyen-Orient sont presque revenus à leur niveau d’avant-guerre L’article L’Iran exerce-t-il toujours un contrôle sur le détroit d’Ormuz&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr"/>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 16:03</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:57</t>
+        </is>
+      </c>
+      <c r="D1000" s="3" t="inlineStr">
+        <is>
+          <t>Quelle géopolitique pour la primaire socialiste ?</t>
+        </is>
+      </c>
+      <c r="E1000" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/06/quelle-geopolitique-pour-la-primaire-socialiste/</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>Nous avons interrogé les cinq candidats. Voici leurs réponses L’article Quelle géopolitique pour la primaire socialiste&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -33095,6 +33382,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E989" r:id="rId988"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E990" r:id="rId989"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E991" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E992" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E993" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E994" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E995" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E996" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E997" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E998" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E999" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1000" r:id="rId999"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1000"/>
+  <dimension ref="A1:G1010"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -32124,7 +32124,6 @@
           <t>S’il fallait autrefois attendre de longs jours avant de recevoir une missive, notre époque semble avoir aboli les distances et le temps. Mais cette communication si immédiate en apparence n’est qu’une métamorphose de l’attente.</t>
         </is>
       </c>
-      <c r="G992" t="inlineStr"/>
     </row>
     <row r="993">
       <c r="A993" s="2" t="inlineStr">
@@ -32157,7 +32156,6 @@
           <t>En 1960, des chercheurs annonçaient la fin du monde pour le 13 novembre 2026, sous l’effet d’une croissance démographique incontrôlée. Retour sur une prédiction qui mêlait science rigoureuse et art de la mise en scène.</t>
         </is>
       </c>
-      <c r="G993" t="inlineStr"/>
     </row>
     <row r="994">
       <c r="A994" s="2" t="inlineStr">
@@ -32190,7 +32188,6 @@
           <t>Les revendications des lycéens sur les moyens de l’éducation nationale sont récurrentes, mais le contexte global et la forme du mouvement –&amp;nbsp;né dans les banlieues populaires&amp;nbsp;– sont nouveaux, tout comme la réponse, d’abord policière, du gouvernement.</t>
         </is>
       </c>
-      <c r="G994" t="inlineStr"/>
     </row>
     <row r="995">
       <c r="A995" s="2" t="inlineStr">
@@ -32223,7 +32220,6 @@
           <t>Face à la Chine, l’UE transforme son marché en levier juridique&amp;nbsp;: salariés, subventions et travail forcé deviennent les nouveaux terrains de la confrontation.</t>
         </is>
       </c>
-      <c r="G995" t="inlineStr"/>
     </row>
     <row r="996">
       <c r="A996" s="2" t="inlineStr">
@@ -32256,7 +32252,6 @@
           <t>Trump peut-il concilier IA de pointe et réduction du déficit&amp;#160;? L’article Aux États-Unis, l’IA creuse le déficit commercial est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G996" t="inlineStr"/>
     </row>
     <row r="997">
       <c r="A997" s="2" t="inlineStr">
@@ -32289,7 +32284,6 @@
           <t>La hausse des exportations de brut n’est toutefois pas nécessairement une bonne nouvelle pour Moscou L’article Économie russe&amp;#160;: les recettes tirées des exportations de pétrole brut atteignent leur niveau le plus élevé depuis 2022 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G997" t="inlineStr"/>
     </row>
     <row r="998">
       <c r="A998" s="2" t="inlineStr">
@@ -32322,7 +32316,6 @@
           <t>De Montesquieu à Madison, le coup de force contre la presse marque une rupture historique aux États-Unis L’article Trump veut vassaliser la presse américaine est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G998" t="inlineStr"/>
     </row>
     <row r="999">
       <c r="A999" s="2" t="inlineStr">
@@ -32355,7 +32348,6 @@
           <t>Les flux pétroliers en provenance du Moyen-Orient sont presque revenus à leur niveau d’avant-guerre L’article L’Iran exerce-t-il toujours un contrôle sur le détroit d’Ormuz&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G999" t="inlineStr"/>
     </row>
     <row r="1000">
       <c r="A1000" s="2" t="inlineStr">
@@ -32388,7 +32380,336 @@
           <t>Nous avons interrogé les cinq candidats. Voici leurs réponses L’article Quelle géopolitique pour la primaire socialiste&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1000" t="inlineStr"/>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:05</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:56</t>
+        </is>
+      </c>
+      <c r="D1001" s="3" t="inlineStr">
+        <is>
+          <t>De la grossesse à l’accouchement, les pères s’impliquaient déjà dans la naissance des enfants aux XVIIIᵉ et XIXᵉ siècles</t>
+        </is>
+      </c>
+      <c r="E1001" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/de-la-grossesse-a-laccouchement-les-peres-simpliquaient-deja-dans-la-naissance-des-enfants-aux-xviii-et-xix-siecles-291741</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>S’engager précocement dans l’arrivée d’un enfant n’est ni une invention récente ni une spécificité féminine. C’est ce que révèlent les dernières recherches sur l’histoire de la paternité.</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr"/>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:05</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:56</t>
+        </is>
+      </c>
+      <c r="D1002" s="3" t="inlineStr">
+        <is>
+          <t>Quand le régime de Mussolini faisait espionner un opposant par son propre frère</t>
+        </is>
+      </c>
+      <c r="E1002" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/quand-le-regime-de-mussolini-faisait-espionner-un-opposant-par-son-propre-frere-292259</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>Peintre et photographe italien exilé à Paris, Attilio&amp;nbsp;De&amp;nbsp;Feo a été espionné, des années durant, par son frère et son neveu, qu’il hébergeait.</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr"/>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:05</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:44</t>
+        </is>
+      </c>
+      <c r="D1003" s="3" t="inlineStr">
+        <is>
+          <t>Guess who’s back ! Le Royaume-Uni va-t-il revenir au sein de l’Union européenne ?</t>
+        </is>
+      </c>
+      <c r="E1003" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/guess-whos-back-le-royaume-uni-va-t-il-revenir-au-sein-de-lunion-europeenne-293622</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>Andy Burnham veut rapprocher le Royaume-Uni de l’UE. Mais les obstacles politiques demeurent nombreux.</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr"/>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:05</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:44</t>
+        </is>
+      </c>
+      <c r="D1004" s="3" t="inlineStr">
+        <is>
+          <t>Le four tahitien, un laboratoire scientifique sous nos pieds</t>
+        </is>
+      </c>
+      <c r="E1004" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-four-tahitien-un-laboratoire-scientifique-sous-nos-pieds-292869</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>L’ahimā’a, four tahitien traditionnel, peut devenir un véritable objet de recherche, au carrefour des sciences, de l’environnement, de l’alimentation ou encore de la linguistique.</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr"/>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:05</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:56</t>
+        </is>
+      </c>
+      <c r="D1005" s="3" t="inlineStr">
+        <is>
+          <t>Le mouvement lycéen s’essouffle-t-il ?</t>
+        </is>
+      </c>
+      <c r="E1005" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/08/le-mouvement-lyceen-sessouffle-t-il/</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>375 lycées étaient perturbés jeudi à la mi-journée – contre 891 mardi L’article Le mouvement lycéen s’essouffle-t-il&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr"/>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:05</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:18</t>
+        </is>
+      </c>
+      <c r="D1006" s="3" t="inlineStr">
+        <is>
+          <t>Les centres de données vont-ils impacter les midterms ?</t>
+        </is>
+      </c>
+      <c r="E1006" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/08/les-centres-de-donnees-vont-ils-impacter-les-midterms/</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>Les trois quarts des Américains craignent que l’IA ne mette en péril la survie de l’humanité L’article Les centres de données vont-ils impacter les midterms&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr"/>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:05</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:00</t>
+        </is>
+      </c>
+      <c r="D1007" s="3" t="inlineStr">
+        <is>
+          <t>La défense européenne face au complexe bureaucratique-industriel national</t>
+        </is>
+      </c>
+      <c r="E1007" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/08/la-defense-europeenne-face-au-complexe-bureaucratique-industriel-national/</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>Le réarmement du continent bute sur un verrou qui nous empêche de transformer nos dépenses en puissance L’article La défense européenne face au complexe bureaucratique-industriel national est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr"/>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:05</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:40</t>
+        </is>
+      </c>
+      <c r="D1008" s="3" t="inlineStr">
+        <is>
+          <t>Marco Rubio invente l’Occident de Trump</t>
+        </is>
+      </c>
+      <c r="E1008" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/08/marco-rubio-invente-loccident-de-trump/</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>La doctrine occidentaliste dans le discours d’Athènes du secrétaire d’État L’article Marco Rubio invente l’Occident de Trump est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr"/>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:05</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>2026-10-08 04:30</t>
+        </is>
+      </c>
+      <c r="D1009" s="3" t="inlineStr">
+        <is>
+          <t>Qui contrôle le détroit de Bab el-Mandeb ?</t>
+        </is>
+      </c>
+      <c r="E1009" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/08/qui-controle-le-detroit-de-bab-el-mandeb/</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>Les Houthis contestent des pertes de territoires annoncées par Aden L’article Qui contrôle le détroit de Bab el-Mandeb&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr"/>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:05</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>2026-10-07 16:57</t>
+        </is>
+      </c>
+      <c r="D1010" s="3" t="inlineStr">
+        <is>
+          <t>Après l’épreuve de la preuve</t>
+        </is>
+      </c>
+      <c r="E1010" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/07/apres-lepreuve-de-la-preuve/</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>De l’affaire Dreyfus à Gaza, enquête sur les pathologies contemporaines du débat public L’article Après l’épreuve de la preuve est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -33391,6 +33712,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E998" r:id="rId997"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E999" r:id="rId998"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1000" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1001" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1002" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1003" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1004" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1005" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1006" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1007" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1008" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1009" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1010" r:id="rId1009"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1010"/>
+  <dimension ref="A1:G1020"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -32412,7 +32412,6 @@
           <t>S’engager précocement dans l’arrivée d’un enfant n’est ni une invention récente ni une spécificité féminine. C’est ce que révèlent les dernières recherches sur l’histoire de la paternité.</t>
         </is>
       </c>
-      <c r="G1001" t="inlineStr"/>
     </row>
     <row r="1002">
       <c r="A1002" s="2" t="inlineStr">
@@ -32445,7 +32444,6 @@
           <t>Peintre et photographe italien exilé à Paris, Attilio&amp;nbsp;De&amp;nbsp;Feo a été espionné, des années durant, par son frère et son neveu, qu’il hébergeait.</t>
         </is>
       </c>
-      <c r="G1002" t="inlineStr"/>
     </row>
     <row r="1003">
       <c r="A1003" s="2" t="inlineStr">
@@ -32478,7 +32476,6 @@
           <t>Andy Burnham veut rapprocher le Royaume-Uni de l’UE. Mais les obstacles politiques demeurent nombreux.</t>
         </is>
       </c>
-      <c r="G1003" t="inlineStr"/>
     </row>
     <row r="1004">
       <c r="A1004" s="2" t="inlineStr">
@@ -32511,7 +32508,6 @@
           <t>L’ahimā’a, four tahitien traditionnel, peut devenir un véritable objet de recherche, au carrefour des sciences, de l’environnement, de l’alimentation ou encore de la linguistique.</t>
         </is>
       </c>
-      <c r="G1004" t="inlineStr"/>
     </row>
     <row r="1005">
       <c r="A1005" s="2" t="inlineStr">
@@ -32544,7 +32540,6 @@
           <t>375 lycées étaient perturbés jeudi à la mi-journée – contre 891 mardi L’article Le mouvement lycéen s’essouffle-t-il&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1005" t="inlineStr"/>
     </row>
     <row r="1006">
       <c r="A1006" s="2" t="inlineStr">
@@ -32577,7 +32572,6 @@
           <t>Les trois quarts des Américains craignent que l’IA ne mette en péril la survie de l’humanité L’article Les centres de données vont-ils impacter les midterms&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1006" t="inlineStr"/>
     </row>
     <row r="1007">
       <c r="A1007" s="2" t="inlineStr">
@@ -32610,7 +32604,6 @@
           <t>Le réarmement du continent bute sur un verrou qui nous empêche de transformer nos dépenses en puissance L’article La défense européenne face au complexe bureaucratique-industriel national est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1007" t="inlineStr"/>
     </row>
     <row r="1008">
       <c r="A1008" s="2" t="inlineStr">
@@ -32643,7 +32636,6 @@
           <t>La doctrine occidentaliste dans le discours d’Athènes du secrétaire d’État L’article Marco Rubio invente l’Occident de Trump est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1008" t="inlineStr"/>
     </row>
     <row r="1009">
       <c r="A1009" s="2" t="inlineStr">
@@ -32676,7 +32668,6 @@
           <t>Les Houthis contestent des pertes de territoires annoncées par Aden L’article Qui contrôle le détroit de Bab el-Mandeb&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1009" t="inlineStr"/>
     </row>
     <row r="1010">
       <c r="A1010" s="2" t="inlineStr">
@@ -32709,7 +32700,336 @@
           <t>De l’affaire Dreyfus à Gaza, enquête sur les pathologies contemporaines du débat public L’article Après l’épreuve de la preuve est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1010" t="inlineStr"/>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:47</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>2026-10-09 14:30</t>
+        </is>
+      </c>
+      <c r="D1011" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi les universités américaines remettent en question leur examen d’entrée historique</t>
+        </is>
+      </c>
+      <c r="E1011" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-les-universites-americaines-remettent-en-question-leur-examen-dentree-historique-294061</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>Créé en 1926, le SAT, examen standardisé d’admission dans les universités américaines, fête ses 100 ans. Longtemps incontournable, il est aujourd’hui remis en question en raison des inégalités sociales qu’il reflète.</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr"/>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:47</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>2026-10-09 14:30</t>
+        </is>
+      </c>
+      <c r="D1012" s="3" t="inlineStr">
+        <is>
+          <t>À quoi pourrait ressembler une journée à l’école en 2035 ?</t>
+        </is>
+      </c>
+      <c r="E1012" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/a-quoi-pourrait-ressembler-une-journee-a-lecole-en-2035-294062</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>À quoi ressemblera l’école en 2035 ? Intelligence artificielle, réalité virtuelle et projets collaboratifs pourraient bouleverser les méthodes d’apprentissage.</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr"/>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:47</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>2026-10-09 14:29</t>
+        </is>
+      </c>
+      <c r="D1013" s="3" t="inlineStr">
+        <is>
+          <t>Quel rôle le collège et le lycée jouent-ils dans la santé mentale des élèves ? Une étude australienne lève un coin du voile</t>
+        </is>
+      </c>
+      <c r="E1013" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/quel-role-le-college-et-le-lycee-jouent-ils-dans-la-sante-mentale-des-eleves-une-etude-australienne-leve-un-coin-du-voile-294060</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>Quel rôle joue l’école dans la santé mentale des adolescents ? Selon une étude australienne menée auprès de plus de 1 500 élèves, le sentiment d’appartenance à la communauté scolaire serait un facteur déterminant de leur bien-être psychologique.</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr"/>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:47</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>2026-10-09 14:29</t>
+        </is>
+      </c>
+      <c r="D1014" s="3" t="inlineStr">
+        <is>
+          <t>En Nouvelle-Zélande, la réforme de l’éducation risque-t-elle de creuser les écarts entre élèves ?</t>
+        </is>
+      </c>
+      <c r="E1014" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/en-nouvelle-zelande-la-reforme-de-leducation-risque-t-elle-de-creuser-les-ecarts-entre-eleves-293961</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>En Nouvelle-Zélande, une vaste réforme de l’éducation promet de relever le niveau scolaire. Mais alors que de plus en plus d’élèves quittent les classes ordinaires, elle risque d’accentuer les difficultés des plus vulnérables si leur accompagnement ne suit pas.</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr"/>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:47</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>2026-10-09 14:28</t>
+        </is>
+      </c>
+      <c r="D1015" s="3" t="inlineStr">
+        <is>
+          <t>L’Angleterre fait de l’inclusion une priorité scolaire, mais que signifie-t-elle vraiment ?</t>
+        </is>
+      </c>
+      <c r="E1015" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/langleterre-fait-de-linclusion-une-priorite-scolaire-mais-que-signifie-t-elle-vraiment-293959</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>Accueillir des élèves en situation de handicap dans une classe ordinaire ne suffit pas. Les recherches montrent que l’inclusion scolaire dépend aussi de leur capacité à participer pleinement à la vie de l’établissement et à s’y sentir à leur place.</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr"/>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:47</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:07</t>
+        </is>
+      </c>
+      <c r="D1016" s="3" t="inlineStr">
+        <is>
+          <t>Navi Pillay, prix Nobel de la paix 2026 : le droit international contre la loi du plus fort</t>
+        </is>
+      </c>
+      <c r="E1016" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/navi-pillay-prix-nobel-de-la-paix-2026-le-droit-international-contre-la-loi-du-plus-fort-294072</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>Navi Pillay, 85 ans, a derrière elle une vie de juriste nationale (dans l’Afrique du Sud de l’apartheid) et internationale de premier plan. Sa désignation est un choix fort du Comité Nobel, qui suscite déjà éloges et condamnations.</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr"/>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:47</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>2026-10-09 10:14</t>
+        </is>
+      </c>
+      <c r="D1017" s="3" t="inlineStr">
+        <is>
+          <t>La contribution de l’Europe à la croissance mondiale a été divisée par deux depuis 2022</t>
+        </is>
+      </c>
+      <c r="E1017" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/09/la-contribution-de-leurope-a-la-croissance-mondiale-a-ete-divisee-par-deux-depuis-2022/</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>L’Asie de l’Est et l’Amérique du Nord sont les principaux moteurs de la croissance mondiale L’article La contribution de l’Europe à la croissance mondiale a été divisée par deux depuis 2022 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr"/>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:47</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:07</t>
+        </is>
+      </c>
+      <c r="D1018" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi les élites russes ne se retournent-elles pas contre Poutine ?</t>
+        </is>
+      </c>
+      <c r="E1018" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/09/pourquoi-les-elites-russes-ne-se-retournent-elles-pas-contre-poutine/</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>Une enquête signée par l’une des analystes les plus subtiles de la Russie contemporaine L’article Pourquoi les élites russes ne se retournent-elles pas contre Poutine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr"/>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:47</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>2026-10-09 04:30</t>
+        </is>
+      </c>
+      <c r="D1019" s="3" t="inlineStr">
+        <is>
+          <t>La Méditerranée est une mer de plus en plus tropicale</t>
+        </is>
+      </c>
+      <c r="E1019" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/09/la-mediterranee-est-une-mer-de-plus-en-plus-tropicale/</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>Des orages ont fait pleuvoir l'équivalent de plusieurs mois en l'espace de quelques jours L’article La Méditerranée est une mer de plus en plus tropicale est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr"/>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:47</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>2026-10-08 18:21</t>
+        </is>
+      </c>
+      <c r="D1020" s="3" t="inlineStr">
+        <is>
+          <t>Communiqué – Lycées : ne pas faire des enseignants les gestionnaires de l’impuissance publique</t>
+        </is>
+      </c>
+      <c r="E1020" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/communique-lycees-ne-pas-faire-des-enseignants-les-gestionnaires-de-limpuissance-publique/</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>Face au mouvement social lycéen, le gouvernement a décidé la mise en place de temps de « temps de démocratie interne » au sein des établissements. Si la démarche témoigne d’une attention particulière au mouvement, la mise en place de ces temps de débats soulève de nombreuses difficultés. Organiser en quelques heures ou quelques jours [&amp;#8230;] L’article Communiqué &amp;#8211; Lycées : ne pas faire des enseignants les gestionnaires de l&amp;rsquo;impuissance publique est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -33722,6 +34042,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1008" r:id="rId1007"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1009" r:id="rId1008"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1010" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1011" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1012" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1013" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1014" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1015" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1016" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1017" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1018" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1019" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1020" r:id="rId1019"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1020"/>
+  <dimension ref="A1:G1024"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -32732,7 +32732,6 @@
           <t>Créé en 1926, le SAT, examen standardisé d’admission dans les universités américaines, fête ses 100 ans. Longtemps incontournable, il est aujourd’hui remis en question en raison des inégalités sociales qu’il reflète.</t>
         </is>
       </c>
-      <c r="G1011" t="inlineStr"/>
     </row>
     <row r="1012">
       <c r="A1012" s="2" t="inlineStr">
@@ -32765,7 +32764,6 @@
           <t>À quoi ressemblera l’école en 2035 ? Intelligence artificielle, réalité virtuelle et projets collaboratifs pourraient bouleverser les méthodes d’apprentissage.</t>
         </is>
       </c>
-      <c r="G1012" t="inlineStr"/>
     </row>
     <row r="1013">
       <c r="A1013" s="2" t="inlineStr">
@@ -32798,7 +32796,6 @@
           <t>Quel rôle joue l’école dans la santé mentale des adolescents ? Selon une étude australienne menée auprès de plus de 1 500 élèves, le sentiment d’appartenance à la communauté scolaire serait un facteur déterminant de leur bien-être psychologique.</t>
         </is>
       </c>
-      <c r="G1013" t="inlineStr"/>
     </row>
     <row r="1014">
       <c r="A1014" s="2" t="inlineStr">
@@ -32831,7 +32828,6 @@
           <t>En Nouvelle-Zélande, une vaste réforme de l’éducation promet de relever le niveau scolaire. Mais alors que de plus en plus d’élèves quittent les classes ordinaires, elle risque d’accentuer les difficultés des plus vulnérables si leur accompagnement ne suit pas.</t>
         </is>
       </c>
-      <c r="G1014" t="inlineStr"/>
     </row>
     <row r="1015">
       <c r="A1015" s="2" t="inlineStr">
@@ -32864,7 +32860,6 @@
           <t>Accueillir des élèves en situation de handicap dans une classe ordinaire ne suffit pas. Les recherches montrent que l’inclusion scolaire dépend aussi de leur capacité à participer pleinement à la vie de l’établissement et à s’y sentir à leur place.</t>
         </is>
       </c>
-      <c r="G1015" t="inlineStr"/>
     </row>
     <row r="1016">
       <c r="A1016" s="2" t="inlineStr">
@@ -32897,7 +32892,6 @@
           <t>Navi Pillay, 85 ans, a derrière elle une vie de juriste nationale (dans l’Afrique du Sud de l’apartheid) et internationale de premier plan. Sa désignation est un choix fort du Comité Nobel, qui suscite déjà éloges et condamnations.</t>
         </is>
       </c>
-      <c r="G1016" t="inlineStr"/>
     </row>
     <row r="1017">
       <c r="A1017" s="2" t="inlineStr">
@@ -32930,7 +32924,6 @@
           <t>L’Asie de l’Est et l’Amérique du Nord sont les principaux moteurs de la croissance mondiale L’article La contribution de l’Europe à la croissance mondiale a été divisée par deux depuis 2022 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1017" t="inlineStr"/>
     </row>
     <row r="1018">
       <c r="A1018" s="2" t="inlineStr">
@@ -32963,7 +32956,6 @@
           <t>Une enquête signée par l’une des analystes les plus subtiles de la Russie contemporaine L’article Pourquoi les élites russes ne se retournent-elles pas contre Poutine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1018" t="inlineStr"/>
     </row>
     <row r="1019">
       <c r="A1019" s="2" t="inlineStr">
@@ -32996,7 +32988,6 @@
           <t>Des orages ont fait pleuvoir l'équivalent de plusieurs mois en l'espace de quelques jours L’article La Méditerranée est une mer de plus en plus tropicale est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1019" t="inlineStr"/>
     </row>
     <row r="1020">
       <c r="A1020" s="2" t="inlineStr">
@@ -33029,7 +33020,138 @@
           <t>Face au mouvement social lycéen, le gouvernement a décidé la mise en place de temps de « temps de démocratie interne » au sein des établissements. Si la démarche témoigne d’une attention particulière au mouvement, la mise en place de ces temps de débats soulève de nombreuses difficultés. Organiser en quelques heures ou quelques jours [&amp;#8230;] L’article Communiqué &amp;#8211; Lycées : ne pas faire des enseignants les gestionnaires de l&amp;rsquo;impuissance publique est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G1020" t="inlineStr"/>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10 15:00</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>2026-10-10 08:53</t>
+        </is>
+      </c>
+      <c r="D1021" s="3" t="inlineStr">
+        <is>
+          <t>Ce que cache l’accord sur le diesel entre Trump et Poutine</t>
+        </is>
+      </c>
+      <c r="E1021" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/10/ce-que-cache-laccord-sur-le-diesel-entre-trump-et-poutine/</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>Sous couvert de faire baisser les prix à la pompe qui atteignent un record historique aux États-Unis, la Maison-Blanche offre un levier de plus au régime russe L’article Ce que cache l’accord sur le diesel entre Trump et Poutine est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr"/>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10 15:00</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>2026-10-10 07:31</t>
+        </is>
+      </c>
+      <c r="D1022" s="3" t="inlineStr">
+        <is>
+          <t>Xi Jinping et le problème du Ciel</t>
+        </is>
+      </c>
+      <c r="E1022" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/10/un-seul-ciel-pour-tous/</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>Une nouvelle lecture du tianxia et de l'empire universel. L’article Xi Jinping et le problème du Ciel est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr"/>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10 15:00</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>2026-10-10 04:30</t>
+        </is>
+      </c>
+      <c r="D1023" s="3" t="inlineStr">
+        <is>
+          <t>Les producteurs européens s’attendent à une chute de 25 % de la production de pommes de terre</t>
+        </is>
+      </c>
+      <c r="E1023" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/10/les-producteurs-europeens-sattendent-a-une-chute-de-25-de-la-production-de-pommes-de-terre/</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>Le réchauffement climatique fait peser la menace d’une friteflation L’article Les producteurs européens s’attendent à une chute de 25&amp;#160;% de la production de pommes de terre est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr"/>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10 15:00</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:00</t>
+        </is>
+      </c>
+      <c r="D1024" s="3" t="inlineStr">
+        <is>
+          <t>À l’approche de l’hiver, Poutine accélère sa guerre contre les infrastructures énergétiques ukrainiennes</t>
+        </is>
+      </c>
+      <c r="E1024" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/09/a-lapproche-de-lhiver-poutine-accelere-sa-guerre-contre-les-infrastructures-energetiques-ukrainiennes/</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>Pour faire plier l’Ukraine, Moscou veut plonger le pays dans le noir et le froid L’article À l’approche de l’hiver, Poutine accélère sa guerre contre les infrastructures énergétiques ukrainiennes est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -34052,6 +34174,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1018" r:id="rId1017"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1019" r:id="rId1018"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1020" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1021" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1022" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1023" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1024" r:id="rId1023"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1024"/>
+  <dimension ref="A1:G1029"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -33052,7 +33052,6 @@
           <t>Sous couvert de faire baisser les prix à la pompe qui atteignent un record historique aux États-Unis, la Maison-Blanche offre un levier de plus au régime russe L’article Ce que cache l’accord sur le diesel entre Trump et Poutine est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1021" t="inlineStr"/>
     </row>
     <row r="1022">
       <c r="A1022" s="2" t="inlineStr">
@@ -33085,7 +33084,6 @@
           <t>Une nouvelle lecture du tianxia et de l'empire universel. L’article Xi Jinping et le problème du Ciel est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1022" t="inlineStr"/>
     </row>
     <row r="1023">
       <c r="A1023" s="2" t="inlineStr">
@@ -33118,7 +33116,6 @@
           <t>Le réchauffement climatique fait peser la menace d’une friteflation L’article Les producteurs européens s’attendent à une chute de 25&amp;#160;% de la production de pommes de terre est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1023" t="inlineStr"/>
     </row>
     <row r="1024">
       <c r="A1024" s="2" t="inlineStr">
@@ -33151,7 +33148,171 @@
           <t>Pour faire plier l’Ukraine, Moscou veut plonger le pays dans le noir et le froid L’article À l’approche de l’hiver, Poutine accélère sa guerre contre les infrastructures énergétiques ukrainiennes est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1024" t="inlineStr"/>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11 15:18</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:51</t>
+        </is>
+      </c>
+      <c r="D1025" s="3" t="inlineStr">
+        <is>
+          <t>Près de 2,7 € de retombées économiques pour chaque euro investi : les universités, moteurs de croissance des territoires</t>
+        </is>
+      </c>
+      <c r="E1025" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pres-de-2-7-de-retombees-economiques-pour-chaque-euro-investi-les-universites-moteurs-de-croissance-des-territoires-293061</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>Si les dépenses des universités ont des effets économiques directs sur les territoires, des travaux montrent combien la formation et la recherche jouent aussi sur leur compétitivité.</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr"/>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11 15:18</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:52</t>
+        </is>
+      </c>
+      <c r="D1026" s="3" t="inlineStr">
+        <is>
+          <t>Trump peut-il acheter les midterms ?</t>
+        </is>
+      </c>
+      <c r="E1026" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/trump-peut-il-acheter-les-midterms-293621</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>Donald Trump l’a promis&amp;nbsp;: si les républicains gagnent les midterms, chaque citoyen adulte recevra 5&amp;nbsp;000&amp;nbsp;dollars. Une promesse risquée à bien des égards.</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr"/>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11 15:18</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>2026-10-11 10:30</t>
+        </is>
+      </c>
+      <c r="D1027" s="3" t="inlineStr">
+        <is>
+          <t>Le Zhejiang, laboratoire de Xi Jinping</t>
+        </is>
+      </c>
+      <c r="E1027" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/11/le-zhejiang-laboratoire-de-xi-jinping/</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>Ce que la province raconte du projet du Parti communiste pour la Chine L’article Le Zhejiang, laboratoire de Xi Jinping est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1027" t="inlineStr"/>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11 15:18</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>2026-10-11 08:31</t>
+        </is>
+      </c>
+      <c r="D1028" s="3" t="inlineStr">
+        <is>
+          <t>La nouvelle lutte des classes sera une lutte des générations</t>
+        </is>
+      </c>
+      <c r="E1028" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/11/la-nouvelle-lutte-des-classes-sera-une-lutte-des-generations/</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>Pour Pierre Rosanvallon, un conflit silencieux autour du temps et de l’avenir est en train de bouleverser la politique L’article La nouvelle lutte des classes sera une lutte des générations est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr"/>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11 15:18</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>2026-10-11 04:30</t>
+        </is>
+      </c>
+      <c r="D1029" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : une entreprise du pays sur trois est déficitaire</t>
+        </is>
+      </c>
+      <c r="E1029" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/11/economie-russe-une-entreprise-du-pays-sur-trois-est-deficitaire/</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>Le nombre de secteurs d’activité non rentables a été multiplié par 4 en un an L’article Économie russe&amp;#160;: une entreprise du pays sur trois est déficitaire est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -34178,6 +34339,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1022" r:id="rId1021"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1023" r:id="rId1022"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1024" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1025" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1026" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1027" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1028" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1029" r:id="rId1028"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1029"/>
+  <dimension ref="A1:G1035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -33180,7 +33180,6 @@
           <t>Si les dépenses des universités ont des effets économiques directs sur les territoires, des travaux montrent combien la formation et la recherche jouent aussi sur leur compétitivité.</t>
         </is>
       </c>
-      <c r="G1025" t="inlineStr"/>
     </row>
     <row r="1026">
       <c r="A1026" s="2" t="inlineStr">
@@ -33213,7 +33212,6 @@
           <t>Donald Trump l’a promis&amp;nbsp;: si les républicains gagnent les midterms, chaque citoyen adulte recevra 5&amp;nbsp;000&amp;nbsp;dollars. Une promesse risquée à bien des égards.</t>
         </is>
       </c>
-      <c r="G1026" t="inlineStr"/>
     </row>
     <row r="1027">
       <c r="A1027" s="2" t="inlineStr">
@@ -33246,7 +33244,6 @@
           <t>Ce que la province raconte du projet du Parti communiste pour la Chine L’article Le Zhejiang, laboratoire de Xi Jinping est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1027" t="inlineStr"/>
     </row>
     <row r="1028">
       <c r="A1028" s="2" t="inlineStr">
@@ -33279,7 +33276,6 @@
           <t>Pour Pierre Rosanvallon, un conflit silencieux autour du temps et de l’avenir est en train de bouleverser la politique L’article La nouvelle lutte des classes sera une lutte des générations est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1028" t="inlineStr"/>
     </row>
     <row r="1029">
       <c r="A1029" s="2" t="inlineStr">
@@ -33312,7 +33308,204 @@
           <t>Le nombre de secteurs d’activité non rentables a été multiplié par 4 en un an L’article Économie russe&amp;#160;: une entreprise du pays sur trois est déficitaire est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1029" t="inlineStr"/>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 18:32</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:05</t>
+        </is>
+      </c>
+      <c r="D1030" s="3" t="inlineStr">
+        <is>
+          <t>« Vous pouvez nous prendre le téléphone, mais pas la parole » : le mouvement lycéen et le sentiment de ne pas être écouté</t>
+        </is>
+      </c>
+      <c r="E1030" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/vous-pouvez-nous-prendre-le-telephone-mais-pas-la-parole-le-mouvement-lyceen-et-le-sentiment-de-ne-pas-etre-ecoute-294157</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>Les lycéens français se plaignent de ne pas être entendus par les institutions. Un sentiment qui s’exprime très fortement dans la mobilisation actuelle et se nourrit des déceptions face à Parcoursup.</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr"/>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 18:32</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:54</t>
+        </is>
+      </c>
+      <c r="D1031" s="3" t="inlineStr">
+        <is>
+          <t>Exilés en Géorgie, les artistes russes anti-guerre doivent réinventer leur art et leur engagement</t>
+        </is>
+      </c>
+      <c r="E1031" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/exiles-en-georgie-les-artistes-russes-anti-guerre-doivent-reinventer-leur-art-et-leur-engagement-293232</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>Les artistes russes exilés en Géorgie y ont trouvé un espace de liberté et de création. Pour autant, leur intégration dans le pays d’accueil a été, au mieux, partielle.</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr"/>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 18:32</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>2026-10-12 17:06</t>
+        </is>
+      </c>
+      <c r="D1032" s="3" t="inlineStr">
+        <is>
+          <t>Quelle heure est-il sur la Lune ?</t>
+        </is>
+      </c>
+      <c r="E1032" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/12/quelle-heure-est-il-sur-la-lune/</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>Près de 70 pays se réunissent à Versailles pour répondre à la question L’article Quelle heure est-il sur la Lune&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr"/>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 18:32</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:47</t>
+        </is>
+      </c>
+      <c r="D1033" s="3" t="inlineStr">
+        <is>
+          <t>Les frappes ukrainiennes sur des centres de données de Yandex ont-elles affaibli les fermes à trolls russes ?</t>
+        </is>
+      </c>
+      <c r="E1033" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/12/les-frappes-ukrainiennes-sur-des-centres-de-donnees-de-yandex-ont-elles-affaibli-les-fermes-a-trolls-russes/</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>Les conséquences de ces attaques pourraient être durables L’article Les frappes ukrainiennes sur des centres de données de Yandex ont-elles affaibli les fermes à trolls russes&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr"/>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 18:32</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:18</t>
+        </is>
+      </c>
+      <c r="D1034" s="3" t="inlineStr">
+        <is>
+          <t>La tentative de Trump de promouvoir la « super intelligence » peine à convaincre</t>
+        </is>
+      </c>
+      <c r="E1034" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/12/la-tentative-de-trump-de-promouvoir-la-super-intelligence-peine-a-convaincre/</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>Seulement 1 dirigeant sur 5 a pleinement adopté le terme de «&amp;#160;super intelligence&amp;#160;» L’article La tentative de Trump de promouvoir la «&amp;#160;super intelligence&amp;#160;» peine à convaincre est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr"/>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 18:32</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>2026-10-12 04:00</t>
+        </is>
+      </c>
+      <c r="D1035" s="3" t="inlineStr">
+        <is>
+          <t>Trump et Xi Jinping ne sont pas en train de faire la paix</t>
+        </is>
+      </c>
+      <c r="E1035" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/12/xi-et-trump-dans-loeil-du-cyclone/</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>La réalité géoéconomique derrière les sourires de Washington L’article Trump et Xi Jinping ne sont pas en train de faire la paix est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -34344,6 +34537,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1027" r:id="rId1026"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1028" r:id="rId1027"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1029" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1030" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1031" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1032" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1033" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1034" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1035" r:id="rId1034"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1035"/>
+  <dimension ref="A1:G1046"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -33340,7 +33340,6 @@
           <t>Les lycéens français se plaignent de ne pas être entendus par les institutions. Un sentiment qui s’exprime très fortement dans la mobilisation actuelle et se nourrit des déceptions face à Parcoursup.</t>
         </is>
       </c>
-      <c r="G1030" t="inlineStr"/>
     </row>
     <row r="1031">
       <c r="A1031" s="2" t="inlineStr">
@@ -33373,7 +33372,6 @@
           <t>Les artistes russes exilés en Géorgie y ont trouvé un espace de liberté et de création. Pour autant, leur intégration dans le pays d’accueil a été, au mieux, partielle.</t>
         </is>
       </c>
-      <c r="G1031" t="inlineStr"/>
     </row>
     <row r="1032">
       <c r="A1032" s="2" t="inlineStr">
@@ -33406,7 +33404,6 @@
           <t>Près de 70 pays se réunissent à Versailles pour répondre à la question L’article Quelle heure est-il sur la Lune&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1032" t="inlineStr"/>
     </row>
     <row r="1033">
       <c r="A1033" s="2" t="inlineStr">
@@ -33439,7 +33436,6 @@
           <t>Les conséquences de ces attaques pourraient être durables L’article Les frappes ukrainiennes sur des centres de données de Yandex ont-elles affaibli les fermes à trolls russes&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1033" t="inlineStr"/>
     </row>
     <row r="1034">
       <c r="A1034" s="2" t="inlineStr">
@@ -33472,7 +33468,6 @@
           <t>Seulement 1 dirigeant sur 5 a pleinement adopté le terme de «&amp;#160;super intelligence&amp;#160;» L’article La tentative de Trump de promouvoir la «&amp;#160;super intelligence&amp;#160;» peine à convaincre est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1034" t="inlineStr"/>
     </row>
     <row r="1035">
       <c r="A1035" s="2" t="inlineStr">
@@ -33505,7 +33500,369 @@
           <t>La réalité géoéconomique derrière les sourires de Washington L’article Trump et Xi Jinping ne sont pas en train de faire la paix est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1035" t="inlineStr"/>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:41</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:59</t>
+        </is>
+      </c>
+      <c r="D1036" s="3" t="inlineStr">
+        <is>
+          <t>Au château de Chambord, cinq siècles de plaisirs gastronomiques</t>
+        </is>
+      </c>
+      <c r="E1036" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/au-chateau-de-chambord-cinq-siecles-de-plaisirs-gastronomiques-293857</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>Pour retracer l’histoire gourmande du château de Chambord, célébrée dans une exposition, l’historien de la gastronomie doit tenter de démêler le vrai du faux et enquêter pour pallier les lacunes des archives.</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr"/>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:41</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:12</t>
+        </is>
+      </c>
+      <c r="D1037" s="3" t="inlineStr">
+        <is>
+          <t>Les secondes intercalaires synchronisent nos horloges avec la rotation de la Terre depuis des décennies, mais elles pourraient disparaître</t>
+        </is>
+      </c>
+      <c r="E1037" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-secondes-intercalaires-synchronisent-nos-horloges-avec-la-rotation-de-la-terre-depuis-des-decennies-mais-elles-pourraient-disparaitre-294266</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>Les secondes intercalaires maintiennent nos horloges en phase avec la rotation de la Terre, mais perturbent les systèmes informatiques. Leur suppression est à l’étude, avec un changement presque imperceptible au quotidien.</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr"/>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:41</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:02</t>
+        </is>
+      </c>
+      <c r="D1038" s="3" t="inlineStr">
+        <is>
+          <t>Sciences ou entrepreneuriat ? Comment les témoignages vidéo de professionnels influencent les choix d’orientation des jeunes</t>
+        </is>
+      </c>
+      <c r="E1038" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/sciences-ou-entrepreneuriat-comment-les-temoignages-video-de-professionnels-influencent-les-choix-dorientation-des-jeunes-289005</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>Les témoignages de professionnels et la rencontre avec des «&amp;nbsp;role models&amp;nbsp;» influencent les choix d’orientation des jeunes, mais pas toujours dans le sens attendu.</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr"/>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:41</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:06</t>
+        </is>
+      </c>
+      <c r="D1039" s="3" t="inlineStr">
+        <is>
+          <t>Santé mondiale : Le multilatéralisme est en crise, mais peut-on vraiment s’en passer ?</t>
+        </is>
+      </c>
+      <c r="E1039" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/sante-mondiale-le-multilateralisme-est-en-crise-mais-peut-on-vraiment-sen-passer-294064</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>Le multilatéralisme est actuellement en crise. S’il est tentant de le remplacer par des accords de coopération impliquant un nombre de participants plus restreint, cette approche n’est pas toujours la bonne.</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr"/>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:41</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:04</t>
+        </is>
+      </c>
+      <c r="D1040" s="3" t="inlineStr">
+        <is>
+          <t>Une chasse à l’homme contraire au droit et très lucrative pour Trump et ses amis</t>
+        </is>
+      </c>
+      <c r="E1040" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/une-chasse-a-lhomme-contraire-au-droit-et-tres-lucrative-pour-trump-et-ses-amis-294131</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>Derrière les opérations musclées et souvent illégales de l’ICE, il y a des entreprises proches de Donald Trump, spécialisées dans la détention et la surveillance, qui obtiennent de juteux contrats.</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr"/>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:41</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:03</t>
+        </is>
+      </c>
+      <c r="D1041" s="3" t="inlineStr">
+        <is>
+          <t>Europe, Chine, États-Unis : trois manières différentes de réguler l’IA</t>
+        </is>
+      </c>
+      <c r="E1041" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/europe-chine-etats-unis-trois-manieres-differentes-de-reguler-lia-293160</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>En ce qui concerne l’IA, Union européenne, États-Unis et Chine combinent régulation, innovation et politique industrielle. Leurs différences tiennent surtout aux institutions et aux outils mobilisés.</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr"/>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:41</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:13</t>
+        </is>
+      </c>
+      <c r="D1042" s="3" t="inlineStr">
+        <is>
+          <t>La langue française à l’ère de l’automatisation intégrale</t>
+        </is>
+      </c>
+      <c r="E1042" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/13/la-langue-francaise-a-lere-de-lautomatisation-integrale/</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>Le français à l’ère de l’automatisation intégrale L’article La langue française à l’ère de l’automatisation intégrale est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr"/>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:41</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:24</t>
+        </is>
+      </c>
+      <c r="D1043" s="3" t="inlineStr">
+        <is>
+          <t>Que comprend le plan de paix en quatre points que les États-Unis promeuvent pour l’Ukraine ?</t>
+        </is>
+      </c>
+      <c r="E1043" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/13/que-comprend-le-plan-de-paix-en-quatre-points-que-les-etats-unis-promeuvent-pour-lukraine/</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>Kiev a qualifié l’initiative de «&amp;#160;coup de pub plutôt réussi&amp;#160;» L’article Que comprend le plan de paix en quatre points que les États-Unis promeuvent pour l’Ukraine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr"/>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:41</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:30</t>
+        </is>
+      </c>
+      <c r="D1044" s="3" t="inlineStr">
+        <is>
+          <t>L’IA fait changer d’échelle les menaces cyber</t>
+        </is>
+      </c>
+      <c r="E1044" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/13/lia-fait-changer-dechelle-les-menaces-cyber/</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>Il faut moins de 30 minutes aux cybercriminels pour se propager au sein d’un réseau compromis L’article L’IA fait changer d’échelle les menaces cyber est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr"/>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:41</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>2026-10-13 04:30</t>
+        </is>
+      </c>
+      <c r="D1045" s="3" t="inlineStr">
+        <is>
+          <t>Au rythme actuel, la France deviendrait le pays le plus endetté de l’Union au cours des années 2030</t>
+        </is>
+      </c>
+      <c r="E1045" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/13/au-rythme-actuel-la-france-deviendrait-le-pays-le-plus-endette-de-lunion-au-cours-des-annees-2030/</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>Le pays pourrait ainsi dépasser l’Italie d’ici sept ans L’article Au rythme actuel, la France deviendrait le pays le plus endetté de l’Union au cours des années 2030 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr"/>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:41</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>2026-10-13 04:00</t>
+        </is>
+      </c>
+      <c r="D1046" s="3" t="inlineStr">
+        <is>
+          <t>Et si, au fond, dans la tête de Poutine il n’y avait rien ?</t>
+        </is>
+      </c>
+      <c r="E1046" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/13/et-si-au-fond-dans-la-tete-de-poutine-il-ny-avait-rien/</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>Une enquête sur les mystères qui font tenir le récit du Kremlin L’article Et si, au fond, dans la tête de Poutine il n’y avait rien&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -34543,6 +34900,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1033" r:id="rId1032"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1034" r:id="rId1033"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1035" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1036" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1037" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1038" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1039" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1040" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1041" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1042" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1043" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1044" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1045" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1046" r:id="rId1045"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1046"/>
+  <dimension ref="A1:G1053"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -33532,7 +33532,6 @@
           <t>Pour retracer l’histoire gourmande du château de Chambord, célébrée dans une exposition, l’historien de la gastronomie doit tenter de démêler le vrai du faux et enquêter pour pallier les lacunes des archives.</t>
         </is>
       </c>
-      <c r="G1036" t="inlineStr"/>
     </row>
     <row r="1037">
       <c r="A1037" s="2" t="inlineStr">
@@ -33565,7 +33564,6 @@
           <t>Les secondes intercalaires maintiennent nos horloges en phase avec la rotation de la Terre, mais perturbent les systèmes informatiques. Leur suppression est à l’étude, avec un changement presque imperceptible au quotidien.</t>
         </is>
       </c>
-      <c r="G1037" t="inlineStr"/>
     </row>
     <row r="1038">
       <c r="A1038" s="2" t="inlineStr">
@@ -33598,7 +33596,6 @@
           <t>Les témoignages de professionnels et la rencontre avec des «&amp;nbsp;role models&amp;nbsp;» influencent les choix d’orientation des jeunes, mais pas toujours dans le sens attendu.</t>
         </is>
       </c>
-      <c r="G1038" t="inlineStr"/>
     </row>
     <row r="1039">
       <c r="A1039" s="2" t="inlineStr">
@@ -33631,7 +33628,6 @@
           <t>Le multilatéralisme est actuellement en crise. S’il est tentant de le remplacer par des accords de coopération impliquant un nombre de participants plus restreint, cette approche n’est pas toujours la bonne.</t>
         </is>
       </c>
-      <c r="G1039" t="inlineStr"/>
     </row>
     <row r="1040">
       <c r="A1040" s="2" t="inlineStr">
@@ -33664,7 +33660,6 @@
           <t>Derrière les opérations musclées et souvent illégales de l’ICE, il y a des entreprises proches de Donald Trump, spécialisées dans la détention et la surveillance, qui obtiennent de juteux contrats.</t>
         </is>
       </c>
-      <c r="G1040" t="inlineStr"/>
     </row>
     <row r="1041">
       <c r="A1041" s="2" t="inlineStr">
@@ -33697,7 +33692,6 @@
           <t>En ce qui concerne l’IA, Union européenne, États-Unis et Chine combinent régulation, innovation et politique industrielle. Leurs différences tiennent surtout aux institutions et aux outils mobilisés.</t>
         </is>
       </c>
-      <c r="G1041" t="inlineStr"/>
     </row>
     <row r="1042">
       <c r="A1042" s="2" t="inlineStr">
@@ -33730,7 +33724,6 @@
           <t>Le français à l’ère de l’automatisation intégrale L’article La langue française à l’ère de l’automatisation intégrale est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1042" t="inlineStr"/>
     </row>
     <row r="1043">
       <c r="A1043" s="2" t="inlineStr">
@@ -33763,7 +33756,6 @@
           <t>Kiev a qualifié l’initiative de «&amp;#160;coup de pub plutôt réussi&amp;#160;» L’article Que comprend le plan de paix en quatre points que les États-Unis promeuvent pour l’Ukraine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1043" t="inlineStr"/>
     </row>
     <row r="1044">
       <c r="A1044" s="2" t="inlineStr">
@@ -33796,7 +33788,6 @@
           <t>Il faut moins de 30 minutes aux cybercriminels pour se propager au sein d’un réseau compromis L’article L’IA fait changer d’échelle les menaces cyber est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1044" t="inlineStr"/>
     </row>
     <row r="1045">
       <c r="A1045" s="2" t="inlineStr">
@@ -33829,7 +33820,6 @@
           <t>Le pays pourrait ainsi dépasser l’Italie d’ici sept ans L’article Au rythme actuel, la France deviendrait le pays le plus endetté de l’Union au cours des années 2030 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1045" t="inlineStr"/>
     </row>
     <row r="1046">
       <c r="A1046" s="2" t="inlineStr">
@@ -33862,7 +33852,237 @@
           <t>Une enquête sur les mystères qui font tenir le récit du Kremlin L’article Et si, au fond, dans la tête de Poutine il n’y avait rien&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1046" t="inlineStr"/>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:18</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:21</t>
+        </is>
+      </c>
+      <c r="D1047" s="3" t="inlineStr">
+        <is>
+          <t>À Vendeuvre-du-Poitou, les féconds étés de Michel Foucault</t>
+        </is>
+      </c>
+      <c r="E1047" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/a-vendeuvre-du-poitou-les-feconds-etes-de-michel-foucault-293858</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>La propriété familiale du «&amp;nbsp;Piroir&amp;nbsp;», dans le Poitou, fut un refuge important pour Michel&amp;nbsp;Foucault. Il y a travaillé et retravaillé ses textes les plus importants.</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr"/>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:18</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:19</t>
+        </is>
+      </c>
+      <c r="D1048" s="3" t="inlineStr">
+        <is>
+          <t>Santé mentale des adolescents et mobilisations lycéennes, des causes communes ?</t>
+        </is>
+      </c>
+      <c r="E1048" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/sante-mentale-des-adolescents-et-mobilisations-lyceennes-des-causes-communes-294221</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>À l’heure des mobilisations lycéennes, des données permettent de mettre en regard la dégradation de la santé mentale des jeunes et des conditions de leur scolarité (pression, impact de Parcoursup…).</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr"/>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:18</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:19</t>
+        </is>
+      </c>
+      <c r="D1049" s="3" t="inlineStr">
+        <is>
+          <t>Face à Donald Trump et Peter Thiel, la contre-offensive des jésuites américains aux côtés de Léon XIV</t>
+        </is>
+      </c>
+      <c r="E1049" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/face-a-donald-trump-et-peter-thiel-la-contre-offensive-des-jesuites-americains-aux-cotes-de-leon-xiv-293750</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>Les jésuites américains relaient l’encyclique de Léon XIV et combattent l’influence de Peter Thiel, défendant migrants, démocratie et régulation technologique.</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr"/>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:18</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:04</t>
+        </is>
+      </c>
+      <c r="D1050" s="3" t="inlineStr">
+        <is>
+          <t>ICE : une chasse à l’homme contraire au droit et très lucrative pour Trump et ses amis</t>
+        </is>
+      </c>
+      <c r="E1050" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/ice-une-chasse-a-lhomme-contraire-au-droit-et-tres-lucrative-pour-trump-et-ses-amis-294131</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>Derrière les opérations musclées et souvent illégales de l’ICE, il y a des entreprises proches de Donald Trump, spécialisées dans la détention et la surveillance, qui obtiennent de juteux contrats.</t>
+        </is>
+      </c>
+      <c r="G1050" t="inlineStr"/>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:18</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:06</t>
+        </is>
+      </c>
+      <c r="D1051" s="3" t="inlineStr">
+        <is>
+          <t>La vassalisation cognitive est une menace existentielle</t>
+        </is>
+      </c>
+      <c r="E1051" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/14/la-vassalisation-cognitive-est-menace-existentielle/</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>En abandonnant l’intelligence artificielle aux géants américains, nous sommes en train de perdre le contrôle de notre cerveau L’article La vassalisation cognitive est une menace existentielle est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1051" t="inlineStr"/>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:18</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:33</t>
+        </is>
+      </c>
+      <c r="D1052" s="3" t="inlineStr">
+        <is>
+          <t>L’Ukraine peut-elle encore compter sur Starlink ?</t>
+        </is>
+      </c>
+      <c r="E1052" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/14/lukraine-peut-elle-encore-compter-sur-starlink/</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>Elon Musk a imposé des limites à l’armée ukrainienne L’article L’Ukraine peut-elle encore compter sur Starlink&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr"/>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:18</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:30</t>
+        </is>
+      </c>
+      <c r="D1053" s="3" t="inlineStr">
+        <is>
+          <t>Le siège houthiste de Taïz menace le gouvernement yéménite</t>
+        </is>
+      </c>
+      <c r="E1053" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/14/le-siege-houthiste-de-taiz-menace-le-gouvernement-yemenite/</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>La chute de la ville pourrait ouvrir la voie à une marche vers Aden L’article Le siège houthiste de Taïz menace le gouvernement yéménite est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -34911,6 +35131,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1044" r:id="rId1043"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1045" r:id="rId1044"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1046" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1047" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1048" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1049" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1050" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1051" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1052" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1053" r:id="rId1052"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1053"/>
+  <dimension ref="A1:G1058"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -33884,7 +33884,6 @@
           <t>La propriété familiale du «&amp;nbsp;Piroir&amp;nbsp;», dans le Poitou, fut un refuge important pour Michel&amp;nbsp;Foucault. Il y a travaillé et retravaillé ses textes les plus importants.</t>
         </is>
       </c>
-      <c r="G1047" t="inlineStr"/>
     </row>
     <row r="1048">
       <c r="A1048" s="2" t="inlineStr">
@@ -33917,7 +33916,6 @@
           <t>À l’heure des mobilisations lycéennes, des données permettent de mettre en regard la dégradation de la santé mentale des jeunes et des conditions de leur scolarité (pression, impact de Parcoursup…).</t>
         </is>
       </c>
-      <c r="G1048" t="inlineStr"/>
     </row>
     <row r="1049">
       <c r="A1049" s="2" t="inlineStr">
@@ -33950,7 +33948,6 @@
           <t>Les jésuites américains relaient l’encyclique de Léon XIV et combattent l’influence de Peter Thiel, défendant migrants, démocratie et régulation technologique.</t>
         </is>
       </c>
-      <c r="G1049" t="inlineStr"/>
     </row>
     <row r="1050">
       <c r="A1050" s="2" t="inlineStr">
@@ -33983,7 +33980,6 @@
           <t>Derrière les opérations musclées et souvent illégales de l’ICE, il y a des entreprises proches de Donald Trump, spécialisées dans la détention et la surveillance, qui obtiennent de juteux contrats.</t>
         </is>
       </c>
-      <c r="G1050" t="inlineStr"/>
     </row>
     <row r="1051">
       <c r="A1051" s="2" t="inlineStr">
@@ -34016,7 +34012,6 @@
           <t>En abandonnant l’intelligence artificielle aux géants américains, nous sommes en train de perdre le contrôle de notre cerveau L’article La vassalisation cognitive est une menace existentielle est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1051" t="inlineStr"/>
     </row>
     <row r="1052">
       <c r="A1052" s="2" t="inlineStr">
@@ -34049,7 +34044,6 @@
           <t>Elon Musk a imposé des limites à l’armée ukrainienne L’article L’Ukraine peut-elle encore compter sur Starlink&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1052" t="inlineStr"/>
     </row>
     <row r="1053">
       <c r="A1053" s="2" t="inlineStr">
@@ -34082,7 +34076,171 @@
           <t>La chute de la ville pourrait ouvrir la voie à une marche vers Aden L’article Le siège houthiste de Taïz menace le gouvernement yéménite est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1053" t="inlineStr"/>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:53</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:15</t>
+        </is>
+      </c>
+      <c r="D1054" s="3" t="inlineStr">
+        <is>
+          <t>En Russie, les deux tiers des écoles participent à la propagande de guerre</t>
+        </is>
+      </c>
+      <c r="E1054" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/15/en-russie-les-deux-tiers-des-ecoles-participent-a-la-propagande-de-guerre/</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>Les enfants de 9 à 14 ans sont la cible principale L’article En Russie, les deux tiers des écoles participent à la propagande de guerre est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr"/>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:53</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>2026-10-15 11:51</t>
+        </is>
+      </c>
+      <c r="D1055" s="3" t="inlineStr">
+        <is>
+          <t>Poutine a-t-il trouvé une nouvelle majorité en Allemagne ?</t>
+        </is>
+      </c>
+      <c r="E1055" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/15/poutine-a-t-il-trouve-une-nouvelle-majorite-en-allemagne/</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>En Saxe-Anhalt, l’extrême droite de l’AfD et la gauche national-populiste allemandes s’unissent contre l’Ukraine L’article Poutine a-t-il trouvé une nouvelle majorité en Allemagne&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr"/>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:53</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:30</t>
+        </is>
+      </c>
+      <c r="D1056" s="3" t="inlineStr">
+        <is>
+          <t>Dans 98 % des pays, les dirigeants sont plus âgés que la population</t>
+        </is>
+      </c>
+      <c r="E1056" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/15/dans-98-des-pays-les-dirigeants-sont-plus-ages-que-la-population/</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>Seuls les Pays-Bas, la Lituanie et le Monténégro font exception à la règle L’article Dans 98&amp;#160;% des pays, les dirigeants sont plus âgés que la population est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr"/>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:53</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:00</t>
+        </is>
+      </c>
+      <c r="D1057" s="3" t="inlineStr">
+        <is>
+          <t>L’IA a gagné les marchés, mais elle est en train de perdre l’opinion mondiale</t>
+        </is>
+      </c>
+      <c r="E1057" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/15/intelligence-artificielle-inverser-lerosion-de-la-confiance/</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>Un sondage sondage exclusif sur le grand retournement contre l’IA L’article L&amp;rsquo;IA a gagné les marchés, mais elle est en train de perdre l&amp;rsquo;opinion mondiale est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr"/>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:53</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>2026-10-14 16:16</t>
+        </is>
+      </c>
+      <c r="D1058" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi Pékin purge l’influent ancien maire de Chongqing, Huang Qifan ?</t>
+        </is>
+      </c>
+      <c r="E1058" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/14/pourquoi-pekin-purge-linfluent-ancien-maire-de-chongqing-huang-qifan/</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>La succession de Xi est une préoccupation de plus en plus pressante L’article Pourquoi Pékin purge l’influent ancien maire de Chongqing, Huang Qifan&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1058" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -35138,6 +35296,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1051" r:id="rId1050"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1052" r:id="rId1051"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1053" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1054" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1055" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1056" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1057" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1058" r:id="rId1057"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1058"/>
+  <dimension ref="A1:G1073"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -34108,7 +34108,6 @@
           <t>Les enfants de 9 à 14 ans sont la cible principale L’article En Russie, les deux tiers des écoles participent à la propagande de guerre est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1054" t="inlineStr"/>
     </row>
     <row r="1055">
       <c r="A1055" s="2" t="inlineStr">
@@ -34141,7 +34140,6 @@
           <t>En Saxe-Anhalt, l’extrême droite de l’AfD et la gauche national-populiste allemandes s’unissent contre l’Ukraine L’article Poutine a-t-il trouvé une nouvelle majorité en Allemagne&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1055" t="inlineStr"/>
     </row>
     <row r="1056">
       <c r="A1056" s="2" t="inlineStr">
@@ -34174,7 +34172,6 @@
           <t>Seuls les Pays-Bas, la Lituanie et le Monténégro font exception à la règle L’article Dans 98&amp;#160;% des pays, les dirigeants sont plus âgés que la population est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1056" t="inlineStr"/>
     </row>
     <row r="1057">
       <c r="A1057" s="2" t="inlineStr">
@@ -34207,7 +34204,6 @@
           <t>Un sondage sondage exclusif sur le grand retournement contre l’IA L’article L&amp;rsquo;IA a gagné les marchés, mais elle est en train de perdre l&amp;rsquo;opinion mondiale est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1057" t="inlineStr"/>
     </row>
     <row r="1058">
       <c r="A1058" s="2" t="inlineStr">
@@ -34240,7 +34236,501 @@
           <t>La succession de Xi est une préoccupation de plus en plus pressante L’article Pourquoi Pékin purge l’influent ancien maire de Chongqing, Huang Qifan&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1058" t="inlineStr"/>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:43</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:56</t>
+        </is>
+      </c>
+      <c r="D1059" s="3" t="inlineStr">
+        <is>
+          <t>Mouvement lycéen : au-delà des revendications matérielles et de Parcoursup, un appel à rompre avec le « monde d’hier »</t>
+        </is>
+      </c>
+      <c r="E1059" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/mouvement-lyceen-au-dela-des-revendications-materielles-et-de-parcoursup-un-appel-a-rompre-avec-le-monde-dhier-294327</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>Au-delà d’un manque de moyens, les lycéens dénoncent la pression d’un système toujours plus compétitif. Ce désir de «&amp;nbsp;renverser la table&amp;nbsp;» révèle l’urgence de repenser le dialogue démocratique.</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr"/>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:43</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:43</t>
+        </is>
+      </c>
+      <c r="D1060" s="3" t="inlineStr">
+        <is>
+          <t>La refondation de Democratic Socialists of America</t>
+        </is>
+      </c>
+      <c r="E1060" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/la-refondation-de-democratic-socialists-of-america-294085</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>Retour sur les années 2017-2018, période décisive dans l’histoire des Democratic Socialists of America, formation située très à gauche sur l’échiquier politique états-unien, qui entretient une relation complexe avec le Parti démocrate.</t>
+        </is>
+      </c>
+      <c r="G1060" t="inlineStr"/>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:43</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:17</t>
+        </is>
+      </c>
+      <c r="D1061" s="3" t="inlineStr">
+        <is>
+          <t>En mer Noire, la Russie escalade aux abords de l’OTAN</t>
+        </is>
+      </c>
+      <c r="E1061" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/16/en-mer-noire-la-russie-escalade-aux-abords-de-lotan/</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>Sept navires ont été attaqués au large de la Roumanie et de la Bulgarie au mois d’octobre L’article En mer Noire, la Russie escalade aux abords de l’OTAN est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1061" t="inlineStr"/>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:43</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:30</t>
+        </is>
+      </c>
+      <c r="D1062" s="3" t="inlineStr">
+        <is>
+          <t>La Chine ment-elle sur son nombre d’habitants ?</t>
+        </is>
+      </c>
+      <c r="E1062" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/16/la-chine-ment-elle-sur-son-nombre-dhabitants/</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>Selon Yi Fuxian, la population chinoise pourrait tomber à 320 millions en 2100 L’article La Chine ment-elle sur son nombre d’habitants&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1062" t="inlineStr"/>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:43</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:00</t>
+        </is>
+      </c>
+      <c r="D1063" s="3" t="inlineStr">
+        <is>
+          <t>Giorgia Meloni a choisi de soutenir Kiev contre Trump</t>
+        </is>
+      </c>
+      <c r="E1063" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/16/giorgia-meloni-a-choisi-de-soutenir-kiev-contre-trump/</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>Nous traduisons et commentons le discours prononcé par la présidente du Conseil au Sénat L’article Giorgia Meloni a choisi de soutenir Kiev contre Trump est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1063" t="inlineStr"/>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:43</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>2026-10-15 15:44</t>
+        </is>
+      </c>
+      <c r="D1064" s="3" t="inlineStr">
+        <is>
+          <t>L’Iran multiplie les attaques dans le détroit d’Ormuz</t>
+        </is>
+      </c>
+      <c r="E1064" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/15/liran-multiplie-les-attaques-dans-le-detroit-dormuz/</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>Près de deux navires par jour ont été visés en octobre L’article L’Iran multiplie les attaques dans le détroit d’Ormuz est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr"/>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:43</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:00</t>
+        </is>
+      </c>
+      <c r="D1065" s="3" t="inlineStr">
+        <is>
+          <t>Olivier Antoine – Géopolitique du soja</t>
+        </is>
+      </c>
+      <c r="E1065" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/olivier-antoine-geopolitique-du-soja/</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio avec diaporama intégré pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#160; &amp;#60;div style= »padding:50% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1236359361?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#82</t>
+        </is>
+      </c>
+      <c r="G1065" t="inlineStr"/>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:43</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:00</t>
+        </is>
+      </c>
+      <c r="D1066" s="3" t="inlineStr">
+        <is>
+          <t>Les savants, 500 ans de querelles scientifiques – Les collections de L’Histoire</t>
+        </is>
+      </c>
+      <c r="E1066" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/les-savants-500-ans-de-querelles-scientifiques-les-collections-de-lhistoire/</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. Vous pouvez retrouver le sommaire de ce numéro en cliquant ici. &amp;#160; &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1236359368?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;</t>
+        </is>
+      </c>
+      <c r="G1066" t="inlineStr"/>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:43</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:00</t>
+        </is>
+      </c>
+      <c r="D1067" s="3" t="inlineStr">
+        <is>
+          <t>Au contact citoyens, citoyennes ! Présentation de l’association et de ses ressources pédagogiques</t>
+        </is>
+      </c>
+      <c r="E1067" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/au-contact-citoyens-citoyennes-presentation-de-lassociation-et-de-ses-ressources-pedagogiques/</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio avec vidéo intégrée pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.3% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1236359367?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; fram</t>
+        </is>
+      </c>
+      <c r="G1067" t="inlineStr"/>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:43</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:00</t>
+        </is>
+      </c>
+      <c r="D1068" s="3" t="inlineStr">
+        <is>
+          <t>Marie-Bénédicte Vincent – Histoire du parti nazi</t>
+        </is>
+      </c>
+      <c r="E1068" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/marie-benedicte-vincent-histoire-du-parti-nazi/</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1236359366?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr"/>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:43</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:00</t>
+        </is>
+      </c>
+      <c r="D1069" s="3" t="inlineStr">
+        <is>
+          <t>Lancelot Arzel – Un Musée-mémorial du terrorisme… pour quoi faire?</t>
+        </is>
+      </c>
+      <c r="E1069" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/lancelot-arzel-un-musee-memorial-du-terrorisme-pour-quoi-faire/</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio avec diaporama intégré pour protéger le droit à l&amp;#8217;image des participants. &amp;#60;div style= »padding:56.3% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1236359569?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; framebor</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr"/>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:43</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:00</t>
+        </is>
+      </c>
+      <c r="D1070" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce Agrégation interne – Carole Reynaud-Paligot – L’école aux colonies</t>
+        </is>
+      </c>
+      <c r="E1070" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/coup-de-pouce-agregation-interne-carole-reynaud-paligot-lecole-aux-colonies/</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Carole Reynaud-Paligot consacrée au sujet « l&amp;#8217;école aux colonies ». Le podcast est proposé en version audio hybride avec [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Carole Reynaud-Paligot &amp;#8211; L&amp;rsquo;école aux colonies est apparu</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr"/>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:43</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:00</t>
+        </is>
+      </c>
+      <c r="D1071" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce Agrégation interne – Jean-Paul Momont – Le tourisme en montagne</t>
+        </is>
+      </c>
+      <c r="E1071" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/coup-de-pouce-agregation-interne-jean-paul-momont-le-tourisme-en-montagne/</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Jean-Paul Momont consacrée au tourisme en montagne. Le podcast est proposé en version audio hybride avec diaporama [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Jean-Paul Momont &amp;#8211; Le tourisme en montagne est apparu en premier sur APHG </t>
+        </is>
+      </c>
+      <c r="G1071" t="inlineStr"/>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:43</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:00</t>
+        </is>
+      </c>
+      <c r="D1072" s="3" t="inlineStr">
+        <is>
+          <t>Henry Rousso – Quand le cinéma s’en mêle. La Bataille de Gaulle, Ombres et lumières, Notre salut.</t>
+        </is>
+      </c>
+      <c r="E1072" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/henry-rousso-quand-le-cinema-sen-mele-la-bataille-de-gaulle-ombres-et-lumieres-notre-salut/</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1236359703?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
+        </is>
+      </c>
+      <c r="G1072" t="inlineStr"/>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:43</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:00</t>
+        </is>
+      </c>
+      <c r="D1073" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce Capes interne – Méthodologie pour le dossier RAEP</t>
+        </is>
+      </c>
+      <c r="E1073" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/coup-de-pouce-capes-interne-methodologie-pour-le-dossier-raep/</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>Pour cette troisième séance, Marie Digout, Thomas Gosselin et Marine Sorano vous proposent d&amp;#8217;aborder la méthodologie du dossier RAEP avec Lionnel Trigueros, ancien membre du jury. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1236359711?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; allow= »autoplay; fullscreen; pic</t>
+        </is>
+      </c>
+      <c r="G1073" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -35301,6 +35791,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1056" r:id="rId1055"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1057" r:id="rId1056"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1058" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1059" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1060" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1061" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1062" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1063" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1064" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1065" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1066" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1067" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1068" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1069" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1070" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1071" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1072" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1073" r:id="rId1072"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1073"/>
+  <dimension ref="A1:G1078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -34268,7 +34268,6 @@
           <t>Au-delà d’un manque de moyens, les lycéens dénoncent la pression d’un système toujours plus compétitif. Ce désir de «&amp;nbsp;renverser la table&amp;nbsp;» révèle l’urgence de repenser le dialogue démocratique.</t>
         </is>
       </c>
-      <c r="G1059" t="inlineStr"/>
     </row>
     <row r="1060">
       <c r="A1060" s="2" t="inlineStr">
@@ -34301,7 +34300,6 @@
           <t>Retour sur les années 2017-2018, période décisive dans l’histoire des Democratic Socialists of America, formation située très à gauche sur l’échiquier politique états-unien, qui entretient une relation complexe avec le Parti démocrate.</t>
         </is>
       </c>
-      <c r="G1060" t="inlineStr"/>
     </row>
     <row r="1061">
       <c r="A1061" s="2" t="inlineStr">
@@ -34334,7 +34332,6 @@
           <t>Sept navires ont été attaqués au large de la Roumanie et de la Bulgarie au mois d’octobre L’article En mer Noire, la Russie escalade aux abords de l’OTAN est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1061" t="inlineStr"/>
     </row>
     <row r="1062">
       <c r="A1062" s="2" t="inlineStr">
@@ -34367,7 +34364,6 @@
           <t>Selon Yi Fuxian, la population chinoise pourrait tomber à 320 millions en 2100 L’article La Chine ment-elle sur son nombre d’habitants&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1062" t="inlineStr"/>
     </row>
     <row r="1063">
       <c r="A1063" s="2" t="inlineStr">
@@ -34400,7 +34396,6 @@
           <t>Nous traduisons et commentons le discours prononcé par la présidente du Conseil au Sénat L’article Giorgia Meloni a choisi de soutenir Kiev contre Trump est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1063" t="inlineStr"/>
     </row>
     <row r="1064">
       <c r="A1064" s="2" t="inlineStr">
@@ -34433,7 +34428,6 @@
           <t>Près de deux navires par jour ont été visés en octobre L’article L’Iran multiplie les attaques dans le détroit d’Ormuz est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1064" t="inlineStr"/>
     </row>
     <row r="1065">
       <c r="A1065" s="2" t="inlineStr">
@@ -34466,7 +34460,6 @@
           <t>Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio avec diaporama intégré pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#160; &amp;#60;div style= »padding:50% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1236359361?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#82</t>
         </is>
       </c>
-      <c r="G1065" t="inlineStr"/>
     </row>
     <row r="1066">
       <c r="A1066" s="2" t="inlineStr">
@@ -34499,7 +34492,6 @@
           <t>Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. Vous pouvez retrouver le sommaire de ce numéro en cliquant ici. &amp;#160; &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1236359368?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;</t>
         </is>
       </c>
-      <c r="G1066" t="inlineStr"/>
     </row>
     <row r="1067">
       <c r="A1067" s="2" t="inlineStr">
@@ -34532,7 +34524,6 @@
           <t>Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio avec vidéo intégrée pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.3% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1236359367?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; fram</t>
         </is>
       </c>
-      <c r="G1067" t="inlineStr"/>
     </row>
     <row r="1068">
       <c r="A1068" s="2" t="inlineStr">
@@ -34565,7 +34556,6 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1236359366?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
         </is>
       </c>
-      <c r="G1068" t="inlineStr"/>
     </row>
     <row r="1069">
       <c r="A1069" s="2" t="inlineStr">
@@ -34598,7 +34588,6 @@
           <t>Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio avec diaporama intégré pour protéger le droit à l&amp;#8217;image des participants. &amp;#60;div style= »padding:56.3% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1236359569?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; framebor</t>
         </is>
       </c>
-      <c r="G1069" t="inlineStr"/>
     </row>
     <row r="1070">
       <c r="A1070" s="2" t="inlineStr">
@@ -34631,7 +34620,6 @@
           <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Carole Reynaud-Paligot consacrée au sujet « l&amp;#8217;école aux colonies ». Le podcast est proposé en version audio hybride avec [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Carole Reynaud-Paligot &amp;#8211; L&amp;rsquo;école aux colonies est apparu</t>
         </is>
       </c>
-      <c r="G1070" t="inlineStr"/>
     </row>
     <row r="1071">
       <c r="A1071" s="2" t="inlineStr">
@@ -34664,7 +34652,6 @@
           <t xml:space="preserve">Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Jean-Paul Momont consacrée au tourisme en montagne. Le podcast est proposé en version audio hybride avec diaporama [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Jean-Paul Momont &amp;#8211; Le tourisme en montagne est apparu en premier sur APHG </t>
         </is>
       </c>
-      <c r="G1071" t="inlineStr"/>
     </row>
     <row r="1072">
       <c r="A1072" s="2" t="inlineStr">
@@ -34697,7 +34684,6 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1236359703?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
         </is>
       </c>
-      <c r="G1072" t="inlineStr"/>
     </row>
     <row r="1073">
       <c r="A1073" s="2" t="inlineStr">
@@ -34730,7 +34716,171 @@
           <t>Pour cette troisième séance, Marie Digout, Thomas Gosselin et Marine Sorano vous proposent d&amp;#8217;aborder la méthodologie du dossier RAEP avec Lionnel Trigueros, ancien membre du jury. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1236359711?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; allow= »autoplay; fullscreen; pic</t>
         </is>
       </c>
-      <c r="G1073" t="inlineStr"/>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17 12:39</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:08</t>
+        </is>
+      </c>
+      <c r="D1074" s="3" t="inlineStr">
+        <is>
+          <t>Face aux incertitudes budgétaires de 2027, les universités françaises poussées à changer de modèle ?</t>
+        </is>
+      </c>
+      <c r="E1074" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/face-aux-incertitudes-budgetaires-de-2027-les-universites-francaises-poussees-a-changer-de-modele-293365</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>Les universités françaises abordent 2027 dans une situation financière de plus en plus fragile. Les choix budgétaires à venir pourraient accélérer une transformation profonde de leur modèle de financement.</t>
+        </is>
+      </c>
+      <c r="G1074" t="inlineStr"/>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17 12:39</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>2026-10-17 05:28</t>
+        </is>
+      </c>
+      <c r="D1075" s="3" t="inlineStr">
+        <is>
+          <t>Portraits de la génération sacrifiée du Donbass</t>
+        </is>
+      </c>
+      <c r="E1075" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/17/portraits-de-la-generation-sacrifiee-du-donbass/</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>Quand la photographie garde trace d’une jeunesse traversée par la guerre L’article Portraits de la génération sacrifiée du Donbass est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1075" t="inlineStr"/>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17 12:39</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:30</t>
+        </is>
+      </c>
+      <c r="D1076" s="3" t="inlineStr">
+        <is>
+          <t>L’administration renoue avec l’amateurisme du premier mandat de Trump</t>
+        </is>
+      </c>
+      <c r="E1076" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/17/ladministration-renoue-avec-lamateurisme-du-premier-mandat-de-trump/</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>Aux États-Unis, la corruption devient une question clef de la campagne pour les élections de mi-mandat. L’article L’administration renoue avec l’amateurisme du premier mandat de Trump est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr"/>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17 12:39</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>2026-10-16 16:38</t>
+        </is>
+      </c>
+      <c r="D1077" s="3" t="inlineStr">
+        <is>
+          <t>Pékin prépare un contrôle inédit sur l’exportation de ses modèles d’IA</t>
+        </is>
+      </c>
+      <c r="E1077" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/16/pekin-prepare-un-controle-inedit-sur-lexportation-de-ses-modeles-dia/</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>Est-ce la fin des grands modèles open source chinois&amp;#160;? L’article Pékin prépare un contrôle inédit sur l’exportation de ses modèles d’IA est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1077" t="inlineStr"/>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17 12:39</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>2026-10-16 14:58</t>
+        </is>
+      </c>
+      <c r="D1078" s="3" t="inlineStr">
+        <is>
+          <t>L’Europe doit réapprendre à planifier</t>
+        </is>
+      </c>
+      <c r="E1078" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/16/leurope-doit-reapprendre-a-planifier/</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>De la Chine à Monnet, la crise de la voiture électrique montre pourquoi l’Europe doit réinventer au plus vite une politique industrielle démocratique L’article L’Europe doit réapprendre à planifier est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1078" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -35806,6 +35956,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1071" r:id="rId1070"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1072" r:id="rId1071"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1073" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1074" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1075" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1076" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1077" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1078" r:id="rId1077"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1078"/>
+  <dimension ref="A1:G1082"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -34748,7 +34748,6 @@
           <t>Les universités françaises abordent 2027 dans une situation financière de plus en plus fragile. Les choix budgétaires à venir pourraient accélérer une transformation profonde de leur modèle de financement.</t>
         </is>
       </c>
-      <c r="G1074" t="inlineStr"/>
     </row>
     <row r="1075">
       <c r="A1075" s="2" t="inlineStr">
@@ -34781,7 +34780,6 @@
           <t>Quand la photographie garde trace d’une jeunesse traversée par la guerre L’article Portraits de la génération sacrifiée du Donbass est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1075" t="inlineStr"/>
     </row>
     <row r="1076">
       <c r="A1076" s="2" t="inlineStr">
@@ -34814,7 +34812,6 @@
           <t>Aux États-Unis, la corruption devient une question clef de la campagne pour les élections de mi-mandat. L’article L’administration renoue avec l’amateurisme du premier mandat de Trump est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1076" t="inlineStr"/>
     </row>
     <row r="1077">
       <c r="A1077" s="2" t="inlineStr">
@@ -34847,7 +34844,6 @@
           <t>Est-ce la fin des grands modèles open source chinois&amp;#160;? L’article Pékin prépare un contrôle inédit sur l’exportation de ses modèles d’IA est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1077" t="inlineStr"/>
     </row>
     <row r="1078">
       <c r="A1078" s="2" t="inlineStr">
@@ -34880,7 +34876,138 @@
           <t>De la Chine à Monnet, la crise de la voiture électrique montre pourquoi l’Europe doit réinventer au plus vite une politique industrielle démocratique L’article L’Europe doit réapprendre à planifier est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1078" t="inlineStr"/>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18 12:57</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:54</t>
+        </is>
+      </c>
+      <c r="D1079" s="3" t="inlineStr">
+        <is>
+          <t>Au Liban, le sexe transactionnel comme stratégie de survie</t>
+        </is>
+      </c>
+      <c r="E1079" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/au-liban-le-sexe-transactionnel-comme-strategie-de-survie-287215</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>Quand stabilité et protection font défaut, les personnes déplacées, plongées dans une situation précaire, n’ont parfois d’autre choix que de recourir au travail sexuel.</t>
+        </is>
+      </c>
+      <c r="G1079" t="inlineStr"/>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18 12:57</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:42</t>
+        </is>
+      </c>
+      <c r="D1080" s="3" t="inlineStr">
+        <is>
+          <t>La rencontre oubliée de Foucault et la géopolitique</t>
+        </is>
+      </c>
+      <c r="E1080" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/18/la-rencontre-oubliee-de-foucault-et-la-geopolitique/</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>Le témoignage inédit sur ce jour de 1975 où Yves Lacoste amena l’auteur des Mots et les Choses à repenser les liens entre espace et pouvoir L’article La rencontre oubliée de Foucault et la géopolitique est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1080" t="inlineStr"/>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18 12:57</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:30</t>
+        </is>
+      </c>
+      <c r="D1081" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : les dépenses publiques se rapprochent de la moyenne de l’OCDE</t>
+        </is>
+      </c>
+      <c r="E1081" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/18/economie-russe-les-depenses-publiques-se-rapprochent-de-la-moyenne-de-locde/</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>L’écart entre la Russie et l’OCDE est passé de 10 à 3 points de PIB depuis 2011 L’article Économie russe&amp;#160;: les dépenses publiques se rapprochent de la moyenne de l’OCDE est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr"/>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18 12:57</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>2026-10-18 10:44</t>
+        </is>
+      </c>
+      <c r="D1082" s="3" t="inlineStr">
+        <is>
+          <t>Podcast : participer au prix Samuel Paty, retour d’expérience</t>
+        </is>
+      </c>
+      <c r="E1082" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/podcast-participer-au-prix-samuel-paty-retour-dexperience/</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>Extra classe, podcast du réseau Canopé, a recueilli le témoignage d&amp;#8217;un de nos adhérents, Jonathan Hiriart, au sujet de sa participation au prix Samuel Paty. Un épisode qui « vous invite à découvrir comment la compréhension des mécanismes du débat, associée à la pratique de la webradio, peut créer une étonnante alchimie et une belle expérience [&amp;#8230;] L’article Podcast : participer au prix Samuel Paty, retour d&amp;rsquo;expérience est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G1082" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -35961,6 +36088,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1076" r:id="rId1075"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1077" r:id="rId1076"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1078" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1079" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1080" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1081" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1082" r:id="rId1081"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1082"/>
+  <dimension ref="A1:G1090"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -34908,7 +34908,6 @@
           <t>Quand stabilité et protection font défaut, les personnes déplacées, plongées dans une situation précaire, n’ont parfois d’autre choix que de recourir au travail sexuel.</t>
         </is>
       </c>
-      <c r="G1079" t="inlineStr"/>
     </row>
     <row r="1080">
       <c r="A1080" s="2" t="inlineStr">
@@ -34941,7 +34940,6 @@
           <t>Le témoignage inédit sur ce jour de 1975 où Yves Lacoste amena l’auteur des Mots et les Choses à repenser les liens entre espace et pouvoir L’article La rencontre oubliée de Foucault et la géopolitique est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1080" t="inlineStr"/>
     </row>
     <row r="1081">
       <c r="A1081" s="2" t="inlineStr">
@@ -34974,7 +34972,6 @@
           <t>L’écart entre la Russie et l’OCDE est passé de 10 à 3 points de PIB depuis 2011 L’article Économie russe&amp;#160;: les dépenses publiques se rapprochent de la moyenne de l’OCDE est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1081" t="inlineStr"/>
     </row>
     <row r="1082">
       <c r="A1082" s="2" t="inlineStr">
@@ -35007,7 +35004,270 @@
           <t>Extra classe, podcast du réseau Canopé, a recueilli le témoignage d&amp;#8217;un de nos adhérents, Jonathan Hiriart, au sujet de sa participation au prix Samuel Paty. Un épisode qui « vous invite à découvrir comment la compréhension des mécanismes du débat, associée à la pratique de la webradio, peut créer une étonnante alchimie et une belle expérience [&amp;#8230;] L’article Podcast : participer au prix Samuel Paty, retour d&amp;rsquo;expérience est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G1082" t="inlineStr"/>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:09</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:03</t>
+        </is>
+      </c>
+      <c r="D1083" s="3" t="inlineStr">
+        <is>
+          <t>L’école à l’ère de l’individualisme compétitif ? Derrière les discours sur l’excellence, l’illusion méritocratique</t>
+        </is>
+      </c>
+      <c r="E1083" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/lecole-a-lere-de-lindividualisme-competitif-derriere-les-discours-sur-lexcellence-lillusion-meritocratique-293231</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>Si le discours sur le mérite a changé de forme, il continue de valider la reproduction d’inégalités sociales et scolaires soulignées dans les années&amp;nbsp;1970 par les sociologues P.&amp;nbsp;Bourdieu et J.-C.&amp;nbsp;Passeron.</t>
+        </is>
+      </c>
+      <c r="G1083" t="inlineStr"/>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:09</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:01</t>
+        </is>
+      </c>
+      <c r="D1084" s="3" t="inlineStr">
+        <is>
+          <t>« Bismillah, c’est les ténèbres » : quand une possible infiltration policière devient un mème à succès</t>
+        </is>
+      </c>
+      <c r="E1084" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/bismillah-cest-les-tenebres-quand-une-possible-infiltration-policiere-devient-un-meme-a-succes-294652</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>Cette formule absurde, provenant d’un message Snapchat, que l’on voit maintenant brandie dans les manifestations lycéennes en dit long sur les stéréotypes qui circulent au sujet de la jeunesse, mais aussi sur la créativité et la résilience des manifestants.</t>
+        </is>
+      </c>
+      <c r="G1084" t="inlineStr"/>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:09</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:06</t>
+        </is>
+      </c>
+      <c r="D1085" s="3" t="inlineStr">
+        <is>
+          <t>À Okinawa, deux quotidiens locaux au cœur de la contestation de la présence des bases américaines</t>
+        </is>
+      </c>
+      <c r="E1085" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/a-okinawa-deux-quotidiens-locaux-au-coeur-de-la-contestation-de-la-presence-des-bases-americaines-294583</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>À Okinawa, deux&amp;nbsp;quotidiens locaux dénoncent les bases américaines, nourrissent les mobilisations et transmettent une mémoire de la guerre différente du récit national japonais.</t>
+        </is>
+      </c>
+      <c r="G1085" t="inlineStr"/>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:09</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:02</t>
+        </is>
+      </c>
+      <c r="D1086" s="3" t="inlineStr">
+        <is>
+          <t>L’Andorre, le Vatican, Monaco et Saint-Marin : pourquoi ces micro-États si riches utilisent l’euro</t>
+        </is>
+      </c>
+      <c r="E1086" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/landorre-le-vatican-monaco-et-saint-marin-pourquoi-ces-micro-etats-si-riches-utilisent-leuro-291789</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>Les quatre micro-États utilisent l’euro et frappent leurs propres pièces nationales, sans être formellement membres de l’Union européenne ni de la zone euro.</t>
+        </is>
+      </c>
+      <c r="G1086" t="inlineStr"/>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:09</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>2026-10-19 15:18</t>
+        </is>
+      </c>
+      <c r="D1087" s="3" t="inlineStr">
+        <is>
+          <t>La guerre des centres de données : l’Ukraine frappe le « cœur de fer » de l’Internet russe</t>
+        </is>
+      </c>
+      <c r="E1087" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/19/la-guerre-des-centres-de-donnees-lukraine-frappe-le-coeur-de-fer-de-linternet-russe/</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>Depuis 2014, le Kremlin a patiemment bâti pour les Russes un Internet de repli, censé résister quand tout le reste est coupé. Les frappes contre Yandex montrent les limites de ce modèle L’article La guerre des centres de données&amp;#160;: l’Ukraine frappe le «&amp;#160;cœur de fer&amp;#160;» de l’Internet russe est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr"/>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:09</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:58</t>
+        </is>
+      </c>
+      <c r="D1088" s="3" t="inlineStr">
+        <is>
+          <t>Léon XIV est le dirigeant étranger le plus apprécié des Français</t>
+        </is>
+      </c>
+      <c r="E1088" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/19/leon-xiv-est-le-dirigeant-etranger-le-plus-apprecie-des-francais/</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>Donald Trump est quant à lui le plus rejeté L’article Léon XIV est le dirigeant étranger le plus apprécié des Français est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr"/>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:09</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>2026-10-19 04:00</t>
+        </is>
+      </c>
+      <c r="D1089" s="3" t="inlineStr">
+        <is>
+          <t>Au-delà de la France, la crise du coût de la vie embrase l’Europe</t>
+        </is>
+      </c>
+      <c r="E1089" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/19/au-dela-de-la-france-la-crise-du-cout-de-la-vie-embrase-leurope/</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>Depuis samedi, des centaines de milliers de personnes ont manifesté dans cinq pays européens L’article Au-delà de la France, la crise du coût de la vie embrase l’Europe est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr"/>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:09</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:00</t>
+        </is>
+      </c>
+      <c r="D1090" s="3" t="inlineStr">
+        <is>
+          <t>Aux portes de l’Asie du Sud-Est, le pari stratégique du Guangxi</t>
+        </is>
+      </c>
+      <c r="E1090" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/18/le-pivot-geopolitique-de-lacceleration-de-xi-se-trouve-au-guangxi/</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>Pourquoi le Parti mise-t-il des milliards sur cette région oubliée de Chine&amp;#160;? L’article Aux portes de l&amp;rsquo;Asie du Sud-Est, le pari stratégique du Guangxi est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -36092,6 +36352,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1080" r:id="rId1079"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1081" r:id="rId1080"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1082" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1083" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1084" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1085" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1086" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1087" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1088" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1089" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1090" r:id="rId1089"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1090"/>
+  <dimension ref="A1:G1105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -35036,7 +35036,6 @@
           <t>Si le discours sur le mérite a changé de forme, il continue de valider la reproduction d’inégalités sociales et scolaires soulignées dans les années&amp;nbsp;1970 par les sociologues P.&amp;nbsp;Bourdieu et J.-C.&amp;nbsp;Passeron.</t>
         </is>
       </c>
-      <c r="G1083" t="inlineStr"/>
     </row>
     <row r="1084">
       <c r="A1084" s="2" t="inlineStr">
@@ -35069,7 +35068,6 @@
           <t>Cette formule absurde, provenant d’un message Snapchat, que l’on voit maintenant brandie dans les manifestations lycéennes en dit long sur les stéréotypes qui circulent au sujet de la jeunesse, mais aussi sur la créativité et la résilience des manifestants.</t>
         </is>
       </c>
-      <c r="G1084" t="inlineStr"/>
     </row>
     <row r="1085">
       <c r="A1085" s="2" t="inlineStr">
@@ -35102,7 +35100,6 @@
           <t>À Okinawa, deux&amp;nbsp;quotidiens locaux dénoncent les bases américaines, nourrissent les mobilisations et transmettent une mémoire de la guerre différente du récit national japonais.</t>
         </is>
       </c>
-      <c r="G1085" t="inlineStr"/>
     </row>
     <row r="1086">
       <c r="A1086" s="2" t="inlineStr">
@@ -35135,7 +35132,6 @@
           <t>Les quatre micro-États utilisent l’euro et frappent leurs propres pièces nationales, sans être formellement membres de l’Union européenne ni de la zone euro.</t>
         </is>
       </c>
-      <c r="G1086" t="inlineStr"/>
     </row>
     <row r="1087">
       <c r="A1087" s="2" t="inlineStr">
@@ -35168,7 +35164,6 @@
           <t>Depuis 2014, le Kremlin a patiemment bâti pour les Russes un Internet de repli, censé résister quand tout le reste est coupé. Les frappes contre Yandex montrent les limites de ce modèle L’article La guerre des centres de données&amp;#160;: l’Ukraine frappe le «&amp;#160;cœur de fer&amp;#160;» de l’Internet russe est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1087" t="inlineStr"/>
     </row>
     <row r="1088">
       <c r="A1088" s="2" t="inlineStr">
@@ -35201,7 +35196,6 @@
           <t>Donald Trump est quant à lui le plus rejeté L’article Léon XIV est le dirigeant étranger le plus apprécié des Français est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1088" t="inlineStr"/>
     </row>
     <row r="1089">
       <c r="A1089" s="2" t="inlineStr">
@@ -35234,7 +35228,6 @@
           <t>Depuis samedi, des centaines de milliers de personnes ont manifesté dans cinq pays européens L’article Au-delà de la France, la crise du coût de la vie embrase l’Europe est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1089" t="inlineStr"/>
     </row>
     <row r="1090">
       <c r="A1090" s="2" t="inlineStr">
@@ -35267,7 +35260,501 @@
           <t>Pourquoi le Parti mise-t-il des milliards sur cette région oubliée de Chine&amp;#160;? L’article Aux portes de l&amp;rsquo;Asie du Sud-Est, le pari stratégique du Guangxi est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1090" t="inlineStr"/>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:03</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:58</t>
+        </is>
+      </c>
+      <c r="D1091" s="3" t="inlineStr">
+        <is>
+          <t>Les séries de Monet, méditations sur le temps</t>
+        </is>
+      </c>
+      <c r="E1091" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-series-de-monet-meditations-sur-le-temps-293564</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>Comment la peinture peut-elle saisir le temps&amp;nbsp;? Et de quel(s) temps s’agit-il&amp;nbsp;? Avec ses nombreuses séries, l’œuvre de Monet se prête particulièrement à cette réflexion.</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr"/>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:03</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:52</t>
+        </is>
+      </c>
+      <c r="D1092" s="3" t="inlineStr">
+        <is>
+          <t>De la dénonciation du soviétisme à une série glorifiant Staline : l’itinéraire emblématique de Vladimir Bortko en Russie</t>
+        </is>
+      </c>
+      <c r="E1092" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/de-la-denonciation-du-sovietisme-a-une-serie-glorifiant-staline-litineraire-emblematique-de-vladimir-bortko-en-russie-293630</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>Vladimir Bortko, détracteur du soviétisme pendant la perestroïka, célèbre désormais Staline et souhaite que la Russie frappe l’Ukraine avec ses armes nucléaires.</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr"/>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:03</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:44</t>
+        </is>
+      </c>
+      <c r="D1093" s="3" t="inlineStr">
+        <is>
+          <t>Notre paie s’appelle un « salaire », mais est-ce vraiment parce que les soldats romains étaient payés en sel ?</t>
+        </is>
+      </c>
+      <c r="E1093" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/notre-paie-sappelle-un-salaire-mais-est-ce-vraiment-parce-que-les-soldats-romains-etaient-payes-en-sel-292155</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>Le mot «&amp;nbsp;salaire&amp;nbsp;» vient-il du sel versé aux soldats romains&amp;nbsp;? Si cette idée est largement répandue, les sources historiques montrent qu’ils étaient en réalité payés en pièces de monnaie et recevaient même des primes.</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr"/>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:03</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:39</t>
+        </is>
+      </c>
+      <c r="D1094" s="3" t="inlineStr">
+        <is>
+          <t>Comment les déjections d’oiseaux ont façonné l’agriculture moderne et contribué à l’expansion de l’empire américain</t>
+        </is>
+      </c>
+      <c r="E1094" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-les-dejections-doiseaux-ont-faconne-lagriculture-moderne-et-contribue-a-lexpansion-de-lempire-americain-288944</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>L’histoire du guano, premier engrais mondialisé, montre comment l’agriculture moderne s’est construite grâce à des chaînes d’approvisionnement internationales, au prix de l’exploitation de travailleurs.</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr"/>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:03</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:34</t>
+        </is>
+      </c>
+      <c r="D1095" s="3" t="inlineStr">
+        <is>
+          <t>L’histoire de l’enfance : une clé pour comprendre comment change la société française, entre infantisme et nouveaux droits</t>
+        </is>
+      </c>
+      <c r="E1095" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/lhistoire-de-lenfance-une-cle-pour-comprendre-comment-change-la-societe-francaise-entre-infantisme-et-nouveaux-droits-294522</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>Si les cadres familiaux et éducatifs ont évolué, si les enfants disposent de droits et ne travaillent plus à la mine, leur «&amp;nbsp;cause&amp;nbsp;» est encore loin d’être inattaquable et inattaquée.</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr"/>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:03</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:24</t>
+        </is>
+      </c>
+      <c r="D1096" s="3" t="inlineStr">
+        <is>
+          <t>Quand les riches Anglais profitaient de la Révolution française pour s’emparer des livres rares</t>
+        </is>
+      </c>
+      <c r="E1096" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/quand-les-riches-anglais-profitaient-de-la-revolution-francaise-pour-semparer-des-livres-rares-294195</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>Pendant la Révolution française, de riches collectionneurs anglais ont profité du démantèlement des monastères pour acquérir des livres rares, parfois sous la contrainte ou par le vol. Une enquête révèle les origines troubles de leurs collections.</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr"/>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:03</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:23</t>
+        </is>
+      </c>
+      <c r="D1097" s="3" t="inlineStr">
+        <is>
+          <t>Christophe Colomb se croyait investi d’une mission divine, comme le révèlent ses écrits</t>
+        </is>
+      </c>
+      <c r="E1097" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/christophe-colomb-se-croyait-investi-dune-mission-divine-comme-le-revelent-ses-ecrits-293955</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>Christophe Colomb se croyait investi d’une mission divine. Ses écrits révèlent comment la volonté de convertir les peuples autochtones au christianisme a accompagné, dès 1492, la conquête et la colonisation des Amériques.</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr"/>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:03</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>2026-10-20 08:32</t>
+        </is>
+      </c>
+      <c r="D1098" s="3" t="inlineStr">
+        <is>
+          <t>Religieuses possédées et déviances sexuelles : l’histoire des « Diables », le film censuré puis restauré de Ken Russell</t>
+        </is>
+      </c>
+      <c r="E1098" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/religieuses-possedees-et-deviances-sexuelles-lhistoire-des-diables-le-film-censure-puis-restaure-de-ken-russell-294264</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>Le film de 1971 ressort dans une version intégrale conforme à la vision du réalisateur, dévoilant ses scènes controversées longtemps considérées comme perdues.</t>
+        </is>
+      </c>
+      <c r="G1098" t="inlineStr"/>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:03</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:56</t>
+        </is>
+      </c>
+      <c r="D1099" s="3" t="inlineStr">
+        <is>
+          <t>Après plus de cinq mois de crise, la Roumanie a un gouvernement</t>
+        </is>
+      </c>
+      <c r="E1099" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/20/apres-plus-de-cinq-mois-de-crise-la-roumanie-a-un-gouvernement/</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>Luca Niculescu a obtenu mardi 20 octobre la confiance du Parlement L’article Après plus de cinq mois de crise, la Roumanie a un gouvernement est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr"/>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:03</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:00</t>
+        </is>
+      </c>
+      <c r="D1100" s="3" t="inlineStr">
+        <is>
+          <t>En se rapprochant de Poutine, Trump s’éloigne davantage de son électorat</t>
+        </is>
+      </c>
+      <c r="E1100" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/20/en-se-rapprochant-de-poutine-trump-seloigne-davantage-de-son-electorat/</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>Seulement 12&amp;#160;% de ses électeurs ont une opinion positive de Moscou L’article En se rapprochant de Poutine, Trump s’éloigne davantage de son électorat est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr"/>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:03</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>2026-10-20 04:30</t>
+        </is>
+      </c>
+      <c r="D1101" s="3" t="inlineStr">
+        <is>
+          <t>Pour comprendre les manifestations en Europe, faut-il regarder le prix du gaz ?</t>
+        </is>
+      </c>
+      <c r="E1101" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/20/pour-comprendre-les-manifestations-en-europe-faut-il-regarder-le-prix-du-gaz/</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>En France, le prix du MWh de gaz payé par les ménages a presque doublé en cinq ans L’article Pour comprendre les manifestations en Europe, faut-il regarder le prix du gaz&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr"/>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:03</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>2026-10-20 04:13</t>
+        </is>
+      </c>
+      <c r="D1102" s="3" t="inlineStr">
+        <is>
+          <t>Le piège italien de la politique française</t>
+        </is>
+      </c>
+      <c r="E1102" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/20/le-piege-italien-politique-francaise/</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>En Italie, tous les populistes ont plié devant le vincolo esterno . Une leçon romaine pour 2027 L’article Le piège italien de la politique française est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1102" t="inlineStr"/>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:03</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>2026-10-19 18:38</t>
+        </is>
+      </c>
+      <c r="D1103" s="3" t="inlineStr">
+        <is>
+          <t>Quelles villes sont concernées par les couvre-feux ?</t>
+        </is>
+      </c>
+      <c r="E1103" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/19/quelles-villes-et-quels-perimetres-sont-concernes-par-les-couvre-feux/</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>À 20h ce soir, ces mesures «&amp;#160;partielles&amp;#160;» et «&amp;#160;localisées&amp;#160;» concernent huit communes et villes. L’article Quelles villes sont concernées par les couvre-feux&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr"/>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:03</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>2026-10-19 17:04</t>
+        </is>
+      </c>
+      <c r="D1104" s="3" t="inlineStr">
+        <is>
+          <t>Cartographier les réactions internationales aux violences en France</t>
+        </is>
+      </c>
+      <c r="E1104" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/19/cartographier-les-reactions-internationales-aux-violences-en-france/</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>La majorité des dirigeants pointent la France pour justifier leurs politiques internes L’article Cartographier les réactions internationales aux violences en France est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1104" t="inlineStr"/>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:03</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>2026-10-20 10:02</t>
+        </is>
+      </c>
+      <c r="D1105" s="3" t="inlineStr">
+        <is>
+          <t>Les élèves ont débattu pour faire vivre la démocratie : retour sur le prix Samuel Paty 2026</t>
+        </is>
+      </c>
+      <c r="E1105" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/les-eleves-ont-debattu-pour-faire-vivre-la-democratie-retour-sur-le-prix-samuel-paty-2026/</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>La cérémonie du prix Samuel Paty 2026 a récompensé les écoles primaires, collèges et lycées pour des travaux extrêmement riches. Elle a marqué comme chaque année un temps fort après les hommages scolaires à Samuel Paty et à Dominique Bernard, professeurs victimes du terrorisme. Les classes présentes, après avoir visité des lieux symboles de la [&amp;#8230;] L’article Les élèves ont débattu pour faire vivre la démocratie : retour sur le prix Samuel Paty 2026 est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G1105" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -36360,6 +36847,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1088" r:id="rId1087"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1089" r:id="rId1088"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1090" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1091" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1092" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1093" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1094" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1095" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1096" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1097" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1098" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1099" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1100" r:id="rId1099"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1101" r:id="rId1100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1102" r:id="rId1101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1103" r:id="rId1102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1104" r:id="rId1103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1105" r:id="rId1104"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1105"/>
+  <dimension ref="A1:G1120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -35292,7 +35292,6 @@
           <t>Comment la peinture peut-elle saisir le temps&amp;nbsp;? Et de quel(s) temps s’agit-il&amp;nbsp;? Avec ses nombreuses séries, l’œuvre de Monet se prête particulièrement à cette réflexion.</t>
         </is>
       </c>
-      <c r="G1091" t="inlineStr"/>
     </row>
     <row r="1092">
       <c r="A1092" s="2" t="inlineStr">
@@ -35325,7 +35324,6 @@
           <t>Vladimir Bortko, détracteur du soviétisme pendant la perestroïka, célèbre désormais Staline et souhaite que la Russie frappe l’Ukraine avec ses armes nucléaires.</t>
         </is>
       </c>
-      <c r="G1092" t="inlineStr"/>
     </row>
     <row r="1093">
       <c r="A1093" s="2" t="inlineStr">
@@ -35358,7 +35356,6 @@
           <t>Le mot «&amp;nbsp;salaire&amp;nbsp;» vient-il du sel versé aux soldats romains&amp;nbsp;? Si cette idée est largement répandue, les sources historiques montrent qu’ils étaient en réalité payés en pièces de monnaie et recevaient même des primes.</t>
         </is>
       </c>
-      <c r="G1093" t="inlineStr"/>
     </row>
     <row r="1094">
       <c r="A1094" s="2" t="inlineStr">
@@ -35391,7 +35388,6 @@
           <t>L’histoire du guano, premier engrais mondialisé, montre comment l’agriculture moderne s’est construite grâce à des chaînes d’approvisionnement internationales, au prix de l’exploitation de travailleurs.</t>
         </is>
       </c>
-      <c r="G1094" t="inlineStr"/>
     </row>
     <row r="1095">
       <c r="A1095" s="2" t="inlineStr">
@@ -35424,7 +35420,6 @@
           <t>Si les cadres familiaux et éducatifs ont évolué, si les enfants disposent de droits et ne travaillent plus à la mine, leur «&amp;nbsp;cause&amp;nbsp;» est encore loin d’être inattaquable et inattaquée.</t>
         </is>
       </c>
-      <c r="G1095" t="inlineStr"/>
     </row>
     <row r="1096">
       <c r="A1096" s="2" t="inlineStr">
@@ -35457,7 +35452,6 @@
           <t>Pendant la Révolution française, de riches collectionneurs anglais ont profité du démantèlement des monastères pour acquérir des livres rares, parfois sous la contrainte ou par le vol. Une enquête révèle les origines troubles de leurs collections.</t>
         </is>
       </c>
-      <c r="G1096" t="inlineStr"/>
     </row>
     <row r="1097">
       <c r="A1097" s="2" t="inlineStr">
@@ -35490,7 +35484,6 @@
           <t>Christophe Colomb se croyait investi d’une mission divine. Ses écrits révèlent comment la volonté de convertir les peuples autochtones au christianisme a accompagné, dès 1492, la conquête et la colonisation des Amériques.</t>
         </is>
       </c>
-      <c r="G1097" t="inlineStr"/>
     </row>
     <row r="1098">
       <c r="A1098" s="2" t="inlineStr">
@@ -35523,7 +35516,6 @@
           <t>Le film de 1971 ressort dans une version intégrale conforme à la vision du réalisateur, dévoilant ses scènes controversées longtemps considérées comme perdues.</t>
         </is>
       </c>
-      <c r="G1098" t="inlineStr"/>
     </row>
     <row r="1099">
       <c r="A1099" s="2" t="inlineStr">
@@ -35556,7 +35548,6 @@
           <t>Luca Niculescu a obtenu mardi 20 octobre la confiance du Parlement L’article Après plus de cinq mois de crise, la Roumanie a un gouvernement est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1099" t="inlineStr"/>
     </row>
     <row r="1100">
       <c r="A1100" s="2" t="inlineStr">
@@ -35589,7 +35580,6 @@
           <t>Seulement 12&amp;#160;% de ses électeurs ont une opinion positive de Moscou L’article En se rapprochant de Poutine, Trump s’éloigne davantage de son électorat est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1100" t="inlineStr"/>
     </row>
     <row r="1101">
       <c r="A1101" s="2" t="inlineStr">
@@ -35622,7 +35612,6 @@
           <t>En France, le prix du MWh de gaz payé par les ménages a presque doublé en cinq ans L’article Pour comprendre les manifestations en Europe, faut-il regarder le prix du gaz&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1101" t="inlineStr"/>
     </row>
     <row r="1102">
       <c r="A1102" s="2" t="inlineStr">
@@ -35655,7 +35644,6 @@
           <t>En Italie, tous les populistes ont plié devant le vincolo esterno . Une leçon romaine pour 2027 L’article Le piège italien de la politique française est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1102" t="inlineStr"/>
     </row>
     <row r="1103">
       <c r="A1103" s="2" t="inlineStr">
@@ -35688,7 +35676,6 @@
           <t>À 20h ce soir, ces mesures «&amp;#160;partielles&amp;#160;» et «&amp;#160;localisées&amp;#160;» concernent huit communes et villes. L’article Quelles villes sont concernées par les couvre-feux&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1103" t="inlineStr"/>
     </row>
     <row r="1104">
       <c r="A1104" s="2" t="inlineStr">
@@ -35721,7 +35708,6 @@
           <t>La majorité des dirigeants pointent la France pour justifier leurs politiques internes L’article Cartographier les réactions internationales aux violences en France est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1104" t="inlineStr"/>
     </row>
     <row r="1105">
       <c r="A1105" s="2" t="inlineStr">
@@ -35754,7 +35740,501 @@
           <t>La cérémonie du prix Samuel Paty 2026 a récompensé les écoles primaires, collèges et lycées pour des travaux extrêmement riches. Elle a marqué comme chaque année un temps fort après les hommages scolaires à Samuel Paty et à Dominique Bernard, professeurs victimes du terrorisme. Les classes présentes, après avoir visité des lieux symboles de la [&amp;#8230;] L’article Les élèves ont débattu pour faire vivre la démocratie : retour sur le prix Samuel Paty 2026 est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G1105" t="inlineStr"/>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:19</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:24</t>
+        </is>
+      </c>
+      <c r="D1106" s="3" t="inlineStr">
+        <is>
+          <t>Quand les riches Anglais profitaient de la Révolution française pour s’emparer de livres rares</t>
+        </is>
+      </c>
+      <c r="E1106" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/quand-les-riches-anglais-profitaient-de-la-revolution-francaise-pour-semparer-de-livres-rares-294195</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>Pendant la Révolution française, de riches collectionneurs anglais ont profité du démantèlement des monastères pour acquérir des livres rares, parfois sous la contrainte ou par le vol. Une enquête révèle les origines troubles de leurs collections.</t>
+        </is>
+      </c>
+      <c r="G1106" t="inlineStr"/>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:19</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:54</t>
+        </is>
+      </c>
+      <c r="D1107" s="3" t="inlineStr">
+        <is>
+          <t>Face à l’autisme, les grands-parents, des soutiens précieux pour les familles</t>
+        </is>
+      </c>
+      <c r="E1107" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/face-a-lautisme-les-grands-parents-des-soutiens-precieux-pour-les-familles-292286</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>En France, les grands-parents d’enfants autistes jouent un rôle majeur auprès de leur famille, mais restent encore peu reconnus par les équipes soignantes.</t>
+        </is>
+      </c>
+      <c r="G1107" t="inlineStr"/>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:19</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:53</t>
+        </is>
+      </c>
+      <c r="D1108" s="3" t="inlineStr">
+        <is>
+          <t>Combien coûte un élève en France ?</t>
+        </is>
+      </c>
+      <c r="E1108" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/combien-coute-un-eleve-en-france-293993</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>En 2025, la dépense moyenne annuelle s’établit à 9&amp;nbsp;440&amp;nbsp;euros par élève pour le premier degré, 11&amp;nbsp;780&amp;nbsp;euros pour le second degré et à 13&amp;nbsp;350&amp;nbsp;euros pour le supérieur.</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr"/>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:19</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:20</t>
+        </is>
+      </c>
+      <c r="D1109" s="3" t="inlineStr">
+        <is>
+          <t>Comment changer l'école ?</t>
+        </is>
+      </c>
+      <c r="E1109" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-changer-lecole-294919</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>Comment changer l'école&amp;nbsp;? Dans Le Grand Entretien, une spécialiste des mathématiques et des questions éducatives partage son expertise&amp;nbsp;: Laure Saint-Raymond, professeure au Collège de France et membre de l’Académie des sciences depuis 2013.</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr"/>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:19</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:55</t>
+        </is>
+      </c>
+      <c r="D1110" s="3" t="inlineStr">
+        <is>
+          <t>Iran : l’échec stratégique de Donald Trump</t>
+        </is>
+      </c>
+      <c r="E1110" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/iran-lechec-strategique-de-donald-trump-294376</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>L’impasse à Ormuz révèle l’échec de la stratégie de Trump face à l’Iran et les limites de la puissance américaine, incapable d’imposer ses conditions à Téhéran.</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr"/>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:19</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:48</t>
+        </is>
+      </c>
+      <c r="D1111" s="3" t="inlineStr">
+        <is>
+          <t>« Si les démocrates gagnent, l’Amérique brûlera comme la France » : comment Trump instrumentalise la crise française</t>
+        </is>
+      </c>
+      <c r="E1111" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/si-les-democrates-gagnent-lamerique-brulera-comme-la-france-comment-trump-instrumentalise-la-crise-francaise-294881</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>Trump et ses alliés instrumentalisent les violences en France pour mobiliser leur électorat, dénoncer l’immigration et promouvoir un récit de déclin civilisationnel.</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr"/>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:19</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:27</t>
+        </is>
+      </c>
+      <c r="D1112" s="3" t="inlineStr">
+        <is>
+          <t>Les frappes de drones ukrainiens contre les centres de données russes pourraient changer notre regard sur la désinformation</t>
+        </is>
+      </c>
+      <c r="E1112" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-frappes-de-drones-ukrainiens-contre-les-centres-de-donnees-russes-pourraient-changer-notre-regard-sur-la-desinformation-294883</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>Les frappes ukrainiennes contre des centres de données russes rappellent que la désinformation repose sur des infrastructures physiques. Elles révèlent aussi les fragilités d’une souveraineté numérique fondée sur l’isolement.</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr"/>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:19</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:57</t>
+        </is>
+      </c>
+      <c r="D1113" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi il est erroné de ne voir les houthistes que comme des supplétifs de l’Iran</t>
+        </is>
+      </c>
+      <c r="E1113" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-il-est-errone-de-ne-voir-les-houthistes-que-comme-des-suppletifs-de-liran-294610</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>Les houthistes, qui contrôlent un tiers du Yémen, s’en prennent à l’Arabie saoudite qui soutient le gouvernement internationalement reconnu installé à Aden.</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr"/>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:19</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:31</t>
+        </is>
+      </c>
+      <c r="D1114" s="3" t="inlineStr">
+        <is>
+          <t>Manifestations : la tentation de l’ingérence étrangère</t>
+        </is>
+      </c>
+      <c r="E1114" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/21/manifestations-la-tentation-de-lingerence-etrangere/</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>Dans la colère qui s’exprime dans les rues européennes, Moscou et Washington trouvent un terrain propice à leur guerre politique L’article Manifestations&amp;#160;: la tentation de l&amp;rsquo;ingérence étrangère est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr"/>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:19</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:15</t>
+        </is>
+      </c>
+      <c r="D1115" s="3" t="inlineStr">
+        <is>
+          <t>Les flux de pétrole du golfe Persique ont dépassé leur niveau pré-guerre</t>
+        </is>
+      </c>
+      <c r="E1115" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/21/les-flux-de-petrole-du-golfe-persique-ont-depasse-leur-niveau-pre-guerre/</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>Une partie du pétrole iranien transiterait par les Émirats arabes unis L’article Les flux de pétrole du golfe Persique ont dépassé leur niveau pré-guerre est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr"/>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:19</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>2026-10-21 04:30</t>
+        </is>
+      </c>
+      <c r="D1116" s="3" t="inlineStr">
+        <is>
+          <t>Il y a eu plus de transits sur la route maritime du Nord en neuf mois qu’au cours de l’année 2025</t>
+        </is>
+      </c>
+      <c r="E1116" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/21/il-y-a-eu-plus-de-transits-sur-la-route-maritime-du-nord-en-neuf-mois-quau-cours-de-lannee-2025/</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>La fonte des glaces facilite la circulation maritime dans l’Arctique L’article Il y a eu plus de transits sur la route maritime du Nord en neuf mois qu’au cours de l’année 2025 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr"/>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:19</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>2026-10-21 04:00</t>
+        </is>
+      </c>
+      <c r="D1117" s="3" t="inlineStr">
+        <is>
+          <t>La planète brûle. Les médias regardent ailleurs</t>
+        </is>
+      </c>
+      <c r="E1117" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/21/la-planete-brule-les-medias-regardent-ailleurs/</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>La disruption climatique s'accélère, l'inquiétude augmente, pourtant la couverture du réchauffement a chuté. Pourquoi&amp;#160;? L’article La planète brûle. Les médias regardent ailleurs est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr"/>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:19</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>2026-10-20 17:16</t>
+        </is>
+      </c>
+      <c r="D1118" s="3" t="inlineStr">
+        <is>
+          <t>Après les midterms, la politique internationale de Trump va devenir encore plus déjantée</t>
+        </is>
+      </c>
+      <c r="E1118" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/20/apres-les-midterms-la-politique-internationale-de-trump-va-devenir-encore-plus-dejante/</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>L’un des meilleurs spécialistes américains des relations internationales démonte les idées reçues et les faux espoirs L’article Après les midterms, la politique internationale de Trump va devenir encore plus déjantée est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr"/>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:19</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>2026-10-20 16:54</t>
+        </is>
+      </c>
+      <c r="D1119" s="3" t="inlineStr">
+        <is>
+          <t>Le front digital des émeutes en France</t>
+        </is>
+      </c>
+      <c r="E1119" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/20/le-front-digital-des-emeutes-en-france/</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>Sans prendre le contrôle de cette infrastructure critique, aucun système démocratique ne pourra subsister L’article Le front digital des émeutes en France est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr"/>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:19</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>2026-10-20 16:45</t>
+        </is>
+      </c>
+      <c r="D1120" s="3" t="inlineStr">
+        <is>
+          <t>Anthropic représente-t-elle le futur du travail à l’ère de l’IA ?</t>
+        </is>
+      </c>
+      <c r="E1120" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/20/anthropic-represente-t-elle-le-futur-du-travail-a-lere-de-lia/</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>Dans l’entreprise, les agents IA cumulent 6 fois plus d’heures de travail que les humains L’article Anthropic représente-t-elle le futur du travail à l’ère de l’IA&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -36862,6 +37342,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1103" r:id="rId1102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1104" r:id="rId1103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1105" r:id="rId1104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1106" r:id="rId1105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1107" r:id="rId1106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1108" r:id="rId1107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1109" r:id="rId1108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1110" r:id="rId1109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1111" r:id="rId1110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1112" r:id="rId1111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1113" r:id="rId1112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1114" r:id="rId1113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1115" r:id="rId1114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1116" r:id="rId1115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1117" r:id="rId1116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1118" r:id="rId1117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1119" r:id="rId1118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1120" r:id="rId1119"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1120"/>
+  <dimension ref="A1:G1129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -35772,7 +35772,6 @@
           <t>Pendant la Révolution française, de riches collectionneurs anglais ont profité du démantèlement des monastères pour acquérir des livres rares, parfois sous la contrainte ou par le vol. Une enquête révèle les origines troubles de leurs collections.</t>
         </is>
       </c>
-      <c r="G1106" t="inlineStr"/>
     </row>
     <row r="1107">
       <c r="A1107" s="2" t="inlineStr">
@@ -35805,7 +35804,6 @@
           <t>En France, les grands-parents d’enfants autistes jouent un rôle majeur auprès de leur famille, mais restent encore peu reconnus par les équipes soignantes.</t>
         </is>
       </c>
-      <c r="G1107" t="inlineStr"/>
     </row>
     <row r="1108">
       <c r="A1108" s="2" t="inlineStr">
@@ -35838,7 +35836,6 @@
           <t>En 2025, la dépense moyenne annuelle s’établit à 9&amp;nbsp;440&amp;nbsp;euros par élève pour le premier degré, 11&amp;nbsp;780&amp;nbsp;euros pour le second degré et à 13&amp;nbsp;350&amp;nbsp;euros pour le supérieur.</t>
         </is>
       </c>
-      <c r="G1108" t="inlineStr"/>
     </row>
     <row r="1109">
       <c r="A1109" s="2" t="inlineStr">
@@ -35871,7 +35868,6 @@
           <t>Comment changer l'école&amp;nbsp;? Dans Le Grand Entretien, une spécialiste des mathématiques et des questions éducatives partage son expertise&amp;nbsp;: Laure Saint-Raymond, professeure au Collège de France et membre de l’Académie des sciences depuis 2013.</t>
         </is>
       </c>
-      <c r="G1109" t="inlineStr"/>
     </row>
     <row r="1110">
       <c r="A1110" s="2" t="inlineStr">
@@ -35904,7 +35900,6 @@
           <t>L’impasse à Ormuz révèle l’échec de la stratégie de Trump face à l’Iran et les limites de la puissance américaine, incapable d’imposer ses conditions à Téhéran.</t>
         </is>
       </c>
-      <c r="G1110" t="inlineStr"/>
     </row>
     <row r="1111">
       <c r="A1111" s="2" t="inlineStr">
@@ -35937,7 +35932,6 @@
           <t>Trump et ses alliés instrumentalisent les violences en France pour mobiliser leur électorat, dénoncer l’immigration et promouvoir un récit de déclin civilisationnel.</t>
         </is>
       </c>
-      <c r="G1111" t="inlineStr"/>
     </row>
     <row r="1112">
       <c r="A1112" s="2" t="inlineStr">
@@ -35970,7 +35964,6 @@
           <t>Les frappes ukrainiennes contre des centres de données russes rappellent que la désinformation repose sur des infrastructures physiques. Elles révèlent aussi les fragilités d’une souveraineté numérique fondée sur l’isolement.</t>
         </is>
       </c>
-      <c r="G1112" t="inlineStr"/>
     </row>
     <row r="1113">
       <c r="A1113" s="2" t="inlineStr">
@@ -36003,7 +35996,6 @@
           <t>Les houthistes, qui contrôlent un tiers du Yémen, s’en prennent à l’Arabie saoudite qui soutient le gouvernement internationalement reconnu installé à Aden.</t>
         </is>
       </c>
-      <c r="G1113" t="inlineStr"/>
     </row>
     <row r="1114">
       <c r="A1114" s="2" t="inlineStr">
@@ -36036,7 +36028,6 @@
           <t>Dans la colère qui s’exprime dans les rues européennes, Moscou et Washington trouvent un terrain propice à leur guerre politique L’article Manifestations&amp;#160;: la tentation de l&amp;rsquo;ingérence étrangère est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1114" t="inlineStr"/>
     </row>
     <row r="1115">
       <c r="A1115" s="2" t="inlineStr">
@@ -36069,7 +36060,6 @@
           <t>Une partie du pétrole iranien transiterait par les Émirats arabes unis L’article Les flux de pétrole du golfe Persique ont dépassé leur niveau pré-guerre est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1115" t="inlineStr"/>
     </row>
     <row r="1116">
       <c r="A1116" s="2" t="inlineStr">
@@ -36102,7 +36092,6 @@
           <t>La fonte des glaces facilite la circulation maritime dans l’Arctique L’article Il y a eu plus de transits sur la route maritime du Nord en neuf mois qu’au cours de l’année 2025 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1116" t="inlineStr"/>
     </row>
     <row r="1117">
       <c r="A1117" s="2" t="inlineStr">
@@ -36135,7 +36124,6 @@
           <t>La disruption climatique s'accélère, l'inquiétude augmente, pourtant la couverture du réchauffement a chuté. Pourquoi&amp;#160;? L’article La planète brûle. Les médias regardent ailleurs est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1117" t="inlineStr"/>
     </row>
     <row r="1118">
       <c r="A1118" s="2" t="inlineStr">
@@ -36168,7 +36156,6 @@
           <t>L’un des meilleurs spécialistes américains des relations internationales démonte les idées reçues et les faux espoirs L’article Après les midterms, la politique internationale de Trump va devenir encore plus déjantée est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1118" t="inlineStr"/>
     </row>
     <row r="1119">
       <c r="A1119" s="2" t="inlineStr">
@@ -36201,7 +36188,6 @@
           <t>Sans prendre le contrôle de cette infrastructure critique, aucun système démocratique ne pourra subsister L’article Le front digital des émeutes en France est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1119" t="inlineStr"/>
     </row>
     <row r="1120">
       <c r="A1120" s="2" t="inlineStr">
@@ -36234,7 +36220,303 @@
           <t>Dans l’entreprise, les agents IA cumulent 6 fois plus d’heures de travail que les humains L’article Anthropic représente-t-elle le futur du travail à l’ère de l’IA&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1120" t="inlineStr"/>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:18</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:44</t>
+        </is>
+      </c>
+      <c r="D1121" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi nous avons de plus en plus de mal à lire des textes longs – et comment entretenir cette capacité</t>
+        </is>
+      </c>
+      <c r="E1121" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-nous-avons-de-plus-en-plus-de-mal-a-lire-des-textes-longs-et-comment-entretenir-cette-capacite-293870</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>Quelles sont les conditions essentielles à préserver pour que la lecture reste un moyen pour chacun de se construire et de donner forme à son expérience&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr"/>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:18</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:46</t>
+        </is>
+      </c>
+      <c r="D1122" s="3" t="inlineStr">
+        <is>
+          <t>Parler de religion quand on est un démocrate dans un État républicain : le pari de James Talarico pour remporter l’élection sénatoriale au Texas</t>
+        </is>
+      </c>
+      <c r="E1122" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/parler-de-religion-quand-on-est-un-democrate-dans-un-etat-republicain-le-pari-de-james-talarico-pour-remporter-lelection-senatoriale-au-texas-294618</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>Candidat à un poste de sénateur du Texas au Congrès fédéral, James&amp;nbsp;Talarico n’est pas un démocrate ordinaire&amp;nbsp;: il met sans cesse sa foi en avant, ce qui est généralement l’apanage des candidats républicains.</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr"/>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:18</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:43</t>
+        </is>
+      </c>
+      <c r="D1123" s="3" t="inlineStr">
+        <is>
+          <t>Ultimatum de Trump à la Cour pénale internationale : un catalyseur de la souveraineté européenne ?</t>
+        </is>
+      </c>
+      <c r="E1123" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/ultimatum-de-trump-a-la-cour-penale-internationale-un-catalyseur-de-la-souverainete-europeenne-294377</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>Donald Trump a franchi une étape dans les menaces contre la Cour pénale internationale. L’UE a-t-elle les moyens de riposter&amp;nbsp;? Le peut-elle&amp;nbsp;? L’euro numérique serait-il un outil plus efficace&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr"/>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:18</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:55</t>
+        </is>
+      </c>
+      <c r="D1124" s="3" t="inlineStr">
+        <is>
+          <t>Comment des acteurs étrangers ont attisé la colère en ligne autour des manifestations du 17 octobre en France</t>
+        </is>
+      </c>
+      <c r="E1124" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/22/comment-des-acteurs-etrangers-ont-attise-la-colere-en-ligne-autour-des-manifestations-du-17-octobre-en-france/</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>Une étude quantitative révèle l’ampleur de l’amplification étrangère L’article Comment des acteurs étrangers ont attisé la colère en ligne autour des manifestations du 17 octobre en France est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr"/>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:18</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:57</t>
+        </is>
+      </c>
+      <c r="D1125" s="3" t="inlineStr">
+        <is>
+          <t>La crise française de la dette s’accélère</t>
+        </is>
+      </c>
+      <c r="E1125" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/22/la-crise-francaise-de-la-dette-saccelere/</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>L’écart entre les taux d’emprunt français et allemand est à son plus haut niveau depuis 2011 L’article La crise française de la dette s’accélère est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr"/>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:18</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>2026-10-22 04:30</t>
+        </is>
+      </c>
+      <c r="D1126" s="3" t="inlineStr">
+        <is>
+          <t>Aux États-Unis, l’IA siphonne le capital</t>
+        </is>
+      </c>
+      <c r="E1126" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/22/aux-etats-unis-lia-siphonne-le-capital/</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>Les investissements massifs dans l’IA se font au détriment d’autres secteurs L’article Aux États-Unis, l’IA siphonne le capital est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr"/>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:18</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>2026-10-22 04:30</t>
+        </is>
+      </c>
+      <c r="D1127" s="3" t="inlineStr">
+        <is>
+          <t>Bolsonaro et l’influence évangélique : enquête</t>
+        </is>
+      </c>
+      <c r="E1127" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/22/je-ne-peux-pas-vous-demander-de-voter-pour-moi-mais-je-peux-vous-conseiller-ce-que-letude-des-offices-dit-du-vote-religieux-au-bresil/</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>Les pasteurs sont-ils en train de faire basculer le Brésil&amp;#160;? L’article Bolsonaro et l&amp;rsquo;influence évangélique&amp;#160;: enquête est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr"/>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:18</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:37</t>
+        </is>
+      </c>
+      <c r="D1128" s="3" t="inlineStr">
+        <is>
+          <t>La guerre en Ukraine s’étend à l’espace</t>
+        </is>
+      </c>
+      <c r="E1128" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/21/la-guerre-en-ukraine-setend-a-lespace/</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>En Europe, trois sites liés à Starlink ont été ciblé ces dernières semaines L’article La guerre en Ukraine s’étend à l’espace est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr"/>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:18</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:46</t>
+        </is>
+      </c>
+      <c r="D1129" s="3" t="inlineStr">
+        <is>
+          <t>Demi-journée d’étude : À mon tour de voter ! Présidentielle 2027 : comment en parler aux élèves?</t>
+        </is>
+      </c>
+      <c r="E1129" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/demi-journee-detude-a-mon-tour-de-voter-presidentielle-2027-comment-en-parler-aux-eleves/</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>Pensée pour les enseignants de lycées, cette rencontre vise à apporter des clés de lecture et des outils pédagogiques concrets pour aborder les institutions et le vote avec leurs élèves. Autour d&amp;#8217; un état des lieux de l&amp;#8217;opinion démocratique, de regards historiques et d&amp;#8217;échanges pédagogiques, la journée s&amp;#8217;achèvera par une présentation de nos ressources dédiées [&amp;#8230;] L’article Demi-journée d&amp;rsquo;étude : À mon tour de voter ! Présidentielle 2027 : comment en parler aux</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -37357,6 +37639,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1118" r:id="rId1117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1119" r:id="rId1118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1120" r:id="rId1119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1121" r:id="rId1120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1122" r:id="rId1121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1123" r:id="rId1122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1124" r:id="rId1123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1125" r:id="rId1124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1126" r:id="rId1125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1127" r:id="rId1126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1128" r:id="rId1127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1129" r:id="rId1128"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1129"/>
+  <dimension ref="A1:G1140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -36252,7 +36252,6 @@
           <t>Quelles sont les conditions essentielles à préserver pour que la lecture reste un moyen pour chacun de se construire et de donner forme à son expérience&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G1121" t="inlineStr"/>
     </row>
     <row r="1122">
       <c r="A1122" s="2" t="inlineStr">
@@ -36285,7 +36284,6 @@
           <t>Candidat à un poste de sénateur du Texas au Congrès fédéral, James&amp;nbsp;Talarico n’est pas un démocrate ordinaire&amp;nbsp;: il met sans cesse sa foi en avant, ce qui est généralement l’apanage des candidats républicains.</t>
         </is>
       </c>
-      <c r="G1122" t="inlineStr"/>
     </row>
     <row r="1123">
       <c r="A1123" s="2" t="inlineStr">
@@ -36318,7 +36316,6 @@
           <t>Donald Trump a franchi une étape dans les menaces contre la Cour pénale internationale. L’UE a-t-elle les moyens de riposter&amp;nbsp;? Le peut-elle&amp;nbsp;? L’euro numérique serait-il un outil plus efficace&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G1123" t="inlineStr"/>
     </row>
     <row r="1124">
       <c r="A1124" s="2" t="inlineStr">
@@ -36351,7 +36348,6 @@
           <t>Une étude quantitative révèle l’ampleur de l’amplification étrangère L’article Comment des acteurs étrangers ont attisé la colère en ligne autour des manifestations du 17 octobre en France est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1124" t="inlineStr"/>
     </row>
     <row r="1125">
       <c r="A1125" s="2" t="inlineStr">
@@ -36384,7 +36380,6 @@
           <t>L’écart entre les taux d’emprunt français et allemand est à son plus haut niveau depuis 2011 L’article La crise française de la dette s’accélère est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1125" t="inlineStr"/>
     </row>
     <row r="1126">
       <c r="A1126" s="2" t="inlineStr">
@@ -36417,7 +36412,6 @@
           <t>Les investissements massifs dans l’IA se font au détriment d’autres secteurs L’article Aux États-Unis, l’IA siphonne le capital est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1126" t="inlineStr"/>
     </row>
     <row r="1127">
       <c r="A1127" s="2" t="inlineStr">
@@ -36450,7 +36444,6 @@
           <t>Les pasteurs sont-ils en train de faire basculer le Brésil&amp;#160;? L’article Bolsonaro et l&amp;rsquo;influence évangélique&amp;#160;: enquête est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1127" t="inlineStr"/>
     </row>
     <row r="1128">
       <c r="A1128" s="2" t="inlineStr">
@@ -36483,7 +36476,6 @@
           <t>En Europe, trois sites liés à Starlink ont été ciblé ces dernières semaines L’article La guerre en Ukraine s’étend à l’espace est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1128" t="inlineStr"/>
     </row>
     <row r="1129">
       <c r="A1129" s="2" t="inlineStr">
@@ -36516,7 +36508,369 @@
           <t>Pensée pour les enseignants de lycées, cette rencontre vise à apporter des clés de lecture et des outils pédagogiques concrets pour aborder les institutions et le vote avec leurs élèves. Autour d&amp;#8217; un état des lieux de l&amp;#8217;opinion démocratique, de regards historiques et d&amp;#8217;échanges pédagogiques, la journée s&amp;#8217;achèvera par une présentation de nos ressources dédiées [&amp;#8230;] L’article Demi-journée d&amp;rsquo;étude : À mon tour de voter ! Présidentielle 2027 : comment en parler aux</t>
         </is>
       </c>
-      <c r="G1129" t="inlineStr"/>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:01</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:30</t>
+        </is>
+      </c>
+      <c r="D1130" s="3" t="inlineStr">
+        <is>
+          <t>Ratés, faux sondages, marchés prédictifs : la mauvaise passe des sondeurs américains avant les midterms</t>
+        </is>
+      </c>
+      <c r="E1130" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/rates-faux-sondages-marches-predictifs-la-mauvaise-passe-des-sondeurs-americains-avant-les-midterms-294959</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>Ratés à répétition depuis 2016, faux sondages, concurrence des marchés prédictifs et des réponses simulées par l’IA : les instituts américains abordent les élections de mi-mandat du 3 novembre en terrain miné.</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr"/>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:01</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:05</t>
+        </is>
+      </c>
+      <c r="D1131" s="3" t="inlineStr">
+        <is>
+          <t>Les sondages sont des instantanés, pas des prédictions : ce que montre la campagne électorale néo-zélandaise</t>
+        </is>
+      </c>
+      <c r="E1131" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-sondages-sont-des-instantanes-pas-des-predictions-ce-que-montre-la-campagne-electorale-neo-zelandaise-294960</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>En Nouvelle-Zélande, où les législatives ont lieu le 7 novembre 2026, les sondages se multiplient. Mais chacun n’est qu’une photographie floue de l’opinion à un instant passé : il ne permet pas de prédire le résultat du scrutin.</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr"/>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:01</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:43</t>
+        </is>
+      </c>
+      <c r="D1132" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi la multiplication des sondages nuit à l’information des électeurs : les leçons du cas australien</t>
+        </is>
+      </c>
+      <c r="E1132" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-la-multiplication-des-sondages-nuit-a-linformation-des-electeurs-les-lecons-du-cas-australien-294961</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>En Australie, quelque 140 sondages ont été publiés depuis les élections fédérales de 2025, sur fond de poussée de One Nation. Des études montrent que leur couverture façon « journalisme hippique » nourrit le cynisme.</t>
+        </is>
+      </c>
+      <c r="G1132" t="inlineStr"/>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:01</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:48</t>
+        </is>
+      </c>
+      <c r="D1133" s="3" t="inlineStr">
+        <is>
+          <t>La révocation du procureur de la CPI : quand permanence ne rime pas avec prévoyance</t>
+        </is>
+      </c>
+      <c r="E1133" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/la-revocation-du-procureur-de-la-cpi-quand-permanence-ne-rime-pas-avec-prevoyance-293894</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>L’affaire Karim Khan révèle une faille. Face à l’incomplétude des règles, la CPI a dû préciser les garanties et les modalités de la procédure en cours de route.</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr"/>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:01</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:46</t>
+        </is>
+      </c>
+      <c r="D1134" s="3" t="inlineStr">
+        <is>
+          <t>Le paradoxe Alain Soral</t>
+        </is>
+      </c>
+      <c r="E1134" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/23/le-paradoxe-alain-soral/</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>Enquête sur le national-conspirationnisme, l’idéologie de l'extrémiste qui dérange l’extrême droite française L’article Le paradoxe Alain Soral est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr"/>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:01</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:02</t>
+        </is>
+      </c>
+      <c r="D1135" s="3" t="inlineStr">
+        <is>
+          <t>En Italie, la grève des camionneurs paralyse le Sud du pays</t>
+        </is>
+      </c>
+      <c r="E1135" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/23/en-italie-la-greve-des-camionneurs-paralyse-le-sud-du-pays/</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>Les producteurs de mozzarella ont été contraints de suspendre leur production L’article En Italie, la grève des camionneurs paralyse le Sud du pays est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr"/>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:01</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>2026-10-23 04:30</t>
+        </is>
+      </c>
+      <c r="D1136" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : Poutine peut-il se permettre de livrer du carburant aux États-Unis ?</t>
+        </is>
+      </c>
+      <c r="E1136" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/23/economie-russe-poutine-peut-il-se-permettre-de-livrer-du-carburant-aux-etats-unis/</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>Les marges de manœuvre de Moscou sont limitées par la guerre L’article Économie russe&amp;#160;: Poutine peut-il se permettre de livrer du carburant aux États-Unis&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr"/>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:01</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>2026-10-23 04:00</t>
+        </is>
+      </c>
+      <c r="D1137" s="3" t="inlineStr">
+        <is>
+          <t>En Ukraine, le piège du cessez-le-feu trumpiste</t>
+        </is>
+      </c>
+      <c r="E1137" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/23/en-ukraine-le-piege-du-cessez-le-feu-trumpiste/</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>Pourquoi une trêve en Ukraine, sans dissuasion européenne, préparerait la prochaine guerre L’article En Ukraine, le piège du cessez-le-feu trumpiste est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr"/>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:01</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:46</t>
+        </is>
+      </c>
+      <c r="D1138" s="3" t="inlineStr">
+        <is>
+          <t>Les Français cherchent à se procurer des armes d’autodéfense, en amont d’un nouveau week-end de mobilisation</t>
+        </is>
+      </c>
+      <c r="E1138" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/22/les-francais-cherchent-a-se-procurer-des-armes-dautodefense-en-amont-dun-nouveau-week-end-de-mobilisation/</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>Les recherches Google pour «&amp;#160;armurerie&amp;#160;» ou «&amp;#160;batte de baseball&amp;#160;» ont bondi L’article Les Français cherchent à se procurer des armes d’autodéfense, en amont d’un nouveau week-end de mobilisation est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr"/>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:01</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>2026-10-22 18:17</t>
+        </is>
+      </c>
+      <c r="D1139" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce Agrégation interne aux Rendez-vous de l’histoire de Blois 2026 – les supports des interventions</t>
+        </is>
+      </c>
+      <c r="E1139" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/operation-blois-2026/</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page les supports des interventions qui se sont déroulées lors de l&amp;#8217;après-midi organisée le samedi 10 octobre par l&amp;#8217;APHG. Cette page [&amp;#8230;] L’article Coup de pouce Agrégation interne aux Rendez-vous de l&amp;rsquo;histoire de Blois 2026 &amp;#8211; les supports des in</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr"/>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:01</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>2026-10-22 17:57</t>
+        </is>
+      </c>
+      <c r="D1140" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce Agrégation interne – Marie Redon – Le Pacifique dans la nouvelle géopolitique insulaire mondiale</t>
+        </is>
+      </c>
+      <c r="E1140" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/coup-de-pouce-agregation-interne-marie-redon-le-pacifique-dans-la-nouvelle-geopolitique-insulaire-mondiale/</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Marie Redon consacrée au thème « le Pacifique dans la nouvelle géopolitique insulaire mondiale ». Le podcast est proposé [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Marie Redon &amp;#8211; Le Pacifique dans la nouvelle géopolitique insulaire m</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -37648,6 +38002,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1127" r:id="rId1126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1128" r:id="rId1127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1129" r:id="rId1128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1130" r:id="rId1129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1131" r:id="rId1130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1132" r:id="rId1131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1133" r:id="rId1132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1134" r:id="rId1133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1135" r:id="rId1134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1136" r:id="rId1135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1137" r:id="rId1136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1138" r:id="rId1137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1139" r:id="rId1138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1140" r:id="rId1139"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1140"/>
+  <dimension ref="A1:G1144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -36540,7 +36540,6 @@
           <t>Ratés à répétition depuis 2016, faux sondages, concurrence des marchés prédictifs et des réponses simulées par l’IA : les instituts américains abordent les élections de mi-mandat du 3 novembre en terrain miné.</t>
         </is>
       </c>
-      <c r="G1130" t="inlineStr"/>
     </row>
     <row r="1131">
       <c r="A1131" s="2" t="inlineStr">
@@ -36573,7 +36572,6 @@
           <t>En Nouvelle-Zélande, où les législatives ont lieu le 7 novembre 2026, les sondages se multiplient. Mais chacun n’est qu’une photographie floue de l’opinion à un instant passé : il ne permet pas de prédire le résultat du scrutin.</t>
         </is>
       </c>
-      <c r="G1131" t="inlineStr"/>
     </row>
     <row r="1132">
       <c r="A1132" s="2" t="inlineStr">
@@ -36606,7 +36604,6 @@
           <t>En Australie, quelque 140 sondages ont été publiés depuis les élections fédérales de 2025, sur fond de poussée de One Nation. Des études montrent que leur couverture façon « journalisme hippique » nourrit le cynisme.</t>
         </is>
       </c>
-      <c r="G1132" t="inlineStr"/>
     </row>
     <row r="1133">
       <c r="A1133" s="2" t="inlineStr">
@@ -36639,7 +36636,6 @@
           <t>L’affaire Karim Khan révèle une faille. Face à l’incomplétude des règles, la CPI a dû préciser les garanties et les modalités de la procédure en cours de route.</t>
         </is>
       </c>
-      <c r="G1133" t="inlineStr"/>
     </row>
     <row r="1134">
       <c r="A1134" s="2" t="inlineStr">
@@ -36672,7 +36668,6 @@
           <t>Enquête sur le national-conspirationnisme, l’idéologie de l'extrémiste qui dérange l’extrême droite française L’article Le paradoxe Alain Soral est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1134" t="inlineStr"/>
     </row>
     <row r="1135">
       <c r="A1135" s="2" t="inlineStr">
@@ -36705,7 +36700,6 @@
           <t>Les producteurs de mozzarella ont été contraints de suspendre leur production L’article En Italie, la grève des camionneurs paralyse le Sud du pays est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1135" t="inlineStr"/>
     </row>
     <row r="1136">
       <c r="A1136" s="2" t="inlineStr">
@@ -36738,7 +36732,6 @@
           <t>Les marges de manœuvre de Moscou sont limitées par la guerre L’article Économie russe&amp;#160;: Poutine peut-il se permettre de livrer du carburant aux États-Unis&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1136" t="inlineStr"/>
     </row>
     <row r="1137">
       <c r="A1137" s="2" t="inlineStr">
@@ -36771,7 +36764,6 @@
           <t>Pourquoi une trêve en Ukraine, sans dissuasion européenne, préparerait la prochaine guerre L’article En Ukraine, le piège du cessez-le-feu trumpiste est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1137" t="inlineStr"/>
     </row>
     <row r="1138">
       <c r="A1138" s="2" t="inlineStr">
@@ -36804,7 +36796,6 @@
           <t>Les recherches Google pour «&amp;#160;armurerie&amp;#160;» ou «&amp;#160;batte de baseball&amp;#160;» ont bondi L’article Les Français cherchent à se procurer des armes d’autodéfense, en amont d’un nouveau week-end de mobilisation est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1138" t="inlineStr"/>
     </row>
     <row r="1139">
       <c r="A1139" s="2" t="inlineStr">
@@ -36837,7 +36828,6 @@
           <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page les supports des interventions qui se sont déroulées lors de l&amp;#8217;après-midi organisée le samedi 10 octobre par l&amp;#8217;APHG. Cette page [&amp;#8230;] L’article Coup de pouce Agrégation interne aux Rendez-vous de l&amp;rsquo;histoire de Blois 2026 &amp;#8211; les supports des in</t>
         </is>
       </c>
-      <c r="G1139" t="inlineStr"/>
     </row>
     <row r="1140">
       <c r="A1140" s="2" t="inlineStr">
@@ -36870,7 +36860,138 @@
           <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Marie Redon consacrée au thème « le Pacifique dans la nouvelle géopolitique insulaire mondiale ». Le podcast est proposé [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Marie Redon &amp;#8211; Le Pacifique dans la nouvelle géopolitique insulaire m</t>
         </is>
       </c>
-      <c r="G1140" t="inlineStr"/>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 13:03</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:33</t>
+        </is>
+      </c>
+      <c r="D1141" s="3" t="inlineStr">
+        <is>
+          <t>Après une guerre, quelle éducation pour construire la paix ?</t>
+        </is>
+      </c>
+      <c r="E1141" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/apres-une-guerre-quelle-education-pour-construire-la-paix-290799</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>Après un conflit, reconstruire l’éducation ne consiste pas seulement à rouvrir les écoles. Les programmes, les manuels et leur gouvernance pèsent aussi sur la mémoire collective.</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr"/>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 13:03</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:00</t>
+        </is>
+      </c>
+      <c r="D1142" s="3" t="inlineStr">
+        <is>
+          <t>En Serbie, les étudiants manifestent depuis deux ans. Peuvent-ils faire tomber Vučić dans les urnes ?</t>
+        </is>
+      </c>
+      <c r="E1142" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/24/bojan-vranic-serbie/</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>Ce dimanche 25 octobre, les élections législatives mettent à l’épreuve quatorze ans de domination politique L’article En Serbie, les étudiants manifestent depuis deux ans. Peuvent-ils faire tomber Vučić dans les urnes&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr"/>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 13:03</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>2026-10-24 04:30</t>
+        </is>
+      </c>
+      <c r="D1143" s="3" t="inlineStr">
+        <is>
+          <t>À une semaine des élections de mi-mandat, Obama s’engage dans la campagne</t>
+        </is>
+      </c>
+      <c r="E1143" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/24/a-une-semaine-des-elections-de-mi-mandat-obama-sengage-dans-la-campagne/</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>L’ancien président démocrate était jusqu’à présent resté en retrait L’article À une semaine des élections de mi-mandat, Obama s’engage dans la campagne est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr"/>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 13:03</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>2026-10-23 16:12</t>
+        </is>
+      </c>
+      <c r="D1144" s="3" t="inlineStr">
+        <is>
+          <t>Une start-up de la Silicon Valley vient de lever 200 millions de dollars pour concevoir des chiens de guerre génétiquement modifiés</t>
+        </is>
+      </c>
+      <c r="E1144" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/23/un-programme-captain-america-pour-chiens-au-texas-une-start-up-veut-modifier-genetiquement-les-auxiliaires-canins-de-larmee-americaine/</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>Le «&amp;#160;programme Captain America pour les chiens&amp;#160;» n’est pas une plaisanterie dystopique L’article Une start-up de la Silicon Valley vient de lever 200 millions de dollars pour concevoir des chiens de guerre génétiquement modifiés est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -38013,6 +38134,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1138" r:id="rId1137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1139" r:id="rId1138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1140" r:id="rId1139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1141" r:id="rId1140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1142" r:id="rId1141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1143" r:id="rId1142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1144" r:id="rId1143"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1144"/>
+  <dimension ref="A1:G1150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -36892,7 +36892,6 @@
           <t>Après un conflit, reconstruire l’éducation ne consiste pas seulement à rouvrir les écoles. Les programmes, les manuels et leur gouvernance pèsent aussi sur la mémoire collective.</t>
         </is>
       </c>
-      <c r="G1141" t="inlineStr"/>
     </row>
     <row r="1142">
       <c r="A1142" s="2" t="inlineStr">
@@ -36925,7 +36924,6 @@
           <t>Ce dimanche 25 octobre, les élections législatives mettent à l’épreuve quatorze ans de domination politique L’article En Serbie, les étudiants manifestent depuis deux ans. Peuvent-ils faire tomber Vučić dans les urnes&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1142" t="inlineStr"/>
     </row>
     <row r="1143">
       <c r="A1143" s="2" t="inlineStr">
@@ -36958,7 +36956,6 @@
           <t>L’ancien président démocrate était jusqu’à présent resté en retrait L’article À une semaine des élections de mi-mandat, Obama s’engage dans la campagne est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1143" t="inlineStr"/>
     </row>
     <row r="1144">
       <c r="A1144" s="2" t="inlineStr">
@@ -36991,7 +36988,204 @@
           <t>Le «&amp;#160;programme Captain America pour les chiens&amp;#160;» n’est pas une plaisanterie dystopique L’article Une start-up de la Silicon Valley vient de lever 200 millions de dollars pour concevoir des chiens de guerre génétiquement modifiés est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1144" t="inlineStr"/>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 13:32</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>2026-10-25 07:05</t>
+        </is>
+      </c>
+      <c r="D1145" s="3" t="inlineStr">
+        <is>
+          <t>Qui peut protéger le royaume saoudien ?</t>
+        </is>
+      </c>
+      <c r="E1145" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/qui-peut-proteger-le-royaume-saoudien-294696</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>Abandonné par Washington, Riyad, plus que jamais dans la ligne de mire de l’Iran et des houthistes du Yémen, doit se chercher de nouveaux parrains.</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr"/>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 13:32</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>2026-10-25 07:02</t>
+        </is>
+      </c>
+      <c r="D1146" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi l’eau potable manque encore dans l’archipel de Marajó, l’une des régions les plus riches en eau du monde</t>
+        </is>
+      </c>
+      <c r="E1146" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-leau-potable-manque-encore-dans-larchipel-de-marajo-lune-des-regions-les-plus-riches-en-eau-du-monde-295018</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>Dans l’archipel de Marajó, en Amazonie brésilienne, des milliers de familles restent privées d’eau potable malgré l’abondance de l’eau.</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr"/>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 13:32</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>2026-10-25 13:06</t>
+        </is>
+      </c>
+      <c r="D1147" s="3" t="inlineStr">
+        <is>
+          <t>L’autre visage du miracle chinois est dans le Hunan</t>
+        </is>
+      </c>
+      <c r="E1147" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/25/le-hunan-lautre-visage-du-miracle-chinois/</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>Des usines soviétiques aux géants industriels, de Mao à la culture virale, plongée dans une province qui raconte les métamorphoses de la Chine de Xi. L’article L’autre visage du miracle chinois est dans le Hunan est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr"/>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 13:32</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>2026-10-25 05:30</t>
+        </is>
+      </c>
+      <c r="D1148" s="3" t="inlineStr">
+        <is>
+          <t>Au Brésil, la victoire de Flávio Bolsonaro relancerait la déforestation de l’Amazonie</t>
+        </is>
+      </c>
+      <c r="E1148" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/25/au-bresil-la-victoire-de-flavio-bolsonaro-relancerait-la-deforestation-de-lamazonie/</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>En 18 ans, le Brésil a déboisé l’équivalent de la Grèce en Amazonie L’article Au Brésil, la victoire de Flávio Bolsonaro relancerait la déforestation de l’Amazonie est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr"/>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 13:32</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>2026-10-25 05:00</t>
+        </is>
+      </c>
+      <c r="D1149" s="3" t="inlineStr">
+        <is>
+          <t>L’incroyable histoire d’Ahmad Khan</t>
+        </is>
+      </c>
+      <c r="E1149" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/25/incroyable-histoire-dahmad-khan/</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>Le périple du fils d’un nabab indien déchu du XVIIIe siècle qui gagne l’Europe pour demander réparation L’article L’incroyable histoire d’Ahmad Khan est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr"/>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 13:32</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>2026-10-24 15:31</t>
+        </is>
+      </c>
+      <c r="D1150" s="3" t="inlineStr">
+        <is>
+          <t>Bukele a lancé une opération militaire spéciale contre les gangs à Haïti</t>
+        </is>
+      </c>
+      <c r="E1150" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/24/bukele-a-lance-une-operation-militaire-speciale-contre-les-gangs-a-haiti/</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>Dans l’ombre de Port-au-Prince une nouvelle force d’intervention intra-américaine est-elle en train de voir le jour&amp;#160;? L’article Bukele a lancé une opération militaire spéciale contre les gangs à Haïti est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -38138,6 +38332,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1142" r:id="rId1141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1143" r:id="rId1142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1144" r:id="rId1143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1145" r:id="rId1144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1146" r:id="rId1145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1147" r:id="rId1146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1148" r:id="rId1147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1149" r:id="rId1148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1150" r:id="rId1149"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1150"/>
+  <dimension ref="A1:G1155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -37020,7 +37020,6 @@
           <t>Abandonné par Washington, Riyad, plus que jamais dans la ligne de mire de l’Iran et des houthistes du Yémen, doit se chercher de nouveaux parrains.</t>
         </is>
       </c>
-      <c r="G1145" t="inlineStr"/>
     </row>
     <row r="1146">
       <c r="A1146" s="2" t="inlineStr">
@@ -37053,7 +37052,6 @@
           <t>Dans l’archipel de Marajó, en Amazonie brésilienne, des milliers de familles restent privées d’eau potable malgré l’abondance de l’eau.</t>
         </is>
       </c>
-      <c r="G1146" t="inlineStr"/>
     </row>
     <row r="1147">
       <c r="A1147" s="2" t="inlineStr">
@@ -37086,7 +37084,6 @@
           <t>Des usines soviétiques aux géants industriels, de Mao à la culture virale, plongée dans une province qui raconte les métamorphoses de la Chine de Xi. L’article L’autre visage du miracle chinois est dans le Hunan est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1147" t="inlineStr"/>
     </row>
     <row r="1148">
       <c r="A1148" s="2" t="inlineStr">
@@ -37119,7 +37116,6 @@
           <t>En 18 ans, le Brésil a déboisé l’équivalent de la Grèce en Amazonie L’article Au Brésil, la victoire de Flávio Bolsonaro relancerait la déforestation de l’Amazonie est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1148" t="inlineStr"/>
     </row>
     <row r="1149">
       <c r="A1149" s="2" t="inlineStr">
@@ -37152,7 +37148,6 @@
           <t>Le périple du fils d’un nabab indien déchu du XVIIIe siècle qui gagne l’Europe pour demander réparation L’article L’incroyable histoire d’Ahmad Khan est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1149" t="inlineStr"/>
     </row>
     <row r="1150">
       <c r="A1150" s="2" t="inlineStr">
@@ -37185,7 +37180,171 @@
           <t>Dans l’ombre de Port-au-Prince une nouvelle force d’intervention intra-américaine est-elle en train de voir le jour&amp;#160;? L’article Bukele a lancé une opération militaire spéciale contre les gangs à Haïti est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1150" t="inlineStr"/>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 15:48</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>2026-10-26 11:16</t>
+        </is>
+      </c>
+      <c r="D1151" s="3" t="inlineStr">
+        <is>
+          <t>Au Brésil, Lula réélu grâce à une mobilisation qui a déjoué les pronostics</t>
+        </is>
+      </c>
+      <c r="E1151" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/au-bresil-lula-reelu-grace-a-une-mobilisation-qui-a-dejoue-les-pronostics-295195</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>La réélection de Lula à la présidence du Brésil doit beaucoup à une mobilisation sur les réseaux sociaux qui s’est prolongée dans la rue. Mais face à une droite majoritaire au Parlement et dans les États, son nouveau mandat s’annonce difficile.</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr"/>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 15:48</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:44</t>
+        </is>
+      </c>
+      <c r="D1152" s="3" t="inlineStr">
+        <is>
+          <t>Comment l’Amérique latine réagit à la victoire de Lula</t>
+        </is>
+      </c>
+      <c r="E1152" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/26/comment-lamerique-latine-reagit-a-la-victoire-de-lula/</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>La défaite de Flávio Bolsonaro met en lumière l’isolement de Milei L’article Comment l’Amérique latine réagit à la victoire de Lula est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr"/>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 15:48</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>2026-10-26 07:08</t>
+        </is>
+      </c>
+      <c r="D1153" s="3" t="inlineStr">
+        <is>
+          <t>Lula : « Le Brésil n’est l’arrière-cour de personne »</t>
+        </is>
+      </c>
+      <c r="E1153" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/26/lula-discours-victoire-bresil/</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>Réélu à 80 ans, le président du Brésil cible Trump, les Bolsonaro et les géants de la tech. Son discours de victoire intégral. L’article Lula&amp;#160;: «&amp;#160;Le Brésil n’est l’arrière-cour de personne&amp;#160;» est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1153" t="inlineStr"/>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 15:48</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:58</t>
+        </is>
+      </c>
+      <c r="D1154" s="3" t="inlineStr">
+        <is>
+          <t>Le nouvel ordre énergétique mondial</t>
+        </is>
+      </c>
+      <c r="E1154" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/26/le-nouvel-ordre-energetique-mondial/</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>Selon le directeur de l’Agence internationale de l’énergie, après l’hégémonie du pétrole, «&amp;#160;l’âge de l’électricité est là.&amp;#160;» L’article Le nouvel ordre énergétique mondial est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr"/>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 15:48</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>2026-10-25 20:38</t>
+        </is>
+      </c>
+      <c r="D1155" s="3" t="inlineStr">
+        <is>
+          <t>Législatives serbes. Vučić : « Nous avons perdu les élections »</t>
+        </is>
+      </c>
+      <c r="E1155" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/25/legislatives-serbes-vucic-nous-avons-perdu-les-elections/</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>Avec une participation record depuis la chute de la Yougoslavie, la Liste étudiante a remporté le scrutin L’article Législatives serbes. Vučić&amp;#160;: «&amp;#160;Nous avons perdu les élections&amp;#160;» est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -38338,6 +38497,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1148" r:id="rId1147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1149" r:id="rId1148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1150" r:id="rId1149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1151" r:id="rId1150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1152" r:id="rId1151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1153" r:id="rId1152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1154" r:id="rId1153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1155" r:id="rId1154"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1155"/>
+  <dimension ref="A1:G1165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -37212,7 +37212,6 @@
           <t>La réélection de Lula à la présidence du Brésil doit beaucoup à une mobilisation sur les réseaux sociaux qui s’est prolongée dans la rue. Mais face à une droite majoritaire au Parlement et dans les États, son nouveau mandat s’annonce difficile.</t>
         </is>
       </c>
-      <c r="G1151" t="inlineStr"/>
     </row>
     <row r="1152">
       <c r="A1152" s="2" t="inlineStr">
@@ -37245,7 +37244,6 @@
           <t>La défaite de Flávio Bolsonaro met en lumière l’isolement de Milei L’article Comment l’Amérique latine réagit à la victoire de Lula est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1152" t="inlineStr"/>
     </row>
     <row r="1153">
       <c r="A1153" s="2" t="inlineStr">
@@ -37278,7 +37276,6 @@
           <t>Réélu à 80 ans, le président du Brésil cible Trump, les Bolsonaro et les géants de la tech. Son discours de victoire intégral. L’article Lula&amp;#160;: «&amp;#160;Le Brésil n’est l’arrière-cour de personne&amp;#160;» est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1153" t="inlineStr"/>
     </row>
     <row r="1154">
       <c r="A1154" s="2" t="inlineStr">
@@ -37311,7 +37308,6 @@
           <t>Selon le directeur de l’Agence internationale de l’énergie, après l’hégémonie du pétrole, «&amp;#160;l’âge de l’électricité est là.&amp;#160;» L’article Le nouvel ordre énergétique mondial est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1154" t="inlineStr"/>
     </row>
     <row r="1155">
       <c r="A1155" s="2" t="inlineStr">
@@ -37344,7 +37340,336 @@
           <t>Avec une participation record depuis la chute de la Yougoslavie, la Liste étudiante a remporté le scrutin L’article Législatives serbes. Vučić&amp;#160;: «&amp;#160;Nous avons perdu les élections&amp;#160;» est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1155" t="inlineStr"/>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:05</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:14</t>
+        </is>
+      </c>
+      <c r="D1156" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi le narcotrafic résiste si bien à la répression policière ? Ce que l’expérience brésilienne peut enseigner à la France</t>
+        </is>
+      </c>
+      <c r="E1156" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-le-narcotrafic-resiste-si-bien-a-la-repression-policiere-ce-que-lexperience-bresilienne-peut-enseigner-a-la-france-291853</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>Le durcissement de la réponse pénale pour contrer la montée du narcotrafic est-il vraiment efficace&amp;nbsp;? Étude de cas au Brésil et en Guyane française.</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr"/>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:05</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:13</t>
+        </is>
+      </c>
+      <c r="D1157" s="3" t="inlineStr">
+        <is>
+          <t>Couper l’aide au développement au nom de l’intérêt national : le paradoxe des pays donateurs</t>
+        </is>
+      </c>
+      <c r="E1157" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/couper-laide-au-developpement-au-nom-de-linteret-national-le-paradoxe-des-pays-donateurs-293771</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>L’aide publique au développement profite aussi aux donateurs, parfois plus qu’aux bénéficiaires.</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr"/>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:05</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>2026-10-27 11:02</t>
+        </is>
+      </c>
+      <c r="D1158" s="3" t="inlineStr">
+        <is>
+          <t>Brésil : la victoire de Lula à la présidentielle freine la montée de l’extrême droite en Amérique latine</t>
+        </is>
+      </c>
+      <c r="E1158" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/bresil-la-victoire-de-lula-a-la-presidentielle-freine-la-montee-de-lextreme-droite-en-amerique-latine-295267</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>Au Brésil, Lula a remporté l’élection présidentielle grâce notamment à la mobilisation de ses partisans et des abstentionnistes du premier tour.</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr"/>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:05</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:33</t>
+        </is>
+      </c>
+      <c r="D1159" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi les dirigeants finlandais et norvégien ont-ils repris le dialogue avec Poutine</t>
+        </is>
+      </c>
+      <c r="E1159" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/27/pourquoi-les-dirigeants-finlandais-et-norvegien-ont-ils-repris-le-dialogue-avec-poutine/</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>Helsinki et Oslo pourraient jouer un rôle clef dans les négociations L’article Pourquoi les dirigeants finlandais et norvégien ont-ils repris le dialogue avec Poutine est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr"/>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:05</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>2026-10-27 12:15</t>
+        </is>
+      </c>
+      <c r="D1160" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : jusqu’à quand Moscou peut-il financer la guerre contre l’Ukraine ?</t>
+        </is>
+      </c>
+      <c r="E1160" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/27/economie-russe-jusqua-quand-moscou-peut-il-financer-la-guerre-contre-lukraine/</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>Le Kremlin prévoit de consacrer 35&amp;#160;% de son budget 2027 à la défense L’article Économie russe&amp;#160;: jusqu’à quand Moscou peut-il financer la guerre contre l’Ukraine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr"/>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:05</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:39</t>
+        </is>
+      </c>
+      <c r="D1161" s="3" t="inlineStr">
+        <is>
+          <t>Le plan des étudiants serbes qui ont renversé Vučić (texte intégral)</t>
+        </is>
+      </c>
+      <c r="E1161" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/27/le-plan-des-etudiants-serbes-qui-ont-renverse-vucic-texte-integral/</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>Les mystérieux étudiants qui ont pris le pouvoir en Serbie peuvent-ils vraiment réinventer la démocratie&amp;#160;? L’article Le plan des étudiants serbes qui ont renversé Vučić (texte intégral) est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr"/>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:05</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>2026-10-27 05:30</t>
+        </is>
+      </c>
+      <c r="D1162" s="3" t="inlineStr">
+        <is>
+          <t>En Israël, Netanyahou compte sur la guerre pour se maintenir au pouvoir</t>
+        </is>
+      </c>
+      <c r="E1162" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/27/en-israel-netanyahou-compte-sur-la-guerre-pour-se-maintenir-au-pouvoir/</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>En amont des élections, Netanyahou a multiplié les tentatives pour obtenir auprès de Trump une reprise des frappes contre l’Iran L’article En Israël, Netanyahou compte sur la guerre pour se maintenir au pouvoir est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr"/>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:05</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>2026-10-27 05:30</t>
+        </is>
+      </c>
+      <c r="D1163" s="3" t="inlineStr">
+        <is>
+          <t>Le contrat social français est cassé. Comment le réparer ?</t>
+        </is>
+      </c>
+      <c r="E1163" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/27/le-contrat-social-francais-est-casse-comment-le-reparer/</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>De Hobbes à Tocqueville, les secrets d’un art politique oublié&amp;#160;: la démocratie L’article Le contrat social français est cassé. Comment le réparer&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr"/>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:05</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>2026-10-26 17:31</t>
+        </is>
+      </c>
+      <c r="D1164" s="3" t="inlineStr">
+        <is>
+          <t>Ce sont les Américains qui ont le plus subi les conséquences de la hausse des prix des carburants</t>
+        </is>
+      </c>
+      <c r="E1164" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/26/ce-sont-les-americains-qui-ont-le-plus-subi-les-consequences-de-la-hausse-des-prix-des-carburants/</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>La guerre avec l’Iran a provoqué un surcoût de carburant de 471 dollars par personne aux États-Unis L’article Ce sont les Américains qui ont le plus subi les conséquences de la hausse des prix des carburants est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr"/>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:05</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:46</t>
+        </is>
+      </c>
+      <c r="D1165" s="3" t="inlineStr">
+        <is>
+          <t>Pour compenser ses pertes en Ukraine, l’armée russe se tourne vers l’Afrique</t>
+        </is>
+      </c>
+      <c r="E1165" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/26/pour-compenser-ses-pertes-en-ukraine-larmee-russe-se-tourne-vers-lafrique/</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>Les recrutements ont été multipliés par 23 au Burundi L’article Pour compenser ses pertes en Ukraine, l’armée russe se tourne vers l’Afrique est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -38502,6 +38827,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1153" r:id="rId1152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1154" r:id="rId1153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1155" r:id="rId1154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1156" r:id="rId1155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1157" r:id="rId1156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1158" r:id="rId1157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1159" r:id="rId1158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1160" r:id="rId1159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1161" r:id="rId1160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1162" r:id="rId1161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1163" r:id="rId1162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1164" r:id="rId1163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1165" r:id="rId1164"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1165"/>
+  <dimension ref="A1:G1171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -37372,7 +37372,6 @@
           <t>Le durcissement de la réponse pénale pour contrer la montée du narcotrafic est-il vraiment efficace&amp;nbsp;? Étude de cas au Brésil et en Guyane française.</t>
         </is>
       </c>
-      <c r="G1156" t="inlineStr"/>
     </row>
     <row r="1157">
       <c r="A1157" s="2" t="inlineStr">
@@ -37405,7 +37404,6 @@
           <t>L’aide publique au développement profite aussi aux donateurs, parfois plus qu’aux bénéficiaires.</t>
         </is>
       </c>
-      <c r="G1157" t="inlineStr"/>
     </row>
     <row r="1158">
       <c r="A1158" s="2" t="inlineStr">
@@ -37438,7 +37436,6 @@
           <t>Au Brésil, Lula a remporté l’élection présidentielle grâce notamment à la mobilisation de ses partisans et des abstentionnistes du premier tour.</t>
         </is>
       </c>
-      <c r="G1158" t="inlineStr"/>
     </row>
     <row r="1159">
       <c r="A1159" s="2" t="inlineStr">
@@ -37471,7 +37468,6 @@
           <t>Helsinki et Oslo pourraient jouer un rôle clef dans les négociations L’article Pourquoi les dirigeants finlandais et norvégien ont-ils repris le dialogue avec Poutine est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1159" t="inlineStr"/>
     </row>
     <row r="1160">
       <c r="A1160" s="2" t="inlineStr">
@@ -37504,7 +37500,6 @@
           <t>Le Kremlin prévoit de consacrer 35&amp;#160;% de son budget 2027 à la défense L’article Économie russe&amp;#160;: jusqu’à quand Moscou peut-il financer la guerre contre l’Ukraine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1160" t="inlineStr"/>
     </row>
     <row r="1161">
       <c r="A1161" s="2" t="inlineStr">
@@ -37537,7 +37532,6 @@
           <t>Les mystérieux étudiants qui ont pris le pouvoir en Serbie peuvent-ils vraiment réinventer la démocratie&amp;#160;? L’article Le plan des étudiants serbes qui ont renversé Vučić (texte intégral) est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1161" t="inlineStr"/>
     </row>
     <row r="1162">
       <c r="A1162" s="2" t="inlineStr">
@@ -37570,7 +37564,6 @@
           <t>En amont des élections, Netanyahou a multiplié les tentatives pour obtenir auprès de Trump une reprise des frappes contre l’Iran L’article En Israël, Netanyahou compte sur la guerre pour se maintenir au pouvoir est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1162" t="inlineStr"/>
     </row>
     <row r="1163">
       <c r="A1163" s="2" t="inlineStr">
@@ -37603,7 +37596,6 @@
           <t>De Hobbes à Tocqueville, les secrets d’un art politique oublié&amp;#160;: la démocratie L’article Le contrat social français est cassé. Comment le réparer&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1163" t="inlineStr"/>
     </row>
     <row r="1164">
       <c r="A1164" s="2" t="inlineStr">
@@ -37636,7 +37628,6 @@
           <t>La guerre avec l’Iran a provoqué un surcoût de carburant de 471 dollars par personne aux États-Unis L’article Ce sont les Américains qui ont le plus subi les conséquences de la hausse des prix des carburants est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1164" t="inlineStr"/>
     </row>
     <row r="1165">
       <c r="A1165" s="2" t="inlineStr">
@@ -37669,7 +37660,204 @@
           <t>Les recrutements ont été multipliés par 23 au Burundi L’article Pour compenser ses pertes en Ukraine, l’armée russe se tourne vers l’Afrique est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1165" t="inlineStr"/>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:41</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:43</t>
+        </is>
+      </c>
+      <c r="D1166" s="3" t="inlineStr">
+        <is>
+          <t>Iran : l’État profond des Gardiens de la révolution</t>
+        </is>
+      </c>
+      <c r="E1166" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/iran-letat-profond-des-gardiens-de-la-revolution-293363</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>Un récent ouvrage très complet permet de mieux comprendre le fonctionnement des Gardiens de la révolution islamique iranienne.</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr"/>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:41</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:05</t>
+        </is>
+      </c>
+      <c r="D1167" s="3" t="inlineStr">
+        <is>
+          <t>Les bourses chinoises ont perdu près de 2 500 milliards de dollars depuis mai</t>
+        </is>
+      </c>
+      <c r="E1167" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/28/les-bourses-chinoises-ont-perdu-pres-de-2-500-milliards-de-dollars-depuis-mai/</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>Pékin a fait appel à son «&amp;#160;équipe nationale&amp;#160;» pour stabiliser les marchés L’article Les bourses chinoises ont perdu près de 2 500 milliards de dollars depuis mai est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr"/>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:41</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>2026-10-28 05:30</t>
+        </is>
+      </c>
+      <c r="D1168" s="3" t="inlineStr">
+        <is>
+          <t>L’impact de l’IA sur l’emploi se diffuse au-delà du secteur technologique</t>
+        </is>
+      </c>
+      <c r="E1168" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/28/limpact-de-lia-sur-lemploi-se-diffuse-au-dela-du-secteur-technologique/</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>Son adoption va de pair avec une croissance plus faible de l’emploi L’article L’impact de l’IA sur l’emploi se diffuse au-delà du secteur technologique est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr"/>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:41</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>2026-10-28 05:00</t>
+        </is>
+      </c>
+      <c r="D1169" s="3" t="inlineStr">
+        <is>
+          <t>Pour sauver la biodiversité, il faut repenser la liberté</t>
+        </is>
+      </c>
+      <c r="E1169" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/28/la-cop-biodiversite-sur-lautel-de-la-liberte/</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>Comprendre l’impasse structurelle de la COP17 L’article Pour sauver la biodiversité, il faut repenser la liberté est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr"/>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:41</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>2026-10-27 16:08</t>
+        </is>
+      </c>
+      <c r="D1170" s="3" t="inlineStr">
+        <is>
+          <t>La vérité d’une histoire russe</t>
+        </is>
+      </c>
+      <c r="E1170" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/27/la-verite-dune-histoire-russe/</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>Dans Adieu ma Russie Nicolas Werth perce l’ombre et les mensonges du siècle de son père et du nôtre L’article La vérité d’une histoire russe est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr"/>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:41</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:01</t>
+        </is>
+      </c>
+      <c r="D1171" s="3" t="inlineStr">
+        <is>
+          <t>Compte-rendu : Journée d’étude « Histoire ludique »</t>
+        </is>
+      </c>
+      <c r="E1171" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/compte-rendu-journee-detude-histoire-ludique/</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>Dans le cadre des Rendez-vous de l&amp;#8217;histoire de Blois, l&amp;#8217;APHG a soutenu une journée d&amp;#8217;étude dédiée à l&amp;#8217;histoire ludique sur le thème « Marchands de jeux, jeux de marchands ». Maxime Féréol en a fait un compte-rendu accessible sur le site du Réseau francophone d&amp;#8217;histoire ludique. L’article Compte-rendu : Journée d&amp;rsquo;étude « Histoire ludique » est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -38837,6 +39025,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1163" r:id="rId1162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1164" r:id="rId1163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1165" r:id="rId1164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1166" r:id="rId1165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1167" r:id="rId1166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1168" r:id="rId1167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1169" r:id="rId1168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1170" r:id="rId1169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1171" r:id="rId1170"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1171"/>
+  <dimension ref="A1:G1179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -37692,7 +37692,6 @@
           <t>Un récent ouvrage très complet permet de mieux comprendre le fonctionnement des Gardiens de la révolution islamique iranienne.</t>
         </is>
       </c>
-      <c r="G1166" t="inlineStr"/>
     </row>
     <row r="1167">
       <c r="A1167" s="2" t="inlineStr">
@@ -37725,7 +37724,6 @@
           <t>Pékin a fait appel à son «&amp;#160;équipe nationale&amp;#160;» pour stabiliser les marchés L’article Les bourses chinoises ont perdu près de 2 500 milliards de dollars depuis mai est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1167" t="inlineStr"/>
     </row>
     <row r="1168">
       <c r="A1168" s="2" t="inlineStr">
@@ -37758,7 +37756,6 @@
           <t>Son adoption va de pair avec une croissance plus faible de l’emploi L’article L’impact de l’IA sur l’emploi se diffuse au-delà du secteur technologique est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1168" t="inlineStr"/>
     </row>
     <row r="1169">
       <c r="A1169" s="2" t="inlineStr">
@@ -37791,7 +37788,6 @@
           <t>Comprendre l’impasse structurelle de la COP17 L’article Pour sauver la biodiversité, il faut repenser la liberté est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1169" t="inlineStr"/>
     </row>
     <row r="1170">
       <c r="A1170" s="2" t="inlineStr">
@@ -37824,7 +37820,6 @@
           <t>Dans Adieu ma Russie Nicolas Werth perce l’ombre et les mensonges du siècle de son père et du nôtre L’article La vérité d’une histoire russe est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1170" t="inlineStr"/>
     </row>
     <row r="1171">
       <c r="A1171" s="2" t="inlineStr">
@@ -37857,7 +37852,270 @@
           <t>Dans le cadre des Rendez-vous de l&amp;#8217;histoire de Blois, l&amp;#8217;APHG a soutenu une journée d&amp;#8217;étude dédiée à l&amp;#8217;histoire ludique sur le thème « Marchands de jeux, jeux de marchands ». Maxime Féréol en a fait un compte-rendu accessible sur le site du Réseau francophone d&amp;#8217;histoire ludique. L’article Compte-rendu : Journée d&amp;rsquo;étude « Histoire ludique » est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G1171" t="inlineStr"/>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:48</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>2026-10-29 10:52</t>
+        </is>
+      </c>
+      <c r="D1172" s="3" t="inlineStr">
+        <is>
+          <t>En Israël, Netanyahou désavoué dans les urnes peut encore rester au pouvoir</t>
+        </is>
+      </c>
+      <c r="E1172" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/en-israel-netanyahou-desavoue-dans-les-urnes-peut-encore-rester-au-pouvoir-295469</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>Les élections législatives du 27 octobre 2026 en Israël ont désavoué la coalition de Benjamin Netanyahou sans dégager de majorité alternative. Le politiste Dov Waxman décrypte les résultats et les obstacles à la formation d’un nouveau gouvernement.</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr"/>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:48</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:14</t>
+        </is>
+      </c>
+      <c r="D1173" s="3" t="inlineStr">
+        <is>
+          <t>La part des États-Unis dans le commerce canadien est à son plus bas depuis 30 ans</t>
+        </is>
+      </c>
+      <c r="E1173" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/29/la-part-des-etats-unis-dans-le-commerce-canadien-est-a-son-plus-bas-depuis-30-ans/</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>Le commerce du Canada avec la Chine et l’Union a bondi L’article La part des États-Unis dans le commerce canadien est à son plus bas depuis 30 ans est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr"/>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:48</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:39</t>
+        </is>
+      </c>
+      <c r="D1174" s="3" t="inlineStr">
+        <is>
+          <t>Comment le communisme a fait de la Chine une superpuissance capitaliste</t>
+        </is>
+      </c>
+      <c r="E1174" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/29/comment-le-communisme-a-fait-de-la-chine-une-superpuissance-capitaliste/</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>L’histoire paradoxale de la puissance chinoise à partir de la formation et désintégration de sa classe ouvrière L’article Comment le communisme a fait de la Chine une superpuissance capitaliste est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr"/>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:48</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>2026-10-29 05:30</t>
+        </is>
+      </c>
+      <c r="D1175" s="3" t="inlineStr">
+        <is>
+          <t>L’hubris de Citrini : quand l’IA devient la nouvelle cocaïne des traders</t>
+        </is>
+      </c>
+      <c r="E1175" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/29/lhubris-de-citrini-quand-lia-devient-la-nouvelle-cocaine-des-traders/</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>50 000 dollars de puissance de calcul suffisent-ils pour créer un antivenin&amp;#160;? L’article L’hubris de Citrini&amp;#160;: quand l’IA devient la nouvelle cocaïne des traders est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr"/>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:48</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>2026-10-29 05:00</t>
+        </is>
+      </c>
+      <c r="D1176" s="3" t="inlineStr">
+        <is>
+          <t>Faire de l’euro une monnaie géopolitique</t>
+        </is>
+      </c>
+      <c r="E1176" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/29/faire-de-leuro-une-monnaie-geopolitique/</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>La conversion stratégique et la nouvelle doctrine d’un ancien gardien de l’orthodoxie, aujourd'hui candidat à la succession de Lagarde L’article Faire de l&amp;rsquo;euro une monnaie géopolitique est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr"/>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:48</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>2026-10-28 17:00</t>
+        </is>
+      </c>
+      <c r="D1177" s="3" t="inlineStr">
+        <is>
+          <t>Obama contre Trump : « Nous devons redresser notre boussole morale »</t>
+        </is>
+      </c>
+      <c r="E1177" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/28/obama-contre-trump-nous-devons-redresser-notre-boussole-morale/</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>Nous traduisons et commentons le discours de Barack Obama à Cleveland dans l’Ohio L’article Obama contre Trump&amp;#160;: «&amp;#160;Nous devons redresser notre boussole morale&amp;#160;» est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr"/>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:48</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:56</t>
+        </is>
+      </c>
+      <c r="D1178" s="3" t="inlineStr">
+        <is>
+          <t>Aucun gagnant clair en Israël : après les élections, vers de longues négociations ?</t>
+        </is>
+      </c>
+      <c r="E1178" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/28/aucun-gagnant-clair-en-israel-apres-les-elections-vers-de-longues-negociations/</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>Les coalitions de Netanyahou et d'Eisenkot sont au coude-à-coude L’article Aucun gagnant clair en Israël&amp;#160;: après les élections, vers de longues négociations&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr"/>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:48</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:41</t>
+        </is>
+      </c>
+      <c r="D1179" s="3" t="inlineStr">
+        <is>
+          <t>Pour réaliser le rapport Draghi, la BCE doit-elle effacer 3 000 milliards de dette ?</t>
+        </is>
+      </c>
+      <c r="E1179" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/28/pour-realiser-le-rapport-draghi-la-bce-doit-elle-effacer-3-000-milliards-de-dette/</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>Selon l’économiste française, annuler les dettes détenues par les banques centrales serait un levier clef pour financer l’avenir de l’Europe L’article Pour réaliser le rapport Draghi, la BCE doit-elle effacer 3 000 milliards de dette&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -39031,6 +39289,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1169" r:id="rId1168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1170" r:id="rId1169"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1171" r:id="rId1170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1172" r:id="rId1171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1173" r:id="rId1172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1174" r:id="rId1173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1175" r:id="rId1174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1176" r:id="rId1175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1177" r:id="rId1176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1178" r:id="rId1177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1179" r:id="rId1178"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1179"/>
+  <dimension ref="A1:G1186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -37884,7 +37884,6 @@
           <t>Les élections législatives du 27 octobre 2026 en Israël ont désavoué la coalition de Benjamin Netanyahou sans dégager de majorité alternative. Le politiste Dov Waxman décrypte les résultats et les obstacles à la formation d’un nouveau gouvernement.</t>
         </is>
       </c>
-      <c r="G1172" t="inlineStr"/>
     </row>
     <row r="1173">
       <c r="A1173" s="2" t="inlineStr">
@@ -37917,7 +37916,6 @@
           <t>Le commerce du Canada avec la Chine et l’Union a bondi L’article La part des États-Unis dans le commerce canadien est à son plus bas depuis 30 ans est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1173" t="inlineStr"/>
     </row>
     <row r="1174">
       <c r="A1174" s="2" t="inlineStr">
@@ -37950,7 +37948,6 @@
           <t>L’histoire paradoxale de la puissance chinoise à partir de la formation et désintégration de sa classe ouvrière L’article Comment le communisme a fait de la Chine une superpuissance capitaliste est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1174" t="inlineStr"/>
     </row>
     <row r="1175">
       <c r="A1175" s="2" t="inlineStr">
@@ -37983,7 +37980,6 @@
           <t>50 000 dollars de puissance de calcul suffisent-ils pour créer un antivenin&amp;#160;? L’article L’hubris de Citrini&amp;#160;: quand l’IA devient la nouvelle cocaïne des traders est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1175" t="inlineStr"/>
     </row>
     <row r="1176">
       <c r="A1176" s="2" t="inlineStr">
@@ -38016,7 +38012,6 @@
           <t>La conversion stratégique et la nouvelle doctrine d’un ancien gardien de l’orthodoxie, aujourd'hui candidat à la succession de Lagarde L’article Faire de l&amp;rsquo;euro une monnaie géopolitique est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1176" t="inlineStr"/>
     </row>
     <row r="1177">
       <c r="A1177" s="2" t="inlineStr">
@@ -38049,7 +38044,6 @@
           <t>Nous traduisons et commentons le discours de Barack Obama à Cleveland dans l’Ohio L’article Obama contre Trump&amp;#160;: «&amp;#160;Nous devons redresser notre boussole morale&amp;#160;» est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1177" t="inlineStr"/>
     </row>
     <row r="1178">
       <c r="A1178" s="2" t="inlineStr">
@@ -38082,7 +38076,6 @@
           <t>Les coalitions de Netanyahou et d'Eisenkot sont au coude-à-coude L’article Aucun gagnant clair en Israël&amp;#160;: après les élections, vers de longues négociations&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1178" t="inlineStr"/>
     </row>
     <row r="1179">
       <c r="A1179" s="2" t="inlineStr">
@@ -38115,7 +38108,237 @@
           <t>Selon l’économiste française, annuler les dettes détenues par les banques centrales serait un levier clef pour financer l’avenir de l’Europe L’article Pour réaliser le rapport Draghi, la BCE doit-elle effacer 3 000 milliards de dette&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1179" t="inlineStr"/>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:30</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:22</t>
+        </is>
+      </c>
+      <c r="D1180" s="3" t="inlineStr">
+        <is>
+          <t>Fascisme : une histoire américaine</t>
+        </is>
+      </c>
+      <c r="E1180" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/fascisme-une-histoire-americaine-294393</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>Un récent ouvrage revient sur l’histoire de cette mouvance politique aux multiples visages qui, depuis un siècle, a pesé de diverses façons sur les États-Unis.</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr"/>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:30</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:22</t>
+        </is>
+      </c>
+      <c r="D1181" s="3" t="inlineStr">
+        <is>
+          <t>« Midterms » aux États-Unis : pourquoi les républicains sont sur la défensive, jusque dans leurs bastions</t>
+        </is>
+      </c>
+      <c r="E1181" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/midterms-aux-etats-unis-pourquoi-les-republicains-sont-sur-la-defensive-jusque-dans-leurs-bastions-295383</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>Le 3&amp;nbsp;novembre, les Américains votent aux élections de mi-mandat, où le parti du président est presque toujours sanctionné. Les républicains de Trump pourraient perdre la Chambre des représentants&amp;nbsp;; le Sénat s’annonce plus incertain.</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr"/>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:30</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:28</t>
+        </is>
+      </c>
+      <c r="D1182" s="3" t="inlineStr">
+        <is>
+          <t>Les Nations unies face aux puissances de l’intelligence artificielle</t>
+        </is>
+      </c>
+      <c r="E1182" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/30/les-nations-unies-face-aux-puissances-de-lintelligence-artificielle/</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>Le ministre français des Affaires étrangères revient sur une séquence inédite au Conseil de sécurité L’article Les Nations unies face aux puissances de l’intelligence artificielle est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr"/>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:30</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>2026-10-30 14:34</t>
+        </is>
+      </c>
+      <c r="D1183" s="3" t="inlineStr">
+        <is>
+          <t>Trumplation : comment Trump a fait repartir l’inflation américaine</t>
+        </is>
+      </c>
+      <c r="E1183" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/30/trumplation-comment-trump-a-fait-repartir-linflation-americaine/</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>À quatre jours des élections de mi-mandat, le Bureau of Economic Analysis a publié de nouvelles statistiques qui inquiètent la Maison-Blanche L’article Trumplation&amp;#160;: comment Trump a fait repartir l’inflation américaine est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr"/>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:30</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>2026-10-30 06:42</t>
+        </is>
+      </c>
+      <c r="D1184" s="3" t="inlineStr">
+        <is>
+          <t>Les 7 meilleures publicités des midterms (avec deux bonus)</t>
+        </is>
+      </c>
+      <c r="E1184" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/30/les-7-meilleures-publicites-des-midterms-avec-deux-bonus/</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>Les vidéos de la campagne la plus chère de l’histoire qu’il faut avoir vues L’article Les 7 meilleures publicités des midterms (avec deux bonus) est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr"/>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:30</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>2026-10-30 05:30</t>
+        </is>
+      </c>
+      <c r="D1185" s="3" t="inlineStr">
+        <is>
+          <t>Au Texas, Elon Musk a déversé presque autant d’argent dans la campagne sénatoriale que tout le camp démocrate</t>
+        </is>
+      </c>
+      <c r="E1185" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/30/au-texas-elon-musk-a-deverse-presque-autant-dargent-dans-la-campagne-senatoriale-que-tout-le-camp-democrate/</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>La course au Sénat du Texas est devenue la plus chère de l’histoire L’article Au Texas, Elon Musk a déversé presque autant d’argent dans la campagne sénatoriale que tout le camp démocrate est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr"/>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:30</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:31</t>
+        </is>
+      </c>
+      <c r="D1186" s="3" t="inlineStr">
+        <is>
+          <t>En Chine, 55 % des plus grandes fortunes viennent de la tech</t>
+        </is>
+      </c>
+      <c r="E1186" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/29/en-chine-55-des-plus-grandes-fortunes-viennent-de-la-tech/</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>C’est plus de deux fois plus qu’aux États-Unis L’article En Chine, 55&amp;#160;% des plus grandes fortunes viennent de la tech est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -39297,6 +39520,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1177" r:id="rId1176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1178" r:id="rId1177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1179" r:id="rId1178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1180" r:id="rId1179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1181" r:id="rId1180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1182" r:id="rId1181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1183" r:id="rId1182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1184" r:id="rId1183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1185" r:id="rId1184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1186" r:id="rId1185"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1186"/>
+  <dimension ref="A1:G1194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -38140,7 +38140,6 @@
           <t>Un récent ouvrage revient sur l’histoire de cette mouvance politique aux multiples visages qui, depuis un siècle, a pesé de diverses façons sur les États-Unis.</t>
         </is>
       </c>
-      <c r="G1180" t="inlineStr"/>
     </row>
     <row r="1181">
       <c r="A1181" s="2" t="inlineStr">
@@ -38173,7 +38172,6 @@
           <t>Le 3&amp;nbsp;novembre, les Américains votent aux élections de mi-mandat, où le parti du président est presque toujours sanctionné. Les républicains de Trump pourraient perdre la Chambre des représentants&amp;nbsp;; le Sénat s’annonce plus incertain.</t>
         </is>
       </c>
-      <c r="G1181" t="inlineStr"/>
     </row>
     <row r="1182">
       <c r="A1182" s="2" t="inlineStr">
@@ -38206,7 +38204,6 @@
           <t>Le ministre français des Affaires étrangères revient sur une séquence inédite au Conseil de sécurité L’article Les Nations unies face aux puissances de l’intelligence artificielle est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1182" t="inlineStr"/>
     </row>
     <row r="1183">
       <c r="A1183" s="2" t="inlineStr">
@@ -38239,7 +38236,6 @@
           <t>À quatre jours des élections de mi-mandat, le Bureau of Economic Analysis a publié de nouvelles statistiques qui inquiètent la Maison-Blanche L’article Trumplation&amp;#160;: comment Trump a fait repartir l’inflation américaine est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1183" t="inlineStr"/>
     </row>
     <row r="1184">
       <c r="A1184" s="2" t="inlineStr">
@@ -38272,7 +38268,6 @@
           <t>Les vidéos de la campagne la plus chère de l’histoire qu’il faut avoir vues L’article Les 7 meilleures publicités des midterms (avec deux bonus) est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1184" t="inlineStr"/>
     </row>
     <row r="1185">
       <c r="A1185" s="2" t="inlineStr">
@@ -38305,7 +38300,6 @@
           <t>La course au Sénat du Texas est devenue la plus chère de l’histoire L’article Au Texas, Elon Musk a déversé presque autant d’argent dans la campagne sénatoriale que tout le camp démocrate est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1185" t="inlineStr"/>
     </row>
     <row r="1186">
       <c r="A1186" s="2" t="inlineStr">
@@ -38338,7 +38332,270 @@
           <t>C’est plus de deux fois plus qu’aux États-Unis L’article En Chine, 55&amp;#160;% des plus grandes fortunes viennent de la tech est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G1186" t="inlineStr"/>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 14:58</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>2026-10-31 07:39</t>
+        </is>
+      </c>
+      <c r="D1187" s="3" t="inlineStr">
+        <is>
+          <t>De Rome à nos jours, les guerres de la bière ont créé et défait les empires</t>
+        </is>
+      </c>
+      <c r="E1187" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/de-rome-a-nos-jours-les-guerres-de-la-biere-ont-cree-et-defait-les-empires-277761</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>De l’Empire carolingien à l’Empire britannique, en passant par le Saint-Empire romain germanique, la bière a généré plus de conflits qu’aucun autre alcool au monde.</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr"/>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 14:58</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>2026-10-30 16:13</t>
+        </is>
+      </c>
+      <c r="D1188" s="3" t="inlineStr">
+        <is>
+          <t>Comment les Victoriens ont transformé la communication avec les morts en commerce lucratif</t>
+        </is>
+      </c>
+      <c r="E1188" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-les-victoriens-ont-transforme-la-communication-avec-les-morts-en-commerce-lucratif-295517</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>Dans la Grande-Bretagne du XIXᵉ siècle, les technologies qui transformaient le commerce et les loisirs ont aussi rendu les fantômes visibles, reproductibles et rentables. Une histoire qui éclaire le marché actuel des technologies du deuil.</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr"/>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 14:58</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>2026-10-31 07:40</t>
+        </is>
+      </c>
+      <c r="D1189" s="3" t="inlineStr">
+        <is>
+          <t>À l’école maternelle, pourquoi la joie de travailler avec les enfants ne suffit pas à tenir</t>
+        </is>
+      </c>
+      <c r="E1189" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/a-lecole-maternelle-pourquoi-la-joie-de-travailler-avec-les-enfants-ne-suffit-pas-a-tenir-293060</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>Enseignants, Atsem, animateurs&amp;nbsp;: trois&amp;nbsp;enquêtes auprès de 181&amp;nbsp;professionnels de la petite enfance montrent une joie réelle dans l’exercice du métier, tout comme une fatigue liée aux conditions de travail.</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr"/>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 14:58</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>2026-10-30 16:14</t>
+        </is>
+      </c>
+      <c r="D1190" s="3" t="inlineStr">
+        <is>
+          <t>Quarante jours pour arriver, quarante jours pour partir : comment la culture arménienne accompagne les morts et les naissances</t>
+        </is>
+      </c>
+      <c r="E1190" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/quarante-jours-pour-arriver-quarante-jours-pour-partir-comment-la-culture-armenienne-accompagne-les-morts-et-les-naissances-295512</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>En Arménie, la naissance comme la mort ouvrent une période de 40 jours, le karasunk. Entre christianisme et croyances populaires, cette tradition protège ceux qui passent d’un état de la vie à un autre.</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr"/>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 14:58</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>2026-10-31 05:30</t>
+        </is>
+      </c>
+      <c r="D1191" s="3" t="inlineStr">
+        <is>
+          <t>Quels sont les scrutins à suivre lors des élections de mi-mandat ?</t>
+        </is>
+      </c>
+      <c r="E1191" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/31/quels-sont-les-scrutins-a-suivre-lors-des-elections-de-mi-mandat/</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>Un guide pour se préparer aux élections les plus importantes de cette fin d’année L’article Quels sont les scrutins à suivre lors des élections de mi-mandat&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr"/>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 14:58</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>2026-10-31 05:00</t>
+        </is>
+      </c>
+      <c r="D1192" s="3" t="inlineStr">
+        <is>
+          <t>21 livres à lire en novembre 2026</t>
+        </is>
+      </c>
+      <c r="E1192" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/31/livres-a-lire-en-novembre-2026/</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>De Rousseau à Kissinger en passant par Kojève et son «&amp;#160;Empire latin&amp;#160;»&amp;#160;: les parutions à ne pas manquer ce mois-ci L’article 21 livres à lire en novembre 2026 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr"/>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 14:58</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>2026-10-30 17:57</t>
+        </is>
+      </c>
+      <c r="D1193" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : la récolte de pommes de terre pourrait tomber à son plus bas niveau depuis au moins 25 ans</t>
+        </is>
+      </c>
+      <c r="E1193" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/30/economie-russe-la-recolte-de-pommes-de-terre-pourrait-tomber-a-son-plus-bas-niveau-depuis-au-moins-25-ans/</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>Le prix du tubercule a bondi de 29&amp;#160;% en un an L’article Économie russe&amp;#160;: la récolte de pommes de terre pourrait tomber à son plus bas niveau depuis au moins 25 ans est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr"/>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 14:58</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>2026-10-30 14:34</t>
+        </is>
+      </c>
+      <c r="D1194" s="3" t="inlineStr">
+        <is>
+          <t>Trumpflation : comment Trump a fait repartir l’inflation américaine</t>
+        </is>
+      </c>
+      <c r="E1194" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/10/30/trumpflation-comment-trump-a-fait-repartir-linflation-americaine/</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>À quatre jours des élections de mi-mandat, le Bureau of Economic Analysis a publié de nouvelles statistiques qui inquiètent la Maison-Blanche L’article Trumpflation&amp;#160;: comment Trump a fait repartir l’inflation américaine est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -39527,6 +39784,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1184" r:id="rId1183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1185" r:id="rId1184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1186" r:id="rId1185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1187" r:id="rId1186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1188" r:id="rId1187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1189" r:id="rId1188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1190" r:id="rId1189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1191" r:id="rId1190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1192" r:id="rId1191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1193" r:id="rId1192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1194" r:id="rId1193"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
